--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3104" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3457" uniqueCount="67">
   <si>
     <t>Ngày</t>
   </si>
@@ -149,19 +149,19 @@
     <t>2026-08-02</t>
   </si>
   <si>
-    <t>120253483200380712</t>
-  </si>
-  <si>
     <t>120253483200390712</t>
   </si>
   <si>
     <t>120253483628540712</t>
   </si>
   <si>
-    <t>120252922477470712</t>
+    <t>120253483200380712</t>
   </si>
   <si>
     <t>120252922477480712</t>
+  </si>
+  <si>
+    <t>120252922477470712</t>
   </si>
   <si>
     <t>120253417262500712</t>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
   </si>
 </sst>
 </file>
@@ -570,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I395"/>
+  <dimension ref="A1:I440"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -1495,7 +1501,7 @@
         <v>45</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1510.0</v>
+        <v>2747.0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>12</v>
@@ -1521,16 +1527,16 @@
         <v>13</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>2747.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>44</v>
@@ -1550,16 +1556,16 @@
         <v>13</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>65819.0</v>
+        <v>102721.0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>44</v>
@@ -1579,7 +1585,7 @@
         <v>13</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>470.0</v>
@@ -1750,13 +1756,13 @@
         <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>430.0</v>
+        <v>35805.0</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>12</v>
@@ -1782,10 +1788,10 @@
         <v>13</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>35805.0</v>
+        <v>1510.0</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>12</v>
@@ -1808,13 +1814,13 @@
         <v>44</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>102721.0</v>
+        <v>5790.0</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>12</v>
@@ -1840,10 +1846,10 @@
         <v>30</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>573.0</v>
+        <v>430.0</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
@@ -1895,19 +1901,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>157090.0</v>
+        <v>498079.0</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>44</v>
@@ -1924,13 +1930,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>111418.0</v>
+        <v>573.0</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>12</v>
@@ -1956,10 +1962,10 @@
         <v>10</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>35215.0</v>
+        <v>111418.0</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>12</v>
@@ -1988,7 +1994,7 @@
         <v>49</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>5790.0</v>
+        <v>35215.0</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>12</v>
@@ -2069,19 +2075,19 @@
         <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>498079.0</v>
+        <v>3585.0</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>44</v>
@@ -2101,10 +2107,10 @@
         <v>30</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>3585.0</v>
+        <v>487.0</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>12</v>
@@ -2130,10 +2136,10 @@
         <v>30</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>487.0</v>
+        <v>283422.0</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>12</v>
@@ -2159,10 +2165,10 @@
         <v>30</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>283422.0</v>
+        <v>157090.0</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>12</v>
@@ -2217,10 +2223,10 @@
         <v>13</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>83.0</v>
+        <v>3486.0</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>12</v>
@@ -2246,10 +2252,10 @@
         <v>13</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>15476.0</v>
+        <v>80337.0</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>12</v>
@@ -2275,10 +2281,10 @@
         <v>13</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>80337.0</v>
+        <v>1275.0</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>12</v>
@@ -2304,10 +2310,10 @@
         <v>13</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>1275.0</v>
+        <v>10496.0</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>12</v>
@@ -2333,10 +2339,10 @@
         <v>13</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>10496.0</v>
+        <v>83.0</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>12</v>
@@ -2362,10 +2368,10 @@
         <v>13</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>5532.0</v>
+        <v>831603.0</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>12</v>
@@ -2391,10 +2397,10 @@
         <v>13</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3486.0</v>
+        <v>1721.0</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>12</v>
@@ -2420,10 +2426,10 @@
         <v>13</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>1721.0</v>
+        <v>5532.0</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>12</v>
@@ -2449,10 +2455,10 @@
         <v>13</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>831603.0</v>
+        <v>10890.0</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>12</v>
@@ -2478,10 +2484,10 @@
         <v>13</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>10890.0</v>
+        <v>378256.0</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>12</v>
@@ -2507,10 +2513,10 @@
         <v>13</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>378256.0</v>
+        <v>14414.0</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>12</v>
@@ -2536,10 +2542,10 @@
         <v>13</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>14414.0</v>
+        <v>15476.0</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>12</v>
@@ -2562,19 +2568,19 @@
         <v>51</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>17497.0</v>
+        <v>85165.0</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>51</v>
@@ -2591,13 +2597,13 @@
         <v>51</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>3752.0</v>
+        <v>17497.0</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>12</v>
@@ -2623,10 +2629,10 @@
         <v>10</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>8487.0</v>
+        <v>256233.0</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>12</v>
@@ -2652,10 +2658,10 @@
         <v>30</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3300.0</v>
+        <v>3752.0</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>12</v>
@@ -2681,10 +2687,10 @@
         <v>10</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>256233.0</v>
+        <v>100851.0</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>12</v>
@@ -2710,10 +2716,10 @@
         <v>10</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>100851.0</v>
+        <v>373138.0</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>12</v>
@@ -2739,10 +2745,10 @@
         <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>373138.0</v>
+        <v>61630.0</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>12</v>
@@ -2768,10 +2774,10 @@
         <v>10</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>61630.0</v>
+        <v>8487.0</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>12</v>
@@ -2797,16 +2803,16 @@
         <v>30</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>85165.0</v>
+        <v>5448.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F77" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>51</v>
@@ -2826,10 +2832,10 @@
         <v>30</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>5448.0</v>
+        <v>669.0</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>12</v>
@@ -2855,10 +2861,10 @@
         <v>30</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>669.0</v>
+        <v>351708.0</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>12</v>
@@ -2884,16 +2890,16 @@
         <v>30</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>351708.0</v>
+        <v>187504.0</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>51</v>
@@ -2913,16 +2919,16 @@
         <v>30</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>187504.0</v>
+        <v>4349.0</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F81" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>51</v>
@@ -2942,10 +2948,10 @@
         <v>30</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>4349.0</v>
+        <v>3300.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
@@ -2971,10 +2977,10 @@
         <v>13</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>14080.0</v>
+        <v>2226.0</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>12</v>
@@ -3058,10 +3064,10 @@
         <v>13</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>112.0</v>
+        <v>2497.0</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>12</v>
@@ -3087,10 +3093,10 @@
         <v>13</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>2226.0</v>
+        <v>112.0</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>12</v>
@@ -3116,10 +3122,10 @@
         <v>13</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>4423.0</v>
+        <v>19856.0</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -3145,10 +3151,10 @@
         <v>13</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>4645.0</v>
+        <v>14080.0</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>12</v>
@@ -3174,16 +3180,16 @@
         <v>13</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>309962.0</v>
+        <v>4645.0</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F90" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>53</v>
@@ -3203,16 +3209,16 @@
         <v>13</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>20121.0</v>
+        <v>309962.0</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>53</v>
@@ -3232,10 +3238,10 @@
         <v>13</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>569.0</v>
+        <v>20121.0</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>12</v>
@@ -3261,10 +3267,10 @@
         <v>13</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>204042.0</v>
+        <v>569.0</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>12</v>
@@ -3290,10 +3296,10 @@
         <v>13</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>19856.0</v>
+        <v>204042.0</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>12</v>
@@ -3351,7 +3357,7 @@
         <v>47</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>2497.0</v>
+        <v>122.0</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>12</v>
@@ -3380,7 +3386,7 @@
         <v>45</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>122.0</v>
+        <v>4423.0</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>12</v>
@@ -3406,10 +3412,10 @@
         <v>10</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>38896.0</v>
+        <v>2580.0</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>12</v>
@@ -3432,13 +3438,13 @@
         <v>53</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>8698.0</v>
+        <v>4782.0</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>12</v>
@@ -3464,16 +3470,16 @@
         <v>10</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>294779.0</v>
+        <v>8698.0</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>53</v>
@@ -3493,10 +3499,10 @@
         <v>10</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>66166.0</v>
+        <v>294779.0</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>16</v>
@@ -3525,13 +3531,13 @@
         <v>49</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>2384.0</v>
+        <v>66166.0</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G102" s="8" t="s">
         <v>53</v>
@@ -3551,10 +3557,10 @@
         <v>10</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>2580.0</v>
+        <v>2384.0</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>12</v>
@@ -3577,19 +3583,19 @@
         <v>53</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>4782.0</v>
+        <v>98382.0</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G104" s="8" t="s">
         <v>53</v>
@@ -3606,19 +3612,19 @@
         <v>53</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>115599.0</v>
+        <v>38896.0</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F105" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>53</v>
@@ -3638,10 +3644,10 @@
         <v>30</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>202034.0</v>
+        <v>1375.0</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>12</v>
@@ -3664,19 +3670,19 @@
         <v>53</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>98382.0</v>
+        <v>202034.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>53</v>
@@ -3754,16 +3760,16 @@
         <v>30</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>1375.0</v>
+        <v>115599.0</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>53</v>
@@ -3783,10 +3789,10 @@
         <v>13</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>230.0</v>
+        <v>25484.0</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>12</v>
@@ -3812,16 +3818,16 @@
         <v>13</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>199793.0</v>
+        <v>299654.0</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>54</v>
@@ -3841,7 +3847,7 @@
         <v>13</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D113" s="6" t="n">
         <v>290.0</v>
@@ -3899,10 +3905,10 @@
         <v>13</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>1127.0</v>
+        <v>230.0</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>12</v>
@@ -3928,10 +3934,10 @@
         <v>13</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>25484.0</v>
+        <v>343.0</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>12</v>
@@ -3986,10 +3992,10 @@
         <v>13</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>1325.0</v>
+        <v>1127.0</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>12</v>
@@ -4015,10 +4021,10 @@
         <v>13</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>343.0</v>
+        <v>511.0</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>12</v>
@@ -4044,16 +4050,16 @@
         <v>13</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>511.0</v>
+        <v>109034.0</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F120" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>54</v>
@@ -4073,10 +4079,10 @@
         <v>13</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>109034.0</v>
+        <v>20525.0</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>16</v>
@@ -4102,16 +4108,16 @@
         <v>13</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>20525.0</v>
+        <v>199793.0</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F122" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G122" s="8" t="s">
         <v>54</v>
@@ -4128,19 +4134,19 @@
         <v>54</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>299654.0</v>
+        <v>365.0</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F123" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>54</v>
@@ -4160,10 +4166,10 @@
         <v>13</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>26515.0</v>
+        <v>1325.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
@@ -4186,13 +4192,13 @@
         <v>54</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>365.0</v>
+        <v>287568.0</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>12</v>
@@ -4215,13 +4221,13 @@
         <v>54</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>12.0</v>
+        <v>26515.0</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>12</v>
@@ -4247,16 +4253,16 @@
         <v>10</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>7646.0</v>
+        <v>619458.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G127" s="8" t="s">
         <v>54</v>
@@ -4276,16 +4282,16 @@
         <v>10</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>619458.0</v>
+        <v>3016.0</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F128" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G128" s="8" t="s">
         <v>54</v>
@@ -4308,7 +4314,7 @@
         <v>48</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>3016.0</v>
+        <v>119.0</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>12</v>
@@ -4334,10 +4340,10 @@
         <v>10</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>119.0</v>
+        <v>7646.0</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>12</v>
@@ -4363,10 +4369,10 @@
         <v>30</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>287568.0</v>
+        <v>33308.0</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>12</v>
@@ -4392,10 +4398,10 @@
         <v>30</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>33308.0</v>
+        <v>22735.0</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>12</v>
@@ -4421,10 +4427,10 @@
         <v>30</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>22735.0</v>
+        <v>130258.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>12</v>
@@ -4450,10 +4456,10 @@
         <v>30</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>130258.0</v>
+        <v>939.0</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>12</v>
@@ -4479,10 +4485,10 @@
         <v>30</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>939.0</v>
+        <v>5182.0</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>12</v>
@@ -4508,10 +4514,10 @@
         <v>30</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>5182.0</v>
+        <v>12.0</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>12</v>
@@ -4682,10 +4688,10 @@
         <v>13</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>38461.0</v>
+        <v>69.0</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>12</v>
@@ -4885,10 +4891,10 @@
         <v>13</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>69.0</v>
+        <v>38461.0</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>12</v>
@@ -4914,10 +4920,10 @@
         <v>13</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>21698.0</v>
+        <v>325679.0</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>12</v>
@@ -5030,10 +5036,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>325679.0</v>
+        <v>21698.0</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>12</v>
@@ -5059,7 +5065,7 @@
         <v>10</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D155" s="6" t="n">
         <v>143.0</v>
@@ -5349,7 +5355,7 @@
         <v>13</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D165" s="6" t="n">
         <v>6378.0</v>
@@ -5378,7 +5384,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D166" s="6" t="n">
         <v>35065.0</v>
@@ -5639,7 +5645,7 @@
         <v>13</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D175" s="6" t="n">
         <v>10115.0</v>
@@ -5726,7 +5732,7 @@
         <v>10</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D178" s="6" t="n">
         <v>1182.0</v>
@@ -5871,7 +5877,7 @@
         <v>10</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D183" s="6" t="n">
         <v>6519.0</v>
@@ -6074,10 +6080,10 @@
         <v>13</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>12137.0</v>
+        <v>35195.0</v>
       </c>
       <c r="E190" s="7" t="s">
         <v>12</v>
@@ -6364,10 +6370,10 @@
         <v>13</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>35195.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>12</v>
@@ -6393,16 +6399,16 @@
         <v>13</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>1573.0</v>
+        <v>365576.0</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F201" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F201" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G201" s="8" t="s">
         <v>57</v>
@@ -6422,16 +6428,16 @@
         <v>13</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>365576.0</v>
+        <v>195553.0</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F202" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>57</v>
@@ -6480,10 +6486,10 @@
         <v>13</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>195553.0</v>
+        <v>28802.0</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>12</v>
@@ -6506,13 +6512,13 @@
         <v>57</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>264473.0</v>
+        <v>476600.0</v>
       </c>
       <c r="E205" s="7" t="s">
         <v>16</v>
@@ -6538,16 +6544,16 @@
         <v>30</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>9109.0</v>
+        <v>264473.0</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F206" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F206" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>57</v>
@@ -6567,10 +6573,10 @@
         <v>30</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>210.0</v>
+        <v>9109.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6593,19 +6599,19 @@
         <v>57</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>476600.0</v>
+        <v>210.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>57</v>
@@ -6654,10 +6660,10 @@
         <v>30</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>49095.0</v>
+        <v>74588.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6683,10 +6689,10 @@
         <v>30</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>83141.0</v>
+        <v>49095.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6709,13 +6715,13 @@
         <v>57</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>43423.0</v>
+        <v>83141.0</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>12</v>
@@ -6741,10 +6747,10 @@
         <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>28802.0</v>
+        <v>43423.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6767,13 +6773,13 @@
         <v>57</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>74588.0</v>
+        <v>1573.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6799,10 +6805,10 @@
         <v>13</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>142958.0</v>
+        <v>28745.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6828,10 +6834,10 @@
         <v>13</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>2938.0</v>
+        <v>8204.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
@@ -6857,10 +6863,10 @@
         <v>13</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>21893.0</v>
+        <v>2938.0</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>12</v>
@@ -6886,10 +6892,10 @@
         <v>13</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>47108.0</v>
+        <v>21893.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6915,10 +6921,10 @@
         <v>13</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>28745.0</v>
+        <v>47108.0</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>12</v>
@@ -6944,16 +6950,16 @@
         <v>13</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>570723.0</v>
+        <v>1087.0</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F220" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>58</v>
@@ -6973,16 +6979,16 @@
         <v>13</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>55407.0</v>
+        <v>400774.0</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F221" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G221" s="8" t="s">
         <v>58</v>
@@ -7002,16 +7008,16 @@
         <v>13</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>8125.0</v>
+        <v>142958.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F222" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>58</v>
@@ -7031,16 +7037,16 @@
         <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>17602.0</v>
+        <v>55407.0</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F223" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F223" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>58</v>
@@ -7060,16 +7066,16 @@
         <v>13</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>1087.0</v>
+        <v>8125.0</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F224" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F224" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>58</v>
@@ -7089,16 +7095,16 @@
         <v>13</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>13953.0</v>
+        <v>570723.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F225" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>58</v>
@@ -7118,10 +7124,10 @@
         <v>13</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>8204.0</v>
+        <v>17602.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7147,10 +7153,10 @@
         <v>13</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>400774.0</v>
+        <v>13953.0</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
@@ -7173,13 +7179,13 @@
         <v>58</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>196510.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>12</v>
@@ -7202,13 +7208,13 @@
         <v>58</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>3681.0</v>
+        <v>196510.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7234,16 +7240,16 @@
         <v>10</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>2847.0</v>
+        <v>65877.0</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F230" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F230" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>58</v>
@@ -7263,10 +7269,10 @@
         <v>10</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>586581.0</v>
+        <v>74089.0</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>12</v>
@@ -7292,10 +7298,10 @@
         <v>10</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>37213.0</v>
+        <v>2847.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>12</v>
@@ -7321,16 +7327,16 @@
         <v>10</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>65877.0</v>
+        <v>586581.0</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F233" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G233" s="8" t="s">
         <v>58</v>
@@ -7350,10 +7356,10 @@
         <v>10</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>8052.0</v>
+        <v>37213.0</v>
       </c>
       <c r="E234" s="7" t="s">
         <v>12</v>
@@ -7376,13 +7382,13 @@
         <v>58</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>74089.0</v>
+        <v>52019.0</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>12</v>
@@ -7405,13 +7411,13 @@
         <v>58</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>515691.0</v>
+        <v>8052.0</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>12</v>
@@ -7437,10 +7443,10 @@
         <v>30</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>77697.0</v>
+        <v>61111.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7466,10 +7472,10 @@
         <v>30</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>7771.0</v>
+        <v>77697.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7495,16 +7501,16 @@
         <v>30</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>118765.0</v>
+        <v>7771.0</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F239" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>58</v>
@@ -7521,19 +7527,19 @@
         <v>58</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>52019.0</v>
+        <v>118765.0</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F240" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F240" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G240" s="8" t="s">
         <v>58</v>
@@ -7553,10 +7559,10 @@
         <v>30</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>61111.0</v>
+        <v>515691.0</v>
       </c>
       <c r="E241" s="7" t="s">
         <v>12</v>
@@ -7640,16 +7646,16 @@
         <v>13</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D244" s="6" t="n">
-        <v>284471.0</v>
+        <v>5434.0</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F244" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F244" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>59</v>
@@ -7669,10 +7675,10 @@
         <v>13</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D245" s="6" t="n">
-        <v>5434.0</v>
+        <v>1388.0</v>
       </c>
       <c r="E245" s="7" t="s">
         <v>12</v>
@@ -7698,10 +7704,10 @@
         <v>13</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D246" s="6" t="n">
-        <v>1388.0</v>
+        <v>1210.0</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>12</v>
@@ -7727,10 +7733,10 @@
         <v>13</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>1210.0</v>
+        <v>33073.0</v>
       </c>
       <c r="E247" s="7" t="s">
         <v>12</v>
@@ -7756,10 +7762,10 @@
         <v>13</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>33073.0</v>
+        <v>23722.0</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>12</v>
@@ -7785,10 +7791,10 @@
         <v>13</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>23722.0</v>
+        <v>279499.0</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>12</v>
@@ -7814,10 +7820,10 @@
         <v>13</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>279499.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E250" s="7" t="s">
         <v>12</v>
@@ -7933,7 +7939,7 @@
         <v>45</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>5458.0</v>
+        <v>27632.0</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>12</v>
@@ -7959,16 +7965,16 @@
         <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>27632.0</v>
+        <v>284471.0</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F255" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F255" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G255" s="8" t="s">
         <v>59</v>
@@ -7985,13 +7991,13 @@
         <v>59</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D256" s="6" t="n">
-        <v>31570.0</v>
+        <v>17105.0</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>12</v>
@@ -8014,13 +8020,13 @@
         <v>59</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>17105.0</v>
+        <v>790.0</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>12</v>
@@ -8046,10 +8052,10 @@
         <v>30</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>302914.0</v>
+        <v>27683.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8075,10 +8081,10 @@
         <v>10</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>3186.0</v>
+        <v>31570.0</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>12</v>
@@ -8101,13 +8107,13 @@
         <v>59</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>27683.0</v>
+        <v>566118.0</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>12</v>
@@ -8133,10 +8139,10 @@
         <v>10</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>566118.0</v>
+        <v>25241.0</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>12</v>
@@ -8165,7 +8171,7 @@
         <v>48</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>25241.0</v>
+        <v>32891.0</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>12</v>
@@ -8191,10 +8197,10 @@
         <v>10</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>790.0</v>
+        <v>3186.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8217,13 +8223,13 @@
         <v>59</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>32891.0</v>
+        <v>302914.0</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>12</v>
@@ -8249,10 +8255,10 @@
         <v>30</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>10553.0</v>
+        <v>150.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8278,10 +8284,10 @@
         <v>30</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>150.0</v>
+        <v>6744.0</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>12</v>
@@ -8307,10 +8313,10 @@
         <v>30</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>6744.0</v>
+        <v>47292.0</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>12</v>
@@ -8336,10 +8342,10 @@
         <v>30</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D268" s="6" t="n">
-        <v>47292.0</v>
+        <v>7698.0</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>12</v>
@@ -8365,10 +8371,10 @@
         <v>30</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>7698.0</v>
+        <v>160020.0</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>12</v>
@@ -8394,10 +8400,10 @@
         <v>30</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>160020.0</v>
+        <v>10553.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8452,7 +8458,7 @@
         <v>13</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D272" s="6" t="n">
         <v>15.0</v>
@@ -8597,10 +8603,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>2731.0</v>
+        <v>170.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8713,10 +8719,10 @@
         <v>13</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>170.0</v>
+        <v>96105.0</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>12</v>
@@ -8742,10 +8748,10 @@
         <v>13</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>96105.0</v>
+        <v>38472.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8771,10 +8777,10 @@
         <v>13</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>220465.0</v>
+        <v>2731.0</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>12</v>
@@ -8829,10 +8835,10 @@
         <v>13</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>38472.0</v>
+        <v>220465.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8974,16 +8980,16 @@
         <v>10</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>6706.0</v>
+        <v>621367.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F290" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F290" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>60</v>
@@ -9006,7 +9012,7 @@
         <v>49</v>
       </c>
       <c r="D291" s="6" t="n">
-        <v>4451.0</v>
+        <v>6706.0</v>
       </c>
       <c r="E291" s="7" t="s">
         <v>12</v>
@@ -9032,10 +9038,10 @@
         <v>10</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D292" s="6" t="n">
-        <v>281.0</v>
+        <v>4451.0</v>
       </c>
       <c r="E292" s="7" t="s">
         <v>12</v>
@@ -9061,16 +9067,16 @@
         <v>10</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>621367.0</v>
+        <v>281.0</v>
       </c>
       <c r="E293" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F293" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F293" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G293" s="8" t="s">
         <v>60</v>
@@ -9090,16 +9096,16 @@
         <v>30</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>318547.0</v>
+        <v>87988.0</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F294" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F294" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G294" s="8" t="s">
         <v>60</v>
@@ -9119,16 +9125,16 @@
         <v>30</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>11792.0</v>
+        <v>318547.0</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F295" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F295" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G295" s="8" t="s">
         <v>60</v>
@@ -9148,16 +9154,16 @@
         <v>30</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D296" s="6" t="n">
-        <v>260392.0</v>
+        <v>21208.0</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F296" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F296" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G296" s="8" t="s">
         <v>60</v>
@@ -9177,10 +9183,10 @@
         <v>30</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D297" s="6" t="n">
-        <v>21208.0</v>
+        <v>27356.0</v>
       </c>
       <c r="E297" s="7" t="s">
         <v>12</v>
@@ -9206,16 +9212,16 @@
         <v>30</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>87988.0</v>
+        <v>18189.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F298" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F298" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>60</v>
@@ -9235,10 +9241,10 @@
         <v>30</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>18189.0</v>
+        <v>260392.0</v>
       </c>
       <c r="E299" s="7" t="s">
         <v>16</v>
@@ -9264,10 +9270,10 @@
         <v>30</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>27356.0</v>
+        <v>11792.0</v>
       </c>
       <c r="E300" s="7" t="s">
         <v>12</v>
@@ -9293,10 +9299,10 @@
         <v>13</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>10887.0</v>
+        <v>5125.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9322,16 +9328,16 @@
         <v>13</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D302" s="6" t="n">
-        <v>32243.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E302" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F302" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F302" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G302" s="8" t="s">
         <v>61</v>
@@ -9351,10 +9357,10 @@
         <v>13</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D303" s="6" t="n">
-        <v>306672.0</v>
+        <v>18161.0</v>
       </c>
       <c r="E303" s="7" t="s">
         <v>12</v>
@@ -9377,19 +9383,19 @@
         <v>61</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D304" s="6" t="n">
-        <v>278356.0</v>
+        <v>1798.0</v>
       </c>
       <c r="E304" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F304" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F304" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G304" s="8" t="s">
         <v>61</v>
@@ -9409,10 +9415,10 @@
         <v>13</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>4517.0</v>
+        <v>49827.0</v>
       </c>
       <c r="E305" s="7" t="s">
         <v>12</v>
@@ -9438,16 +9444,16 @@
         <v>13</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>414833.0</v>
+        <v>10887.0</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F306" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G306" s="8" t="s">
         <v>61</v>
@@ -9467,10 +9473,10 @@
         <v>13</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>49827.0</v>
+        <v>4517.0</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>12</v>
@@ -9496,16 +9502,16 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>16117.0</v>
+        <v>278356.0</v>
       </c>
       <c r="E308" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F308" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F308" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G308" s="8" t="s">
         <v>61</v>
@@ -9525,10 +9531,10 @@
         <v>13</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>18161.0</v>
+        <v>306672.0</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>12</v>
@@ -9554,10 +9560,10 @@
         <v>13</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>5125.0</v>
+        <v>32243.0</v>
       </c>
       <c r="E310" s="7" t="s">
         <v>12</v>
@@ -9580,13 +9586,13 @@
         <v>61</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>1798.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>12</v>
@@ -9641,10 +9647,10 @@
         <v>30</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>32300.0</v>
+        <v>3372.0</v>
       </c>
       <c r="E313" s="7" t="s">
         <v>12</v>
@@ -9667,13 +9673,13 @@
         <v>61</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D314" s="6" t="n">
-        <v>3372.0</v>
+        <v>2153.0</v>
       </c>
       <c r="E314" s="7" t="s">
         <v>12</v>
@@ -9696,13 +9702,13 @@
         <v>61</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D315" s="6" t="n">
-        <v>2153.0</v>
+        <v>191.0</v>
       </c>
       <c r="E315" s="7" t="s">
         <v>12</v>
@@ -9728,16 +9734,16 @@
         <v>10</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>25684.0</v>
+        <v>7578.0</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F316" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F316" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G316" s="8" t="s">
         <v>61</v>
@@ -9754,19 +9760,19 @@
         <v>61</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D317" s="6" t="n">
-        <v>191.0</v>
+        <v>560394.0</v>
       </c>
       <c r="E317" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F317" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F317" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G317" s="8" t="s">
         <v>61</v>
@@ -9786,16 +9792,16 @@
         <v>10</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D318" s="6" t="n">
-        <v>560394.0</v>
+        <v>19353.0</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F318" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F318" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G318" s="8" t="s">
         <v>61</v>
@@ -9815,16 +9821,16 @@
         <v>10</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D319" s="6" t="n">
-        <v>19353.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F319" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F319" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G319" s="8" t="s">
         <v>61</v>
@@ -9844,10 +9850,10 @@
         <v>10</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>7578.0</v>
+        <v>3475.0</v>
       </c>
       <c r="E320" s="7" t="s">
         <v>12</v>
@@ -9873,10 +9879,10 @@
         <v>10</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D321" s="6" t="n">
-        <v>3475.0</v>
+        <v>2152.0</v>
       </c>
       <c r="E321" s="7" t="s">
         <v>12</v>
@@ -9899,13 +9905,13 @@
         <v>61</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>2152.0</v>
+        <v>400544.0</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>12</v>
@@ -9931,10 +9937,10 @@
         <v>30</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>400544.0</v>
+        <v>17918.0</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>12</v>
@@ -9960,10 +9966,10 @@
         <v>30</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>17918.0</v>
+        <v>7822.0</v>
       </c>
       <c r="E324" s="7" t="s">
         <v>12</v>
@@ -9989,10 +9995,10 @@
         <v>30</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D325" s="6" t="n">
-        <v>7822.0</v>
+        <v>32300.0</v>
       </c>
       <c r="E325" s="7" t="s">
         <v>12</v>
@@ -10018,16 +10024,16 @@
         <v>13</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>288195.0</v>
+        <v>155203.0</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F326" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F326" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G326" s="8" t="s">
         <v>62</v>
@@ -10047,16 +10053,16 @@
         <v>13</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D327" s="6" t="n">
-        <v>1049.0</v>
+        <v>288195.0</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F327" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F327" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G327" s="8" t="s">
         <v>62</v>
@@ -10076,10 +10082,10 @@
         <v>13</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D328" s="6" t="n">
-        <v>373443.0</v>
+        <v>1049.0</v>
       </c>
       <c r="E328" s="7" t="s">
         <v>12</v>
@@ -10105,16 +10111,16 @@
         <v>13</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D329" s="6" t="n">
-        <v>177177.0</v>
+        <v>373443.0</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F329" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>62</v>
@@ -10134,16 +10140,16 @@
         <v>13</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D330" s="6" t="n">
-        <v>15369.0</v>
+        <v>177177.0</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F330" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F330" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G330" s="8" t="s">
         <v>62</v>
@@ -10163,10 +10169,10 @@
         <v>13</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D331" s="6" t="n">
-        <v>25040.0</v>
+        <v>15369.0</v>
       </c>
       <c r="E331" s="7" t="s">
         <v>12</v>
@@ -10192,16 +10198,16 @@
         <v>13</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D332" s="6" t="n">
-        <v>240445.0</v>
+        <v>25040.0</v>
       </c>
       <c r="E332" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F332" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F332" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G332" s="8" t="s">
         <v>62</v>
@@ -10221,10 +10227,10 @@
         <v>13</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D333" s="6" t="n">
-        <v>28904.0</v>
+        <v>16196.0</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>12</v>
@@ -10250,10 +10256,10 @@
         <v>13</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D334" s="6" t="n">
-        <v>7928.0</v>
+        <v>28904.0</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>12</v>
@@ -10279,10 +10285,10 @@
         <v>13</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D335" s="6" t="n">
-        <v>155203.0</v>
+        <v>7928.0</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>12</v>
@@ -10308,10 +10314,10 @@
         <v>13</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>16196.0</v>
+        <v>866.0</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>12</v>
@@ -10337,16 +10343,16 @@
         <v>13</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D337" s="6" t="n">
-        <v>39009.0</v>
+        <v>240445.0</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F337" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F337" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G337" s="8" t="s">
         <v>62</v>
@@ -10363,13 +10369,13 @@
         <v>62</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>866.0</v>
+        <v>1449.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10392,19 +10398,19 @@
         <v>62</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>21302.0</v>
+        <v>488224.0</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F339" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F339" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G339" s="8" t="s">
         <v>62</v>
@@ -10424,10 +10430,10 @@
         <v>30</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D340" s="6" t="n">
-        <v>182371.0</v>
+        <v>256566.0</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>12</v>
@@ -10453,10 +10459,10 @@
         <v>30</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D341" s="6" t="n">
-        <v>177268.0</v>
+        <v>6148.0</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>12</v>
@@ -10479,13 +10485,13 @@
         <v>62</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>15943.0</v>
+        <v>39009.0</v>
       </c>
       <c r="E342" s="7" t="s">
         <v>12</v>
@@ -10540,10 +10546,10 @@
         <v>30</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D344" s="6" t="n">
-        <v>1449.0</v>
+        <v>15943.0</v>
       </c>
       <c r="E344" s="7" t="s">
         <v>12</v>
@@ -10569,10 +10575,10 @@
         <v>30</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D345" s="6" t="n">
-        <v>6148.0</v>
+        <v>177268.0</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>12</v>
@@ -10598,10 +10604,10 @@
         <v>30</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>256566.0</v>
+        <v>182371.0</v>
       </c>
       <c r="E346" s="7" t="s">
         <v>12</v>
@@ -10624,19 +10630,19 @@
         <v>62</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D347" s="6" t="n">
-        <v>488224.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E347" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F347" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F347" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G347" s="8" t="s">
         <v>62</v>
@@ -10656,16 +10662,16 @@
         <v>13</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D348" s="6" t="n">
-        <v>104026.0</v>
+        <v>69412.0</v>
       </c>
       <c r="E348" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F348" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F348" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G348" s="8" t="s">
         <v>63</v>
@@ -10685,10 +10691,10 @@
         <v>13</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D349" s="6" t="n">
-        <v>9380.0</v>
+        <v>7560.0</v>
       </c>
       <c r="E349" s="7" t="s">
         <v>12</v>
@@ -10714,10 +10720,10 @@
         <v>13</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D350" s="6" t="n">
-        <v>185.0</v>
+        <v>805776.0</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>12</v>
@@ -10743,10 +10749,10 @@
         <v>13</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D351" s="6" t="n">
-        <v>7510.0</v>
+        <v>14289.0</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>12</v>
@@ -10772,10 +10778,10 @@
         <v>13</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D352" s="6" t="n">
-        <v>7560.0</v>
+        <v>62866.0</v>
       </c>
       <c r="E352" s="7" t="s">
         <v>12</v>
@@ -10830,10 +10836,10 @@
         <v>13</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D354" s="6" t="n">
-        <v>62866.0</v>
+        <v>14390.0</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>12</v>
@@ -10859,10 +10865,10 @@
         <v>13</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D355" s="6" t="n">
-        <v>14289.0</v>
+        <v>7510.0</v>
       </c>
       <c r="E355" s="7" t="s">
         <v>12</v>
@@ -10888,10 +10894,10 @@
         <v>13</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D356" s="6" t="n">
-        <v>805776.0</v>
+        <v>185.0</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>12</v>
@@ -10917,10 +10923,10 @@
         <v>13</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D357" s="6" t="n">
-        <v>15854.0</v>
+        <v>9380.0</v>
       </c>
       <c r="E357" s="7" t="s">
         <v>12</v>
@@ -10946,16 +10952,16 @@
         <v>13</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D358" s="6" t="n">
-        <v>69412.0</v>
+        <v>104026.0</v>
       </c>
       <c r="E358" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F358" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F358" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G358" s="8" t="s">
         <v>63</v>
@@ -10975,10 +10981,10 @@
         <v>13</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>14390.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>12</v>
@@ -11001,13 +11007,13 @@
         <v>63</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D360" s="6" t="n">
-        <v>42515.0</v>
+        <v>837.0</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>12</v>
@@ -11030,19 +11036,19 @@
         <v>63</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D361" s="6" t="n">
-        <v>2365.0</v>
+        <v>303397.0</v>
       </c>
       <c r="E361" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F361" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F361" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G361" s="8" t="s">
         <v>63</v>
@@ -11062,16 +11068,16 @@
         <v>30</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D362" s="6" t="n">
-        <v>303397.0</v>
+        <v>82520.0</v>
       </c>
       <c r="E362" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F362" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F362" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G362" s="8" t="s">
         <v>63</v>
@@ -11088,13 +11094,13 @@
         <v>63</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D363" s="6" t="n">
-        <v>837.0</v>
+        <v>2331.0</v>
       </c>
       <c r="E363" s="7" t="s">
         <v>12</v>
@@ -11117,19 +11123,19 @@
         <v>63</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D364" s="6" t="n">
-        <v>419250.0</v>
+        <v>111759.0</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F364" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>63</v>
@@ -11149,16 +11155,16 @@
         <v>10</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D365" s="6" t="n">
-        <v>96851.0</v>
+        <v>5088.0</v>
       </c>
       <c r="E365" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F365" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G365" s="8" t="s">
         <v>63</v>
@@ -11178,10 +11184,10 @@
         <v>10</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D366" s="6" t="n">
-        <v>103343.0</v>
+        <v>1766.0</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>12</v>
@@ -11207,10 +11213,10 @@
         <v>10</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D367" s="6" t="n">
-        <v>1766.0</v>
+        <v>2365.0</v>
       </c>
       <c r="E367" s="7" t="s">
         <v>12</v>
@@ -11236,16 +11242,16 @@
         <v>10</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D368" s="6" t="n">
-        <v>5088.0</v>
+        <v>96851.0</v>
       </c>
       <c r="E368" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F368" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F368" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G368" s="8" t="s">
         <v>63</v>
@@ -11262,19 +11268,19 @@
         <v>63</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D369" s="6" t="n">
-        <v>111759.0</v>
+        <v>419250.0</v>
       </c>
       <c r="E369" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F369" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F369" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G369" s="8" t="s">
         <v>63</v>
@@ -11294,10 +11300,10 @@
         <v>30</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D370" s="6" t="n">
-        <v>2331.0</v>
+        <v>42515.0</v>
       </c>
       <c r="E370" s="7" t="s">
         <v>12</v>
@@ -11320,13 +11326,13 @@
         <v>63</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D371" s="6" t="n">
-        <v>82520.0</v>
+        <v>103343.0</v>
       </c>
       <c r="E371" s="7" t="s">
         <v>12</v>
@@ -11352,10 +11358,10 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>8817.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E372" s="7" t="s">
         <v>12</v>
@@ -11381,10 +11387,10 @@
         <v>13</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D373" s="6" t="n">
-        <v>894.0</v>
+        <v>4119.0</v>
       </c>
       <c r="E373" s="7" t="s">
         <v>12</v>
@@ -11410,10 +11416,10 @@
         <v>13</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D374" s="6" t="n">
-        <v>815.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>12</v>
@@ -11439,10 +11445,10 @@
         <v>13</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D375" s="6" t="n">
-        <v>91275.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E375" s="7" t="s">
         <v>12</v>
@@ -11468,10 +11474,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>228939.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11497,10 +11503,10 @@
         <v>13</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D377" s="6" t="n">
-        <v>5337.0</v>
+        <v>228939.0</v>
       </c>
       <c r="E377" s="7" t="s">
         <v>12</v>
@@ -11526,10 +11532,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>3142.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11555,10 +11561,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>102120.0</v>
+        <v>815.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11584,10 +11590,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>96052.0</v>
+        <v>894.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11613,16 +11619,16 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>4119.0</v>
+        <v>404269.0</v>
       </c>
       <c r="E381" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F381" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F381" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>64</v>
@@ -11642,7 +11648,7 @@
         <v>13</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D382" s="6" t="n">
         <v>3681.0</v>
@@ -11668,13 +11674,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>7380.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11703,7 +11709,7 @@
         <v>40</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>25325.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11729,16 +11735,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D385" s="6" t="n">
-        <v>251397.0</v>
+        <v>12024.0</v>
       </c>
       <c r="E385" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F385" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F385" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G385" s="8" t="s">
         <v>64</v>
@@ -11758,10 +11764,10 @@
         <v>30</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D386" s="6" t="n">
-        <v>12024.0</v>
+        <v>42128.0</v>
       </c>
       <c r="E386" s="7" t="s">
         <v>12</v>
@@ -11787,10 +11793,10 @@
         <v>30</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D387" s="6" t="n">
-        <v>42045.0</v>
+        <v>13204.0</v>
       </c>
       <c r="E387" s="7" t="s">
         <v>12</v>
@@ -11816,10 +11822,10 @@
         <v>30</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D388" s="6" t="n">
-        <v>13204.0</v>
+        <v>7380.0</v>
       </c>
       <c r="E388" s="7" t="s">
         <v>12</v>
@@ -11848,7 +11854,7 @@
         <v>35</v>
       </c>
       <c r="D389" s="6" t="n">
-        <v>69155.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E389" s="7" t="s">
         <v>12</v>
@@ -11874,10 +11880,10 @@
         <v>10</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>774.0</v>
+        <v>3572.0</v>
       </c>
       <c r="E390" s="7" t="s">
         <v>12</v>
@@ -11903,10 +11909,10 @@
         <v>10</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D391" s="6" t="n">
-        <v>17755.0</v>
+        <v>18087.0</v>
       </c>
       <c r="E391" s="7" t="s">
         <v>12</v>
@@ -11935,7 +11941,7 @@
         <v>32</v>
       </c>
       <c r="D392" s="6" t="n">
-        <v>304947.0</v>
+        <v>306171.0</v>
       </c>
       <c r="E392" s="7" t="s">
         <v>12</v>
@@ -11964,7 +11970,7 @@
         <v>15</v>
       </c>
       <c r="D393" s="6" t="n">
-        <v>7076.0</v>
+        <v>7160.0</v>
       </c>
       <c r="E393" s="7" t="s">
         <v>12</v>
@@ -11993,7 +11999,7 @@
         <v>11</v>
       </c>
       <c r="D394" s="6" t="n">
-        <v>12334.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E394" s="7" t="s">
         <v>12</v>
@@ -12016,19 +12022,19 @@
         <v>64</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>401079.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E395" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F395" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G395" s="8" t="s">
         <v>64</v>
@@ -12037,6 +12043,1311 @@
         <v>64</v>
       </c>
       <c r="I395" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B396" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D396" s="6" t="n">
+        <v>5697.0</v>
+      </c>
+      <c r="E396" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F396" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G396" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H396" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I396" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D397" s="6" t="n">
+        <v>2360.0</v>
+      </c>
+      <c r="E397" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F397" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G397" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H397" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I397" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D398" s="6" t="n">
+        <v>5080.0</v>
+      </c>
+      <c r="E398" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F398" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G398" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H398" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I398" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D399" s="6" t="n">
+        <v>629.0</v>
+      </c>
+      <c r="E399" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F399" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G399" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H399" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I399" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D400" s="6" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="E400" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F400" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G400" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H400" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I400" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D401" s="6" t="n">
+        <v>376673.0</v>
+      </c>
+      <c r="E401" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F401" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G401" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H401" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I401" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C402" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D402" s="6" t="n">
+        <v>133369.0</v>
+      </c>
+      <c r="E402" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F402" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G402" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H402" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I402" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B403" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D403" s="6" t="n">
+        <v>621.0</v>
+      </c>
+      <c r="E403" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F403" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G403" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H403" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I403" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C404" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D404" s="6" t="n">
+        <v>727215.0</v>
+      </c>
+      <c r="E404" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F404" s="7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G404" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H404" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I404" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B405" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D405" s="6" t="n">
+        <v>6582.0</v>
+      </c>
+      <c r="E405" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F405" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G405" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H405" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I405" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D406" s="6" t="n">
+        <v>65752.0</v>
+      </c>
+      <c r="E406" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F406" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G406" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H406" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I406" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B407" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D407" s="6" t="n">
+        <v>9750.0</v>
+      </c>
+      <c r="E407" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F407" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G407" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H407" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I407" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B408" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D408" s="6" t="n">
+        <v>5282.0</v>
+      </c>
+      <c r="E408" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F408" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G408" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H408" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I408" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D409" s="6" t="n">
+        <v>73210.0</v>
+      </c>
+      <c r="E409" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F409" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G409" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H409" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I409" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D410" s="6" t="n">
+        <v>35159.0</v>
+      </c>
+      <c r="E410" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F410" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G410" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H410" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I410" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B411" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D411" s="6" t="n">
+        <v>4067.0</v>
+      </c>
+      <c r="E411" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F411" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G411" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H411" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I411" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B412" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D412" s="6" t="n">
+        <v>160711.0</v>
+      </c>
+      <c r="E412" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F412" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G412" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H412" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I412" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B413" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D413" s="6" t="n">
+        <v>285250.0</v>
+      </c>
+      <c r="E413" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F413" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G413" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H413" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I413" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B414" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C414" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D414" s="6" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="E414" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F414" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G414" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H414" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I414" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B415" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D415" s="6" t="n">
+        <v>217102.0</v>
+      </c>
+      <c r="E415" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F415" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G415" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H415" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I415" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B416" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D416" s="6" t="n">
+        <v>318.0</v>
+      </c>
+      <c r="E416" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F416" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G416" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H416" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I416" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B417" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D417" s="6" t="n">
+        <v>548.0</v>
+      </c>
+      <c r="E417" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F417" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G417" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H417" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I417" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B418" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D418" s="6" t="n">
+        <v>126941.0</v>
+      </c>
+      <c r="E418" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F418" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G418" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H418" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I418" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B419" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D419" s="6" t="n">
+        <v>7149.0</v>
+      </c>
+      <c r="E419" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F419" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G419" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H419" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I419" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B420" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C420" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D420" s="6" t="n">
+        <v>594689.0</v>
+      </c>
+      <c r="E420" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F420" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G420" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H420" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I420" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B421" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D421" s="6" t="n">
+        <v>39117.0</v>
+      </c>
+      <c r="E421" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F421" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G421" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H421" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I421" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B422" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C422" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D422" s="6" t="n">
+        <v>1355.0</v>
+      </c>
+      <c r="E422" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F422" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G422" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H422" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I422" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B423" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D423" s="6" t="n">
+        <v>172415.0</v>
+      </c>
+      <c r="E423" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F423" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G423" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H423" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I423" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C424" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D424" s="6" t="n">
+        <v>13478.0</v>
+      </c>
+      <c r="E424" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F424" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G424" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H424" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I424" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B425" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D425" s="6" t="n">
+        <v>91303.0</v>
+      </c>
+      <c r="E425" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F425" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G425" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H425" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I425" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C426" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D426" s="6" t="n">
+        <v>612.0</v>
+      </c>
+      <c r="E426" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F426" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G426" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H426" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I426" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B427" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C427" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D427" s="6" t="n">
+        <v>213.0</v>
+      </c>
+      <c r="E427" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F427" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G427" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H427" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I427" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B428" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D428" s="6" t="n">
+        <v>12850.0</v>
+      </c>
+      <c r="E428" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F428" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G428" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H428" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I428" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B429" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C429" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D429" s="6" t="n">
+        <v>13788.0</v>
+      </c>
+      <c r="E429" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F429" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G429" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H429" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I429" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D430" s="6" t="n">
+        <v>3890.0</v>
+      </c>
+      <c r="E430" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F430" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G430" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H430" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I430" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B431" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C431" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D431" s="6" t="n">
+        <v>34171.0</v>
+      </c>
+      <c r="E431" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F431" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G431" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H431" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I431" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B432" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C432" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D432" s="6" t="n">
+        <v>292.0</v>
+      </c>
+      <c r="E432" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F432" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G432" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H432" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I432" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B433" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C433" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D433" s="6" t="n">
+        <v>1261.0</v>
+      </c>
+      <c r="E433" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G433" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H433" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I433" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B434" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C434" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D434" s="6" t="n">
+        <v>119175.0</v>
+      </c>
+      <c r="E434" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F434" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G434" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H434" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I434" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B435" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C435" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D435" s="6" t="n">
+        <v>4580.0</v>
+      </c>
+      <c r="E435" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F435" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G435" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H435" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I435" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B436" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C436" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D436" s="6" t="n">
+        <v>105.0</v>
+      </c>
+      <c r="E436" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F436" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G436" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H436" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I436" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B437" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C437" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D437" s="6" t="n">
+        <v>62267.0</v>
+      </c>
+      <c r="E437" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F437" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G437" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H437" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I437" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B438" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C438" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D438" s="6" t="n">
+        <v>80345.0</v>
+      </c>
+      <c r="E438" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F438" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G438" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H438" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I438" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B439" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D439" s="6" t="n">
+        <v>20220.0</v>
+      </c>
+      <c r="E439" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F439" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G439" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H439" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I439" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B440" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C440" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D440" s="6" t="n">
+        <v>482.0</v>
+      </c>
+      <c r="E440" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F440" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G440" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H440" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I440" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3457" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3694" uniqueCount="68">
   <si>
     <t>Ngày</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
   </si>
 </sst>
 </file>
@@ -576,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I440"/>
+  <dimension ref="A1:I470"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -4137,10 +4140,10 @@
         <v>10</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>365.0</v>
+        <v>119.0</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>12</v>
@@ -4221,19 +4224,19 @@
         <v>54</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>26515.0</v>
+        <v>619458.0</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F126" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G126" s="8" t="s">
         <v>54</v>
@@ -4253,16 +4256,16 @@
         <v>10</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>619458.0</v>
+        <v>3016.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F127" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G127" s="8" t="s">
         <v>54</v>
@@ -4282,10 +4285,10 @@
         <v>10</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>3016.0</v>
+        <v>7646.0</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>12</v>
@@ -4311,10 +4314,10 @@
         <v>10</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>119.0</v>
+        <v>365.0</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>12</v>
@@ -4337,13 +4340,13 @@
         <v>54</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>7646.0</v>
+        <v>26515.0</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>12</v>
@@ -4398,10 +4401,10 @@
         <v>30</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>22735.0</v>
+        <v>130258.0</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>12</v>
@@ -4427,10 +4430,10 @@
         <v>30</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>130258.0</v>
+        <v>939.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>12</v>
@@ -4456,10 +4459,10 @@
         <v>30</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>939.0</v>
+        <v>5182.0</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>12</v>
@@ -4485,10 +4488,10 @@
         <v>30</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>5182.0</v>
+        <v>12.0</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>12</v>
@@ -4514,10 +4517,10 @@
         <v>30</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>12.0</v>
+        <v>22735.0</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>12</v>
@@ -4543,10 +4546,10 @@
         <v>13</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>43267.0</v>
+        <v>480065.0</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>12</v>
@@ -4572,10 +4575,10 @@
         <v>13</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>9757.0</v>
+        <v>2761.0</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>12</v>
@@ -4601,10 +4604,10 @@
         <v>13</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>2761.0</v>
+        <v>7072.0</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>12</v>
@@ -4630,10 +4633,10 @@
         <v>13</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>7072.0</v>
+        <v>9789.0</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
@@ -4659,10 +4662,10 @@
         <v>13</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>9789.0</v>
+        <v>43267.0</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>12</v>
@@ -4688,10 +4691,10 @@
         <v>13</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>69.0</v>
+        <v>1882.0</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>12</v>
@@ -4717,10 +4720,10 @@
         <v>13</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>480065.0</v>
+        <v>42366.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>12</v>
@@ -4746,10 +4749,10 @@
         <v>13</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>42366.0</v>
+        <v>832.0</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>12</v>
@@ -4775,10 +4778,10 @@
         <v>13</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>832.0</v>
+        <v>312933.0</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>12</v>
@@ -4804,10 +4807,10 @@
         <v>13</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>1882.0</v>
+        <v>25102.0</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>12</v>
@@ -4833,16 +4836,16 @@
         <v>13</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>25102.0</v>
+        <v>47872.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>55</v>
@@ -4862,16 +4865,16 @@
         <v>13</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>47872.0</v>
+        <v>69.0</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F148" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G148" s="8" t="s">
         <v>55</v>
@@ -4920,10 +4923,10 @@
         <v>13</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>325679.0</v>
+        <v>9757.0</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>12</v>
@@ -4946,13 +4949,13 @@
         <v>55</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>312933.0</v>
+        <v>576515.0</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>12</v>
@@ -5149,13 +5152,13 @@
         <v>55</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>576515.0</v>
+        <v>325679.0</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>12</v>
@@ -5674,16 +5677,16 @@
         <v>30</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>115261.0</v>
+        <v>275877.0</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G176" s="8" t="s">
         <v>56</v>
@@ -5761,16 +5764,16 @@
         <v>30</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>275877.0</v>
+        <v>115261.0</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G179" s="8" t="s">
         <v>56</v>
@@ -6512,13 +6515,13 @@
         <v>57</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>476600.0</v>
+        <v>264473.0</v>
       </c>
       <c r="E205" s="7" t="s">
         <v>16</v>
@@ -6544,16 +6547,16 @@
         <v>30</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>264473.0</v>
+        <v>9109.0</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F206" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>57</v>
@@ -6573,10 +6576,10 @@
         <v>30</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>9109.0</v>
+        <v>210.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6599,19 +6602,19 @@
         <v>57</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>210.0</v>
+        <v>476600.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F208" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F208" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>57</v>
@@ -6660,10 +6663,10 @@
         <v>30</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>74588.0</v>
+        <v>49095.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6689,10 +6692,10 @@
         <v>30</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>49095.0</v>
+        <v>83141.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6715,13 +6718,13 @@
         <v>57</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>83141.0</v>
+        <v>43423.0</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>12</v>
@@ -6747,10 +6750,10 @@
         <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>43423.0</v>
+        <v>1573.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6773,13 +6776,13 @@
         <v>57</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>1573.0</v>
+        <v>74588.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6950,16 +6953,16 @@
         <v>13</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>1087.0</v>
+        <v>8125.0</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F220" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F220" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>58</v>
@@ -7008,16 +7011,16 @@
         <v>13</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>142958.0</v>
+        <v>55407.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F222" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F222" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>58</v>
@@ -7037,10 +7040,10 @@
         <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>55407.0</v>
+        <v>570723.0</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>16</v>
@@ -7066,16 +7069,16 @@
         <v>13</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>8125.0</v>
+        <v>17602.0</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F224" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>58</v>
@@ -7095,16 +7098,16 @@
         <v>13</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>570723.0</v>
+        <v>1087.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F225" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>58</v>
@@ -7124,10 +7127,10 @@
         <v>13</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>17602.0</v>
+        <v>13953.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7153,10 +7156,10 @@
         <v>13</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>13953.0</v>
+        <v>142958.0</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
@@ -7179,13 +7182,13 @@
         <v>58</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>3681.0</v>
+        <v>196510.0</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>12</v>
@@ -7208,13 +7211,13 @@
         <v>58</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>196510.0</v>
+        <v>8052.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7240,16 +7243,16 @@
         <v>10</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>65877.0</v>
+        <v>74089.0</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F230" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>58</v>
@@ -7269,10 +7272,10 @@
         <v>10</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>74089.0</v>
+        <v>2847.0</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>12</v>
@@ -7298,10 +7301,10 @@
         <v>10</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>2847.0</v>
+        <v>586581.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>12</v>
@@ -7327,10 +7330,10 @@
         <v>10</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>586581.0</v>
+        <v>37213.0</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>12</v>
@@ -7356,16 +7359,16 @@
         <v>10</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>37213.0</v>
+        <v>65877.0</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F234" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F234" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>58</v>
@@ -7414,10 +7417,10 @@
         <v>10</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>8052.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>12</v>
@@ -7646,16 +7649,16 @@
         <v>13</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D244" s="6" t="n">
-        <v>5434.0</v>
+        <v>284471.0</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F244" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F244" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>59</v>
@@ -7675,10 +7678,10 @@
         <v>13</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D245" s="6" t="n">
-        <v>1388.0</v>
+        <v>5434.0</v>
       </c>
       <c r="E245" s="7" t="s">
         <v>12</v>
@@ -7704,10 +7707,10 @@
         <v>13</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D246" s="6" t="n">
-        <v>1210.0</v>
+        <v>1388.0</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>12</v>
@@ -7733,10 +7736,10 @@
         <v>13</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>33073.0</v>
+        <v>1210.0</v>
       </c>
       <c r="E247" s="7" t="s">
         <v>12</v>
@@ -7762,10 +7765,10 @@
         <v>13</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>23722.0</v>
+        <v>33073.0</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>12</v>
@@ -7791,10 +7794,10 @@
         <v>13</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>279499.0</v>
+        <v>23722.0</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>12</v>
@@ -7820,10 +7823,10 @@
         <v>13</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>5458.0</v>
+        <v>279499.0</v>
       </c>
       <c r="E250" s="7" t="s">
         <v>12</v>
@@ -7936,10 +7939,10 @@
         <v>13</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>27632.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>12</v>
@@ -7965,16 +7968,16 @@
         <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>284471.0</v>
+        <v>27632.0</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F255" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G255" s="8" t="s">
         <v>59</v>
@@ -8023,10 +8026,10 @@
         <v>10</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>790.0</v>
+        <v>3186.0</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>12</v>
@@ -8052,10 +8055,10 @@
         <v>30</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>27683.0</v>
+        <v>302914.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8078,13 +8081,13 @@
         <v>59</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>31570.0</v>
+        <v>27683.0</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>12</v>
@@ -8110,10 +8113,10 @@
         <v>10</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>566118.0</v>
+        <v>31570.0</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>12</v>
@@ -8139,10 +8142,10 @@
         <v>10</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>25241.0</v>
+        <v>566118.0</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>12</v>
@@ -8168,10 +8171,10 @@
         <v>10</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>32891.0</v>
+        <v>25241.0</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>12</v>
@@ -8197,10 +8200,10 @@
         <v>10</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>3186.0</v>
+        <v>790.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8223,13 +8226,13 @@
         <v>59</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>302914.0</v>
+        <v>32891.0</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>12</v>
@@ -8255,10 +8258,10 @@
         <v>30</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>150.0</v>
+        <v>10553.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8284,10 +8287,10 @@
         <v>30</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>6744.0</v>
+        <v>150.0</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>12</v>
@@ -8313,10 +8316,10 @@
         <v>30</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>47292.0</v>
+        <v>6744.0</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>12</v>
@@ -8342,10 +8345,10 @@
         <v>30</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D268" s="6" t="n">
-        <v>7698.0</v>
+        <v>47292.0</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>12</v>
@@ -8371,10 +8374,10 @@
         <v>30</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>160020.0</v>
+        <v>7698.0</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>12</v>
@@ -8400,10 +8403,10 @@
         <v>30</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>10553.0</v>
+        <v>160020.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8429,10 +8432,10 @@
         <v>13</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D271" s="6" t="n">
-        <v>233437.0</v>
+        <v>40129.0</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>12</v>
@@ -8603,10 +8606,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>170.0</v>
+        <v>220465.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8632,10 +8635,10 @@
         <v>13</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D278" s="6" t="n">
-        <v>40129.0</v>
+        <v>115.0</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>12</v>
@@ -8661,10 +8664,10 @@
         <v>13</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D279" s="6" t="n">
-        <v>115.0</v>
+        <v>3979.0</v>
       </c>
       <c r="E279" s="7" t="s">
         <v>12</v>
@@ -8690,10 +8693,10 @@
         <v>13</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>3979.0</v>
+        <v>170.0</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>12</v>
@@ -8835,10 +8838,10 @@
         <v>13</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>220465.0</v>
+        <v>233437.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8890,19 +8893,19 @@
         <v>60</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D287" s="6" t="n">
-        <v>1780.0</v>
+        <v>318547.0</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F287" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F287" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G287" s="8" t="s">
         <v>60</v>
@@ -8951,16 +8954,16 @@
         <v>10</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>1308.0</v>
+        <v>621367.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F289" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F289" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>60</v>
@@ -8980,16 +8983,16 @@
         <v>10</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>621367.0</v>
+        <v>4451.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F290" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>60</v>
@@ -9009,10 +9012,10 @@
         <v>10</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D291" s="6" t="n">
-        <v>6706.0</v>
+        <v>281.0</v>
       </c>
       <c r="E291" s="7" t="s">
         <v>12</v>
@@ -9038,10 +9041,10 @@
         <v>10</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D292" s="6" t="n">
-        <v>4451.0</v>
+        <v>1780.0</v>
       </c>
       <c r="E292" s="7" t="s">
         <v>12</v>
@@ -9067,10 +9070,10 @@
         <v>10</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>281.0</v>
+        <v>6706.0</v>
       </c>
       <c r="E293" s="7" t="s">
         <v>12</v>
@@ -9096,10 +9099,10 @@
         <v>30</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>87988.0</v>
+        <v>27356.0</v>
       </c>
       <c r="E294" s="7" t="s">
         <v>12</v>
@@ -9125,16 +9128,16 @@
         <v>30</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>318547.0</v>
+        <v>11792.0</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F295" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F295" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G295" s="8" t="s">
         <v>60</v>
@@ -9154,16 +9157,16 @@
         <v>30</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D296" s="6" t="n">
-        <v>21208.0</v>
+        <v>260392.0</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F296" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F296" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G296" s="8" t="s">
         <v>60</v>
@@ -9183,10 +9186,10 @@
         <v>30</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D297" s="6" t="n">
-        <v>27356.0</v>
+        <v>21208.0</v>
       </c>
       <c r="E297" s="7" t="s">
         <v>12</v>
@@ -9212,16 +9215,16 @@
         <v>30</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>18189.0</v>
+        <v>87988.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F298" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>60</v>
@@ -9238,19 +9241,19 @@
         <v>60</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>260392.0</v>
+        <v>1308.0</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F299" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G299" s="8" t="s">
         <v>60</v>
@@ -9270,16 +9273,16 @@
         <v>30</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>11792.0</v>
+        <v>18189.0</v>
       </c>
       <c r="E300" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F300" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F300" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G300" s="8" t="s">
         <v>60</v>
@@ -9299,10 +9302,10 @@
         <v>13</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>5125.0</v>
+        <v>4517.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9328,16 +9331,16 @@
         <v>13</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D302" s="6" t="n">
-        <v>414833.0</v>
+        <v>32243.0</v>
       </c>
       <c r="E302" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F302" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F302" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G302" s="8" t="s">
         <v>61</v>
@@ -9357,10 +9360,10 @@
         <v>13</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D303" s="6" t="n">
-        <v>18161.0</v>
+        <v>306672.0</v>
       </c>
       <c r="E303" s="7" t="s">
         <v>12</v>
@@ -9383,19 +9386,19 @@
         <v>61</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D304" s="6" t="n">
-        <v>1798.0</v>
+        <v>278356.0</v>
       </c>
       <c r="E304" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F304" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F304" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G304" s="8" t="s">
         <v>61</v>
@@ -9415,10 +9418,10 @@
         <v>13</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>49827.0</v>
+        <v>18161.0</v>
       </c>
       <c r="E305" s="7" t="s">
         <v>12</v>
@@ -9473,10 +9476,10 @@
         <v>13</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>4517.0</v>
+        <v>49827.0</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>12</v>
@@ -9502,10 +9505,10 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>278356.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E308" s="7" t="s">
         <v>16</v>
@@ -9531,10 +9534,10 @@
         <v>13</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>306672.0</v>
+        <v>5125.0</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>12</v>
@@ -9557,13 +9560,13 @@
         <v>61</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>32243.0</v>
+        <v>1798.0</v>
       </c>
       <c r="E310" s="7" t="s">
         <v>12</v>
@@ -9589,10 +9592,10 @@
         <v>13</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>16117.0</v>
+        <v>49079.0</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>12</v>
@@ -9618,10 +9621,10 @@
         <v>13</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>49079.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E312" s="7" t="s">
         <v>12</v>
@@ -9702,19 +9705,19 @@
         <v>61</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D315" s="6" t="n">
-        <v>191.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F315" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F315" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G315" s="8" t="s">
         <v>61</v>
@@ -9731,13 +9734,13 @@
         <v>61</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>7578.0</v>
+        <v>191.0</v>
       </c>
       <c r="E316" s="7" t="s">
         <v>12</v>
@@ -9821,16 +9824,16 @@
         <v>10</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D319" s="6" t="n">
-        <v>25684.0</v>
+        <v>7578.0</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F319" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G319" s="8" t="s">
         <v>61</v>
@@ -10024,16 +10027,16 @@
         <v>13</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>155203.0</v>
+        <v>288195.0</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F326" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F326" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G326" s="8" t="s">
         <v>62</v>
@@ -10053,16 +10056,16 @@
         <v>13</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D327" s="6" t="n">
-        <v>288195.0</v>
+        <v>1049.0</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F327" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G327" s="8" t="s">
         <v>62</v>
@@ -10082,10 +10085,10 @@
         <v>13</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D328" s="6" t="n">
-        <v>1049.0</v>
+        <v>373443.0</v>
       </c>
       <c r="E328" s="7" t="s">
         <v>12</v>
@@ -10111,16 +10114,16 @@
         <v>13</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D329" s="6" t="n">
-        <v>373443.0</v>
+        <v>177177.0</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F329" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F329" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>62</v>
@@ -10140,16 +10143,16 @@
         <v>13</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D330" s="6" t="n">
-        <v>177177.0</v>
+        <v>15369.0</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F330" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G330" s="8" t="s">
         <v>62</v>
@@ -10169,10 +10172,10 @@
         <v>13</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D331" s="6" t="n">
-        <v>15369.0</v>
+        <v>25040.0</v>
       </c>
       <c r="E331" s="7" t="s">
         <v>12</v>
@@ -10198,10 +10201,10 @@
         <v>13</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D332" s="6" t="n">
-        <v>25040.0</v>
+        <v>16196.0</v>
       </c>
       <c r="E332" s="7" t="s">
         <v>12</v>
@@ -10227,10 +10230,10 @@
         <v>13</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D333" s="6" t="n">
-        <v>16196.0</v>
+        <v>28904.0</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>12</v>
@@ -10256,10 +10259,10 @@
         <v>13</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D334" s="6" t="n">
-        <v>28904.0</v>
+        <v>7928.0</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>12</v>
@@ -10285,10 +10288,10 @@
         <v>13</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D335" s="6" t="n">
-        <v>7928.0</v>
+        <v>155203.0</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>12</v>
@@ -10314,10 +10317,10 @@
         <v>13</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>866.0</v>
+        <v>39009.0</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>12</v>
@@ -10369,13 +10372,13 @@
         <v>62</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>1449.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10398,19 +10401,19 @@
         <v>62</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>488224.0</v>
+        <v>182371.0</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F339" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G339" s="8" t="s">
         <v>62</v>
@@ -10430,10 +10433,10 @@
         <v>30</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D340" s="6" t="n">
-        <v>256566.0</v>
+        <v>177268.0</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>12</v>
@@ -10459,10 +10462,10 @@
         <v>30</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D341" s="6" t="n">
-        <v>6148.0</v>
+        <v>15943.0</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>12</v>
@@ -10485,13 +10488,13 @@
         <v>62</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>39009.0</v>
+        <v>38261.0</v>
       </c>
       <c r="E342" s="7" t="s">
         <v>12</v>
@@ -10517,10 +10520,10 @@
         <v>30</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D343" s="6" t="n">
-        <v>38261.0</v>
+        <v>1449.0</v>
       </c>
       <c r="E343" s="7" t="s">
         <v>12</v>
@@ -10546,10 +10549,10 @@
         <v>30</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D344" s="6" t="n">
-        <v>15943.0</v>
+        <v>6148.0</v>
       </c>
       <c r="E344" s="7" t="s">
         <v>12</v>
@@ -10575,10 +10578,10 @@
         <v>30</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D345" s="6" t="n">
-        <v>177268.0</v>
+        <v>256566.0</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>12</v>
@@ -10601,19 +10604,19 @@
         <v>62</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>182371.0</v>
+        <v>488224.0</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F346" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F346" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G346" s="8" t="s">
         <v>62</v>
@@ -10633,10 +10636,10 @@
         <v>13</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D347" s="6" t="n">
-        <v>21302.0</v>
+        <v>866.0</v>
       </c>
       <c r="E347" s="7" t="s">
         <v>12</v>
@@ -10662,10 +10665,10 @@
         <v>13</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D348" s="6" t="n">
-        <v>69412.0</v>
+        <v>14390.0</v>
       </c>
       <c r="E348" s="7" t="s">
         <v>12</v>
@@ -10691,10 +10694,10 @@
         <v>13</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D349" s="6" t="n">
-        <v>7560.0</v>
+        <v>9380.0</v>
       </c>
       <c r="E349" s="7" t="s">
         <v>12</v>
@@ -10720,10 +10723,10 @@
         <v>13</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D350" s="6" t="n">
-        <v>805776.0</v>
+        <v>185.0</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>12</v>
@@ -10749,10 +10752,10 @@
         <v>13</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D351" s="6" t="n">
-        <v>14289.0</v>
+        <v>7510.0</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>12</v>
@@ -10778,10 +10781,10 @@
         <v>13</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D352" s="6" t="n">
-        <v>62866.0</v>
+        <v>7560.0</v>
       </c>
       <c r="E352" s="7" t="s">
         <v>12</v>
@@ -10836,10 +10839,10 @@
         <v>13</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D354" s="6" t="n">
-        <v>14390.0</v>
+        <v>62866.0</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>12</v>
@@ -10865,10 +10868,10 @@
         <v>13</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D355" s="6" t="n">
-        <v>7510.0</v>
+        <v>14289.0</v>
       </c>
       <c r="E355" s="7" t="s">
         <v>12</v>
@@ -10894,10 +10897,10 @@
         <v>13</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D356" s="6" t="n">
-        <v>185.0</v>
+        <v>805776.0</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>12</v>
@@ -10923,10 +10926,10 @@
         <v>13</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D357" s="6" t="n">
-        <v>9380.0</v>
+        <v>69412.0</v>
       </c>
       <c r="E357" s="7" t="s">
         <v>12</v>
@@ -10978,13 +10981,13 @@
         <v>63</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>15854.0</v>
+        <v>837.0</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>12</v>
@@ -11007,13 +11010,13 @@
         <v>63</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D360" s="6" t="n">
-        <v>837.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>12</v>
@@ -11036,19 +11039,19 @@
         <v>63</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D361" s="6" t="n">
-        <v>303397.0</v>
+        <v>1766.0</v>
       </c>
       <c r="E361" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F361" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G361" s="8" t="s">
         <v>63</v>
@@ -11068,10 +11071,10 @@
         <v>30</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D362" s="6" t="n">
-        <v>82520.0</v>
+        <v>42515.0</v>
       </c>
       <c r="E362" s="7" t="s">
         <v>12</v>
@@ -11094,19 +11097,19 @@
         <v>63</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D363" s="6" t="n">
-        <v>2331.0</v>
+        <v>419250.0</v>
       </c>
       <c r="E363" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F363" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F363" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G363" s="8" t="s">
         <v>63</v>
@@ -11123,19 +11126,19 @@
         <v>63</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D364" s="6" t="n">
-        <v>111759.0</v>
+        <v>96851.0</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F364" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F364" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>63</v>
@@ -11155,10 +11158,10 @@
         <v>10</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D365" s="6" t="n">
-        <v>5088.0</v>
+        <v>2365.0</v>
       </c>
       <c r="E365" s="7" t="s">
         <v>12</v>
@@ -11184,10 +11187,10 @@
         <v>10</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D366" s="6" t="n">
-        <v>1766.0</v>
+        <v>103343.0</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>12</v>
@@ -11213,10 +11216,10 @@
         <v>10</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D367" s="6" t="n">
-        <v>2365.0</v>
+        <v>5088.0</v>
       </c>
       <c r="E367" s="7" t="s">
         <v>12</v>
@@ -11239,19 +11242,19 @@
         <v>63</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D368" s="6" t="n">
-        <v>96851.0</v>
+        <v>111759.0</v>
       </c>
       <c r="E368" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F368" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G368" s="8" t="s">
         <v>63</v>
@@ -11268,19 +11271,19 @@
         <v>63</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D369" s="6" t="n">
-        <v>419250.0</v>
+        <v>2331.0</v>
       </c>
       <c r="E369" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F369" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G369" s="8" t="s">
         <v>63</v>
@@ -11300,10 +11303,10 @@
         <v>30</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D370" s="6" t="n">
-        <v>42515.0</v>
+        <v>82520.0</v>
       </c>
       <c r="E370" s="7" t="s">
         <v>12</v>
@@ -11326,19 +11329,19 @@
         <v>63</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D371" s="6" t="n">
-        <v>103343.0</v>
+        <v>303397.0</v>
       </c>
       <c r="E371" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F371" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F371" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G371" s="8" t="s">
         <v>63</v>
@@ -11358,10 +11361,10 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>5337.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E372" s="7" t="s">
         <v>12</v>
@@ -11387,16 +11390,16 @@
         <v>13</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D373" s="6" t="n">
-        <v>4119.0</v>
+        <v>404269.0</v>
       </c>
       <c r="E373" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F373" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F373" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G373" s="8" t="s">
         <v>64</v>
@@ -11416,10 +11419,10 @@
         <v>13</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D374" s="6" t="n">
-        <v>96052.0</v>
+        <v>894.0</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>12</v>
@@ -11445,10 +11448,10 @@
         <v>13</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D375" s="6" t="n">
-        <v>102275.0</v>
+        <v>815.0</v>
       </c>
       <c r="E375" s="7" t="s">
         <v>12</v>
@@ -11474,10 +11477,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>8817.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11532,10 +11535,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>91385.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11561,10 +11564,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>815.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11590,10 +11593,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>894.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11619,16 +11622,16 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>404269.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E381" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F381" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F381" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>64</v>
@@ -11648,10 +11651,10 @@
         <v>13</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D382" s="6" t="n">
-        <v>3681.0</v>
+        <v>4119.0</v>
       </c>
       <c r="E382" s="7" t="s">
         <v>12</v>
@@ -11677,10 +11680,10 @@
         <v>13</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>3142.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11703,13 +11706,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>25352.0</v>
+        <v>3572.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11735,16 +11738,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D385" s="6" t="n">
-        <v>12024.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E385" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F385" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F385" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G385" s="8" t="s">
         <v>64</v>
@@ -11764,10 +11767,10 @@
         <v>30</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D386" s="6" t="n">
-        <v>42128.0</v>
+        <v>12024.0</v>
       </c>
       <c r="E386" s="7" t="s">
         <v>12</v>
@@ -11793,10 +11796,10 @@
         <v>30</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D387" s="6" t="n">
-        <v>13204.0</v>
+        <v>42128.0</v>
       </c>
       <c r="E387" s="7" t="s">
         <v>12</v>
@@ -11822,10 +11825,10 @@
         <v>30</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D388" s="6" t="n">
-        <v>7380.0</v>
+        <v>13204.0</v>
       </c>
       <c r="E388" s="7" t="s">
         <v>12</v>
@@ -11851,10 +11854,10 @@
         <v>30</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D389" s="6" t="n">
-        <v>69259.0</v>
+        <v>7380.0</v>
       </c>
       <c r="E389" s="7" t="s">
         <v>12</v>
@@ -11877,13 +11880,13 @@
         <v>64</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>3572.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E390" s="7" t="s">
         <v>12</v>
@@ -11909,10 +11912,10 @@
         <v>10</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D391" s="6" t="n">
-        <v>18087.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E391" s="7" t="s">
         <v>12</v>
@@ -11938,10 +11941,10 @@
         <v>10</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D392" s="6" t="n">
-        <v>306171.0</v>
+        <v>18087.0</v>
       </c>
       <c r="E392" s="7" t="s">
         <v>12</v>
@@ -11967,10 +11970,10 @@
         <v>10</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D393" s="6" t="n">
-        <v>7160.0</v>
+        <v>306171.0</v>
       </c>
       <c r="E393" s="7" t="s">
         <v>12</v>
@@ -11996,10 +11999,10 @@
         <v>10</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D394" s="6" t="n">
-        <v>14304.0</v>
+        <v>7160.0</v>
       </c>
       <c r="E394" s="7" t="s">
         <v>12</v>
@@ -12025,16 +12028,16 @@
         <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>252681.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F395" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F395" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G395" s="8" t="s">
         <v>64</v>
@@ -12054,10 +12057,10 @@
         <v>13</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D396" s="6" t="n">
-        <v>5697.0</v>
+        <v>5080.0</v>
       </c>
       <c r="E396" s="7" t="s">
         <v>12</v>
@@ -12083,16 +12086,16 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D397" s="6" t="n">
-        <v>2360.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E397" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F397" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F397" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G397" s="8" t="s">
         <v>65</v>
@@ -12112,10 +12115,10 @@
         <v>13</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D398" s="6" t="n">
-        <v>5080.0</v>
+        <v>5282.0</v>
       </c>
       <c r="E398" s="7" t="s">
         <v>12</v>
@@ -12141,10 +12144,10 @@
         <v>13</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D399" s="6" t="n">
-        <v>629.0</v>
+        <v>2360.0</v>
       </c>
       <c r="E399" s="7" t="s">
         <v>12</v>
@@ -12170,10 +12173,10 @@
         <v>13</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D400" s="6" t="n">
-        <v>48.0</v>
+        <v>629.0</v>
       </c>
       <c r="E400" s="7" t="s">
         <v>12</v>
@@ -12199,16 +12202,16 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>376673.0</v>
+        <v>48.0</v>
       </c>
       <c r="E401" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F401" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F401" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>65</v>
@@ -12228,16 +12231,16 @@
         <v>13</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D402" s="6" t="n">
-        <v>133369.0</v>
+        <v>378735.0</v>
       </c>
       <c r="E402" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F402" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F402" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G402" s="8" t="s">
         <v>65</v>
@@ -12257,10 +12260,10 @@
         <v>13</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D403" s="6" t="n">
-        <v>621.0</v>
+        <v>133369.0</v>
       </c>
       <c r="E403" s="7" t="s">
         <v>12</v>
@@ -12286,16 +12289,16 @@
         <v>13</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D404" s="6" t="n">
-        <v>727215.0</v>
+        <v>621.0</v>
       </c>
       <c r="E404" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F404" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F404" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G404" s="8" t="s">
         <v>65</v>
@@ -12315,16 +12318,16 @@
         <v>13</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D405" s="6" t="n">
-        <v>6582.0</v>
+        <v>728271.0</v>
       </c>
       <c r="E405" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F405" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F405" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G405" s="8" t="s">
         <v>65</v>
@@ -12344,16 +12347,16 @@
         <v>13</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D406" s="6" t="n">
-        <v>65752.0</v>
+        <v>6582.0</v>
       </c>
       <c r="E406" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F406" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F406" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G406" s="8" t="s">
         <v>65</v>
@@ -12402,10 +12405,10 @@
         <v>13</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>5282.0</v>
+        <v>5697.0</v>
       </c>
       <c r="E408" s="7" t="s">
         <v>12</v>
@@ -12521,7 +12524,7 @@
         <v>11</v>
       </c>
       <c r="D412" s="6" t="n">
-        <v>160711.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E412" s="7" t="s">
         <v>12</v>
@@ -12550,7 +12553,7 @@
         <v>32</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>285250.0</v>
+        <v>285268.0</v>
       </c>
       <c r="E413" s="7" t="s">
         <v>16</v>
@@ -12576,10 +12579,10 @@
         <v>10</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D414" s="6" t="n">
-        <v>60.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E414" s="7" t="s">
         <v>12</v>
@@ -12605,10 +12608,10 @@
         <v>10</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>217102.0</v>
+        <v>60.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12695,7 +12698,7 @@
         <v>38</v>
       </c>
       <c r="D418" s="6" t="n">
-        <v>126941.0</v>
+        <v>126986.0</v>
       </c>
       <c r="E418" s="7" t="s">
         <v>12</v>
@@ -12753,7 +12756,7 @@
         <v>39</v>
       </c>
       <c r="D420" s="6" t="n">
-        <v>594689.0</v>
+        <v>594911.0</v>
       </c>
       <c r="E420" s="7" t="s">
         <v>16</v>
@@ -12808,10 +12811,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>1355.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12837,10 +12840,10 @@
         <v>13</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D423" s="6" t="n">
-        <v>172415.0</v>
+        <v>44956.0</v>
       </c>
       <c r="E423" s="7" t="s">
         <v>12</v>
@@ -12866,10 +12869,10 @@
         <v>13</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D424" s="6" t="n">
-        <v>13478.0</v>
+        <v>8420.0</v>
       </c>
       <c r="E424" s="7" t="s">
         <v>12</v>
@@ -12895,10 +12898,10 @@
         <v>13</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D425" s="6" t="n">
-        <v>91303.0</v>
+        <v>210.0</v>
       </c>
       <c r="E425" s="7" t="s">
         <v>12</v>
@@ -12924,10 +12927,10 @@
         <v>13</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D426" s="6" t="n">
-        <v>612.0</v>
+        <v>784.0</v>
       </c>
       <c r="E426" s="7" t="s">
         <v>12</v>
@@ -12953,10 +12956,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>213.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -12982,10 +12985,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>12850.0</v>
+        <v>8146.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13011,10 +13014,10 @@
         <v>13</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D429" s="6" t="n">
-        <v>13788.0</v>
+        <v>260811.0</v>
       </c>
       <c r="E429" s="7" t="s">
         <v>12</v>
@@ -13037,13 +13040,13 @@
         <v>66</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D430" s="6" t="n">
-        <v>3890.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E430" s="7" t="s">
         <v>12</v>
@@ -13069,10 +13072,10 @@
         <v>13</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>34171.0</v>
+        <v>4241.0</v>
       </c>
       <c r="E431" s="7" t="s">
         <v>12</v>
@@ -13098,16 +13101,16 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>292.0</v>
+        <v>509687.0</v>
       </c>
       <c r="E432" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F432" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F432" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G432" s="8" t="s">
         <v>66</v>
@@ -13124,13 +13127,13 @@
         <v>66</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>1261.0</v>
+        <v>35061.0</v>
       </c>
       <c r="E433" s="7" t="s">
         <v>12</v>
@@ -13153,13 +13156,13 @@
         <v>66</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D434" s="6" t="n">
-        <v>119175.0</v>
+        <v>1355.0</v>
       </c>
       <c r="E434" s="7" t="s">
         <v>12</v>
@@ -13182,13 +13185,13 @@
         <v>66</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>4580.0</v>
+        <v>57903.0</v>
       </c>
       <c r="E435" s="7" t="s">
         <v>12</v>
@@ -13211,13 +13214,13 @@
         <v>66</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D436" s="6" t="n">
-        <v>105.0</v>
+        <v>4083.0</v>
       </c>
       <c r="E436" s="7" t="s">
         <v>12</v>
@@ -13243,10 +13246,10 @@
         <v>10</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D437" s="6" t="n">
-        <v>62267.0</v>
+        <v>5730.0</v>
       </c>
       <c r="E437" s="7" t="s">
         <v>12</v>
@@ -13269,19 +13272,19 @@
         <v>66</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>80345.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E438" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F438" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F438" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G438" s="8" t="s">
         <v>66</v>
@@ -13304,7 +13307,7 @@
         <v>11</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>20220.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E439" s="7" t="s">
         <v>12</v>
@@ -13327,13 +13330,13 @@
         <v>66</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>482.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E440" s="7" t="s">
         <v>12</v>
@@ -13348,6 +13351,876 @@
         <v>66</v>
       </c>
       <c r="I440" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B441" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C441" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D441" s="6" t="n">
+        <v>184302.0</v>
+      </c>
+      <c r="E441" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F441" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G441" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H441" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I441" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B442" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C442" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D442" s="6" t="n">
+        <v>4524.0</v>
+      </c>
+      <c r="E442" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F442" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G442" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H442" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I442" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B443" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D443" s="6" t="n">
+        <v>210036.0</v>
+      </c>
+      <c r="E443" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F443" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G443" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H443" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I443" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B444" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D444" s="6" t="n">
+        <v>9349.0</v>
+      </c>
+      <c r="E444" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F444" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G444" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H444" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I444" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B445" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C445" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D445" s="6" t="n">
+        <v>31883.0</v>
+      </c>
+      <c r="E445" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F445" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G445" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H445" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I445" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B446" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C446" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D446" s="6" t="n">
+        <v>105.0</v>
+      </c>
+      <c r="E446" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F446" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G446" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H446" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I446" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B447" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D447" s="6" t="n">
+        <v>1412.0</v>
+      </c>
+      <c r="E447" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F447" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G447" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H447" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I447" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B448" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C448" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D448" s="6" t="n">
+        <v>94352.0</v>
+      </c>
+      <c r="E448" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F448" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G448" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H448" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I448" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B449" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D449" s="6" t="n">
+        <v>1503.0</v>
+      </c>
+      <c r="E449" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F449" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G449" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H449" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I449" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B450" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D450" s="6" t="n">
+        <v>398292.0</v>
+      </c>
+      <c r="E450" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F450" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G450" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H450" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I450" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B451" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D451" s="6" t="n">
+        <v>16955.0</v>
+      </c>
+      <c r="E451" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F451" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G451" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H451" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I451" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B452" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C452" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D452" s="6" t="n">
+        <v>172657.0</v>
+      </c>
+      <c r="E452" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F452" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G452" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H452" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I452" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B453" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C453" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D453" s="6" t="n">
+        <v>15909.0</v>
+      </c>
+      <c r="E453" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F453" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G453" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H453" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I453" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B454" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C454" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D454" s="6" t="n">
+        <v>176527.0</v>
+      </c>
+      <c r="E454" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F454" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G454" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H454" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I454" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B455" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C455" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D455" s="6" t="n">
+        <v>1963.0</v>
+      </c>
+      <c r="E455" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F455" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G455" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H455" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I455" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B456" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C456" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D456" s="6" t="n">
+        <v>818.0</v>
+      </c>
+      <c r="E456" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F456" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G456" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H456" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I456" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B457" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D457" s="6" t="n">
+        <v>1522.0</v>
+      </c>
+      <c r="E457" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F457" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G457" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H457" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I457" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B458" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C458" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D458" s="6" t="n">
+        <v>27369.0</v>
+      </c>
+      <c r="E458" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F458" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G458" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H458" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I458" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B459" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D459" s="6" t="n">
+        <v>26945.0</v>
+      </c>
+      <c r="E459" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F459" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G459" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H459" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I459" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B460" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C460" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D460" s="6" t="n">
+        <v>57082.0</v>
+      </c>
+      <c r="E460" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F460" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G460" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H460" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I460" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B461" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D461" s="6" t="n">
+        <v>2975.0</v>
+      </c>
+      <c r="E461" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F461" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G461" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H461" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I461" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B462" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C462" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D462" s="6" t="n">
+        <v>941.0</v>
+      </c>
+      <c r="E462" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F462" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G462" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H462" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I462" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B463" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C463" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D463" s="6" t="n">
+        <v>1794.0</v>
+      </c>
+      <c r="E463" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F463" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G463" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H463" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I463" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B464" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C464" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D464" s="6" t="n">
+        <v>58405.0</v>
+      </c>
+      <c r="E464" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F464" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G464" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H464" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I464" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B465" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C465" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D465" s="6" t="n">
+        <v>56860.0</v>
+      </c>
+      <c r="E465" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F465" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G465" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H465" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I465" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B466" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C466" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D466" s="6" t="n">
+        <v>24813.0</v>
+      </c>
+      <c r="E466" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F466" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G466" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H466" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I466" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B467" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C467" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D467" s="6" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="E467" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F467" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G467" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H467" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I467" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B468" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C468" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D468" s="6" t="n">
+        <v>31900.0</v>
+      </c>
+      <c r="E468" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F468" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G468" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H468" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I468" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B469" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C469" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D469" s="6" t="n">
+        <v>23056.0</v>
+      </c>
+      <c r="E469" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F469" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G469" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H469" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I469" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B470" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C470" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D470" s="6" t="n">
+        <v>786.0</v>
+      </c>
+      <c r="E470" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F470" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G470" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H470" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I470" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3694" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3885" uniqueCount="69">
   <si>
     <t>Ngày</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
   </si>
 </sst>
 </file>
@@ -579,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I470"/>
+  <dimension ref="A1:I494"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -3821,16 +3824,16 @@
         <v>13</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>299654.0</v>
+        <v>199793.0</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>54</v>
@@ -3850,16 +3853,16 @@
         <v>13</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>290.0</v>
+        <v>299654.0</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>54</v>
@@ -3879,10 +3882,10 @@
         <v>13</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>120.0</v>
+        <v>290.0</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>12</v>
@@ -4082,16 +4085,16 @@
         <v>13</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>20525.0</v>
+        <v>1325.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F121" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>54</v>
@@ -4111,16 +4114,16 @@
         <v>13</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>199793.0</v>
+        <v>20525.0</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G122" s="8" t="s">
         <v>54</v>
@@ -4137,13 +4140,13 @@
         <v>54</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>12</v>
@@ -4169,10 +4172,10 @@
         <v>13</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>1325.0</v>
+        <v>26515.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
@@ -4285,10 +4288,10 @@
         <v>10</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>7646.0</v>
+        <v>119.0</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>12</v>
@@ -4340,13 +4343,13 @@
         <v>54</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>26515.0</v>
+        <v>12.0</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>12</v>
@@ -4398,13 +4401,13 @@
         <v>54</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>130258.0</v>
+        <v>7646.0</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>12</v>
@@ -4430,10 +4433,10 @@
         <v>30</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>939.0</v>
+        <v>130258.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>12</v>
@@ -4459,10 +4462,10 @@
         <v>30</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>5182.0</v>
+        <v>939.0</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>12</v>
@@ -4488,10 +4491,10 @@
         <v>30</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>12.0</v>
+        <v>5182.0</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>12</v>
@@ -4546,10 +4549,10 @@
         <v>13</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>480065.0</v>
+        <v>43267.0</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>12</v>
@@ -4575,10 +4578,10 @@
         <v>13</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>2761.0</v>
+        <v>9757.0</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>12</v>
@@ -4604,10 +4607,10 @@
         <v>13</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>7072.0</v>
+        <v>2761.0</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>12</v>
@@ -4633,10 +4636,10 @@
         <v>13</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>9789.0</v>
+        <v>7072.0</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
@@ -4662,10 +4665,10 @@
         <v>13</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>43267.0</v>
+        <v>9789.0</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>12</v>
@@ -4720,10 +4723,10 @@
         <v>13</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>42366.0</v>
+        <v>480065.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>12</v>
@@ -4749,10 +4752,10 @@
         <v>13</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>832.0</v>
+        <v>42366.0</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>12</v>
@@ -4778,10 +4781,10 @@
         <v>13</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>312933.0</v>
+        <v>832.0</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>12</v>
@@ -4807,16 +4810,16 @@
         <v>13</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>25102.0</v>
+        <v>47872.0</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F146" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G146" s="8" t="s">
         <v>55</v>
@@ -4836,16 +4839,16 @@
         <v>13</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>47872.0</v>
+        <v>69.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F147" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>55</v>
@@ -4865,10 +4868,10 @@
         <v>13</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>69.0</v>
+        <v>312933.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
@@ -4923,10 +4926,10 @@
         <v>13</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>9757.0</v>
+        <v>25102.0</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>12</v>
@@ -4949,13 +4952,13 @@
         <v>55</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>576515.0</v>
+        <v>325679.0</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>12</v>
@@ -5010,10 +5013,10 @@
         <v>10</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>1746.0</v>
+        <v>576515.0</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>12</v>
@@ -5068,10 +5071,10 @@
         <v>10</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>143.0</v>
+        <v>1746.0</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>12</v>
@@ -5152,13 +5155,13 @@
         <v>55</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>325679.0</v>
+        <v>143.0</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>12</v>
@@ -5677,16 +5680,16 @@
         <v>30</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>275877.0</v>
+        <v>115261.0</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G176" s="8" t="s">
         <v>56</v>
@@ -5764,16 +5767,16 @@
         <v>30</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>115261.0</v>
+        <v>275877.0</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G179" s="8" t="s">
         <v>56</v>
@@ -6054,16 +6057,16 @@
         <v>13</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>269159.0</v>
+        <v>120141.0</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F189" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F189" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G189" s="8" t="s">
         <v>57</v>
@@ -6083,10 +6086,10 @@
         <v>13</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>35195.0</v>
+        <v>464.0</v>
       </c>
       <c r="E190" s="7" t="s">
         <v>12</v>
@@ -6112,10 +6115,10 @@
         <v>13</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>464.0</v>
+        <v>15477.0</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>12</v>
@@ -6141,10 +6144,10 @@
         <v>13</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>15477.0</v>
+        <v>24943.0</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>12</v>
@@ -6170,16 +6173,16 @@
         <v>13</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>24943.0</v>
+        <v>269159.0</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F193" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F193" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G193" s="8" t="s">
         <v>57</v>
@@ -6228,10 +6231,10 @@
         <v>13</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>120141.0</v>
+        <v>24242.0</v>
       </c>
       <c r="E195" s="7" t="s">
         <v>12</v>
@@ -6257,10 +6260,10 @@
         <v>13</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>24242.0</v>
+        <v>6514.0</v>
       </c>
       <c r="E196" s="7" t="s">
         <v>12</v>
@@ -6286,10 +6289,10 @@
         <v>13</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>6514.0</v>
+        <v>18488.0</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>12</v>
@@ -6315,10 +6318,10 @@
         <v>13</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>18488.0</v>
+        <v>55.0</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>12</v>
@@ -6344,10 +6347,10 @@
         <v>13</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>55.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>12</v>
@@ -6373,10 +6376,10 @@
         <v>13</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>12137.0</v>
+        <v>35195.0</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>12</v>
@@ -6399,13 +6402,13 @@
         <v>57</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>365576.0</v>
+        <v>264473.0</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>16</v>
@@ -6431,16 +6434,16 @@
         <v>13</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>195553.0</v>
+        <v>365576.0</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F202" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F202" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>57</v>
@@ -6460,10 +6463,10 @@
         <v>30</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>28338.0</v>
+        <v>13066.0</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>12</v>
@@ -6489,10 +6492,10 @@
         <v>13</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>28802.0</v>
+        <v>195553.0</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>12</v>
@@ -6518,16 +6521,16 @@
         <v>30</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>264473.0</v>
+        <v>9109.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F205" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>57</v>
@@ -6547,10 +6550,10 @@
         <v>30</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>9109.0</v>
+        <v>210.0</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>12</v>
@@ -6576,10 +6579,10 @@
         <v>30</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>210.0</v>
+        <v>28338.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6634,10 +6637,10 @@
         <v>30</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>13066.0</v>
+        <v>74588.0</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>12</v>
@@ -6663,10 +6666,10 @@
         <v>30</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>49095.0</v>
+        <v>83141.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6689,13 +6692,13 @@
         <v>57</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>83141.0</v>
+        <v>43423.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6721,10 +6724,10 @@
         <v>13</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>43423.0</v>
+        <v>1573.0</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>12</v>
@@ -6750,10 +6753,10 @@
         <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>1573.0</v>
+        <v>28802.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6779,10 +6782,10 @@
         <v>30</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>74588.0</v>
+        <v>49095.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6982,10 +6985,10 @@
         <v>13</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>400774.0</v>
+        <v>142958.0</v>
       </c>
       <c r="E221" s="7" t="s">
         <v>12</v>
@@ -7156,10 +7159,10 @@
         <v>13</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>142958.0</v>
+        <v>400774.0</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
@@ -7240,13 +7243,13 @@
         <v>58</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>74089.0</v>
+        <v>52019.0</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>12</v>
@@ -7272,10 +7275,10 @@
         <v>10</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>2847.0</v>
+        <v>74089.0</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>12</v>
@@ -7301,10 +7304,10 @@
         <v>10</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>586581.0</v>
+        <v>2847.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>12</v>
@@ -7330,10 +7333,10 @@
         <v>10</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>37213.0</v>
+        <v>586581.0</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>12</v>
@@ -7385,13 +7388,13 @@
         <v>58</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>52019.0</v>
+        <v>37213.0</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>12</v>
@@ -7446,10 +7449,10 @@
         <v>30</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>61111.0</v>
+        <v>515691.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7475,10 +7478,10 @@
         <v>30</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>77697.0</v>
+        <v>61111.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7504,10 +7507,10 @@
         <v>30</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>7771.0</v>
+        <v>77697.0</v>
       </c>
       <c r="E239" s="7" t="s">
         <v>12</v>
@@ -7533,16 +7536,16 @@
         <v>30</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>118765.0</v>
+        <v>7771.0</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F240" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G240" s="8" t="s">
         <v>58</v>
@@ -7562,16 +7565,16 @@
         <v>30</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>515691.0</v>
+        <v>118765.0</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F241" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F241" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>58</v>
@@ -7765,16 +7768,16 @@
         <v>13</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>33073.0</v>
+        <v>371730.0</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F248" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F248" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>59</v>
@@ -7794,10 +7797,10 @@
         <v>13</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>23722.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>12</v>
@@ -7823,10 +7826,10 @@
         <v>13</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>279499.0</v>
+        <v>23722.0</v>
       </c>
       <c r="E250" s="7" t="s">
         <v>12</v>
@@ -7852,10 +7855,10 @@
         <v>13</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>3296.0</v>
+        <v>279499.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>12</v>
@@ -7881,10 +7884,10 @@
         <v>13</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>160.0</v>
+        <v>33073.0</v>
       </c>
       <c r="E252" s="7" t="s">
         <v>12</v>
@@ -7910,16 +7913,16 @@
         <v>13</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>371730.0</v>
+        <v>3296.0</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F253" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G253" s="8" t="s">
         <v>59</v>
@@ -7939,10 +7942,10 @@
         <v>13</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>5458.0</v>
+        <v>160.0</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>12</v>
@@ -7994,13 +7997,13 @@
         <v>59</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D256" s="6" t="n">
-        <v>17105.0</v>
+        <v>302914.0</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>12</v>
@@ -8023,13 +8026,13 @@
         <v>59</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>3186.0</v>
+        <v>17105.0</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>12</v>
@@ -8052,13 +8055,13 @@
         <v>59</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>302914.0</v>
+        <v>790.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8081,13 +8084,13 @@
         <v>59</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>27683.0</v>
+        <v>3186.0</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>12</v>
@@ -8200,10 +8203,10 @@
         <v>10</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>790.0</v>
+        <v>32891.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8226,13 +8229,13 @@
         <v>59</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>32891.0</v>
+        <v>27683.0</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>12</v>
@@ -8287,10 +8290,10 @@
         <v>30</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>150.0</v>
+        <v>6744.0</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>12</v>
@@ -8316,10 +8319,10 @@
         <v>30</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>6744.0</v>
+        <v>47292.0</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>12</v>
@@ -8345,10 +8348,10 @@
         <v>30</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D268" s="6" t="n">
-        <v>47292.0</v>
+        <v>7698.0</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>12</v>
@@ -8374,10 +8377,10 @@
         <v>30</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>7698.0</v>
+        <v>160020.0</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>12</v>
@@ -8403,10 +8406,10 @@
         <v>30</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>160020.0</v>
+        <v>150.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8461,10 +8464,10 @@
         <v>13</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D272" s="6" t="n">
-        <v>15.0</v>
+        <v>20732.0</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>12</v>
@@ -8490,10 +8493,10 @@
         <v>13</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D273" s="6" t="n">
-        <v>20732.0</v>
+        <v>6937.0</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>12</v>
@@ -8519,10 +8522,10 @@
         <v>13</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D274" s="6" t="n">
-        <v>6937.0</v>
+        <v>15068.0</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>12</v>
@@ -8548,10 +8551,10 @@
         <v>13</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D275" s="6" t="n">
-        <v>15068.0</v>
+        <v>26381.0</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>12</v>
@@ -8577,10 +8580,10 @@
         <v>13</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D276" s="6" t="n">
-        <v>26381.0</v>
+        <v>233437.0</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>12</v>
@@ -8606,10 +8609,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>220465.0</v>
+        <v>170.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8693,10 +8696,10 @@
         <v>13</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>170.0</v>
+        <v>96105.0</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>12</v>
@@ -8722,10 +8725,10 @@
         <v>13</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>96105.0</v>
+        <v>38472.0</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>12</v>
@@ -8751,10 +8754,10 @@
         <v>13</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>38472.0</v>
+        <v>2731.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8780,10 +8783,10 @@
         <v>13</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>2731.0</v>
+        <v>35463.0</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>12</v>
@@ -8809,10 +8812,10 @@
         <v>13</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>35463.0</v>
+        <v>15.0</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>12</v>
@@ -8838,10 +8841,10 @@
         <v>13</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>233437.0</v>
+        <v>20130.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8867,16 +8870,16 @@
         <v>13</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>168847.0</v>
+        <v>220465.0</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F286" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G286" s="8" t="s">
         <v>60</v>
@@ -8922,13 +8925,13 @@
         <v>60</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>20130.0</v>
+        <v>1308.0</v>
       </c>
       <c r="E288" s="7" t="s">
         <v>12</v>
@@ -8980,19 +8983,19 @@
         <v>60</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>4451.0</v>
+        <v>168847.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F290" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F290" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>60</v>
@@ -9012,10 +9015,10 @@
         <v>10</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D291" s="6" t="n">
-        <v>281.0</v>
+        <v>4451.0</v>
       </c>
       <c r="E291" s="7" t="s">
         <v>12</v>
@@ -9041,10 +9044,10 @@
         <v>10</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D292" s="6" t="n">
-        <v>1780.0</v>
+        <v>281.0</v>
       </c>
       <c r="E292" s="7" t="s">
         <v>12</v>
@@ -9070,10 +9073,10 @@
         <v>10</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>6706.0</v>
+        <v>1780.0</v>
       </c>
       <c r="E293" s="7" t="s">
         <v>12</v>
@@ -9096,13 +9099,13 @@
         <v>60</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>27356.0</v>
+        <v>6706.0</v>
       </c>
       <c r="E294" s="7" t="s">
         <v>12</v>
@@ -9128,10 +9131,10 @@
         <v>30</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>11792.0</v>
+        <v>27356.0</v>
       </c>
       <c r="E295" s="7" t="s">
         <v>12</v>
@@ -9241,19 +9244,19 @@
         <v>60</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>1308.0</v>
+        <v>18189.0</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F299" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F299" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G299" s="8" t="s">
         <v>60</v>
@@ -9273,16 +9276,16 @@
         <v>30</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>18189.0</v>
+        <v>11792.0</v>
       </c>
       <c r="E300" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F300" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F300" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G300" s="8" t="s">
         <v>60</v>
@@ -9418,16 +9421,16 @@
         <v>13</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>18161.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F305" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F305" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G305" s="8" t="s">
         <v>61</v>
@@ -9447,10 +9450,10 @@
         <v>13</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>10887.0</v>
+        <v>49827.0</v>
       </c>
       <c r="E306" s="7" t="s">
         <v>12</v>
@@ -9476,10 +9479,10 @@
         <v>13</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>49827.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>12</v>
@@ -9505,16 +9508,16 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>414833.0</v>
+        <v>18161.0</v>
       </c>
       <c r="E308" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F308" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F308" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G308" s="8" t="s">
         <v>61</v>
@@ -9621,10 +9624,10 @@
         <v>13</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>16117.0</v>
+        <v>10887.0</v>
       </c>
       <c r="E312" s="7" t="s">
         <v>12</v>
@@ -9679,10 +9682,10 @@
         <v>10</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D314" s="6" t="n">
-        <v>2153.0</v>
+        <v>3475.0</v>
       </c>
       <c r="E314" s="7" t="s">
         <v>12</v>
@@ -9705,19 +9708,19 @@
         <v>61</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D315" s="6" t="n">
-        <v>25684.0</v>
+        <v>191.0</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F315" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F315" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G315" s="8" t="s">
         <v>61</v>
@@ -9734,13 +9737,13 @@
         <v>61</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>191.0</v>
+        <v>7578.0</v>
       </c>
       <c r="E316" s="7" t="s">
         <v>12</v>
@@ -9766,16 +9769,16 @@
         <v>10</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D317" s="6" t="n">
-        <v>560394.0</v>
+        <v>19353.0</v>
       </c>
       <c r="E317" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F317" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F317" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G317" s="8" t="s">
         <v>61</v>
@@ -9795,10 +9798,10 @@
         <v>10</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D318" s="6" t="n">
-        <v>19353.0</v>
+        <v>2153.0</v>
       </c>
       <c r="E318" s="7" t="s">
         <v>12</v>
@@ -9824,16 +9827,16 @@
         <v>10</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D319" s="6" t="n">
-        <v>7578.0</v>
+        <v>560394.0</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F319" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F319" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G319" s="8" t="s">
         <v>61</v>
@@ -9853,16 +9856,16 @@
         <v>10</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>3475.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F320" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F320" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G320" s="8" t="s">
         <v>61</v>
@@ -10027,16 +10030,16 @@
         <v>13</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>288195.0</v>
+        <v>155203.0</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F326" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F326" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G326" s="8" t="s">
         <v>62</v>
@@ -10056,16 +10059,16 @@
         <v>13</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D327" s="6" t="n">
-        <v>1049.0</v>
+        <v>288195.0</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F327" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F327" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G327" s="8" t="s">
         <v>62</v>
@@ -10085,10 +10088,10 @@
         <v>13</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D328" s="6" t="n">
-        <v>373443.0</v>
+        <v>1049.0</v>
       </c>
       <c r="E328" s="7" t="s">
         <v>12</v>
@@ -10114,16 +10117,16 @@
         <v>13</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D329" s="6" t="n">
-        <v>177177.0</v>
+        <v>373443.0</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F329" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>62</v>
@@ -10143,16 +10146,16 @@
         <v>13</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D330" s="6" t="n">
-        <v>15369.0</v>
+        <v>177177.0</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F330" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F330" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G330" s="8" t="s">
         <v>62</v>
@@ -10172,10 +10175,10 @@
         <v>13</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D331" s="6" t="n">
-        <v>25040.0</v>
+        <v>15369.0</v>
       </c>
       <c r="E331" s="7" t="s">
         <v>12</v>
@@ -10201,10 +10204,10 @@
         <v>13</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D332" s="6" t="n">
-        <v>16196.0</v>
+        <v>25040.0</v>
       </c>
       <c r="E332" s="7" t="s">
         <v>12</v>
@@ -10230,10 +10233,10 @@
         <v>13</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D333" s="6" t="n">
-        <v>28904.0</v>
+        <v>16196.0</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>12</v>
@@ -10259,10 +10262,10 @@
         <v>13</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D334" s="6" t="n">
-        <v>7928.0</v>
+        <v>28904.0</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>12</v>
@@ -10288,10 +10291,10 @@
         <v>13</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D335" s="6" t="n">
-        <v>155203.0</v>
+        <v>7928.0</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>12</v>
@@ -10372,13 +10375,13 @@
         <v>62</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>21302.0</v>
+        <v>38261.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10404,10 +10407,10 @@
         <v>30</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>182371.0</v>
+        <v>256566.0</v>
       </c>
       <c r="E339" s="7" t="s">
         <v>12</v>
@@ -10433,10 +10436,10 @@
         <v>30</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D340" s="6" t="n">
-        <v>177268.0</v>
+        <v>6148.0</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>12</v>
@@ -10462,10 +10465,10 @@
         <v>30</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D341" s="6" t="n">
-        <v>15943.0</v>
+        <v>1449.0</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>12</v>
@@ -10488,19 +10491,19 @@
         <v>62</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>38261.0</v>
+        <v>488224.0</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F342" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F342" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G342" s="8" t="s">
         <v>62</v>
@@ -10520,10 +10523,10 @@
         <v>30</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D343" s="6" t="n">
-        <v>1449.0</v>
+        <v>15943.0</v>
       </c>
       <c r="E343" s="7" t="s">
         <v>12</v>
@@ -10549,10 +10552,10 @@
         <v>30</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D344" s="6" t="n">
-        <v>6148.0</v>
+        <v>177268.0</v>
       </c>
       <c r="E344" s="7" t="s">
         <v>12</v>
@@ -10578,10 +10581,10 @@
         <v>30</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D345" s="6" t="n">
-        <v>256566.0</v>
+        <v>182371.0</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>12</v>
@@ -10604,19 +10607,19 @@
         <v>62</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>488224.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F346" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F346" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G346" s="8" t="s">
         <v>62</v>
@@ -10665,10 +10668,10 @@
         <v>13</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D348" s="6" t="n">
-        <v>14390.0</v>
+        <v>69412.0</v>
       </c>
       <c r="E348" s="7" t="s">
         <v>12</v>
@@ -10694,10 +10697,10 @@
         <v>13</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D349" s="6" t="n">
-        <v>9380.0</v>
+        <v>7560.0</v>
       </c>
       <c r="E349" s="7" t="s">
         <v>12</v>
@@ -10723,10 +10726,10 @@
         <v>13</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D350" s="6" t="n">
-        <v>185.0</v>
+        <v>805776.0</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>12</v>
@@ -10752,10 +10755,10 @@
         <v>13</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D351" s="6" t="n">
-        <v>7510.0</v>
+        <v>14289.0</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>12</v>
@@ -10781,10 +10784,10 @@
         <v>13</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D352" s="6" t="n">
-        <v>7560.0</v>
+        <v>62866.0</v>
       </c>
       <c r="E352" s="7" t="s">
         <v>12</v>
@@ -10839,10 +10842,10 @@
         <v>13</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D354" s="6" t="n">
-        <v>62866.0</v>
+        <v>14390.0</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>12</v>
@@ -10868,10 +10871,10 @@
         <v>13</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D355" s="6" t="n">
-        <v>14289.0</v>
+        <v>7510.0</v>
       </c>
       <c r="E355" s="7" t="s">
         <v>12</v>
@@ -10897,10 +10900,10 @@
         <v>13</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D356" s="6" t="n">
-        <v>805776.0</v>
+        <v>185.0</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>12</v>
@@ -10926,10 +10929,10 @@
         <v>13</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D357" s="6" t="n">
-        <v>69412.0</v>
+        <v>9380.0</v>
       </c>
       <c r="E357" s="7" t="s">
         <v>12</v>
@@ -10984,10 +10987,10 @@
         <v>10</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>837.0</v>
+        <v>103343.0</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>12</v>
@@ -11187,10 +11190,10 @@
         <v>10</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D366" s="6" t="n">
-        <v>103343.0</v>
+        <v>837.0</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>12</v>
@@ -11361,16 +11364,16 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>3681.0</v>
+        <v>404269.0</v>
       </c>
       <c r="E372" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F372" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F372" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G372" s="8" t="s">
         <v>64</v>
@@ -11390,16 +11393,16 @@
         <v>13</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D373" s="6" t="n">
-        <v>404269.0</v>
+        <v>894.0</v>
       </c>
       <c r="E373" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F373" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G373" s="8" t="s">
         <v>64</v>
@@ -11419,10 +11422,10 @@
         <v>13</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D374" s="6" t="n">
-        <v>894.0</v>
+        <v>815.0</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>12</v>
@@ -11448,10 +11451,10 @@
         <v>13</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D375" s="6" t="n">
-        <v>815.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E375" s="7" t="s">
         <v>12</v>
@@ -11477,10 +11480,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>91385.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11677,13 +11680,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>8817.0</v>
+        <v>3572.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11706,13 +11709,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>3572.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11738,16 +11741,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D385" s="6" t="n">
-        <v>252681.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E385" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F385" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F385" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G385" s="8" t="s">
         <v>64</v>
@@ -11764,13 +11767,13 @@
         <v>64</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D386" s="6" t="n">
-        <v>12024.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E386" s="7" t="s">
         <v>12</v>
@@ -11793,13 +11796,13 @@
         <v>64</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D387" s="6" t="n">
-        <v>42128.0</v>
+        <v>7160.0</v>
       </c>
       <c r="E387" s="7" t="s">
         <v>12</v>
@@ -11822,13 +11825,13 @@
         <v>64</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D388" s="6" t="n">
-        <v>13204.0</v>
+        <v>306171.0</v>
       </c>
       <c r="E388" s="7" t="s">
         <v>12</v>
@@ -11851,13 +11854,13 @@
         <v>64</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D389" s="6" t="n">
-        <v>7380.0</v>
+        <v>18087.0</v>
       </c>
       <c r="E389" s="7" t="s">
         <v>12</v>
@@ -11883,10 +11886,10 @@
         <v>30</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>69259.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E390" s="7" t="s">
         <v>12</v>
@@ -11909,13 +11912,13 @@
         <v>64</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D391" s="6" t="n">
-        <v>14304.0</v>
+        <v>7380.0</v>
       </c>
       <c r="E391" s="7" t="s">
         <v>12</v>
@@ -11938,13 +11941,13 @@
         <v>64</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D392" s="6" t="n">
-        <v>18087.0</v>
+        <v>42128.0</v>
       </c>
       <c r="E392" s="7" t="s">
         <v>12</v>
@@ -11967,13 +11970,13 @@
         <v>64</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D393" s="6" t="n">
-        <v>306171.0</v>
+        <v>12024.0</v>
       </c>
       <c r="E393" s="7" t="s">
         <v>12</v>
@@ -11996,19 +11999,19 @@
         <v>64</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D394" s="6" t="n">
-        <v>7160.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E394" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F394" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F394" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G394" s="8" t="s">
         <v>64</v>
@@ -12028,10 +12031,10 @@
         <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>25352.0</v>
+        <v>13204.0</v>
       </c>
       <c r="E395" s="7" t="s">
         <v>12</v>
@@ -12057,16 +12060,16 @@
         <v>13</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D396" s="6" t="n">
-        <v>5080.0</v>
+        <v>378735.0</v>
       </c>
       <c r="E396" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F396" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F396" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G396" s="8" t="s">
         <v>65</v>
@@ -12086,16 +12089,16 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D397" s="6" t="n">
-        <v>65752.0</v>
+        <v>5282.0</v>
       </c>
       <c r="E397" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F397" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F397" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G397" s="8" t="s">
         <v>65</v>
@@ -12115,10 +12118,10 @@
         <v>13</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D398" s="6" t="n">
-        <v>5282.0</v>
+        <v>5080.0</v>
       </c>
       <c r="E398" s="7" t="s">
         <v>12</v>
@@ -12144,10 +12147,10 @@
         <v>13</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D399" s="6" t="n">
-        <v>2360.0</v>
+        <v>629.0</v>
       </c>
       <c r="E399" s="7" t="s">
         <v>12</v>
@@ -12173,10 +12176,10 @@
         <v>13</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D400" s="6" t="n">
-        <v>629.0</v>
+        <v>5697.0</v>
       </c>
       <c r="E400" s="7" t="s">
         <v>12</v>
@@ -12202,16 +12205,16 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>48.0</v>
+        <v>728271.0</v>
       </c>
       <c r="E401" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F401" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F401" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>65</v>
@@ -12231,16 +12234,16 @@
         <v>13</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D402" s="6" t="n">
-        <v>378735.0</v>
+        <v>133369.0</v>
       </c>
       <c r="E402" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F402" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F402" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G402" s="8" t="s">
         <v>65</v>
@@ -12260,10 +12263,10 @@
         <v>13</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D403" s="6" t="n">
-        <v>133369.0</v>
+        <v>621.0</v>
       </c>
       <c r="E403" s="7" t="s">
         <v>12</v>
@@ -12289,10 +12292,10 @@
         <v>13</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D404" s="6" t="n">
-        <v>621.0</v>
+        <v>6582.0</v>
       </c>
       <c r="E404" s="7" t="s">
         <v>12</v>
@@ -12318,16 +12321,16 @@
         <v>13</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D405" s="6" t="n">
-        <v>728271.0</v>
+        <v>48.0</v>
       </c>
       <c r="E405" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F405" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F405" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G405" s="8" t="s">
         <v>65</v>
@@ -12347,16 +12350,16 @@
         <v>13</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D406" s="6" t="n">
-        <v>6582.0</v>
+        <v>9750.0</v>
       </c>
       <c r="E406" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F406" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F406" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G406" s="8" t="s">
         <v>65</v>
@@ -12376,16 +12379,16 @@
         <v>13</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D407" s="6" t="n">
-        <v>9750.0</v>
+        <v>2360.0</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F407" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G407" s="8" t="s">
         <v>65</v>
@@ -12405,16 +12408,16 @@
         <v>13</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>5697.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E408" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F408" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F408" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G408" s="8" t="s">
         <v>65</v>
@@ -12431,13 +12434,13 @@
         <v>65</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D409" s="6" t="n">
-        <v>73210.0</v>
+        <v>35159.0</v>
       </c>
       <c r="E409" s="7" t="s">
         <v>12</v>
@@ -12460,13 +12463,13 @@
         <v>65</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D410" s="6" t="n">
-        <v>35159.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E410" s="7" t="s">
         <v>12</v>
@@ -12518,13 +12521,13 @@
         <v>65</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D412" s="6" t="n">
-        <v>160813.0</v>
+        <v>39117.0</v>
       </c>
       <c r="E412" s="7" t="s">
         <v>12</v>
@@ -12547,19 +12550,19 @@
         <v>65</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>285268.0</v>
+        <v>594911.0</v>
       </c>
       <c r="E413" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F413" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G413" s="8" t="s">
         <v>65</v>
@@ -12576,13 +12579,13 @@
         <v>65</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D414" s="6" t="n">
-        <v>217102.0</v>
+        <v>7149.0</v>
       </c>
       <c r="E414" s="7" t="s">
         <v>12</v>
@@ -12605,13 +12608,13 @@
         <v>65</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>60.0</v>
+        <v>126986.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12637,10 +12640,10 @@
         <v>30</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D416" s="6" t="n">
-        <v>318.0</v>
+        <v>548.0</v>
       </c>
       <c r="E416" s="7" t="s">
         <v>12</v>
@@ -12666,10 +12669,10 @@
         <v>30</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D417" s="6" t="n">
-        <v>548.0</v>
+        <v>318.0</v>
       </c>
       <c r="E417" s="7" t="s">
         <v>12</v>
@@ -12692,13 +12695,13 @@
         <v>65</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D418" s="6" t="n">
-        <v>126986.0</v>
+        <v>60.0</v>
       </c>
       <c r="E418" s="7" t="s">
         <v>12</v>
@@ -12721,13 +12724,13 @@
         <v>65</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D419" s="6" t="n">
-        <v>7149.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E419" s="7" t="s">
         <v>12</v>
@@ -12750,19 +12753,19 @@
         <v>65</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D420" s="6" t="n">
-        <v>594911.0</v>
+        <v>285268.0</v>
       </c>
       <c r="E420" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F420" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G420" s="8" t="s">
         <v>65</v>
@@ -12779,13 +12782,13 @@
         <v>65</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>39117.0</v>
+        <v>73210.0</v>
       </c>
       <c r="E421" s="7" t="s">
         <v>12</v>
@@ -12811,10 +12814,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>1359.0</v>
+        <v>8420.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12840,10 +12843,10 @@
         <v>13</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D423" s="6" t="n">
-        <v>44956.0</v>
+        <v>35061.0</v>
       </c>
       <c r="E423" s="7" t="s">
         <v>12</v>
@@ -12869,10 +12872,10 @@
         <v>13</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D424" s="6" t="n">
-        <v>8420.0</v>
+        <v>58027.0</v>
       </c>
       <c r="E424" s="7" t="s">
         <v>12</v>
@@ -12898,10 +12901,10 @@
         <v>13</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D425" s="6" t="n">
-        <v>210.0</v>
+        <v>784.0</v>
       </c>
       <c r="E425" s="7" t="s">
         <v>12</v>
@@ -12927,10 +12930,10 @@
         <v>13</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D426" s="6" t="n">
-        <v>784.0</v>
+        <v>210.0</v>
       </c>
       <c r="E426" s="7" t="s">
         <v>12</v>
@@ -12985,10 +12988,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>8146.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13014,10 +13017,10 @@
         <v>13</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D429" s="6" t="n">
-        <v>260811.0</v>
+        <v>8146.0</v>
       </c>
       <c r="E429" s="7" t="s">
         <v>12</v>
@@ -13043,10 +13046,10 @@
         <v>13</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D430" s="6" t="n">
-        <v>70064.0</v>
+        <v>261758.0</v>
       </c>
       <c r="E430" s="7" t="s">
         <v>12</v>
@@ -13072,10 +13075,10 @@
         <v>13</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>4241.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E431" s="7" t="s">
         <v>12</v>
@@ -13101,16 +13104,16 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>509687.0</v>
+        <v>4241.0</v>
       </c>
       <c r="E432" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F432" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F432" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G432" s="8" t="s">
         <v>66</v>
@@ -13130,16 +13133,16 @@
         <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>35061.0</v>
+        <v>510218.0</v>
       </c>
       <c r="E433" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F433" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F433" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G433" s="8" t="s">
         <v>66</v>
@@ -13188,10 +13191,10 @@
         <v>13</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>57903.0</v>
+        <v>44956.0</v>
       </c>
       <c r="E435" s="7" t="s">
         <v>12</v>
@@ -13272,13 +13275,13 @@
         <v>66</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>2197.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13301,13 +13304,13 @@
         <v>66</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>108610.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E439" s="7" t="s">
         <v>12</v>
@@ -13333,16 +13336,16 @@
         <v>10</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>3803.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E440" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F440" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F440" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G440" s="8" t="s">
         <v>66</v>
@@ -13365,7 +13368,7 @@
         <v>49</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>184302.0</v>
+        <v>209762.0</v>
       </c>
       <c r="E441" s="7" t="s">
         <v>12</v>
@@ -13420,16 +13423,16 @@
         <v>10</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>210036.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E443" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F443" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F443" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G443" s="8" t="s">
         <v>66</v>
@@ -13478,10 +13481,10 @@
         <v>30</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>31883.0</v>
+        <v>105.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13507,10 +13510,10 @@
         <v>30</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D446" s="6" t="n">
-        <v>105.0</v>
+        <v>1412.0</v>
       </c>
       <c r="E446" s="7" t="s">
         <v>12</v>
@@ -13536,16 +13539,16 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>1412.0</v>
+        <v>94352.0</v>
       </c>
       <c r="E447" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F447" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F447" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G447" s="8" t="s">
         <v>66</v>
@@ -13565,16 +13568,16 @@
         <v>30</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>94352.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E448" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F448" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F448" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G448" s="8" t="s">
         <v>66</v>
@@ -13594,10 +13597,10 @@
         <v>30</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D449" s="6" t="n">
-        <v>1503.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E449" s="7" t="s">
         <v>12</v>
@@ -13623,10 +13626,10 @@
         <v>30</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D450" s="6" t="n">
-        <v>398292.0</v>
+        <v>31883.0</v>
       </c>
       <c r="E450" s="7" t="s">
         <v>12</v>
@@ -13652,10 +13655,10 @@
         <v>13</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D451" s="6" t="n">
-        <v>16955.0</v>
+        <v>4957.0</v>
       </c>
       <c r="E451" s="7" t="s">
         <v>12</v>
@@ -13681,16 +13684,16 @@
         <v>13</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D452" s="6" t="n">
-        <v>172657.0</v>
+        <v>77855.0</v>
       </c>
       <c r="E452" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F452" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F452" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G452" s="8" t="s">
         <v>67</v>
@@ -13710,10 +13713,10 @@
         <v>13</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D453" s="6" t="n">
-        <v>15909.0</v>
+        <v>2727.0</v>
       </c>
       <c r="E453" s="7" t="s">
         <v>12</v>
@@ -13739,16 +13742,16 @@
         <v>13</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D454" s="6" t="n">
-        <v>176527.0</v>
+        <v>1522.0</v>
       </c>
       <c r="E454" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F454" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F454" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G454" s="8" t="s">
         <v>67</v>
@@ -13768,10 +13771,10 @@
         <v>13</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D455" s="6" t="n">
-        <v>1963.0</v>
+        <v>936.0</v>
       </c>
       <c r="E455" s="7" t="s">
         <v>12</v>
@@ -13797,10 +13800,10 @@
         <v>13</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D456" s="6" t="n">
-        <v>818.0</v>
+        <v>175.0</v>
       </c>
       <c r="E456" s="7" t="s">
         <v>12</v>
@@ -13826,16 +13829,16 @@
         <v>13</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D457" s="6" t="n">
-        <v>1522.0</v>
+        <v>354423.0</v>
       </c>
       <c r="E457" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F457" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F457" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G457" s="8" t="s">
         <v>67</v>
@@ -13855,10 +13858,10 @@
         <v>13</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D458" s="6" t="n">
-        <v>27369.0</v>
+        <v>57229.0</v>
       </c>
       <c r="E458" s="7" t="s">
         <v>12</v>
@@ -13884,10 +13887,10 @@
         <v>13</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D459" s="6" t="n">
-        <v>26945.0</v>
+        <v>792.0</v>
       </c>
       <c r="E459" s="7" t="s">
         <v>12</v>
@@ -13910,13 +13913,13 @@
         <v>67</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D460" s="6" t="n">
-        <v>57082.0</v>
+        <v>419398.0</v>
       </c>
       <c r="E460" s="7" t="s">
         <v>12</v>
@@ -13942,10 +13945,10 @@
         <v>13</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D461" s="6" t="n">
-        <v>2975.0</v>
+        <v>872.0</v>
       </c>
       <c r="E461" s="7" t="s">
         <v>12</v>
@@ -13971,10 +13974,10 @@
         <v>13</v>
       </c>
       <c r="C462" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D462" s="6" t="n">
-        <v>941.0</v>
+        <v>106263.0</v>
       </c>
       <c r="E462" s="7" t="s">
         <v>12</v>
@@ -13997,13 +14000,13 @@
         <v>67</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D463" s="6" t="n">
-        <v>1794.0</v>
+        <v>47097.0</v>
       </c>
       <c r="E463" s="7" t="s">
         <v>12</v>
@@ -14026,13 +14029,13 @@
         <v>67</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D464" s="6" t="n">
-        <v>58405.0</v>
+        <v>13052.0</v>
       </c>
       <c r="E464" s="7" t="s">
         <v>12</v>
@@ -14058,10 +14061,10 @@
         <v>30</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D465" s="6" t="n">
-        <v>56860.0</v>
+        <v>3363.0</v>
       </c>
       <c r="E465" s="7" t="s">
         <v>12</v>
@@ -14084,13 +14087,13 @@
         <v>67</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D466" s="6" t="n">
-        <v>24813.0</v>
+        <v>64678.0</v>
       </c>
       <c r="E466" s="7" t="s">
         <v>12</v>
@@ -14116,10 +14119,10 @@
         <v>10</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>22.0</v>
+        <v>116362.0</v>
       </c>
       <c r="E467" s="7" t="s">
         <v>12</v>
@@ -14148,7 +14151,7 @@
         <v>32</v>
       </c>
       <c r="D468" s="6" t="n">
-        <v>31900.0</v>
+        <v>243628.0</v>
       </c>
       <c r="E468" s="7" t="s">
         <v>12</v>
@@ -14174,10 +14177,10 @@
         <v>10</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D469" s="6" t="n">
-        <v>23056.0</v>
+        <v>122518.0</v>
       </c>
       <c r="E469" s="7" t="s">
         <v>12</v>
@@ -14200,13 +14203,13 @@
         <v>67</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D470" s="6" t="n">
-        <v>786.0</v>
+        <v>74709.0</v>
       </c>
       <c r="E470" s="7" t="s">
         <v>12</v>
@@ -14221,6 +14224,702 @@
         <v>67</v>
       </c>
       <c r="I470" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B471" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C471" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D471" s="6" t="n">
+        <v>3174.0</v>
+      </c>
+      <c r="E471" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F471" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G471" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H471" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I471" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B472" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D472" s="6" t="n">
+        <v>646.0</v>
+      </c>
+      <c r="E472" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F472" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G472" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H472" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I472" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B473" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D473" s="6" t="n">
+        <v>198654.0</v>
+      </c>
+      <c r="E473" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F473" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G473" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H473" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I473" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B474" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C474" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D474" s="6" t="n">
+        <v>8245.0</v>
+      </c>
+      <c r="E474" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F474" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G474" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H474" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I474" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B475" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C475" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D475" s="6" t="n">
+        <v>207867.0</v>
+      </c>
+      <c r="E475" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F475" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G475" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H475" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I475" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B476" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C476" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D476" s="6" t="n">
+        <v>6484.0</v>
+      </c>
+      <c r="E476" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F476" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G476" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H476" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I476" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B477" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C477" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D477" s="6" t="n">
+        <v>6691.0</v>
+      </c>
+      <c r="E477" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F477" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G477" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H477" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I477" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B478" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C478" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D478" s="6" t="n">
+        <v>16982.0</v>
+      </c>
+      <c r="E478" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F478" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G478" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H478" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I478" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B479" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C479" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D479" s="6" t="n">
+        <v>3967.0</v>
+      </c>
+      <c r="E479" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F479" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G479" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H479" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I479" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B480" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C480" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D480" s="6" t="n">
+        <v>34609.0</v>
+      </c>
+      <c r="E480" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F480" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G480" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H480" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I480" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B481" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C481" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D481" s="6" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="E481" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F481" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G481" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H481" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I481" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B482" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C482" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D482" s="6" t="n">
+        <v>362.0</v>
+      </c>
+      <c r="E482" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F482" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G482" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H482" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I482" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B483" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D483" s="6" t="n">
+        <v>5790.0</v>
+      </c>
+      <c r="E483" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F483" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G483" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H483" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I483" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B484" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C484" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D484" s="6" t="n">
+        <v>12965.0</v>
+      </c>
+      <c r="E484" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F484" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G484" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H484" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I484" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B485" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C485" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D485" s="6" t="n">
+        <v>87187.0</v>
+      </c>
+      <c r="E485" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F485" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G485" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H485" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I485" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B486" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C486" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D486" s="6" t="n">
+        <v>587.0</v>
+      </c>
+      <c r="E486" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F486" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G486" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H486" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I486" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B487" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C487" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D487" s="6" t="n">
+        <v>2254.0</v>
+      </c>
+      <c r="E487" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F487" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G487" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H487" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I487" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B488" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C488" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D488" s="6" t="n">
+        <v>28431.0</v>
+      </c>
+      <c r="E488" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F488" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G488" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H488" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I488" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B489" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C489" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D489" s="6" t="n">
+        <v>15590.0</v>
+      </c>
+      <c r="E489" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F489" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G489" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H489" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I489" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B490" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C490" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D490" s="6" t="n">
+        <v>18626.0</v>
+      </c>
+      <c r="E490" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F490" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G490" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H490" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I490" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B491" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C491" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D491" s="6" t="n">
+        <v>10065.0</v>
+      </c>
+      <c r="E491" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F491" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G491" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H491" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I491" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B492" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C492" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D492" s="6" t="n">
+        <v>58822.0</v>
+      </c>
+      <c r="E492" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F492" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G492" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H492" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I492" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B493" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C493" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D493" s="6" t="n">
+        <v>2516.0</v>
+      </c>
+      <c r="E493" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F493" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G493" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H493" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I493" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B494" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C494" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D494" s="6" t="n">
+        <v>156334.0</v>
+      </c>
+      <c r="E494" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F494" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G494" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H494" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I494" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3885" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="70">
   <si>
     <t>Ngày</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
   </si>
 </sst>
 </file>
@@ -582,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I494"/>
+  <dimension ref="A1:I524"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -3882,10 +3885,10 @@
         <v>13</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>290.0</v>
+        <v>120.0</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>12</v>
@@ -4143,10 +4146,10 @@
         <v>13</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>120.0</v>
+        <v>290.0</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>12</v>
@@ -4401,13 +4404,13 @@
         <v>54</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>7646.0</v>
+        <v>130258.0</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>12</v>
@@ -4430,13 +4433,13 @@
         <v>54</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>130258.0</v>
+        <v>7646.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>12</v>
@@ -6202,10 +6205,10 @@
         <v>13</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>2314.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E194" s="7" t="s">
         <v>12</v>
@@ -6347,10 +6350,10 @@
         <v>13</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>12137.0</v>
+        <v>2314.0</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>12</v>
@@ -6402,13 +6405,13 @@
         <v>57</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>264473.0</v>
+        <v>476600.0</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>16</v>
@@ -6521,16 +6524,16 @@
         <v>30</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>9109.0</v>
+        <v>264473.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F205" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>57</v>
@@ -6550,10 +6553,10 @@
         <v>30</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>210.0</v>
+        <v>9109.0</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>12</v>
@@ -6579,10 +6582,10 @@
         <v>30</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>28338.0</v>
+        <v>210.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6605,19 +6608,19 @@
         <v>57</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>476600.0</v>
+        <v>28338.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>57</v>
@@ -6666,10 +6669,10 @@
         <v>30</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>83141.0</v>
+        <v>49095.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6692,13 +6695,13 @@
         <v>57</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>43423.0</v>
+        <v>83141.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6724,10 +6727,10 @@
         <v>13</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>1573.0</v>
+        <v>43423.0</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>12</v>
@@ -6753,10 +6756,10 @@
         <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>28802.0</v>
+        <v>1573.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6779,13 +6782,13 @@
         <v>57</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>49095.0</v>
+        <v>28802.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6811,10 +6814,10 @@
         <v>13</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>28745.0</v>
+        <v>47108.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6840,10 +6843,10 @@
         <v>13</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>8204.0</v>
+        <v>13953.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
@@ -6869,10 +6872,10 @@
         <v>13</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>2938.0</v>
+        <v>8204.0</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>12</v>
@@ -6898,10 +6901,10 @@
         <v>13</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>21893.0</v>
+        <v>2938.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6927,10 +6930,10 @@
         <v>13</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>47108.0</v>
+        <v>21893.0</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>12</v>
@@ -6956,16 +6959,16 @@
         <v>13</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>8125.0</v>
+        <v>1087.0</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F220" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>58</v>
@@ -6985,10 +6988,10 @@
         <v>13</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>142958.0</v>
+        <v>28745.0</v>
       </c>
       <c r="E221" s="7" t="s">
         <v>12</v>
@@ -7014,16 +7017,16 @@
         <v>13</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>55407.0</v>
+        <v>142958.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F222" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>58</v>
@@ -7043,10 +7046,10 @@
         <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>570723.0</v>
+        <v>55407.0</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>16</v>
@@ -7072,16 +7075,16 @@
         <v>13</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>17602.0</v>
+        <v>8125.0</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F224" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F224" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>58</v>
@@ -7101,16 +7104,16 @@
         <v>13</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>1087.0</v>
+        <v>570723.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F225" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>58</v>
@@ -7130,10 +7133,10 @@
         <v>13</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>13953.0</v>
+        <v>17602.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7214,13 +7217,13 @@
         <v>58</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>8052.0</v>
+        <v>52019.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7243,19 +7246,19 @@
         <v>58</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>52019.0</v>
+        <v>65877.0</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F230" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F230" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>58</v>
@@ -7272,19 +7275,19 @@
         <v>58</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>74089.0</v>
+        <v>118765.0</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F231" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F231" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>58</v>
@@ -7304,10 +7307,10 @@
         <v>10</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>2847.0</v>
+        <v>74089.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>12</v>
@@ -7333,10 +7336,10 @@
         <v>10</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>586581.0</v>
+        <v>2847.0</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>12</v>
@@ -7362,16 +7365,16 @@
         <v>10</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>65877.0</v>
+        <v>586581.0</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F234" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>58</v>
@@ -7420,10 +7423,10 @@
         <v>10</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>3681.0</v>
+        <v>8052.0</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>12</v>
@@ -7446,13 +7449,13 @@
         <v>58</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>515691.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7478,10 +7481,10 @@
         <v>30</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>61111.0</v>
+        <v>515691.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7507,10 +7510,10 @@
         <v>30</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>77697.0</v>
+        <v>61111.0</v>
       </c>
       <c r="E239" s="7" t="s">
         <v>12</v>
@@ -7536,10 +7539,10 @@
         <v>30</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>7771.0</v>
+        <v>77697.0</v>
       </c>
       <c r="E240" s="7" t="s">
         <v>12</v>
@@ -7565,16 +7568,16 @@
         <v>30</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>118765.0</v>
+        <v>7771.0</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F241" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>58</v>
@@ -7594,10 +7597,10 @@
         <v>13</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D242" s="6" t="n">
-        <v>509.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E242" s="7" t="s">
         <v>12</v>
@@ -7739,16 +7742,16 @@
         <v>13</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>1210.0</v>
+        <v>371730.0</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F247" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F247" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>59</v>
@@ -7768,16 +7771,16 @@
         <v>13</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>371730.0</v>
+        <v>509.0</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F248" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>59</v>
@@ -7797,10 +7800,10 @@
         <v>13</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>5458.0</v>
+        <v>23722.0</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>12</v>
@@ -7826,10 +7829,10 @@
         <v>13</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>23722.0</v>
+        <v>279499.0</v>
       </c>
       <c r="E250" s="7" t="s">
         <v>12</v>
@@ -7855,10 +7858,10 @@
         <v>13</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>279499.0</v>
+        <v>33073.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>12</v>
@@ -7884,10 +7887,10 @@
         <v>13</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>33073.0</v>
+        <v>3296.0</v>
       </c>
       <c r="E252" s="7" t="s">
         <v>12</v>
@@ -7913,10 +7916,10 @@
         <v>13</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>3296.0</v>
+        <v>160.0</v>
       </c>
       <c r="E253" s="7" t="s">
         <v>12</v>
@@ -7942,10 +7945,10 @@
         <v>13</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>160.0</v>
+        <v>27632.0</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>12</v>
@@ -7971,10 +7974,10 @@
         <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>27632.0</v>
+        <v>1210.0</v>
       </c>
       <c r="E255" s="7" t="s">
         <v>12</v>
@@ -7997,13 +8000,13 @@
         <v>59</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D256" s="6" t="n">
-        <v>302914.0</v>
+        <v>17105.0</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>12</v>
@@ -8026,13 +8029,13 @@
         <v>59</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>17105.0</v>
+        <v>790.0</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>12</v>
@@ -8055,13 +8058,13 @@
         <v>59</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>790.0</v>
+        <v>27683.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8087,10 +8090,10 @@
         <v>10</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>3186.0</v>
+        <v>31570.0</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>12</v>
@@ -8116,10 +8119,10 @@
         <v>10</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>31570.0</v>
+        <v>566118.0</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>12</v>
@@ -8145,10 +8148,10 @@
         <v>10</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>566118.0</v>
+        <v>25241.0</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>12</v>
@@ -8174,10 +8177,10 @@
         <v>10</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>25241.0</v>
+        <v>32891.0</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>12</v>
@@ -8203,10 +8206,10 @@
         <v>10</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>32891.0</v>
+        <v>3186.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8232,10 +8235,10 @@
         <v>30</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>27683.0</v>
+        <v>302914.0</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>12</v>
@@ -8261,10 +8264,10 @@
         <v>30</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>10553.0</v>
+        <v>150.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8406,10 +8409,10 @@
         <v>30</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>150.0</v>
+        <v>10553.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8609,10 +8612,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>170.0</v>
+        <v>96105.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8696,10 +8699,10 @@
         <v>13</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>96105.0</v>
+        <v>170.0</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>12</v>
@@ -9305,10 +9308,10 @@
         <v>13</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>4517.0</v>
+        <v>10887.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9624,10 +9627,10 @@
         <v>13</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>10887.0</v>
+        <v>4517.0</v>
       </c>
       <c r="E312" s="7" t="s">
         <v>12</v>
@@ -9856,16 +9859,16 @@
         <v>10</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>25684.0</v>
+        <v>2152.0</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F320" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F320" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G320" s="8" t="s">
         <v>61</v>
@@ -9885,16 +9888,16 @@
         <v>10</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D321" s="6" t="n">
-        <v>2152.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F321" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F321" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G321" s="8" t="s">
         <v>61</v>
@@ -11480,10 +11483,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>3681.0</v>
+        <v>228939.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11509,10 +11512,10 @@
         <v>13</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D377" s="6" t="n">
-        <v>228939.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E377" s="7" t="s">
         <v>12</v>
@@ -11538,10 +11541,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>5337.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11567,10 +11570,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>3142.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11596,10 +11599,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>102275.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11625,10 +11628,10 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>96052.0</v>
+        <v>4119.0</v>
       </c>
       <c r="E381" s="7" t="s">
         <v>12</v>
@@ -11654,10 +11657,10 @@
         <v>13</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D382" s="6" t="n">
-        <v>4119.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E382" s="7" t="s">
         <v>12</v>
@@ -11680,13 +11683,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>3572.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11709,13 +11712,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>8817.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11738,13 +11741,13 @@
         <v>64</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D385" s="6" t="n">
-        <v>69259.0</v>
+        <v>3572.0</v>
       </c>
       <c r="E385" s="7" t="s">
         <v>12</v>
@@ -11886,16 +11889,16 @@
         <v>30</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>25352.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E390" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F390" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F390" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G390" s="8" t="s">
         <v>64</v>
@@ -11915,10 +11918,10 @@
         <v>30</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D391" s="6" t="n">
-        <v>7380.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E391" s="7" t="s">
         <v>12</v>
@@ -11944,10 +11947,10 @@
         <v>30</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D392" s="6" t="n">
-        <v>42128.0</v>
+        <v>13204.0</v>
       </c>
       <c r="E392" s="7" t="s">
         <v>12</v>
@@ -11973,10 +11976,10 @@
         <v>30</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D393" s="6" t="n">
-        <v>12024.0</v>
+        <v>42128.0</v>
       </c>
       <c r="E393" s="7" t="s">
         <v>12</v>
@@ -12002,16 +12005,16 @@
         <v>30</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D394" s="6" t="n">
-        <v>252681.0</v>
+        <v>12024.0</v>
       </c>
       <c r="E394" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F394" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F394" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G394" s="8" t="s">
         <v>64</v>
@@ -12031,10 +12034,10 @@
         <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>13204.0</v>
+        <v>7380.0</v>
       </c>
       <c r="E395" s="7" t="s">
         <v>12</v>
@@ -12350,10 +12353,10 @@
         <v>13</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D406" s="6" t="n">
-        <v>9750.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E406" s="7" t="s">
         <v>16</v>
@@ -12408,10 +12411,10 @@
         <v>13</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>65752.0</v>
+        <v>9750.0</v>
       </c>
       <c r="E408" s="7" t="s">
         <v>16</v>
@@ -12434,13 +12437,13 @@
         <v>65</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D409" s="6" t="n">
-        <v>35159.0</v>
+        <v>73210.0</v>
       </c>
       <c r="E409" s="7" t="s">
         <v>12</v>
@@ -12463,13 +12466,13 @@
         <v>65</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D410" s="6" t="n">
-        <v>160813.0</v>
+        <v>318.0</v>
       </c>
       <c r="E410" s="7" t="s">
         <v>12</v>
@@ -12492,19 +12495,19 @@
         <v>65</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D411" s="6" t="n">
-        <v>4067.0</v>
+        <v>285268.0</v>
       </c>
       <c r="E411" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F411" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F411" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G411" s="8" t="s">
         <v>65</v>
@@ -12521,13 +12524,13 @@
         <v>65</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D412" s="6" t="n">
-        <v>39117.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E412" s="7" t="s">
         <v>12</v>
@@ -12550,19 +12553,19 @@
         <v>65</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>594911.0</v>
+        <v>60.0</v>
       </c>
       <c r="E413" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F413" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F413" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G413" s="8" t="s">
         <v>65</v>
@@ -12582,10 +12585,10 @@
         <v>30</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D414" s="6" t="n">
-        <v>7149.0</v>
+        <v>35159.0</v>
       </c>
       <c r="E414" s="7" t="s">
         <v>12</v>
@@ -12608,13 +12611,13 @@
         <v>65</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>126986.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12669,10 +12672,10 @@
         <v>30</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D417" s="6" t="n">
-        <v>318.0</v>
+        <v>7149.0</v>
       </c>
       <c r="E417" s="7" t="s">
         <v>12</v>
@@ -12695,19 +12698,19 @@
         <v>65</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D418" s="6" t="n">
-        <v>60.0</v>
+        <v>594911.0</v>
       </c>
       <c r="E418" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F418" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F418" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G418" s="8" t="s">
         <v>65</v>
@@ -12724,13 +12727,13 @@
         <v>65</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D419" s="6" t="n">
-        <v>217102.0</v>
+        <v>39117.0</v>
       </c>
       <c r="E419" s="7" t="s">
         <v>12</v>
@@ -12753,19 +12756,19 @@
         <v>65</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D420" s="6" t="n">
-        <v>285268.0</v>
+        <v>4067.0</v>
       </c>
       <c r="E420" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F420" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F420" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G420" s="8" t="s">
         <v>65</v>
@@ -12782,13 +12785,13 @@
         <v>65</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>73210.0</v>
+        <v>126986.0</v>
       </c>
       <c r="E421" s="7" t="s">
         <v>12</v>
@@ -12814,10 +12817,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>8420.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12843,10 +12846,10 @@
         <v>13</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D423" s="6" t="n">
-        <v>35061.0</v>
+        <v>44956.0</v>
       </c>
       <c r="E423" s="7" t="s">
         <v>12</v>
@@ -12901,10 +12904,10 @@
         <v>13</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D425" s="6" t="n">
-        <v>784.0</v>
+        <v>8420.0</v>
       </c>
       <c r="E425" s="7" t="s">
         <v>12</v>
@@ -12959,10 +12962,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>5605.0</v>
+        <v>784.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -12988,10 +12991,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>1359.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13075,10 +13078,10 @@
         <v>13</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>70064.0</v>
+        <v>4241.0</v>
       </c>
       <c r="E431" s="7" t="s">
         <v>12</v>
@@ -13104,16 +13107,16 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>4241.0</v>
+        <v>510218.0</v>
       </c>
       <c r="E432" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F432" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F432" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G432" s="8" t="s">
         <v>66</v>
@@ -13133,16 +13136,16 @@
         <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>510218.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E433" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F433" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G433" s="8" t="s">
         <v>66</v>
@@ -13162,10 +13165,10 @@
         <v>13</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D434" s="6" t="n">
-        <v>1355.0</v>
+        <v>35061.0</v>
       </c>
       <c r="E434" s="7" t="s">
         <v>12</v>
@@ -13191,10 +13194,10 @@
         <v>13</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>44956.0</v>
+        <v>1355.0</v>
       </c>
       <c r="E435" s="7" t="s">
         <v>12</v>
@@ -13217,19 +13220,19 @@
         <v>66</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D436" s="6" t="n">
-        <v>4083.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E436" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F436" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F436" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G436" s="8" t="s">
         <v>66</v>
@@ -13246,13 +13249,13 @@
         <v>66</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D437" s="6" t="n">
-        <v>5730.0</v>
+        <v>4083.0</v>
       </c>
       <c r="E437" s="7" t="s">
         <v>12</v>
@@ -13278,10 +13281,10 @@
         <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>108610.0</v>
+        <v>9349.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13304,13 +13307,13 @@
         <v>66</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>2197.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E439" s="7" t="s">
         <v>12</v>
@@ -13333,19 +13336,19 @@
         <v>66</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>210756.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E440" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F440" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F440" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G440" s="8" t="s">
         <v>66</v>
@@ -13423,10 +13426,10 @@
         <v>10</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>3803.0</v>
+        <v>5730.0</v>
       </c>
       <c r="E443" s="7" t="s">
         <v>12</v>
@@ -13452,10 +13455,10 @@
         <v>10</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D444" s="6" t="n">
-        <v>9349.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E444" s="7" t="s">
         <v>12</v>
@@ -13481,10 +13484,10 @@
         <v>30</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>105.0</v>
+        <v>31883.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13510,10 +13513,10 @@
         <v>30</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D446" s="6" t="n">
-        <v>1412.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E446" s="7" t="s">
         <v>12</v>
@@ -13539,16 +13542,16 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>94352.0</v>
+        <v>105.0</v>
       </c>
       <c r="E447" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F447" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F447" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G447" s="8" t="s">
         <v>66</v>
@@ -13568,10 +13571,10 @@
         <v>30</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>1503.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E448" s="7" t="s">
         <v>12</v>
@@ -13597,16 +13600,16 @@
         <v>30</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D449" s="6" t="n">
-        <v>398394.0</v>
+        <v>94352.0</v>
       </c>
       <c r="E449" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F449" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F449" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G449" s="8" t="s">
         <v>66</v>
@@ -13626,10 +13629,10 @@
         <v>30</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D450" s="6" t="n">
-        <v>31883.0</v>
+        <v>1412.0</v>
       </c>
       <c r="E450" s="7" t="s">
         <v>12</v>
@@ -13655,10 +13658,10 @@
         <v>13</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D451" s="6" t="n">
-        <v>4957.0</v>
+        <v>47101.0</v>
       </c>
       <c r="E451" s="7" t="s">
         <v>12</v>
@@ -13684,16 +13687,16 @@
         <v>13</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D452" s="6" t="n">
-        <v>77855.0</v>
+        <v>872.0</v>
       </c>
       <c r="E452" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F452" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F452" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G452" s="8" t="s">
         <v>67</v>
@@ -13713,10 +13716,10 @@
         <v>13</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D453" s="6" t="n">
-        <v>2727.0</v>
+        <v>420532.0</v>
       </c>
       <c r="E453" s="7" t="s">
         <v>12</v>
@@ -13742,10 +13745,10 @@
         <v>13</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D454" s="6" t="n">
-        <v>1522.0</v>
+        <v>175.0</v>
       </c>
       <c r="E454" s="7" t="s">
         <v>12</v>
@@ -13771,10 +13774,10 @@
         <v>13</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D455" s="6" t="n">
-        <v>936.0</v>
+        <v>792.0</v>
       </c>
       <c r="E455" s="7" t="s">
         <v>12</v>
@@ -13800,10 +13803,10 @@
         <v>13</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D456" s="6" t="n">
-        <v>175.0</v>
+        <v>57845.0</v>
       </c>
       <c r="E456" s="7" t="s">
         <v>12</v>
@@ -13832,7 +13835,7 @@
         <v>24</v>
       </c>
       <c r="D457" s="6" t="n">
-        <v>354423.0</v>
+        <v>357258.0</v>
       </c>
       <c r="E457" s="7" t="s">
         <v>16</v>
@@ -13858,10 +13861,10 @@
         <v>13</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D458" s="6" t="n">
-        <v>57229.0</v>
+        <v>4957.0</v>
       </c>
       <c r="E458" s="7" t="s">
         <v>12</v>
@@ -13887,10 +13890,10 @@
         <v>13</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D459" s="6" t="n">
-        <v>792.0</v>
+        <v>936.0</v>
       </c>
       <c r="E459" s="7" t="s">
         <v>12</v>
@@ -13916,10 +13919,10 @@
         <v>13</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D460" s="6" t="n">
-        <v>419398.0</v>
+        <v>1522.0</v>
       </c>
       <c r="E460" s="7" t="s">
         <v>12</v>
@@ -13945,10 +13948,10 @@
         <v>13</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D461" s="6" t="n">
-        <v>872.0</v>
+        <v>2727.0</v>
       </c>
       <c r="E461" s="7" t="s">
         <v>12</v>
@@ -13974,16 +13977,16 @@
         <v>13</v>
       </c>
       <c r="C462" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D462" s="6" t="n">
-        <v>106263.0</v>
+        <v>78020.0</v>
       </c>
       <c r="E462" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F462" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F462" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G462" s="8" t="s">
         <v>67</v>
@@ -14003,10 +14006,10 @@
         <v>13</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D463" s="6" t="n">
-        <v>47097.0</v>
+        <v>106406.0</v>
       </c>
       <c r="E463" s="7" t="s">
         <v>12</v>
@@ -14029,13 +14032,13 @@
         <v>67</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D464" s="6" t="n">
-        <v>13052.0</v>
+        <v>3174.0</v>
       </c>
       <c r="E464" s="7" t="s">
         <v>12</v>
@@ -14058,13 +14061,13 @@
         <v>67</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D465" s="6" t="n">
-        <v>3363.0</v>
+        <v>13052.0</v>
       </c>
       <c r="E465" s="7" t="s">
         <v>12</v>
@@ -14087,13 +14090,13 @@
         <v>67</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D466" s="6" t="n">
-        <v>64678.0</v>
+        <v>3363.0</v>
       </c>
       <c r="E466" s="7" t="s">
         <v>12</v>
@@ -14116,13 +14119,13 @@
         <v>67</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>116362.0</v>
+        <v>64823.0</v>
       </c>
       <c r="E467" s="7" t="s">
         <v>12</v>
@@ -14151,7 +14154,7 @@
         <v>32</v>
       </c>
       <c r="D468" s="6" t="n">
-        <v>243628.0</v>
+        <v>245670.0</v>
       </c>
       <c r="E468" s="7" t="s">
         <v>12</v>
@@ -14180,7 +14183,7 @@
         <v>49</v>
       </c>
       <c r="D469" s="6" t="n">
-        <v>122518.0</v>
+        <v>122605.0</v>
       </c>
       <c r="E469" s="7" t="s">
         <v>12</v>
@@ -14235,10 +14238,10 @@
         <v>10</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D471" s="6" t="n">
-        <v>3174.0</v>
+        <v>116450.0</v>
       </c>
       <c r="E471" s="7" t="s">
         <v>12</v>
@@ -14293,10 +14296,10 @@
         <v>30</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D473" s="6" t="n">
-        <v>198654.0</v>
+        <v>8245.0</v>
       </c>
       <c r="E473" s="7" t="s">
         <v>12</v>
@@ -14322,10 +14325,10 @@
         <v>30</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D474" s="6" t="n">
-        <v>8245.0</v>
+        <v>207867.0</v>
       </c>
       <c r="E474" s="7" t="s">
         <v>12</v>
@@ -14351,10 +14354,10 @@
         <v>30</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D475" s="6" t="n">
-        <v>207867.0</v>
+        <v>6920.0</v>
       </c>
       <c r="E475" s="7" t="s">
         <v>12</v>
@@ -14377,13 +14380,13 @@
         <v>67</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D476" s="6" t="n">
-        <v>6484.0</v>
+        <v>6691.0</v>
       </c>
       <c r="E476" s="7" t="s">
         <v>12</v>
@@ -14406,13 +14409,13 @@
         <v>67</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D477" s="6" t="n">
-        <v>6691.0</v>
+        <v>199283.0</v>
       </c>
       <c r="E477" s="7" t="s">
         <v>12</v>
@@ -14438,10 +14441,10 @@
         <v>13</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D478" s="6" t="n">
-        <v>16982.0</v>
+        <v>4818.0</v>
       </c>
       <c r="E478" s="7" t="s">
         <v>12</v>
@@ -14467,10 +14470,10 @@
         <v>13</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D479" s="6" t="n">
-        <v>3967.0</v>
+        <v>692.0</v>
       </c>
       <c r="E479" s="7" t="s">
         <v>12</v>
@@ -14496,10 +14499,10 @@
         <v>13</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D480" s="6" t="n">
-        <v>34609.0</v>
+        <v>3849.0</v>
       </c>
       <c r="E480" s="7" t="s">
         <v>12</v>
@@ -14525,10 +14528,10 @@
         <v>13</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D481" s="6" t="n">
-        <v>117.0</v>
+        <v>1252.0</v>
       </c>
       <c r="E481" s="7" t="s">
         <v>12</v>
@@ -14554,10 +14557,10 @@
         <v>13</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D482" s="6" t="n">
-        <v>362.0</v>
+        <v>4053.0</v>
       </c>
       <c r="E482" s="7" t="s">
         <v>12</v>
@@ -14583,10 +14586,10 @@
         <v>13</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D483" s="6" t="n">
-        <v>5790.0</v>
+        <v>158694.0</v>
       </c>
       <c r="E483" s="7" t="s">
         <v>12</v>
@@ -14612,10 +14615,10 @@
         <v>13</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D484" s="6" t="n">
-        <v>12965.0</v>
+        <v>20456.0</v>
       </c>
       <c r="E484" s="7" t="s">
         <v>12</v>
@@ -14638,13 +14641,13 @@
         <v>68</v>
       </c>
       <c r="B485" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D485" s="6" t="n">
-        <v>87187.0</v>
+        <v>548820.0</v>
       </c>
       <c r="E485" s="7" t="s">
         <v>12</v>
@@ -14670,10 +14673,10 @@
         <v>13</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D486" s="6" t="n">
-        <v>587.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E486" s="7" t="s">
         <v>12</v>
@@ -14699,10 +14702,10 @@
         <v>13</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D487" s="6" t="n">
-        <v>2254.0</v>
+        <v>791.0</v>
       </c>
       <c r="E487" s="7" t="s">
         <v>12</v>
@@ -14725,19 +14728,19 @@
         <v>68</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C488" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D488" s="6" t="n">
-        <v>28431.0</v>
+        <v>96265.0</v>
       </c>
       <c r="E488" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F488" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F488" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G488" s="8" t="s">
         <v>68</v>
@@ -14754,19 +14757,19 @@
         <v>68</v>
       </c>
       <c r="B489" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D489" s="6" t="n">
-        <v>15590.0</v>
+        <v>108568.0</v>
       </c>
       <c r="E489" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F489" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F489" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G489" s="8" t="s">
         <v>68</v>
@@ -14783,13 +14786,13 @@
         <v>68</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D490" s="6" t="n">
-        <v>18626.0</v>
+        <v>8962.0</v>
       </c>
       <c r="E490" s="7" t="s">
         <v>12</v>
@@ -14812,13 +14815,13 @@
         <v>68</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D491" s="6" t="n">
-        <v>10065.0</v>
+        <v>69923.0</v>
       </c>
       <c r="E491" s="7" t="s">
         <v>12</v>
@@ -14844,10 +14847,10 @@
         <v>10</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D492" s="6" t="n">
-        <v>58822.0</v>
+        <v>15334.0</v>
       </c>
       <c r="E492" s="7" t="s">
         <v>12</v>
@@ -14870,13 +14873,13 @@
         <v>68</v>
       </c>
       <c r="B493" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="D493" s="6" t="n">
-        <v>2516.0</v>
+        <v>8296.0</v>
       </c>
       <c r="E493" s="7" t="s">
         <v>12</v>
@@ -14899,19 +14902,19 @@
         <v>68</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D494" s="6" t="n">
-        <v>156334.0</v>
+        <v>107584.0</v>
       </c>
       <c r="E494" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F494" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F494" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G494" s="8" t="s">
         <v>68</v>
@@ -14920,6 +14923,876 @@
         <v>68</v>
       </c>
       <c r="I494" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B495" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C495" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D495" s="6" t="n">
+        <v>170208.0</v>
+      </c>
+      <c r="E495" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F495" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G495" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H495" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I495" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B496" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C496" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D496" s="6" t="n">
+        <v>13403.0</v>
+      </c>
+      <c r="E496" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F496" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G496" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H496" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I496" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B497" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C497" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D497" s="6" t="n">
+        <v>296453.0</v>
+      </c>
+      <c r="E497" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F497" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G497" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H497" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I497" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B498" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C498" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D498" s="6" t="n">
+        <v>54343.0</v>
+      </c>
+      <c r="E498" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F498" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G498" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H498" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I498" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B499" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D499" s="6" t="n">
+        <v>4041.0</v>
+      </c>
+      <c r="E499" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F499" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G499" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H499" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I499" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B500" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C500" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D500" s="6" t="n">
+        <v>190026.0</v>
+      </c>
+      <c r="E500" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F500" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G500" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H500" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I500" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B501" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D501" s="6" t="n">
+        <v>205002.0</v>
+      </c>
+      <c r="E501" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F501" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G501" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H501" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I501" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B502" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C502" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D502" s="6" t="n">
+        <v>5306.0</v>
+      </c>
+      <c r="E502" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F502" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G502" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H502" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I502" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B503" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C503" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D503" s="6" t="n">
+        <v>14544.0</v>
+      </c>
+      <c r="E503" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F503" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G503" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H503" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I503" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B504" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C504" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D504" s="6" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="E504" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F504" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G504" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H504" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I504" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B505" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D505" s="6" t="n">
+        <v>1365.0</v>
+      </c>
+      <c r="E505" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F505" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G505" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H505" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I505" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B506" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C506" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D506" s="6" t="n">
+        <v>18163.0</v>
+      </c>
+      <c r="E506" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F506" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G506" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H506" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I506" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B507" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C507" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D507" s="6" t="n">
+        <v>124759.0</v>
+      </c>
+      <c r="E507" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F507" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G507" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H507" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I507" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B508" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C508" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D508" s="6" t="n">
+        <v>2772.0</v>
+      </c>
+      <c r="E508" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F508" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G508" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H508" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I508" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B509" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C509" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D509" s="6" t="n">
+        <v>248.0</v>
+      </c>
+      <c r="E509" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F509" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G509" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H509" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I509" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B510" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C510" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D510" s="6" t="n">
+        <v>27246.0</v>
+      </c>
+      <c r="E510" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F510" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G510" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H510" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I510" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B511" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C511" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D511" s="6" t="n">
+        <v>33546.0</v>
+      </c>
+      <c r="E511" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F511" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G511" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H511" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I511" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B512" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C512" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D512" s="6" t="n">
+        <v>38016.0</v>
+      </c>
+      <c r="E512" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F512" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G512" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H512" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I512" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B513" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C513" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D513" s="6" t="n">
+        <v>883.0</v>
+      </c>
+      <c r="E513" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F513" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G513" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H513" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I513" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B514" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C514" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D514" s="6" t="n">
+        <v>3126.0</v>
+      </c>
+      <c r="E514" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F514" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G514" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H514" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I514" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B515" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C515" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D515" s="6" t="n">
+        <v>5259.0</v>
+      </c>
+      <c r="E515" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F515" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G515" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H515" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I515" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B516" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D516" s="6" t="n">
+        <v>173227.0</v>
+      </c>
+      <c r="E516" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F516" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G516" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H516" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I516" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B517" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D517" s="6" t="n">
+        <v>24301.0</v>
+      </c>
+      <c r="E517" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F517" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G517" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H517" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I517" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B518" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C518" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D518" s="6" t="n">
+        <v>94013.0</v>
+      </c>
+      <c r="E518" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F518" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G518" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H518" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I518" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B519" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D519" s="6" t="n">
+        <v>1733.0</v>
+      </c>
+      <c r="E519" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F519" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G519" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H519" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I519" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B520" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D520" s="6" t="n">
+        <v>36553.0</v>
+      </c>
+      <c r="E520" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F520" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G520" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H520" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I520" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B521" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D521" s="6" t="n">
+        <v>114412.0</v>
+      </c>
+      <c r="E521" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F521" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G521" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H521" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I521" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B522" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D522" s="6" t="n">
+        <v>228012.0</v>
+      </c>
+      <c r="E522" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F522" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G522" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H522" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I522" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B523" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D523" s="6" t="n">
+        <v>62706.0</v>
+      </c>
+      <c r="E523" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F523" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G523" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H523" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I523" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B524" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D524" s="6" t="n">
+        <v>437845.0</v>
+      </c>
+      <c r="E524" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F524" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G524" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H524" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I524" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4350" uniqueCount="71">
   <si>
     <t>Ngày</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
   </si>
 </sst>
 </file>
@@ -585,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I524"/>
+  <dimension ref="A1:I553"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -2261,10 +2264,10 @@
         <v>13</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>80337.0</v>
+        <v>15476.0</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>12</v>
@@ -2290,10 +2293,10 @@
         <v>13</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1275.0</v>
+        <v>80337.0</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>12</v>
@@ -2319,10 +2322,10 @@
         <v>13</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>10496.0</v>
+        <v>1275.0</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>12</v>
@@ -2348,10 +2351,10 @@
         <v>13</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>83.0</v>
+        <v>10496.0</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>12</v>
@@ -2522,10 +2525,10 @@
         <v>13</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>14414.0</v>
+        <v>17497.0</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>12</v>
@@ -2551,10 +2554,10 @@
         <v>13</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>15476.0</v>
+        <v>14414.0</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>12</v>
@@ -2577,19 +2580,19 @@
         <v>51</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>85165.0</v>
+        <v>83.0</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>51</v>
@@ -2606,13 +2609,13 @@
         <v>51</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>17497.0</v>
+        <v>3752.0</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>12</v>
@@ -2635,19 +2638,19 @@
         <v>51</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>256233.0</v>
+        <v>85165.0</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G71" s="8" t="s">
         <v>51</v>
@@ -2664,13 +2667,13 @@
         <v>51</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3752.0</v>
+        <v>100851.0</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>12</v>
@@ -2696,10 +2699,10 @@
         <v>10</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>100851.0</v>
+        <v>373138.0</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>12</v>
@@ -2725,10 +2728,10 @@
         <v>10</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>373138.0</v>
+        <v>61630.0</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>12</v>
@@ -2754,10 +2757,10 @@
         <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>61630.0</v>
+        <v>8487.0</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>12</v>
@@ -2780,13 +2783,13 @@
         <v>51</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>8487.0</v>
+        <v>3300.0</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>12</v>
@@ -2954,13 +2957,13 @@
         <v>51</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>3300.0</v>
+        <v>256233.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
@@ -3131,10 +3134,10 @@
         <v>13</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>19856.0</v>
+        <v>20121.0</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -3247,10 +3250,10 @@
         <v>13</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>20121.0</v>
+        <v>569.0</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>12</v>
@@ -3276,10 +3279,10 @@
         <v>13</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>569.0</v>
+        <v>204042.0</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>12</v>
@@ -3305,10 +3308,10 @@
         <v>13</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>204042.0</v>
+        <v>4423.0</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>12</v>
@@ -3363,10 +3366,10 @@
         <v>13</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>122.0</v>
+        <v>19856.0</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>12</v>
@@ -3392,10 +3395,10 @@
         <v>13</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>4423.0</v>
+        <v>122.0</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>12</v>
@@ -3798,10 +3801,10 @@
         <v>13</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>25484.0</v>
+        <v>230.0</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>12</v>
@@ -3885,10 +3888,10 @@
         <v>13</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>120.0</v>
+        <v>290.0</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>12</v>
@@ -3914,10 +3917,10 @@
         <v>13</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>230.0</v>
+        <v>120.0</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>12</v>
@@ -3943,10 +3946,10 @@
         <v>13</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>343.0</v>
+        <v>1127.0</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>12</v>
@@ -3972,10 +3975,10 @@
         <v>13</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>480946.0</v>
+        <v>25484.0</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>12</v>
@@ -4001,10 +4004,10 @@
         <v>13</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>1127.0</v>
+        <v>480946.0</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>12</v>
@@ -4030,10 +4033,10 @@
         <v>13</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>511.0</v>
+        <v>343.0</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>12</v>
@@ -4059,16 +4062,16 @@
         <v>13</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>109034.0</v>
+        <v>511.0</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F120" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>54</v>
@@ -4088,16 +4091,16 @@
         <v>13</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>1325.0</v>
+        <v>109034.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>54</v>
@@ -4146,10 +4149,10 @@
         <v>13</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>290.0</v>
+        <v>26515.0</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>12</v>
@@ -4175,10 +4178,10 @@
         <v>13</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>26515.0</v>
+        <v>1325.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
@@ -4201,13 +4204,13 @@
         <v>54</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>287568.0</v>
+        <v>365.0</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>12</v>
@@ -4230,19 +4233,19 @@
         <v>54</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>619458.0</v>
+        <v>12.0</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F126" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G126" s="8" t="s">
         <v>54</v>
@@ -4262,10 +4265,10 @@
         <v>10</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>3016.0</v>
+        <v>7646.0</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>12</v>
@@ -4291,16 +4294,16 @@
         <v>10</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>119.0</v>
+        <v>619458.0</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G128" s="8" t="s">
         <v>54</v>
@@ -4320,10 +4323,10 @@
         <v>10</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>365.0</v>
+        <v>3016.0</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>12</v>
@@ -4346,13 +4349,13 @@
         <v>54</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>12.0</v>
+        <v>119.0</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>12</v>
@@ -4378,10 +4381,10 @@
         <v>30</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>33308.0</v>
+        <v>287568.0</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>12</v>
@@ -4407,10 +4410,10 @@
         <v>30</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>130258.0</v>
+        <v>33308.0</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>12</v>
@@ -4433,13 +4436,13 @@
         <v>54</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>7646.0</v>
+        <v>22735.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>12</v>
@@ -4465,10 +4468,10 @@
         <v>30</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>939.0</v>
+        <v>130258.0</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>12</v>
@@ -4494,10 +4497,10 @@
         <v>30</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>5182.0</v>
+        <v>939.0</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>12</v>
@@ -4523,10 +4526,10 @@
         <v>30</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>22735.0</v>
+        <v>5182.0</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>12</v>
@@ -4552,10 +4555,10 @@
         <v>13</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>43267.0</v>
+        <v>480065.0</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>12</v>
@@ -4581,10 +4584,10 @@
         <v>13</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>9757.0</v>
+        <v>2761.0</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>12</v>
@@ -4610,10 +4613,10 @@
         <v>13</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>2761.0</v>
+        <v>7072.0</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>12</v>
@@ -4639,10 +4642,10 @@
         <v>13</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>7072.0</v>
+        <v>9789.0</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
@@ -4668,10 +4671,10 @@
         <v>13</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>9789.0</v>
+        <v>43267.0</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>12</v>
@@ -4697,10 +4700,10 @@
         <v>13</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>1882.0</v>
+        <v>38461.0</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>12</v>
@@ -4726,10 +4729,10 @@
         <v>13</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>480065.0</v>
+        <v>42366.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>12</v>
@@ -4755,10 +4758,10 @@
         <v>13</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>42366.0</v>
+        <v>832.0</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>12</v>
@@ -4784,10 +4787,10 @@
         <v>13</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>832.0</v>
+        <v>1882.0</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>12</v>
@@ -4813,16 +4816,16 @@
         <v>13</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>47872.0</v>
+        <v>25102.0</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F146" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G146" s="8" t="s">
         <v>55</v>
@@ -4842,16 +4845,16 @@
         <v>13</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>69.0</v>
+        <v>47872.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>55</v>
@@ -4871,10 +4874,10 @@
         <v>13</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>312933.0</v>
+        <v>69.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
@@ -4900,10 +4903,10 @@
         <v>13</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>38461.0</v>
+        <v>9757.0</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>12</v>
@@ -4926,13 +4929,13 @@
         <v>55</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>25102.0</v>
+        <v>13050.0</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>12</v>
@@ -4958,10 +4961,10 @@
         <v>13</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>325679.0</v>
+        <v>312933.0</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>12</v>
@@ -4984,13 +4987,13 @@
         <v>55</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>28884.0</v>
+        <v>1746.0</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>12</v>
@@ -5013,13 +5016,13 @@
         <v>55</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>576515.0</v>
+        <v>325679.0</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>12</v>
@@ -5042,13 +5045,13 @@
         <v>55</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>21698.0</v>
+        <v>576515.0</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>12</v>
@@ -5074,10 +5077,10 @@
         <v>10</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>1746.0</v>
+        <v>328.0</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>12</v>
@@ -5100,19 +5103,19 @@
         <v>55</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>328.0</v>
+        <v>250155.0</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F156" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F156" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>55</v>
@@ -5132,16 +5135,16 @@
         <v>30</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>250155.0</v>
+        <v>28884.0</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F157" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G157" s="8" t="s">
         <v>55</v>
@@ -5190,10 +5193,10 @@
         <v>30</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>13050.0</v>
+        <v>37534.0</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>12</v>
@@ -5219,10 +5222,10 @@
         <v>30</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>152007.0</v>
+        <v>112939.0</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>12</v>
@@ -5248,10 +5251,10 @@
         <v>30</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>112939.0</v>
+        <v>36540.0</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>12</v>
@@ -5277,10 +5280,10 @@
         <v>30</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>36540.0</v>
+        <v>31845.0</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>12</v>
@@ -5303,13 +5306,13 @@
         <v>55</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>31845.0</v>
+        <v>21698.0</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>12</v>
@@ -5335,10 +5338,10 @@
         <v>30</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>37534.0</v>
+        <v>152007.0</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>12</v>
@@ -5364,10 +5367,10 @@
         <v>13</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>6378.0</v>
+        <v>26672.0</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>12</v>
@@ -5393,10 +5396,10 @@
         <v>13</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>35065.0</v>
+        <v>171781.0</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
@@ -5422,10 +5425,10 @@
         <v>13</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>171781.0</v>
+        <v>404959.0</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>12</v>
@@ -5451,10 +5454,10 @@
         <v>13</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>404959.0</v>
+        <v>6378.0</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>12</v>
@@ -5480,16 +5483,16 @@
         <v>13</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>1334.0</v>
+        <v>401598.0</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F169" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F169" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>56</v>
@@ -5509,10 +5512,10 @@
         <v>13</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>26672.0</v>
+        <v>44678.0</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>12</v>
@@ -5538,10 +5541,10 @@
         <v>13</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>44678.0</v>
+        <v>621.0</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>12</v>
@@ -5567,10 +5570,10 @@
         <v>13</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>621.0</v>
+        <v>1334.0</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>12</v>
@@ -5596,16 +5599,16 @@
         <v>13</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>401598.0</v>
+        <v>23158.0</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F173" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G173" s="8" t="s">
         <v>56</v>
@@ -5625,10 +5628,10 @@
         <v>13</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>23158.0</v>
+        <v>10115.0</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>12</v>
@@ -5654,10 +5657,10 @@
         <v>13</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>10115.0</v>
+        <v>35065.0</v>
       </c>
       <c r="E175" s="7" t="s">
         <v>12</v>
@@ -5741,10 +5744,10 @@
         <v>10</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>1182.0</v>
+        <v>2647.0</v>
       </c>
       <c r="E178" s="7" t="s">
         <v>12</v>
@@ -5767,19 +5770,19 @@
         <v>56</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>275877.0</v>
+        <v>5782.0</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F179" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G179" s="8" t="s">
         <v>56</v>
@@ -5799,16 +5802,16 @@
         <v>10</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>24571.0</v>
+        <v>399954.0</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F180" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F180" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G180" s="8" t="s">
         <v>56</v>
@@ -5828,10 +5831,10 @@
         <v>10</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>5782.0</v>
+        <v>6519.0</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>12</v>
@@ -5857,16 +5860,16 @@
         <v>10</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>399954.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F182" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G182" s="8" t="s">
         <v>56</v>
@@ -5886,10 +5889,10 @@
         <v>10</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>6519.0</v>
+        <v>24571.0</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>12</v>
@@ -5915,10 +5918,10 @@
         <v>10</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>2647.0</v>
+        <v>2290.0</v>
       </c>
       <c r="E184" s="7" t="s">
         <v>12</v>
@@ -5941,13 +5944,13 @@
         <v>56</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>2290.0</v>
+        <v>11551.0</v>
       </c>
       <c r="E185" s="7" t="s">
         <v>12</v>
@@ -5973,16 +5976,16 @@
         <v>30</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>331374.0</v>
+        <v>8022.0</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F186" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G186" s="8" t="s">
         <v>56</v>
@@ -6002,16 +6005,16 @@
         <v>30</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>11551.0</v>
+        <v>275877.0</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F187" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F187" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G187" s="8" t="s">
         <v>56</v>
@@ -6031,16 +6034,16 @@
         <v>30</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>8022.0</v>
+        <v>331374.0</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F188" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F188" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G188" s="8" t="s">
         <v>56</v>
@@ -6205,10 +6208,10 @@
         <v>13</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>12137.0</v>
+        <v>18488.0</v>
       </c>
       <c r="E194" s="7" t="s">
         <v>12</v>
@@ -6292,10 +6295,10 @@
         <v>13</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>18488.0</v>
+        <v>55.0</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>12</v>
@@ -6321,10 +6324,10 @@
         <v>13</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>55.0</v>
+        <v>2314.0</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>12</v>
@@ -6350,10 +6353,10 @@
         <v>13</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>2314.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>12</v>
@@ -6814,10 +6817,10 @@
         <v>13</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>47108.0</v>
+        <v>28745.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6843,10 +6846,10 @@
         <v>13</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>13953.0</v>
+        <v>8204.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
@@ -6872,10 +6875,10 @@
         <v>13</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>8204.0</v>
+        <v>2938.0</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>12</v>
@@ -6901,10 +6904,10 @@
         <v>13</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>2938.0</v>
+        <v>21893.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6930,10 +6933,10 @@
         <v>13</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>21893.0</v>
+        <v>47108.0</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>12</v>
@@ -6988,10 +6991,10 @@
         <v>13</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>28745.0</v>
+        <v>142958.0</v>
       </c>
       <c r="E221" s="7" t="s">
         <v>12</v>
@@ -7017,16 +7020,16 @@
         <v>13</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>142958.0</v>
+        <v>55407.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F222" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F222" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>58</v>
@@ -7046,16 +7049,16 @@
         <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>55407.0</v>
+        <v>8125.0</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F223" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>58</v>
@@ -7075,16 +7078,16 @@
         <v>13</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>8125.0</v>
+        <v>400774.0</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F224" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>58</v>
@@ -7162,10 +7165,10 @@
         <v>13</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>400774.0</v>
+        <v>13953.0</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
@@ -7188,13 +7191,13 @@
         <v>58</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>196510.0</v>
+        <v>37213.0</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>12</v>
@@ -7220,10 +7223,10 @@
         <v>13</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>52019.0</v>
+        <v>196510.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7249,16 +7252,16 @@
         <v>10</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>65877.0</v>
+        <v>8052.0</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F230" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>58</v>
@@ -7275,19 +7278,19 @@
         <v>58</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>118765.0</v>
+        <v>52019.0</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F231" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>58</v>
@@ -7394,16 +7397,16 @@
         <v>10</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>37213.0</v>
+        <v>65877.0</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F235" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F235" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G235" s="8" t="s">
         <v>58</v>
@@ -7423,10 +7426,10 @@
         <v>10</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>8052.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>12</v>
@@ -7449,13 +7452,13 @@
         <v>58</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>3681.0</v>
+        <v>515691.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7481,10 +7484,10 @@
         <v>30</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>515691.0</v>
+        <v>61111.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7510,10 +7513,10 @@
         <v>30</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>61111.0</v>
+        <v>77697.0</v>
       </c>
       <c r="E239" s="7" t="s">
         <v>12</v>
@@ -7539,10 +7542,10 @@
         <v>30</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>77697.0</v>
+        <v>7771.0</v>
       </c>
       <c r="E240" s="7" t="s">
         <v>12</v>
@@ -7568,16 +7571,16 @@
         <v>30</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>7771.0</v>
+        <v>118765.0</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F241" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F241" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>58</v>
@@ -7597,10 +7600,10 @@
         <v>13</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D242" s="6" t="n">
-        <v>5458.0</v>
+        <v>1210.0</v>
       </c>
       <c r="E242" s="7" t="s">
         <v>12</v>
@@ -7974,10 +7977,10 @@
         <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>1210.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E255" s="7" t="s">
         <v>12</v>
@@ -8438,10 +8441,10 @@
         <v>13</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D271" s="6" t="n">
-        <v>40129.0</v>
+        <v>35463.0</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>12</v>
@@ -8612,10 +8615,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>96105.0</v>
+        <v>170.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8641,10 +8644,10 @@
         <v>13</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D278" s="6" t="n">
-        <v>115.0</v>
+        <v>40129.0</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>12</v>
@@ -8670,10 +8673,10 @@
         <v>13</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D279" s="6" t="n">
-        <v>3979.0</v>
+        <v>115.0</v>
       </c>
       <c r="E279" s="7" t="s">
         <v>12</v>
@@ -8699,10 +8702,10 @@
         <v>13</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>170.0</v>
+        <v>3979.0</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>12</v>
@@ -8728,10 +8731,10 @@
         <v>13</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>38472.0</v>
+        <v>96105.0</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>12</v>
@@ -8757,10 +8760,10 @@
         <v>13</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>2731.0</v>
+        <v>38472.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8786,10 +8789,10 @@
         <v>13</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>35463.0</v>
+        <v>2731.0</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>12</v>
@@ -8841,13 +8844,13 @@
         <v>60</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>20130.0</v>
+        <v>27356.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8899,19 +8902,19 @@
         <v>60</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D287" s="6" t="n">
-        <v>318547.0</v>
+        <v>1780.0</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F287" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F287" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G287" s="8" t="s">
         <v>60</v>
@@ -8928,19 +8931,19 @@
         <v>60</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>1308.0</v>
+        <v>168847.0</v>
       </c>
       <c r="E288" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F288" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F288" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G288" s="8" t="s">
         <v>60</v>
@@ -8960,16 +8963,16 @@
         <v>10</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>621367.0</v>
+        <v>1308.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F289" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>60</v>
@@ -8986,19 +8989,19 @@
         <v>60</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>168847.0</v>
+        <v>6706.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F290" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>60</v>
@@ -9076,16 +9079,16 @@
         <v>10</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>1780.0</v>
+        <v>621367.0</v>
       </c>
       <c r="E293" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F293" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F293" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G293" s="8" t="s">
         <v>60</v>
@@ -9102,19 +9105,19 @@
         <v>60</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>6706.0</v>
+        <v>318547.0</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F294" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F294" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G294" s="8" t="s">
         <v>60</v>
@@ -9134,16 +9137,16 @@
         <v>30</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>27356.0</v>
+        <v>260392.0</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F295" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F295" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G295" s="8" t="s">
         <v>60</v>
@@ -9163,16 +9166,16 @@
         <v>30</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D296" s="6" t="n">
-        <v>260392.0</v>
+        <v>21208.0</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F296" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F296" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G296" s="8" t="s">
         <v>60</v>
@@ -9192,10 +9195,10 @@
         <v>30</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D297" s="6" t="n">
-        <v>21208.0</v>
+        <v>87988.0</v>
       </c>
       <c r="E297" s="7" t="s">
         <v>12</v>
@@ -9221,16 +9224,16 @@
         <v>30</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>87988.0</v>
+        <v>18189.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F298" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F298" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>60</v>
@@ -9247,19 +9250,19 @@
         <v>60</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>18189.0</v>
+        <v>20130.0</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F299" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G299" s="8" t="s">
         <v>60</v>
@@ -9424,16 +9427,16 @@
         <v>13</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>414833.0</v>
+        <v>4517.0</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F305" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G305" s="8" t="s">
         <v>61</v>
@@ -9453,16 +9456,16 @@
         <v>13</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>49827.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F306" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F306" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G306" s="8" t="s">
         <v>61</v>
@@ -9482,10 +9485,10 @@
         <v>13</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>16117.0</v>
+        <v>49827.0</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>12</v>
@@ -9511,10 +9514,10 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>18161.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E308" s="7" t="s">
         <v>12</v>
@@ -9540,10 +9543,10 @@
         <v>13</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>5125.0</v>
+        <v>18161.0</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>12</v>
@@ -9566,13 +9569,13 @@
         <v>61</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>1798.0</v>
+        <v>5125.0</v>
       </c>
       <c r="E310" s="7" t="s">
         <v>12</v>
@@ -9595,13 +9598,13 @@
         <v>61</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>49079.0</v>
+        <v>1798.0</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>12</v>
@@ -9627,10 +9630,10 @@
         <v>13</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>4517.0</v>
+        <v>49079.0</v>
       </c>
       <c r="E312" s="7" t="s">
         <v>12</v>
@@ -9656,10 +9659,10 @@
         <v>30</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>3372.0</v>
+        <v>32300.0</v>
       </c>
       <c r="E313" s="7" t="s">
         <v>12</v>
@@ -9682,13 +9685,13 @@
         <v>61</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D314" s="6" t="n">
-        <v>3475.0</v>
+        <v>3372.0</v>
       </c>
       <c r="E314" s="7" t="s">
         <v>12</v>
@@ -9711,13 +9714,13 @@
         <v>61</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D315" s="6" t="n">
-        <v>191.0</v>
+        <v>2153.0</v>
       </c>
       <c r="E315" s="7" t="s">
         <v>12</v>
@@ -9743,16 +9746,16 @@
         <v>10</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>7578.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F316" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F316" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G316" s="8" t="s">
         <v>61</v>
@@ -9769,13 +9772,13 @@
         <v>61</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D317" s="6" t="n">
-        <v>19353.0</v>
+        <v>191.0</v>
       </c>
       <c r="E317" s="7" t="s">
         <v>12</v>
@@ -9801,16 +9804,16 @@
         <v>10</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D318" s="6" t="n">
-        <v>2153.0</v>
+        <v>560394.0</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F318" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F318" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G318" s="8" t="s">
         <v>61</v>
@@ -9830,16 +9833,16 @@
         <v>10</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D319" s="6" t="n">
-        <v>560394.0</v>
+        <v>19353.0</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F319" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G319" s="8" t="s">
         <v>61</v>
@@ -9859,10 +9862,10 @@
         <v>10</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>2152.0</v>
+        <v>7578.0</v>
       </c>
       <c r="E320" s="7" t="s">
         <v>12</v>
@@ -9888,16 +9891,16 @@
         <v>10</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D321" s="6" t="n">
-        <v>25684.0</v>
+        <v>3475.0</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F321" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G321" s="8" t="s">
         <v>61</v>
@@ -9914,13 +9917,13 @@
         <v>61</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>400544.0</v>
+        <v>2152.0</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>12</v>
@@ -9946,10 +9949,10 @@
         <v>30</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>17918.0</v>
+        <v>400544.0</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>12</v>
@@ -9975,10 +9978,10 @@
         <v>30</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>7822.0</v>
+        <v>17918.0</v>
       </c>
       <c r="E324" s="7" t="s">
         <v>12</v>
@@ -10004,10 +10007,10 @@
         <v>30</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D325" s="6" t="n">
-        <v>32300.0</v>
+        <v>7822.0</v>
       </c>
       <c r="E325" s="7" t="s">
         <v>12</v>
@@ -10033,16 +10036,16 @@
         <v>13</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>155203.0</v>
+        <v>240445.0</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F326" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F326" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G326" s="8" t="s">
         <v>62</v>
@@ -10062,16 +10065,16 @@
         <v>13</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D327" s="6" t="n">
-        <v>288195.0</v>
+        <v>1049.0</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F327" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G327" s="8" t="s">
         <v>62</v>
@@ -10091,10 +10094,10 @@
         <v>13</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D328" s="6" t="n">
-        <v>1049.0</v>
+        <v>373443.0</v>
       </c>
       <c r="E328" s="7" t="s">
         <v>12</v>
@@ -10120,16 +10123,16 @@
         <v>13</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D329" s="6" t="n">
-        <v>373443.0</v>
+        <v>177177.0</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F329" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F329" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>62</v>
@@ -10149,16 +10152,16 @@
         <v>13</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D330" s="6" t="n">
-        <v>177177.0</v>
+        <v>15369.0</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F330" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G330" s="8" t="s">
         <v>62</v>
@@ -10178,10 +10181,10 @@
         <v>13</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D331" s="6" t="n">
-        <v>15369.0</v>
+        <v>25040.0</v>
       </c>
       <c r="E331" s="7" t="s">
         <v>12</v>
@@ -10207,10 +10210,10 @@
         <v>13</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D332" s="6" t="n">
-        <v>25040.0</v>
+        <v>16196.0</v>
       </c>
       <c r="E332" s="7" t="s">
         <v>12</v>
@@ -10236,10 +10239,10 @@
         <v>13</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D333" s="6" t="n">
-        <v>16196.0</v>
+        <v>28904.0</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>12</v>
@@ -10265,10 +10268,10 @@
         <v>13</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D334" s="6" t="n">
-        <v>28904.0</v>
+        <v>7928.0</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>12</v>
@@ -10294,10 +10297,10 @@
         <v>13</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D335" s="6" t="n">
-        <v>7928.0</v>
+        <v>155203.0</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>12</v>
@@ -10323,16 +10326,16 @@
         <v>13</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>39009.0</v>
+        <v>288195.0</v>
       </c>
       <c r="E336" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F336" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F336" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G336" s="8" t="s">
         <v>62</v>
@@ -10352,16 +10355,16 @@
         <v>13</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D337" s="6" t="n">
-        <v>240445.0</v>
+        <v>39009.0</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F337" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F337" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G337" s="8" t="s">
         <v>62</v>
@@ -10381,10 +10384,10 @@
         <v>30</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>38261.0</v>
+        <v>1449.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10407,19 +10410,19 @@
         <v>62</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>256566.0</v>
+        <v>488224.0</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F339" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F339" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G339" s="8" t="s">
         <v>62</v>
@@ -10439,10 +10442,10 @@
         <v>30</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D340" s="6" t="n">
-        <v>6148.0</v>
+        <v>256566.0</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>12</v>
@@ -10468,10 +10471,10 @@
         <v>30</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D341" s="6" t="n">
-        <v>1449.0</v>
+        <v>6148.0</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>12</v>
@@ -10494,19 +10497,19 @@
         <v>62</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>488224.0</v>
+        <v>866.0</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F342" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G342" s="8" t="s">
         <v>62</v>
@@ -10526,10 +10529,10 @@
         <v>30</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D343" s="6" t="n">
-        <v>15943.0</v>
+        <v>38261.0</v>
       </c>
       <c r="E343" s="7" t="s">
         <v>12</v>
@@ -10555,10 +10558,10 @@
         <v>30</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D344" s="6" t="n">
-        <v>177268.0</v>
+        <v>15943.0</v>
       </c>
       <c r="E344" s="7" t="s">
         <v>12</v>
@@ -10584,10 +10587,10 @@
         <v>30</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D345" s="6" t="n">
-        <v>182371.0</v>
+        <v>177268.0</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>12</v>
@@ -10610,13 +10613,13 @@
         <v>62</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>21302.0</v>
+        <v>182371.0</v>
       </c>
       <c r="E346" s="7" t="s">
         <v>12</v>
@@ -10642,10 +10645,10 @@
         <v>13</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D347" s="6" t="n">
-        <v>866.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E347" s="7" t="s">
         <v>12</v>
@@ -10987,13 +10990,13 @@
         <v>63</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>103343.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>12</v>
@@ -11016,13 +11019,13 @@
         <v>63</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D360" s="6" t="n">
-        <v>15854.0</v>
+        <v>837.0</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>12</v>
@@ -11045,19 +11048,19 @@
         <v>63</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D361" s="6" t="n">
-        <v>1766.0</v>
+        <v>303397.0</v>
       </c>
       <c r="E361" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F361" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F361" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G361" s="8" t="s">
         <v>63</v>
@@ -11077,10 +11080,10 @@
         <v>30</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D362" s="6" t="n">
-        <v>42515.0</v>
+        <v>82520.0</v>
       </c>
       <c r="E362" s="7" t="s">
         <v>12</v>
@@ -11103,19 +11106,19 @@
         <v>63</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D363" s="6" t="n">
-        <v>419250.0</v>
+        <v>2331.0</v>
       </c>
       <c r="E363" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F363" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G363" s="8" t="s">
         <v>63</v>
@@ -11132,19 +11135,19 @@
         <v>63</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D364" s="6" t="n">
-        <v>96851.0</v>
+        <v>111759.0</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F364" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>63</v>
@@ -11164,10 +11167,10 @@
         <v>10</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D365" s="6" t="n">
-        <v>2365.0</v>
+        <v>5088.0</v>
       </c>
       <c r="E365" s="7" t="s">
         <v>12</v>
@@ -11193,10 +11196,10 @@
         <v>10</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D366" s="6" t="n">
-        <v>837.0</v>
+        <v>1766.0</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>12</v>
@@ -11222,10 +11225,10 @@
         <v>10</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D367" s="6" t="n">
-        <v>5088.0</v>
+        <v>2365.0</v>
       </c>
       <c r="E367" s="7" t="s">
         <v>12</v>
@@ -11248,19 +11251,19 @@
         <v>63</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D368" s="6" t="n">
-        <v>111759.0</v>
+        <v>96851.0</v>
       </c>
       <c r="E368" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F368" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F368" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G368" s="8" t="s">
         <v>63</v>
@@ -11277,19 +11280,19 @@
         <v>63</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D369" s="6" t="n">
-        <v>2331.0</v>
+        <v>419250.0</v>
       </c>
       <c r="E369" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F369" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F369" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G369" s="8" t="s">
         <v>63</v>
@@ -11309,10 +11312,10 @@
         <v>30</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D370" s="6" t="n">
-        <v>82520.0</v>
+        <v>42515.0</v>
       </c>
       <c r="E370" s="7" t="s">
         <v>12</v>
@@ -11335,19 +11338,19 @@
         <v>63</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D371" s="6" t="n">
-        <v>303397.0</v>
+        <v>103343.0</v>
       </c>
       <c r="E371" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F371" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G371" s="8" t="s">
         <v>63</v>
@@ -11367,16 +11370,16 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>404269.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E372" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F372" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F372" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G372" s="8" t="s">
         <v>64</v>
@@ -11396,10 +11399,10 @@
         <v>13</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D373" s="6" t="n">
-        <v>894.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E373" s="7" t="s">
         <v>12</v>
@@ -11425,10 +11428,10 @@
         <v>13</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D374" s="6" t="n">
-        <v>815.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>12</v>
@@ -11454,10 +11457,10 @@
         <v>13</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D375" s="6" t="n">
-        <v>91385.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E375" s="7" t="s">
         <v>12</v>
@@ -11483,10 +11486,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>228939.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11512,10 +11515,10 @@
         <v>13</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D377" s="6" t="n">
-        <v>8817.0</v>
+        <v>228939.0</v>
       </c>
       <c r="E377" s="7" t="s">
         <v>12</v>
@@ -11541,10 +11544,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>3142.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11570,10 +11573,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>102275.0</v>
+        <v>815.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11599,10 +11602,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>96052.0</v>
+        <v>894.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11628,16 +11631,16 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>4119.0</v>
+        <v>404269.0</v>
       </c>
       <c r="E381" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F381" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F381" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>64</v>
@@ -11657,10 +11660,10 @@
         <v>13</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D382" s="6" t="n">
-        <v>3681.0</v>
+        <v>4119.0</v>
       </c>
       <c r="E382" s="7" t="s">
         <v>12</v>
@@ -11683,13 +11686,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>5337.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11712,13 +11715,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>25352.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11741,13 +11744,13 @@
         <v>64</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D385" s="6" t="n">
-        <v>3572.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E385" s="7" t="s">
         <v>12</v>
@@ -11770,13 +11773,13 @@
         <v>64</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D386" s="6" t="n">
-        <v>14304.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E386" s="7" t="s">
         <v>12</v>
@@ -11886,19 +11889,19 @@
         <v>64</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>252681.0</v>
+        <v>3572.0</v>
       </c>
       <c r="E390" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F390" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F390" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G390" s="8" t="s">
         <v>64</v>
@@ -11918,10 +11921,10 @@
         <v>30</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D391" s="6" t="n">
-        <v>69259.0</v>
+        <v>7380.0</v>
       </c>
       <c r="E391" s="7" t="s">
         <v>12</v>
@@ -12034,16 +12037,16 @@
         <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>7380.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F395" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F395" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G395" s="8" t="s">
         <v>64</v>
@@ -12063,16 +12066,16 @@
         <v>13</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D396" s="6" t="n">
-        <v>378735.0</v>
+        <v>5697.0</v>
       </c>
       <c r="E396" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F396" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F396" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G396" s="8" t="s">
         <v>65</v>
@@ -12092,10 +12095,10 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D397" s="6" t="n">
-        <v>5282.0</v>
+        <v>2360.0</v>
       </c>
       <c r="E397" s="7" t="s">
         <v>12</v>
@@ -12121,10 +12124,10 @@
         <v>13</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D398" s="6" t="n">
-        <v>5080.0</v>
+        <v>5282.0</v>
       </c>
       <c r="E398" s="7" t="s">
         <v>12</v>
@@ -12150,10 +12153,10 @@
         <v>13</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D399" s="6" t="n">
-        <v>629.0</v>
+        <v>5080.0</v>
       </c>
       <c r="E399" s="7" t="s">
         <v>12</v>
@@ -12179,10 +12182,10 @@
         <v>13</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D400" s="6" t="n">
-        <v>5697.0</v>
+        <v>629.0</v>
       </c>
       <c r="E400" s="7" t="s">
         <v>12</v>
@@ -12208,16 +12211,16 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>728271.0</v>
+        <v>48.0</v>
       </c>
       <c r="E401" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F401" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F401" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>65</v>
@@ -12237,16 +12240,16 @@
         <v>13</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D402" s="6" t="n">
-        <v>133369.0</v>
+        <v>378735.0</v>
       </c>
       <c r="E402" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F402" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F402" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G402" s="8" t="s">
         <v>65</v>
@@ -12266,10 +12269,10 @@
         <v>13</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D403" s="6" t="n">
-        <v>621.0</v>
+        <v>133369.0</v>
       </c>
       <c r="E403" s="7" t="s">
         <v>12</v>
@@ -12295,10 +12298,10 @@
         <v>13</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D404" s="6" t="n">
-        <v>6582.0</v>
+        <v>621.0</v>
       </c>
       <c r="E404" s="7" t="s">
         <v>12</v>
@@ -12324,16 +12327,16 @@
         <v>13</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D405" s="6" t="n">
-        <v>48.0</v>
+        <v>728271.0</v>
       </c>
       <c r="E405" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F405" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F405" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G405" s="8" t="s">
         <v>65</v>
@@ -12382,16 +12385,16 @@
         <v>13</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D407" s="6" t="n">
-        <v>2360.0</v>
+        <v>9750.0</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F407" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F407" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G407" s="8" t="s">
         <v>65</v>
@@ -12411,16 +12414,16 @@
         <v>13</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>9750.0</v>
+        <v>6582.0</v>
       </c>
       <c r="E408" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F408" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F408" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G408" s="8" t="s">
         <v>65</v>
@@ -12469,10 +12472,10 @@
         <v>30</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D410" s="6" t="n">
-        <v>318.0</v>
+        <v>35159.0</v>
       </c>
       <c r="E410" s="7" t="s">
         <v>12</v>
@@ -12498,16 +12501,16 @@
         <v>10</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D411" s="6" t="n">
-        <v>285268.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E411" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F411" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F411" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G411" s="8" t="s">
         <v>65</v>
@@ -12527,16 +12530,16 @@
         <v>10</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D412" s="6" t="n">
-        <v>217102.0</v>
+        <v>285268.0</v>
       </c>
       <c r="E412" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F412" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F412" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G412" s="8" t="s">
         <v>65</v>
@@ -12556,10 +12559,10 @@
         <v>10</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>60.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E413" s="7" t="s">
         <v>12</v>
@@ -12582,13 +12585,13 @@
         <v>65</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D414" s="6" t="n">
-        <v>35159.0</v>
+        <v>60.0</v>
       </c>
       <c r="E414" s="7" t="s">
         <v>12</v>
@@ -12611,13 +12614,13 @@
         <v>65</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>160813.0</v>
+        <v>4067.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12643,10 +12646,10 @@
         <v>30</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D416" s="6" t="n">
-        <v>548.0</v>
+        <v>318.0</v>
       </c>
       <c r="E416" s="7" t="s">
         <v>12</v>
@@ -12672,10 +12675,10 @@
         <v>30</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D417" s="6" t="n">
-        <v>7149.0</v>
+        <v>126986.0</v>
       </c>
       <c r="E417" s="7" t="s">
         <v>12</v>
@@ -12701,16 +12704,16 @@
         <v>30</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D418" s="6" t="n">
-        <v>594911.0</v>
+        <v>7149.0</v>
       </c>
       <c r="E418" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F418" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F418" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G418" s="8" t="s">
         <v>65</v>
@@ -12730,16 +12733,16 @@
         <v>30</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D419" s="6" t="n">
-        <v>39117.0</v>
+        <v>594911.0</v>
       </c>
       <c r="E419" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F419" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F419" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G419" s="8" t="s">
         <v>65</v>
@@ -12756,13 +12759,13 @@
         <v>65</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D420" s="6" t="n">
-        <v>4067.0</v>
+        <v>39117.0</v>
       </c>
       <c r="E420" s="7" t="s">
         <v>12</v>
@@ -12788,10 +12791,10 @@
         <v>30</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>126986.0</v>
+        <v>548.0</v>
       </c>
       <c r="E421" s="7" t="s">
         <v>12</v>
@@ -12817,10 +12820,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>1359.0</v>
+        <v>784.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12962,10 +12965,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>784.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -12991,10 +12994,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>70064.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13107,16 +13110,16 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>510218.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E432" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F432" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F432" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G432" s="8" t="s">
         <v>66</v>
@@ -13136,10 +13139,10 @@
         <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>5605.0</v>
+        <v>35061.0</v>
       </c>
       <c r="E433" s="7" t="s">
         <v>12</v>
@@ -13165,10 +13168,10 @@
         <v>13</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D434" s="6" t="n">
-        <v>35061.0</v>
+        <v>1355.0</v>
       </c>
       <c r="E434" s="7" t="s">
         <v>12</v>
@@ -13194,16 +13197,16 @@
         <v>13</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>1355.0</v>
+        <v>510218.0</v>
       </c>
       <c r="E435" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F435" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F435" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G435" s="8" t="s">
         <v>66</v>
@@ -13220,19 +13223,19 @@
         <v>66</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D436" s="6" t="n">
-        <v>210756.0</v>
+        <v>4083.0</v>
       </c>
       <c r="E436" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F436" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F436" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G436" s="8" t="s">
         <v>66</v>
@@ -13249,13 +13252,13 @@
         <v>66</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D437" s="6" t="n">
-        <v>4083.0</v>
+        <v>9349.0</v>
       </c>
       <c r="E437" s="7" t="s">
         <v>12</v>
@@ -13281,10 +13284,10 @@
         <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>9349.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13310,16 +13313,16 @@
         <v>10</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>108610.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E439" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F439" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F439" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G439" s="8" t="s">
         <v>66</v>
@@ -13336,13 +13339,13 @@
         <v>66</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>2197.0</v>
+        <v>209762.0</v>
       </c>
       <c r="E440" s="7" t="s">
         <v>12</v>
@@ -13368,10 +13371,10 @@
         <v>10</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>209762.0</v>
+        <v>4524.0</v>
       </c>
       <c r="E441" s="7" t="s">
         <v>12</v>
@@ -13397,10 +13400,10 @@
         <v>10</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D442" s="6" t="n">
-        <v>4524.0</v>
+        <v>5730.0</v>
       </c>
       <c r="E442" s="7" t="s">
         <v>12</v>
@@ -13426,10 +13429,10 @@
         <v>10</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>5730.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E443" s="7" t="s">
         <v>12</v>
@@ -13452,13 +13455,13 @@
         <v>66</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D444" s="6" t="n">
-        <v>3803.0</v>
+        <v>31883.0</v>
       </c>
       <c r="E444" s="7" t="s">
         <v>12</v>
@@ -13484,10 +13487,10 @@
         <v>30</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>31883.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13513,10 +13516,10 @@
         <v>30</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D446" s="6" t="n">
-        <v>1503.0</v>
+        <v>105.0</v>
       </c>
       <c r="E446" s="7" t="s">
         <v>12</v>
@@ -13542,10 +13545,10 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>105.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E447" s="7" t="s">
         <v>12</v>
@@ -13571,10 +13574,10 @@
         <v>30</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>398394.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E448" s="7" t="s">
         <v>12</v>
@@ -13774,10 +13777,10 @@
         <v>13</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D455" s="6" t="n">
-        <v>792.0</v>
+        <v>57845.0</v>
       </c>
       <c r="E455" s="7" t="s">
         <v>12</v>
@@ -13803,16 +13806,16 @@
         <v>13</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D456" s="6" t="n">
-        <v>57845.0</v>
+        <v>357258.0</v>
       </c>
       <c r="E456" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F456" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F456" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G456" s="8" t="s">
         <v>67</v>
@@ -13832,16 +13835,16 @@
         <v>13</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D457" s="6" t="n">
-        <v>357258.0</v>
+        <v>4957.0</v>
       </c>
       <c r="E457" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F457" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F457" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G457" s="8" t="s">
         <v>67</v>
@@ -13861,10 +13864,10 @@
         <v>13</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D458" s="6" t="n">
-        <v>4957.0</v>
+        <v>936.0</v>
       </c>
       <c r="E458" s="7" t="s">
         <v>12</v>
@@ -13890,10 +13893,10 @@
         <v>13</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D459" s="6" t="n">
-        <v>936.0</v>
+        <v>1522.0</v>
       </c>
       <c r="E459" s="7" t="s">
         <v>12</v>
@@ -13919,10 +13922,10 @@
         <v>13</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D460" s="6" t="n">
-        <v>1522.0</v>
+        <v>2727.0</v>
       </c>
       <c r="E460" s="7" t="s">
         <v>12</v>
@@ -13948,16 +13951,16 @@
         <v>13</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D461" s="6" t="n">
-        <v>2727.0</v>
+        <v>78020.0</v>
       </c>
       <c r="E461" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F461" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F461" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G461" s="8" t="s">
         <v>67</v>
@@ -13977,16 +13980,16 @@
         <v>13</v>
       </c>
       <c r="C462" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D462" s="6" t="n">
-        <v>78020.0</v>
+        <v>106406.0</v>
       </c>
       <c r="E462" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F462" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F462" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G462" s="8" t="s">
         <v>67</v>
@@ -14006,10 +14009,10 @@
         <v>13</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D463" s="6" t="n">
-        <v>106406.0</v>
+        <v>792.0</v>
       </c>
       <c r="E463" s="7" t="s">
         <v>12</v>
@@ -14032,13 +14035,13 @@
         <v>67</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D464" s="6" t="n">
-        <v>3174.0</v>
+        <v>64823.0</v>
       </c>
       <c r="E464" s="7" t="s">
         <v>12</v>
@@ -14093,10 +14096,10 @@
         <v>30</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D466" s="6" t="n">
-        <v>3363.0</v>
+        <v>74709.0</v>
       </c>
       <c r="E466" s="7" t="s">
         <v>12</v>
@@ -14122,10 +14125,10 @@
         <v>13</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>64823.0</v>
+        <v>6691.0</v>
       </c>
       <c r="E467" s="7" t="s">
         <v>12</v>
@@ -14206,13 +14209,13 @@
         <v>67</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D470" s="6" t="n">
-        <v>74709.0</v>
+        <v>3174.0</v>
       </c>
       <c r="E470" s="7" t="s">
         <v>12</v>
@@ -14267,10 +14270,10 @@
         <v>30</v>
       </c>
       <c r="C472" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D472" s="6" t="n">
-        <v>646.0</v>
+        <v>3363.0</v>
       </c>
       <c r="E472" s="7" t="s">
         <v>12</v>
@@ -14296,10 +14299,10 @@
         <v>30</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D473" s="6" t="n">
-        <v>8245.0</v>
+        <v>199283.0</v>
       </c>
       <c r="E473" s="7" t="s">
         <v>12</v>
@@ -14325,10 +14328,10 @@
         <v>30</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D474" s="6" t="n">
-        <v>207867.0</v>
+        <v>8245.0</v>
       </c>
       <c r="E474" s="7" t="s">
         <v>12</v>
@@ -14354,10 +14357,10 @@
         <v>30</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D475" s="6" t="n">
-        <v>6920.0</v>
+        <v>207867.0</v>
       </c>
       <c r="E475" s="7" t="s">
         <v>12</v>
@@ -14380,13 +14383,13 @@
         <v>67</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D476" s="6" t="n">
-        <v>6691.0</v>
+        <v>6920.0</v>
       </c>
       <c r="E476" s="7" t="s">
         <v>12</v>
@@ -14412,10 +14415,10 @@
         <v>30</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D477" s="6" t="n">
-        <v>199283.0</v>
+        <v>646.0</v>
       </c>
       <c r="E477" s="7" t="s">
         <v>12</v>
@@ -14441,10 +14444,10 @@
         <v>13</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D478" s="6" t="n">
-        <v>4818.0</v>
+        <v>158897.0</v>
       </c>
       <c r="E478" s="7" t="s">
         <v>12</v>
@@ -14470,10 +14473,10 @@
         <v>13</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D479" s="6" t="n">
-        <v>692.0</v>
+        <v>3849.0</v>
       </c>
       <c r="E479" s="7" t="s">
         <v>12</v>
@@ -14499,10 +14502,10 @@
         <v>13</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D480" s="6" t="n">
-        <v>3849.0</v>
+        <v>8962.0</v>
       </c>
       <c r="E480" s="7" t="s">
         <v>12</v>
@@ -14557,10 +14560,10 @@
         <v>13</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D482" s="6" t="n">
-        <v>4053.0</v>
+        <v>4818.0</v>
       </c>
       <c r="E482" s="7" t="s">
         <v>12</v>
@@ -14586,16 +14589,16 @@
         <v>13</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D483" s="6" t="n">
-        <v>158694.0</v>
+        <v>108623.0</v>
       </c>
       <c r="E483" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F483" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F483" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G483" s="8" t="s">
         <v>68</v>
@@ -14618,7 +14621,7 @@
         <v>23</v>
       </c>
       <c r="D484" s="6" t="n">
-        <v>20456.0</v>
+        <v>20516.0</v>
       </c>
       <c r="E484" s="7" t="s">
         <v>12</v>
@@ -14644,10 +14647,10 @@
         <v>13</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D485" s="6" t="n">
-        <v>548820.0</v>
+        <v>4118.0</v>
       </c>
       <c r="E485" s="7" t="s">
         <v>12</v>
@@ -14673,10 +14676,10 @@
         <v>13</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D486" s="6" t="n">
-        <v>2658.0</v>
+        <v>549073.0</v>
       </c>
       <c r="E486" s="7" t="s">
         <v>12</v>
@@ -14702,10 +14705,10 @@
         <v>13</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D487" s="6" t="n">
-        <v>791.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E487" s="7" t="s">
         <v>12</v>
@@ -14731,16 +14734,16 @@
         <v>13</v>
       </c>
       <c r="C488" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D488" s="6" t="n">
-        <v>96265.0</v>
+        <v>791.0</v>
       </c>
       <c r="E488" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F488" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F488" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G488" s="8" t="s">
         <v>68</v>
@@ -14760,16 +14763,16 @@
         <v>13</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D489" s="6" t="n">
-        <v>108568.0</v>
+        <v>692.0</v>
       </c>
       <c r="E489" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F489" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F489" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G489" s="8" t="s">
         <v>68</v>
@@ -14786,13 +14789,13 @@
         <v>68</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D490" s="6" t="n">
-        <v>8962.0</v>
+        <v>13403.0</v>
       </c>
       <c r="E490" s="7" t="s">
         <v>12</v>
@@ -14818,16 +14821,16 @@
         <v>13</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D491" s="6" t="n">
-        <v>69923.0</v>
+        <v>96503.0</v>
       </c>
       <c r="E491" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F491" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F491" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G491" s="8" t="s">
         <v>68</v>
@@ -14844,13 +14847,13 @@
         <v>68</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D492" s="6" t="n">
-        <v>15334.0</v>
+        <v>54343.0</v>
       </c>
       <c r="E492" s="7" t="s">
         <v>12</v>
@@ -14876,10 +14879,10 @@
         <v>13</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D493" s="6" t="n">
-        <v>8296.0</v>
+        <v>70327.0</v>
       </c>
       <c r="E493" s="7" t="s">
         <v>12</v>
@@ -14905,16 +14908,16 @@
         <v>10</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D494" s="6" t="n">
-        <v>107584.0</v>
+        <v>296618.0</v>
       </c>
       <c r="E494" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F494" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F494" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G494" s="8" t="s">
         <v>68</v>
@@ -14963,10 +14966,10 @@
         <v>10</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D496" s="6" t="n">
-        <v>13403.0</v>
+        <v>15334.0</v>
       </c>
       <c r="E496" s="7" t="s">
         <v>12</v>
@@ -14992,16 +14995,16 @@
         <v>10</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D497" s="6" t="n">
-        <v>296453.0</v>
+        <v>107735.0</v>
       </c>
       <c r="E497" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F497" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F497" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G497" s="8" t="s">
         <v>68</v>
@@ -15021,10 +15024,10 @@
         <v>30</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D498" s="6" t="n">
-        <v>54343.0</v>
+        <v>4041.0</v>
       </c>
       <c r="E498" s="7" t="s">
         <v>12</v>
@@ -15050,10 +15053,10 @@
         <v>30</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D499" s="6" t="n">
-        <v>4041.0</v>
+        <v>206053.0</v>
       </c>
       <c r="E499" s="7" t="s">
         <v>12</v>
@@ -15079,16 +15082,16 @@
         <v>30</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D500" s="6" t="n">
-        <v>190026.0</v>
+        <v>5306.0</v>
       </c>
       <c r="E500" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F500" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F500" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G500" s="8" t="s">
         <v>68</v>
@@ -15105,13 +15108,13 @@
         <v>68</v>
       </c>
       <c r="B501" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D501" s="6" t="n">
-        <v>205002.0</v>
+        <v>14544.0</v>
       </c>
       <c r="E501" s="7" t="s">
         <v>12</v>
@@ -15134,13 +15137,13 @@
         <v>68</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C502" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D502" s="6" t="n">
-        <v>5306.0</v>
+        <v>8296.0</v>
       </c>
       <c r="E502" s="7" t="s">
         <v>12</v>
@@ -15163,19 +15166,19 @@
         <v>68</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D503" s="6" t="n">
-        <v>14544.0</v>
+        <v>190807.0</v>
       </c>
       <c r="E503" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F503" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F503" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G503" s="8" t="s">
         <v>68</v>
@@ -15195,10 +15198,10 @@
         <v>13</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D504" s="6" t="n">
-        <v>76.0</v>
+        <v>248.0</v>
       </c>
       <c r="E504" s="7" t="s">
         <v>12</v>
@@ -15224,10 +15227,10 @@
         <v>13</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D505" s="6" t="n">
-        <v>1365.0</v>
+        <v>72938.0</v>
       </c>
       <c r="E505" s="7" t="s">
         <v>12</v>
@@ -15253,16 +15256,16 @@
         <v>13</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D506" s="6" t="n">
-        <v>18163.0</v>
+        <v>144021.0</v>
       </c>
       <c r="E506" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F506" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F506" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G506" s="8" t="s">
         <v>69</v>
@@ -15282,10 +15285,10 @@
         <v>13</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D507" s="6" t="n">
-        <v>124759.0</v>
+        <v>123.0</v>
       </c>
       <c r="E507" s="7" t="s">
         <v>12</v>
@@ -15311,10 +15314,10 @@
         <v>13</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D508" s="6" t="n">
-        <v>2772.0</v>
+        <v>5181.0</v>
       </c>
       <c r="E508" s="7" t="s">
         <v>12</v>
@@ -15340,10 +15343,10 @@
         <v>13</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D509" s="6" t="n">
-        <v>248.0</v>
+        <v>4716.0</v>
       </c>
       <c r="E509" s="7" t="s">
         <v>12</v>
@@ -15369,10 +15372,10 @@
         <v>13</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D510" s="6" t="n">
-        <v>27246.0</v>
+        <v>201113.0</v>
       </c>
       <c r="E510" s="7" t="s">
         <v>12</v>
@@ -15398,10 +15401,10 @@
         <v>13</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D511" s="6" t="n">
-        <v>33546.0</v>
+        <v>18261.0</v>
       </c>
       <c r="E511" s="7" t="s">
         <v>12</v>
@@ -15427,10 +15430,10 @@
         <v>13</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D512" s="6" t="n">
-        <v>38016.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E512" s="7" t="s">
         <v>12</v>
@@ -15453,19 +15456,19 @@
         <v>69</v>
       </c>
       <c r="B513" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D513" s="6" t="n">
-        <v>883.0</v>
+        <v>908897.0</v>
       </c>
       <c r="E513" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F513" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F513" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G513" s="8" t="s">
         <v>69</v>
@@ -15488,7 +15491,7 @@
         <v>47</v>
       </c>
       <c r="D514" s="6" t="n">
-        <v>3126.0</v>
+        <v>30675.0</v>
       </c>
       <c r="E514" s="7" t="s">
         <v>12</v>
@@ -15514,10 +15517,10 @@
         <v>13</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D515" s="6" t="n">
-        <v>5259.0</v>
+        <v>2898.0</v>
       </c>
       <c r="E515" s="7" t="s">
         <v>12</v>
@@ -15540,19 +15543,19 @@
         <v>69</v>
       </c>
       <c r="B516" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C516" s="5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D516" s="6" t="n">
-        <v>173227.0</v>
+        <v>62084.0</v>
       </c>
       <c r="E516" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F516" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F516" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G516" s="8" t="s">
         <v>69</v>
@@ -15569,13 +15572,13 @@
         <v>69</v>
       </c>
       <c r="B517" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D517" s="6" t="n">
-        <v>24301.0</v>
+        <v>12907.0</v>
       </c>
       <c r="E517" s="7" t="s">
         <v>12</v>
@@ -15598,13 +15601,13 @@
         <v>69</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D518" s="6" t="n">
-        <v>94013.0</v>
+        <v>1408.0</v>
       </c>
       <c r="E518" s="7" t="s">
         <v>12</v>
@@ -15630,16 +15633,16 @@
         <v>30</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D519" s="6" t="n">
-        <v>1733.0</v>
+        <v>366304.0</v>
       </c>
       <c r="E519" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F519" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F519" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G519" s="8" t="s">
         <v>69</v>
@@ -15656,13 +15659,13 @@
         <v>69</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D520" s="6" t="n">
-        <v>36553.0</v>
+        <v>162523.0</v>
       </c>
       <c r="E520" s="7" t="s">
         <v>12</v>
@@ -15688,10 +15691,10 @@
         <v>10</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D521" s="6" t="n">
-        <v>114412.0</v>
+        <v>372344.0</v>
       </c>
       <c r="E521" s="7" t="s">
         <v>12</v>
@@ -15717,10 +15720,10 @@
         <v>10</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D522" s="6" t="n">
-        <v>228012.0</v>
+        <v>162497.0</v>
       </c>
       <c r="E522" s="7" t="s">
         <v>12</v>
@@ -15746,10 +15749,10 @@
         <v>10</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D523" s="6" t="n">
-        <v>62706.0</v>
+        <v>42853.0</v>
       </c>
       <c r="E523" s="7" t="s">
         <v>12</v>
@@ -15772,13 +15775,13 @@
         <v>69</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D524" s="6" t="n">
-        <v>437845.0</v>
+        <v>44.0</v>
       </c>
       <c r="E524" s="7" t="s">
         <v>12</v>
@@ -15793,6 +15796,847 @@
         <v>69</v>
       </c>
       <c r="I524" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B525" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D525" s="6" t="n">
+        <v>1195.0</v>
+      </c>
+      <c r="E525" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F525" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G525" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H525" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I525" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B526" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D526" s="6" t="n">
+        <v>77128.0</v>
+      </c>
+      <c r="E526" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F526" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G526" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H526" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I526" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B527" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D527" s="6" t="n">
+        <v>7684.0</v>
+      </c>
+      <c r="E527" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F527" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G527" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H527" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I527" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D528" s="6" t="n">
+        <v>1733.0</v>
+      </c>
+      <c r="E528" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F528" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G528" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H528" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I528" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B529" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D529" s="6" t="n">
+        <v>284063.0</v>
+      </c>
+      <c r="E529" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F529" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G529" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H529" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I529" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B530" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D530" s="6" t="n">
+        <v>26286.0</v>
+      </c>
+      <c r="E530" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F530" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G530" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H530" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I530" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D531" s="6" t="n">
+        <v>113002.0</v>
+      </c>
+      <c r="E531" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F531" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G531" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H531" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I531" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D532" s="6" t="n">
+        <v>4708.0</v>
+      </c>
+      <c r="E532" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F532" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G532" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H532" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I532" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B533" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D533" s="6" t="n">
+        <v>258716.0</v>
+      </c>
+      <c r="E533" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F533" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G533" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H533" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I533" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B534" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D534" s="6" t="n">
+        <v>658.0</v>
+      </c>
+      <c r="E534" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F534" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G534" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H534" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I534" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B535" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D535" s="6" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="E535" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F535" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G535" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H535" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I535" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D536" s="6" t="n">
+        <v>311.0</v>
+      </c>
+      <c r="E536" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F536" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G536" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H536" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I536" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B537" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D537" s="6" t="n">
+        <v>95311.0</v>
+      </c>
+      <c r="E537" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F537" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G537" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H537" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I537" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D538" s="6" t="n">
+        <v>6262.0</v>
+      </c>
+      <c r="E538" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F538" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G538" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H538" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I538" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B539" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D539" s="6" t="n">
+        <v>249.0</v>
+      </c>
+      <c r="E539" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F539" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G539" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H539" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I539" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B540" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D540" s="6" t="n">
+        <v>7224.0</v>
+      </c>
+      <c r="E540" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F540" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G540" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H540" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I540" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B541" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D541" s="6" t="n">
+        <v>184.0</v>
+      </c>
+      <c r="E541" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F541" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G541" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H541" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I541" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B542" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D542" s="6" t="n">
+        <v>98845.0</v>
+      </c>
+      <c r="E542" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F542" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G542" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H542" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I542" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B543" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D543" s="6" t="n">
+        <v>38218.0</v>
+      </c>
+      <c r="E543" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F543" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G543" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H543" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I543" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B544" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D544" s="6" t="n">
+        <v>12959.0</v>
+      </c>
+      <c r="E544" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F544" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G544" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H544" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I544" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B545" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D545" s="6" t="n">
+        <v>68500.0</v>
+      </c>
+      <c r="E545" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F545" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G545" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H545" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I545" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B546" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D546" s="6" t="n">
+        <v>128978.0</v>
+      </c>
+      <c r="E546" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F546" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G546" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H546" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I546" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B547" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D547" s="6" t="n">
+        <v>8609.0</v>
+      </c>
+      <c r="E547" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F547" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G547" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H547" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I547" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B548" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C548" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D548" s="6" t="n">
+        <v>50593.0</v>
+      </c>
+      <c r="E548" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F548" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G548" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H548" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I548" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B549" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D549" s="6" t="n">
+        <v>4759.0</v>
+      </c>
+      <c r="E549" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F549" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G549" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H549" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I549" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B550" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C550" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D550" s="6" t="n">
+        <v>49217.0</v>
+      </c>
+      <c r="E550" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F550" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G550" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H550" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I550" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B551" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D551" s="6" t="n">
+        <v>207446.0</v>
+      </c>
+      <c r="E551" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F551" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G551" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H551" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I551" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B552" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D552" s="6" t="n">
+        <v>36286.0</v>
+      </c>
+      <c r="E552" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F552" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G552" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H552" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I552" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B553" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D553" s="6" t="n">
+        <v>712.0</v>
+      </c>
+      <c r="E553" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F553" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G553" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H553" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I553" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4350" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4573" uniqueCount="72">
   <si>
     <t>Ngày</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I553"/>
+  <dimension ref="A1:I581"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -8441,10 +8444,10 @@
         <v>13</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D271" s="6" t="n">
-        <v>35463.0</v>
+        <v>233437.0</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>12</v>
@@ -8470,10 +8473,10 @@
         <v>13</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D272" s="6" t="n">
-        <v>20732.0</v>
+        <v>15.0</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>12</v>
@@ -8499,10 +8502,10 @@
         <v>13</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D273" s="6" t="n">
-        <v>6937.0</v>
+        <v>20732.0</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>12</v>
@@ -8528,10 +8531,10 @@
         <v>13</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D274" s="6" t="n">
-        <v>15068.0</v>
+        <v>6937.0</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>12</v>
@@ -8557,10 +8560,10 @@
         <v>13</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D275" s="6" t="n">
-        <v>26381.0</v>
+        <v>15068.0</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>12</v>
@@ -8586,10 +8589,10 @@
         <v>13</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D276" s="6" t="n">
-        <v>233437.0</v>
+        <v>220465.0</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>12</v>
@@ -8818,10 +8821,10 @@
         <v>13</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>15.0</v>
+        <v>35463.0</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>12</v>
@@ -8844,13 +8847,13 @@
         <v>60</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>27356.0</v>
+        <v>26381.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8876,16 +8879,16 @@
         <v>13</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>220465.0</v>
+        <v>168847.0</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F286" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F286" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G286" s="8" t="s">
         <v>60</v>
@@ -8934,16 +8937,16 @@
         <v>13</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>168847.0</v>
+        <v>20130.0</v>
       </c>
       <c r="E288" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F288" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F288" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G288" s="8" t="s">
         <v>60</v>
@@ -9137,16 +9140,16 @@
         <v>30</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>260392.0</v>
+        <v>11792.0</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F295" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F295" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G295" s="8" t="s">
         <v>60</v>
@@ -9166,16 +9169,16 @@
         <v>30</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D296" s="6" t="n">
-        <v>21208.0</v>
+        <v>260392.0</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F296" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F296" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G296" s="8" t="s">
         <v>60</v>
@@ -9195,10 +9198,10 @@
         <v>30</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D297" s="6" t="n">
-        <v>87988.0</v>
+        <v>21208.0</v>
       </c>
       <c r="E297" s="7" t="s">
         <v>12</v>
@@ -9224,16 +9227,16 @@
         <v>30</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>18189.0</v>
+        <v>87988.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F298" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>60</v>
@@ -9250,19 +9253,19 @@
         <v>60</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>20130.0</v>
+        <v>18189.0</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F299" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F299" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G299" s="8" t="s">
         <v>60</v>
@@ -9282,10 +9285,10 @@
         <v>30</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>11792.0</v>
+        <v>27356.0</v>
       </c>
       <c r="E300" s="7" t="s">
         <v>12</v>
@@ -9311,10 +9314,10 @@
         <v>13</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>10887.0</v>
+        <v>4517.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9427,16 +9430,16 @@
         <v>13</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>4517.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F305" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F305" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G305" s="8" t="s">
         <v>61</v>
@@ -9456,16 +9459,16 @@
         <v>13</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>414833.0</v>
+        <v>10887.0</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F306" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G306" s="8" t="s">
         <v>61</v>
@@ -9514,10 +9517,10 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>16117.0</v>
+        <v>18161.0</v>
       </c>
       <c r="E308" s="7" t="s">
         <v>12</v>
@@ -9543,10 +9546,10 @@
         <v>13</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>18161.0</v>
+        <v>5125.0</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>12</v>
@@ -9569,13 +9572,13 @@
         <v>61</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>5125.0</v>
+        <v>1798.0</v>
       </c>
       <c r="E310" s="7" t="s">
         <v>12</v>
@@ -9598,13 +9601,13 @@
         <v>61</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>1798.0</v>
+        <v>49079.0</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>12</v>
@@ -9630,10 +9633,10 @@
         <v>13</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>49079.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E312" s="7" t="s">
         <v>12</v>
@@ -9659,10 +9662,10 @@
         <v>30</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>32300.0</v>
+        <v>3372.0</v>
       </c>
       <c r="E313" s="7" t="s">
         <v>12</v>
@@ -9685,13 +9688,13 @@
         <v>61</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D314" s="6" t="n">
-        <v>3372.0</v>
+        <v>2153.0</v>
       </c>
       <c r="E314" s="7" t="s">
         <v>12</v>
@@ -9717,10 +9720,10 @@
         <v>10</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D315" s="6" t="n">
-        <v>2153.0</v>
+        <v>7578.0</v>
       </c>
       <c r="E315" s="7" t="s">
         <v>12</v>
@@ -9743,19 +9746,19 @@
         <v>61</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>25684.0</v>
+        <v>191.0</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F316" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F316" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G316" s="8" t="s">
         <v>61</v>
@@ -9772,13 +9775,13 @@
         <v>61</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D317" s="6" t="n">
-        <v>191.0</v>
+        <v>19353.0</v>
       </c>
       <c r="E317" s="7" t="s">
         <v>12</v>
@@ -9804,10 +9807,10 @@
         <v>10</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D318" s="6" t="n">
-        <v>560394.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E318" s="7" t="s">
         <v>16</v>
@@ -9833,16 +9836,16 @@
         <v>10</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D319" s="6" t="n">
-        <v>19353.0</v>
+        <v>560394.0</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F319" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F319" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G319" s="8" t="s">
         <v>61</v>
@@ -9862,10 +9865,10 @@
         <v>10</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>7578.0</v>
+        <v>3475.0</v>
       </c>
       <c r="E320" s="7" t="s">
         <v>12</v>
@@ -9891,10 +9894,10 @@
         <v>10</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D321" s="6" t="n">
-        <v>3475.0</v>
+        <v>2152.0</v>
       </c>
       <c r="E321" s="7" t="s">
         <v>12</v>
@@ -9917,13 +9920,13 @@
         <v>61</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>2152.0</v>
+        <v>400544.0</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>12</v>
@@ -9949,10 +9952,10 @@
         <v>30</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>400544.0</v>
+        <v>17918.0</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>12</v>
@@ -9978,10 +9981,10 @@
         <v>30</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>17918.0</v>
+        <v>7822.0</v>
       </c>
       <c r="E324" s="7" t="s">
         <v>12</v>
@@ -10007,10 +10010,10 @@
         <v>30</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D325" s="6" t="n">
-        <v>7822.0</v>
+        <v>32300.0</v>
       </c>
       <c r="E325" s="7" t="s">
         <v>12</v>
@@ -10036,16 +10039,16 @@
         <v>13</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>240445.0</v>
+        <v>288195.0</v>
       </c>
       <c r="E326" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F326" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G326" s="8" t="s">
         <v>62</v>
@@ -10326,16 +10329,16 @@
         <v>13</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>288195.0</v>
+        <v>39009.0</v>
       </c>
       <c r="E336" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F336" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F336" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G336" s="8" t="s">
         <v>62</v>
@@ -10355,16 +10358,16 @@
         <v>13</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D337" s="6" t="n">
-        <v>39009.0</v>
+        <v>240445.0</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F337" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F337" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G337" s="8" t="s">
         <v>62</v>
@@ -10381,13 +10384,13 @@
         <v>62</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>1449.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10410,19 +10413,19 @@
         <v>62</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>488224.0</v>
+        <v>182371.0</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F339" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G339" s="8" t="s">
         <v>62</v>
@@ -10442,10 +10445,10 @@
         <v>30</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D340" s="6" t="n">
-        <v>256566.0</v>
+        <v>177268.0</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>12</v>
@@ -10471,10 +10474,10 @@
         <v>30</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D341" s="6" t="n">
-        <v>6148.0</v>
+        <v>15943.0</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>12</v>
@@ -10497,13 +10500,13 @@
         <v>62</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>866.0</v>
+        <v>38261.0</v>
       </c>
       <c r="E342" s="7" t="s">
         <v>12</v>
@@ -10529,10 +10532,10 @@
         <v>30</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D343" s="6" t="n">
-        <v>38261.0</v>
+        <v>1449.0</v>
       </c>
       <c r="E343" s="7" t="s">
         <v>12</v>
@@ -10558,10 +10561,10 @@
         <v>30</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D344" s="6" t="n">
-        <v>15943.0</v>
+        <v>6148.0</v>
       </c>
       <c r="E344" s="7" t="s">
         <v>12</v>
@@ -10587,10 +10590,10 @@
         <v>30</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D345" s="6" t="n">
-        <v>177268.0</v>
+        <v>256566.0</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>12</v>
@@ -10613,19 +10616,19 @@
         <v>62</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>182371.0</v>
+        <v>488224.0</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F346" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F346" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G346" s="8" t="s">
         <v>62</v>
@@ -10645,10 +10648,10 @@
         <v>13</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D347" s="6" t="n">
-        <v>21302.0</v>
+        <v>866.0</v>
       </c>
       <c r="E347" s="7" t="s">
         <v>12</v>
@@ -10674,10 +10677,10 @@
         <v>13</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D348" s="6" t="n">
-        <v>69412.0</v>
+        <v>14390.0</v>
       </c>
       <c r="E348" s="7" t="s">
         <v>12</v>
@@ -10703,10 +10706,10 @@
         <v>13</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D349" s="6" t="n">
-        <v>7560.0</v>
+        <v>9380.0</v>
       </c>
       <c r="E349" s="7" t="s">
         <v>12</v>
@@ -10732,10 +10735,10 @@
         <v>13</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D350" s="6" t="n">
-        <v>805776.0</v>
+        <v>185.0</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>12</v>
@@ -10761,10 +10764,10 @@
         <v>13</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D351" s="6" t="n">
-        <v>14289.0</v>
+        <v>7510.0</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>12</v>
@@ -10790,10 +10793,10 @@
         <v>13</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D352" s="6" t="n">
-        <v>62866.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E352" s="7" t="s">
         <v>12</v>
@@ -10848,10 +10851,10 @@
         <v>13</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D354" s="6" t="n">
-        <v>14390.0</v>
+        <v>62866.0</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>12</v>
@@ -10877,10 +10880,10 @@
         <v>13</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D355" s="6" t="n">
-        <v>7510.0</v>
+        <v>14289.0</v>
       </c>
       <c r="E355" s="7" t="s">
         <v>12</v>
@@ -10906,10 +10909,10 @@
         <v>13</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D356" s="6" t="n">
-        <v>185.0</v>
+        <v>805776.0</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>12</v>
@@ -10935,10 +10938,10 @@
         <v>13</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D357" s="6" t="n">
-        <v>9380.0</v>
+        <v>7560.0</v>
       </c>
       <c r="E357" s="7" t="s">
         <v>12</v>
@@ -10993,10 +10996,10 @@
         <v>13</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>15854.0</v>
+        <v>69412.0</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>12</v>
@@ -11019,13 +11022,13 @@
         <v>63</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D360" s="6" t="n">
-        <v>837.0</v>
+        <v>42515.0</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>12</v>
@@ -11048,19 +11051,19 @@
         <v>63</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D361" s="6" t="n">
-        <v>303397.0</v>
+        <v>1766.0</v>
       </c>
       <c r="E361" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F361" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G361" s="8" t="s">
         <v>63</v>
@@ -11077,13 +11080,13 @@
         <v>63</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D362" s="6" t="n">
-        <v>82520.0</v>
+        <v>103343.0</v>
       </c>
       <c r="E362" s="7" t="s">
         <v>12</v>
@@ -11106,19 +11109,19 @@
         <v>63</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D363" s="6" t="n">
-        <v>2331.0</v>
+        <v>419250.0</v>
       </c>
       <c r="E363" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F363" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F363" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G363" s="8" t="s">
         <v>63</v>
@@ -11135,19 +11138,19 @@
         <v>63</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D364" s="6" t="n">
-        <v>111759.0</v>
+        <v>96851.0</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F364" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F364" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>63</v>
@@ -11167,10 +11170,10 @@
         <v>10</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D365" s="6" t="n">
-        <v>5088.0</v>
+        <v>2365.0</v>
       </c>
       <c r="E365" s="7" t="s">
         <v>12</v>
@@ -11196,10 +11199,10 @@
         <v>10</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D366" s="6" t="n">
-        <v>1766.0</v>
+        <v>837.0</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>12</v>
@@ -11225,10 +11228,10 @@
         <v>10</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D367" s="6" t="n">
-        <v>2365.0</v>
+        <v>5088.0</v>
       </c>
       <c r="E367" s="7" t="s">
         <v>12</v>
@@ -11251,19 +11254,19 @@
         <v>63</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D368" s="6" t="n">
-        <v>96851.0</v>
+        <v>111759.0</v>
       </c>
       <c r="E368" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F368" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G368" s="8" t="s">
         <v>63</v>
@@ -11280,19 +11283,19 @@
         <v>63</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D369" s="6" t="n">
-        <v>419250.0</v>
+        <v>2331.0</v>
       </c>
       <c r="E369" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F369" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G369" s="8" t="s">
         <v>63</v>
@@ -11312,10 +11315,10 @@
         <v>30</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D370" s="6" t="n">
-        <v>42515.0</v>
+        <v>82520.0</v>
       </c>
       <c r="E370" s="7" t="s">
         <v>12</v>
@@ -11338,19 +11341,19 @@
         <v>63</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D371" s="6" t="n">
-        <v>103343.0</v>
+        <v>303397.0</v>
       </c>
       <c r="E371" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F371" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F371" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G371" s="8" t="s">
         <v>63</v>
@@ -11370,10 +11373,10 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>5337.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E372" s="7" t="s">
         <v>12</v>
@@ -11399,16 +11402,16 @@
         <v>13</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D373" s="6" t="n">
-        <v>96052.0</v>
+        <v>404269.0</v>
       </c>
       <c r="E373" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F373" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F373" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G373" s="8" t="s">
         <v>64</v>
@@ -11428,10 +11431,10 @@
         <v>13</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D374" s="6" t="n">
-        <v>102275.0</v>
+        <v>894.0</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>12</v>
@@ -11457,10 +11460,10 @@
         <v>13</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D375" s="6" t="n">
-        <v>3142.0</v>
+        <v>815.0</v>
       </c>
       <c r="E375" s="7" t="s">
         <v>12</v>
@@ -11486,10 +11489,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>3681.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11544,10 +11547,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>91385.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11573,10 +11576,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>815.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11602,10 +11605,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>894.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11631,16 +11634,16 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>404269.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E381" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F381" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F381" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>64</v>
@@ -11686,13 +11689,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>14304.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11715,13 +11718,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>8817.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -12066,16 +12069,16 @@
         <v>13</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D396" s="6" t="n">
-        <v>5697.0</v>
+        <v>378735.0</v>
       </c>
       <c r="E396" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F396" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F396" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G396" s="8" t="s">
         <v>65</v>
@@ -12095,10 +12098,10 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D397" s="6" t="n">
-        <v>2360.0</v>
+        <v>5282.0</v>
       </c>
       <c r="E397" s="7" t="s">
         <v>12</v>
@@ -12124,10 +12127,10 @@
         <v>13</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D398" s="6" t="n">
-        <v>5282.0</v>
+        <v>5080.0</v>
       </c>
       <c r="E398" s="7" t="s">
         <v>12</v>
@@ -12153,10 +12156,10 @@
         <v>13</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D399" s="6" t="n">
-        <v>5080.0</v>
+        <v>629.0</v>
       </c>
       <c r="E399" s="7" t="s">
         <v>12</v>
@@ -12182,10 +12185,10 @@
         <v>13</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D400" s="6" t="n">
-        <v>629.0</v>
+        <v>5697.0</v>
       </c>
       <c r="E400" s="7" t="s">
         <v>12</v>
@@ -12211,16 +12214,16 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>48.0</v>
+        <v>9750.0</v>
       </c>
       <c r="E401" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F401" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F401" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>65</v>
@@ -12240,16 +12243,16 @@
         <v>13</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D402" s="6" t="n">
-        <v>378735.0</v>
+        <v>133369.0</v>
       </c>
       <c r="E402" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F402" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F402" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G402" s="8" t="s">
         <v>65</v>
@@ -12269,10 +12272,10 @@
         <v>13</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D403" s="6" t="n">
-        <v>133369.0</v>
+        <v>621.0</v>
       </c>
       <c r="E403" s="7" t="s">
         <v>12</v>
@@ -12298,16 +12301,16 @@
         <v>13</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D404" s="6" t="n">
-        <v>621.0</v>
+        <v>728271.0</v>
       </c>
       <c r="E404" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F404" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F404" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G404" s="8" t="s">
         <v>65</v>
@@ -12327,16 +12330,16 @@
         <v>13</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D405" s="6" t="n">
-        <v>728271.0</v>
+        <v>6582.0</v>
       </c>
       <c r="E405" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F405" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F405" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G405" s="8" t="s">
         <v>65</v>
@@ -12356,16 +12359,16 @@
         <v>13</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D406" s="6" t="n">
-        <v>65752.0</v>
+        <v>48.0</v>
       </c>
       <c r="E406" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F406" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F406" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G406" s="8" t="s">
         <v>65</v>
@@ -12385,16 +12388,16 @@
         <v>13</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D407" s="6" t="n">
-        <v>9750.0</v>
+        <v>2360.0</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F407" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G407" s="8" t="s">
         <v>65</v>
@@ -12411,13 +12414,13 @@
         <v>65</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>6582.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E408" s="7" t="s">
         <v>12</v>
@@ -12443,16 +12446,16 @@
         <v>13</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D409" s="6" t="n">
-        <v>73210.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E409" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F409" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F409" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G409" s="8" t="s">
         <v>65</v>
@@ -12472,10 +12475,10 @@
         <v>30</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D410" s="6" t="n">
-        <v>35159.0</v>
+        <v>318.0</v>
       </c>
       <c r="E410" s="7" t="s">
         <v>12</v>
@@ -12498,13 +12501,13 @@
         <v>65</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D411" s="6" t="n">
-        <v>160813.0</v>
+        <v>73210.0</v>
       </c>
       <c r="E411" s="7" t="s">
         <v>12</v>
@@ -12559,10 +12562,10 @@
         <v>10</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>217102.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E413" s="7" t="s">
         <v>12</v>
@@ -12614,13 +12617,13 @@
         <v>65</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>4067.0</v>
+        <v>35159.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12646,10 +12649,10 @@
         <v>30</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D416" s="6" t="n">
-        <v>318.0</v>
+        <v>548.0</v>
       </c>
       <c r="E416" s="7" t="s">
         <v>12</v>
@@ -12788,13 +12791,13 @@
         <v>65</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>548.0</v>
+        <v>4067.0</v>
       </c>
       <c r="E421" s="7" t="s">
         <v>12</v>
@@ -12965,10 +12968,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>70064.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -13081,10 +13084,10 @@
         <v>13</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>4241.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E431" s="7" t="s">
         <v>12</v>
@@ -13110,10 +13113,10 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>5605.0</v>
+        <v>4241.0</v>
       </c>
       <c r="E432" s="7" t="s">
         <v>12</v>
@@ -13139,16 +13142,16 @@
         <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>35061.0</v>
+        <v>510218.0</v>
       </c>
       <c r="E433" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F433" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F433" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G433" s="8" t="s">
         <v>66</v>
@@ -13168,10 +13171,10 @@
         <v>13</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D434" s="6" t="n">
-        <v>1355.0</v>
+        <v>35061.0</v>
       </c>
       <c r="E434" s="7" t="s">
         <v>12</v>
@@ -13197,16 +13200,16 @@
         <v>13</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>510218.0</v>
+        <v>1355.0</v>
       </c>
       <c r="E435" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F435" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F435" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G435" s="8" t="s">
         <v>66</v>
@@ -13223,13 +13226,13 @@
         <v>66</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D436" s="6" t="n">
-        <v>4083.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E436" s="7" t="s">
         <v>12</v>
@@ -13252,13 +13255,13 @@
         <v>66</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D437" s="6" t="n">
-        <v>9349.0</v>
+        <v>4083.0</v>
       </c>
       <c r="E437" s="7" t="s">
         <v>12</v>
@@ -13284,10 +13287,10 @@
         <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>108610.0</v>
+        <v>5730.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13310,19 +13313,19 @@
         <v>66</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>210756.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E439" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F439" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F439" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G439" s="8" t="s">
         <v>66</v>
@@ -13342,10 +13345,10 @@
         <v>10</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>209762.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E440" s="7" t="s">
         <v>12</v>
@@ -13371,16 +13374,16 @@
         <v>10</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>4524.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E441" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F441" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F441" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G441" s="8" t="s">
         <v>66</v>
@@ -13400,10 +13403,10 @@
         <v>10</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D442" s="6" t="n">
-        <v>5730.0</v>
+        <v>209762.0</v>
       </c>
       <c r="E442" s="7" t="s">
         <v>12</v>
@@ -13429,10 +13432,10 @@
         <v>10</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>3803.0</v>
+        <v>4524.0</v>
       </c>
       <c r="E443" s="7" t="s">
         <v>12</v>
@@ -13455,13 +13458,13 @@
         <v>66</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D444" s="6" t="n">
-        <v>31883.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E444" s="7" t="s">
         <v>12</v>
@@ -13484,13 +13487,13 @@
         <v>66</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>398394.0</v>
+        <v>9349.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13545,10 +13548,10 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>2197.0</v>
+        <v>1412.0</v>
       </c>
       <c r="E447" s="7" t="s">
         <v>12</v>
@@ -13574,16 +13577,16 @@
         <v>30</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>1503.0</v>
+        <v>94352.0</v>
       </c>
       <c r="E448" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F448" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F448" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G448" s="8" t="s">
         <v>66</v>
@@ -13603,16 +13606,16 @@
         <v>30</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D449" s="6" t="n">
-        <v>94352.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E449" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F449" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F449" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G449" s="8" t="s">
         <v>66</v>
@@ -13632,10 +13635,10 @@
         <v>30</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D450" s="6" t="n">
-        <v>1412.0</v>
+        <v>31883.0</v>
       </c>
       <c r="E450" s="7" t="s">
         <v>12</v>
@@ -13661,10 +13664,10 @@
         <v>13</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D451" s="6" t="n">
-        <v>47101.0</v>
+        <v>4957.0</v>
       </c>
       <c r="E451" s="7" t="s">
         <v>12</v>
@@ -13690,16 +13693,16 @@
         <v>13</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D452" s="6" t="n">
-        <v>872.0</v>
+        <v>78020.0</v>
       </c>
       <c r="E452" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F452" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F452" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G452" s="8" t="s">
         <v>67</v>
@@ -13719,10 +13722,10 @@
         <v>13</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D453" s="6" t="n">
-        <v>420532.0</v>
+        <v>2727.0</v>
       </c>
       <c r="E453" s="7" t="s">
         <v>12</v>
@@ -13748,10 +13751,10 @@
         <v>13</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D454" s="6" t="n">
-        <v>175.0</v>
+        <v>1522.0</v>
       </c>
       <c r="E454" s="7" t="s">
         <v>12</v>
@@ -13777,10 +13780,10 @@
         <v>13</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D455" s="6" t="n">
-        <v>57845.0</v>
+        <v>936.0</v>
       </c>
       <c r="E455" s="7" t="s">
         <v>12</v>
@@ -13806,16 +13809,16 @@
         <v>13</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D456" s="6" t="n">
-        <v>357258.0</v>
+        <v>792.0</v>
       </c>
       <c r="E456" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F456" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F456" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G456" s="8" t="s">
         <v>67</v>
@@ -13835,16 +13838,16 @@
         <v>13</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D457" s="6" t="n">
-        <v>4957.0</v>
+        <v>357258.0</v>
       </c>
       <c r="E457" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F457" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F457" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G457" s="8" t="s">
         <v>67</v>
@@ -13864,10 +13867,10 @@
         <v>13</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D458" s="6" t="n">
-        <v>936.0</v>
+        <v>57845.0</v>
       </c>
       <c r="E458" s="7" t="s">
         <v>12</v>
@@ -13893,10 +13896,10 @@
         <v>13</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D459" s="6" t="n">
-        <v>1522.0</v>
+        <v>175.0</v>
       </c>
       <c r="E459" s="7" t="s">
         <v>12</v>
@@ -13922,10 +13925,10 @@
         <v>13</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D460" s="6" t="n">
-        <v>2727.0</v>
+        <v>420532.0</v>
       </c>
       <c r="E460" s="7" t="s">
         <v>12</v>
@@ -13951,16 +13954,16 @@
         <v>13</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D461" s="6" t="n">
-        <v>78020.0</v>
+        <v>47101.0</v>
       </c>
       <c r="E461" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F461" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F461" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G461" s="8" t="s">
         <v>67</v>
@@ -14009,10 +14012,10 @@
         <v>13</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D463" s="6" t="n">
-        <v>792.0</v>
+        <v>872.0</v>
       </c>
       <c r="E463" s="7" t="s">
         <v>12</v>
@@ -14038,10 +14041,10 @@
         <v>13</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D464" s="6" t="n">
-        <v>64823.0</v>
+        <v>13052.0</v>
       </c>
       <c r="E464" s="7" t="s">
         <v>12</v>
@@ -14064,13 +14067,13 @@
         <v>67</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D465" s="6" t="n">
-        <v>13052.0</v>
+        <v>3363.0</v>
       </c>
       <c r="E465" s="7" t="s">
         <v>12</v>
@@ -14093,13 +14096,13 @@
         <v>67</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D466" s="6" t="n">
-        <v>74709.0</v>
+        <v>64823.0</v>
       </c>
       <c r="E466" s="7" t="s">
         <v>12</v>
@@ -14122,13 +14125,13 @@
         <v>67</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>6691.0</v>
+        <v>245670.0</v>
       </c>
       <c r="E467" s="7" t="s">
         <v>12</v>
@@ -14154,10 +14157,10 @@
         <v>10</v>
       </c>
       <c r="C468" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D468" s="6" t="n">
-        <v>245670.0</v>
+        <v>122605.0</v>
       </c>
       <c r="E468" s="7" t="s">
         <v>12</v>
@@ -14183,10 +14186,10 @@
         <v>10</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D469" s="6" t="n">
-        <v>122605.0</v>
+        <v>3174.0</v>
       </c>
       <c r="E469" s="7" t="s">
         <v>12</v>
@@ -14209,13 +14212,13 @@
         <v>67</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D470" s="6" t="n">
-        <v>3174.0</v>
+        <v>74709.0</v>
       </c>
       <c r="E470" s="7" t="s">
         <v>12</v>
@@ -14270,10 +14273,10 @@
         <v>30</v>
       </c>
       <c r="C472" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D472" s="6" t="n">
-        <v>3363.0</v>
+        <v>646.0</v>
       </c>
       <c r="E472" s="7" t="s">
         <v>12</v>
@@ -14299,10 +14302,10 @@
         <v>30</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D473" s="6" t="n">
-        <v>199283.0</v>
+        <v>8245.0</v>
       </c>
       <c r="E473" s="7" t="s">
         <v>12</v>
@@ -14328,10 +14331,10 @@
         <v>30</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D474" s="6" t="n">
-        <v>8245.0</v>
+        <v>207867.0</v>
       </c>
       <c r="E474" s="7" t="s">
         <v>12</v>
@@ -14357,10 +14360,10 @@
         <v>30</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D475" s="6" t="n">
-        <v>207867.0</v>
+        <v>6920.0</v>
       </c>
       <c r="E475" s="7" t="s">
         <v>12</v>
@@ -14383,13 +14386,13 @@
         <v>67</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D476" s="6" t="n">
-        <v>6920.0</v>
+        <v>6691.0</v>
       </c>
       <c r="E476" s="7" t="s">
         <v>12</v>
@@ -14415,10 +14418,10 @@
         <v>30</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D477" s="6" t="n">
-        <v>646.0</v>
+        <v>199283.0</v>
       </c>
       <c r="E477" s="7" t="s">
         <v>12</v>
@@ -14444,10 +14447,10 @@
         <v>13</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D478" s="6" t="n">
-        <v>158897.0</v>
+        <v>4818.0</v>
       </c>
       <c r="E478" s="7" t="s">
         <v>12</v>
@@ -14473,10 +14476,10 @@
         <v>13</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D479" s="6" t="n">
-        <v>3849.0</v>
+        <v>692.0</v>
       </c>
       <c r="E479" s="7" t="s">
         <v>12</v>
@@ -14502,10 +14505,10 @@
         <v>13</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D480" s="6" t="n">
-        <v>8962.0</v>
+        <v>3849.0</v>
       </c>
       <c r="E480" s="7" t="s">
         <v>12</v>
@@ -14531,10 +14534,10 @@
         <v>13</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D481" s="6" t="n">
-        <v>1252.0</v>
+        <v>8962.0</v>
       </c>
       <c r="E481" s="7" t="s">
         <v>12</v>
@@ -14560,10 +14563,10 @@
         <v>13</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D482" s="6" t="n">
-        <v>4818.0</v>
+        <v>1252.0</v>
       </c>
       <c r="E482" s="7" t="s">
         <v>12</v>
@@ -14589,16 +14592,16 @@
         <v>13</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D483" s="6" t="n">
-        <v>108623.0</v>
+        <v>4118.0</v>
       </c>
       <c r="E483" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F483" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F483" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G483" s="8" t="s">
         <v>68</v>
@@ -14618,10 +14621,10 @@
         <v>13</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D484" s="6" t="n">
-        <v>20516.0</v>
+        <v>158897.0</v>
       </c>
       <c r="E484" s="7" t="s">
         <v>12</v>
@@ -14647,10 +14650,10 @@
         <v>13</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D485" s="6" t="n">
-        <v>4118.0</v>
+        <v>20516.0</v>
       </c>
       <c r="E485" s="7" t="s">
         <v>12</v>
@@ -14763,16 +14766,16 @@
         <v>13</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D489" s="6" t="n">
-        <v>692.0</v>
+        <v>108623.0</v>
       </c>
       <c r="E489" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F489" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F489" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G489" s="8" t="s">
         <v>68</v>
@@ -14789,13 +14792,13 @@
         <v>68</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D490" s="6" t="n">
-        <v>13403.0</v>
+        <v>70327.0</v>
       </c>
       <c r="E490" s="7" t="s">
         <v>12</v>
@@ -14847,13 +14850,13 @@
         <v>68</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D492" s="6" t="n">
-        <v>54343.0</v>
+        <v>15334.0</v>
       </c>
       <c r="E492" s="7" t="s">
         <v>12</v>
@@ -14879,10 +14882,10 @@
         <v>13</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D493" s="6" t="n">
-        <v>70327.0</v>
+        <v>8296.0</v>
       </c>
       <c r="E493" s="7" t="s">
         <v>12</v>
@@ -14908,16 +14911,16 @@
         <v>10</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D494" s="6" t="n">
-        <v>296618.0</v>
+        <v>107735.0</v>
       </c>
       <c r="E494" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F494" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F494" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G494" s="8" t="s">
         <v>68</v>
@@ -14937,10 +14940,10 @@
         <v>10</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D495" s="6" t="n">
-        <v>170208.0</v>
+        <v>296618.0</v>
       </c>
       <c r="E495" s="7" t="s">
         <v>12</v>
@@ -14966,10 +14969,10 @@
         <v>10</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D496" s="6" t="n">
-        <v>15334.0</v>
+        <v>170208.0</v>
       </c>
       <c r="E496" s="7" t="s">
         <v>12</v>
@@ -14995,16 +14998,16 @@
         <v>10</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D497" s="6" t="n">
-        <v>107735.0</v>
+        <v>13403.0</v>
       </c>
       <c r="E497" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F497" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F497" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G497" s="8" t="s">
         <v>68</v>
@@ -15024,10 +15027,10 @@
         <v>30</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D498" s="6" t="n">
-        <v>4041.0</v>
+        <v>54343.0</v>
       </c>
       <c r="E498" s="7" t="s">
         <v>12</v>
@@ -15053,10 +15056,10 @@
         <v>30</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D499" s="6" t="n">
-        <v>206053.0</v>
+        <v>4041.0</v>
       </c>
       <c r="E499" s="7" t="s">
         <v>12</v>
@@ -15082,16 +15085,16 @@
         <v>30</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D500" s="6" t="n">
-        <v>5306.0</v>
+        <v>190807.0</v>
       </c>
       <c r="E500" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F500" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F500" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G500" s="8" t="s">
         <v>68</v>
@@ -15108,13 +15111,13 @@
         <v>68</v>
       </c>
       <c r="B501" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D501" s="6" t="n">
-        <v>14544.0</v>
+        <v>206053.0</v>
       </c>
       <c r="E501" s="7" t="s">
         <v>12</v>
@@ -15137,13 +15140,13 @@
         <v>68</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C502" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D502" s="6" t="n">
-        <v>8296.0</v>
+        <v>5306.0</v>
       </c>
       <c r="E502" s="7" t="s">
         <v>12</v>
@@ -15166,19 +15169,19 @@
         <v>68</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D503" s="6" t="n">
-        <v>190807.0</v>
+        <v>14544.0</v>
       </c>
       <c r="E503" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F503" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F503" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G503" s="8" t="s">
         <v>68</v>
@@ -15285,10 +15288,10 @@
         <v>13</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D507" s="6" t="n">
-        <v>123.0</v>
+        <v>62084.0</v>
       </c>
       <c r="E507" s="7" t="s">
         <v>12</v>
@@ -15314,10 +15317,10 @@
         <v>13</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D508" s="6" t="n">
-        <v>5181.0</v>
+        <v>123.0</v>
       </c>
       <c r="E508" s="7" t="s">
         <v>12</v>
@@ -15343,16 +15346,16 @@
         <v>13</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D509" s="6" t="n">
-        <v>4716.0</v>
+        <v>908897.0</v>
       </c>
       <c r="E509" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F509" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F509" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G509" s="8" t="s">
         <v>69</v>
@@ -15372,10 +15375,10 @@
         <v>13</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D510" s="6" t="n">
-        <v>201113.0</v>
+        <v>4716.0</v>
       </c>
       <c r="E510" s="7" t="s">
         <v>12</v>
@@ -15401,10 +15404,10 @@
         <v>13</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D511" s="6" t="n">
-        <v>18261.0</v>
+        <v>30675.0</v>
       </c>
       <c r="E511" s="7" t="s">
         <v>12</v>
@@ -15430,10 +15433,10 @@
         <v>13</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D512" s="6" t="n">
-        <v>1519.0</v>
+        <v>201113.0</v>
       </c>
       <c r="E512" s="7" t="s">
         <v>12</v>
@@ -15459,16 +15462,16 @@
         <v>13</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D513" s="6" t="n">
-        <v>908897.0</v>
+        <v>5181.0</v>
       </c>
       <c r="E513" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F513" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F513" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G513" s="8" t="s">
         <v>69</v>
@@ -15488,10 +15491,10 @@
         <v>13</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D514" s="6" t="n">
-        <v>30675.0</v>
+        <v>18261.0</v>
       </c>
       <c r="E514" s="7" t="s">
         <v>12</v>
@@ -15517,10 +15520,10 @@
         <v>13</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D515" s="6" t="n">
-        <v>2898.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E515" s="7" t="s">
         <v>12</v>
@@ -15546,10 +15549,10 @@
         <v>13</v>
       </c>
       <c r="C516" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D516" s="6" t="n">
-        <v>62084.0</v>
+        <v>2898.0</v>
       </c>
       <c r="E516" s="7" t="s">
         <v>12</v>
@@ -15572,13 +15575,13 @@
         <v>69</v>
       </c>
       <c r="B517" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D517" s="6" t="n">
-        <v>12907.0</v>
+        <v>1408.0</v>
       </c>
       <c r="E517" s="7" t="s">
         <v>12</v>
@@ -15601,13 +15604,13 @@
         <v>69</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D518" s="6" t="n">
-        <v>1408.0</v>
+        <v>12907.0</v>
       </c>
       <c r="E518" s="7" t="s">
         <v>12</v>
@@ -15630,19 +15633,19 @@
         <v>69</v>
       </c>
       <c r="B519" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D519" s="6" t="n">
-        <v>366304.0</v>
+        <v>42853.0</v>
       </c>
       <c r="E519" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F519" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F519" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G519" s="8" t="s">
         <v>69</v>
@@ -15659,19 +15662,19 @@
         <v>69</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D520" s="6" t="n">
-        <v>162523.0</v>
+        <v>366304.0</v>
       </c>
       <c r="E520" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F520" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F520" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G520" s="8" t="s">
         <v>69</v>
@@ -15691,10 +15694,10 @@
         <v>10</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D521" s="6" t="n">
-        <v>372344.0</v>
+        <v>162695.0</v>
       </c>
       <c r="E521" s="7" t="s">
         <v>12</v>
@@ -15720,10 +15723,10 @@
         <v>10</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D522" s="6" t="n">
-        <v>162497.0</v>
+        <v>44.0</v>
       </c>
       <c r="E522" s="7" t="s">
         <v>12</v>
@@ -15749,10 +15752,10 @@
         <v>10</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D523" s="6" t="n">
-        <v>42853.0</v>
+        <v>372386.0</v>
       </c>
       <c r="E523" s="7" t="s">
         <v>12</v>
@@ -15778,10 +15781,10 @@
         <v>10</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D524" s="6" t="n">
-        <v>44.0</v>
+        <v>162639.0</v>
       </c>
       <c r="E524" s="7" t="s">
         <v>12</v>
@@ -15981,10 +15984,10 @@
         <v>13</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D531" s="6" t="n">
-        <v>113002.0</v>
+        <v>133084.0</v>
       </c>
       <c r="E531" s="7" t="s">
         <v>12</v>
@@ -16010,10 +16013,10 @@
         <v>13</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D532" s="6" t="n">
-        <v>4708.0</v>
+        <v>2394.0</v>
       </c>
       <c r="E532" s="7" t="s">
         <v>12</v>
@@ -16039,10 +16042,10 @@
         <v>13</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D533" s="6" t="n">
-        <v>258716.0</v>
+        <v>8250.0</v>
       </c>
       <c r="E533" s="7" t="s">
         <v>12</v>
@@ -16068,10 +16071,10 @@
         <v>13</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D534" s="6" t="n">
-        <v>658.0</v>
+        <v>249.0</v>
       </c>
       <c r="E534" s="7" t="s">
         <v>12</v>
@@ -16097,10 +16100,10 @@
         <v>13</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D535" s="6" t="n">
-        <v>49.0</v>
+        <v>11404.0</v>
       </c>
       <c r="E535" s="7" t="s">
         <v>12</v>
@@ -16126,10 +16129,10 @@
         <v>13</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D536" s="6" t="n">
-        <v>311.0</v>
+        <v>712.0</v>
       </c>
       <c r="E536" s="7" t="s">
         <v>12</v>
@@ -16155,10 +16158,10 @@
         <v>13</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D537" s="6" t="n">
-        <v>95311.0</v>
+        <v>36834.0</v>
       </c>
       <c r="E537" s="7" t="s">
         <v>12</v>
@@ -16184,10 +16187,10 @@
         <v>13</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D538" s="6" t="n">
-        <v>6262.0</v>
+        <v>1287.0</v>
       </c>
       <c r="E538" s="7" t="s">
         <v>12</v>
@@ -16213,10 +16216,10 @@
         <v>13</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D539" s="6" t="n">
-        <v>249.0</v>
+        <v>658.0</v>
       </c>
       <c r="E539" s="7" t="s">
         <v>12</v>
@@ -16242,10 +16245,10 @@
         <v>13</v>
       </c>
       <c r="C540" s="5" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D540" s="6" t="n">
-        <v>7224.0</v>
+        <v>2797.0</v>
       </c>
       <c r="E540" s="7" t="s">
         <v>12</v>
@@ -16268,13 +16271,13 @@
         <v>70</v>
       </c>
       <c r="B541" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D541" s="6" t="n">
-        <v>184.0</v>
+        <v>349507.0</v>
       </c>
       <c r="E541" s="7" t="s">
         <v>12</v>
@@ -16300,10 +16303,10 @@
         <v>13</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D542" s="6" t="n">
-        <v>98845.0</v>
+        <v>6031.0</v>
       </c>
       <c r="E542" s="7" t="s">
         <v>12</v>
@@ -16329,10 +16332,10 @@
         <v>13</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D543" s="6" t="n">
-        <v>38218.0</v>
+        <v>178087.0</v>
       </c>
       <c r="E543" s="7" t="s">
         <v>12</v>
@@ -16358,10 +16361,10 @@
         <v>13</v>
       </c>
       <c r="C544" s="5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D544" s="6" t="n">
-        <v>12959.0</v>
+        <v>155449.0</v>
       </c>
       <c r="E544" s="7" t="s">
         <v>12</v>
@@ -16384,13 +16387,13 @@
         <v>70</v>
       </c>
       <c r="B545" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D545" s="6" t="n">
-        <v>68500.0</v>
+        <v>17644.0</v>
       </c>
       <c r="E545" s="7" t="s">
         <v>12</v>
@@ -16413,13 +16416,13 @@
         <v>70</v>
       </c>
       <c r="B546" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C546" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D546" s="6" t="n">
-        <v>128978.0</v>
+        <v>61145.0</v>
       </c>
       <c r="E546" s="7" t="s">
         <v>12</v>
@@ -16445,10 +16448,10 @@
         <v>30</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D547" s="6" t="n">
-        <v>8609.0</v>
+        <v>97563.0</v>
       </c>
       <c r="E547" s="7" t="s">
         <v>12</v>
@@ -16471,13 +16474,13 @@
         <v>70</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C548" s="5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D548" s="6" t="n">
-        <v>50593.0</v>
+        <v>833.0</v>
       </c>
       <c r="E548" s="7" t="s">
         <v>12</v>
@@ -16503,10 +16506,10 @@
         <v>10</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D549" s="6" t="n">
-        <v>4759.0</v>
+        <v>49096.0</v>
       </c>
       <c r="E549" s="7" t="s">
         <v>12</v>
@@ -16532,10 +16535,10 @@
         <v>10</v>
       </c>
       <c r="C550" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D550" s="6" t="n">
-        <v>49217.0</v>
+        <v>445516.0</v>
       </c>
       <c r="E550" s="7" t="s">
         <v>12</v>
@@ -16561,10 +16564,10 @@
         <v>10</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D551" s="6" t="n">
-        <v>207446.0</v>
+        <v>5446.0</v>
       </c>
       <c r="E551" s="7" t="s">
         <v>12</v>
@@ -16590,10 +16593,10 @@
         <v>10</v>
       </c>
       <c r="C552" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D552" s="6" t="n">
-        <v>36286.0</v>
+        <v>184.0</v>
       </c>
       <c r="E552" s="7" t="s">
         <v>12</v>
@@ -16616,13 +16619,13 @@
         <v>70</v>
       </c>
       <c r="B553" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D553" s="6" t="n">
-        <v>712.0</v>
+        <v>68846.0</v>
       </c>
       <c r="E553" s="7" t="s">
         <v>12</v>
@@ -16637,6 +16640,818 @@
         <v>70</v>
       </c>
       <c r="I553" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B554" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C554" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D554" s="6" t="n">
+        <v>8609.0</v>
+      </c>
+      <c r="E554" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F554" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G554" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H554" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I554" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B555" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D555" s="6" t="n">
+        <v>9668.0</v>
+      </c>
+      <c r="E555" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F555" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G555" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H555" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I555" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B556" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C556" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D556" s="6" t="n">
+        <v>167261.0</v>
+      </c>
+      <c r="E556" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F556" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G556" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H556" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I556" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B557" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C557" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D557" s="6" t="n">
+        <v>16365.0</v>
+      </c>
+      <c r="E557" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F557" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G557" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H557" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I557" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B558" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D558" s="6" t="n">
+        <v>146605.0</v>
+      </c>
+      <c r="E558" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F558" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G558" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H558" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I558" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B559" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D559" s="6" t="n">
+        <v>24743.0</v>
+      </c>
+      <c r="E559" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F559" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G559" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H559" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I559" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B560" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D560" s="6" t="n">
+        <v>17014.0</v>
+      </c>
+      <c r="E560" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F560" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G560" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H560" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I560" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B561" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D561" s="6" t="n">
+        <v>37838.0</v>
+      </c>
+      <c r="E561" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F561" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G561" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H561" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I561" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B562" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C562" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D562" s="6" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="E562" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F562" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G562" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H562" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I562" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B563" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D563" s="6" t="n">
+        <v>24394.0</v>
+      </c>
+      <c r="E563" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F563" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G563" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H563" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I563" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B564" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D564" s="6" t="n">
+        <v>62902.0</v>
+      </c>
+      <c r="E564" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F564" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G564" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H564" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I564" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B565" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D565" s="6" t="n">
+        <v>1163.0</v>
+      </c>
+      <c r="E565" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F565" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G565" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H565" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I565" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B566" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C566" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D566" s="6" t="n">
+        <v>25799.0</v>
+      </c>
+      <c r="E566" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F566" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G566" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H566" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I566" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B567" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C567" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D567" s="6" t="n">
+        <v>44867.0</v>
+      </c>
+      <c r="E567" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F567" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G567" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H567" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I567" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B568" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C568" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D568" s="6" t="n">
+        <v>14066.0</v>
+      </c>
+      <c r="E568" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F568" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G568" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H568" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I568" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B569" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D569" s="6" t="n">
+        <v>3016.0</v>
+      </c>
+      <c r="E569" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F569" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G569" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H569" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I569" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B570" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C570" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D570" s="6" t="n">
+        <v>3681.0</v>
+      </c>
+      <c r="E570" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F570" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G570" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H570" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I570" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B571" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D571" s="6" t="n">
+        <v>2199.0</v>
+      </c>
+      <c r="E571" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F571" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G571" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H571" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I571" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B572" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D572" s="6" t="n">
+        <v>8074.0</v>
+      </c>
+      <c r="E572" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F572" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G572" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H572" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I572" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B573" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D573" s="6" t="n">
+        <v>95045.0</v>
+      </c>
+      <c r="E573" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F573" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G573" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H573" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I573" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B574" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C574" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D574" s="6" t="n">
+        <v>7943.0</v>
+      </c>
+      <c r="E574" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F574" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G574" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H574" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I574" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B575" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D575" s="6" t="n">
+        <v>65641.0</v>
+      </c>
+      <c r="E575" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F575" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G575" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H575" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I575" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B576" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C576" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D576" s="6" t="n">
+        <v>3492.0</v>
+      </c>
+      <c r="E576" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F576" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G576" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H576" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I576" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B577" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D577" s="6" t="n">
+        <v>21702.0</v>
+      </c>
+      <c r="E577" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F577" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G577" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H577" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I577" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B578" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C578" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D578" s="6" t="n">
+        <v>11782.0</v>
+      </c>
+      <c r="E578" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F578" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G578" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H578" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I578" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B579" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C579" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D579" s="6" t="n">
+        <v>116078.0</v>
+      </c>
+      <c r="E579" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F579" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G579" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H579" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I579" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B580" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C580" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D580" s="6" t="n">
+        <v>33155.0</v>
+      </c>
+      <c r="E580" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F580" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G580" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H580" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I580" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B581" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C581" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D581" s="6" t="n">
+        <v>296328.0</v>
+      </c>
+      <c r="E581" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F581" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G581" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H581" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I581" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4573" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4808" uniqueCount="73">
   <si>
     <t>Ngày</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
   </si>
 </sst>
 </file>
@@ -591,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I581"/>
+  <dimension ref="A1:I611"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -4587,10 +4590,10 @@
         <v>13</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>2761.0</v>
+        <v>9757.0</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>12</v>
@@ -4616,10 +4619,10 @@
         <v>13</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>7072.0</v>
+        <v>2761.0</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>12</v>
@@ -4645,10 +4648,10 @@
         <v>13</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>9789.0</v>
+        <v>7072.0</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
@@ -4674,10 +4677,10 @@
         <v>13</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>43267.0</v>
+        <v>9789.0</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>12</v>
@@ -4703,10 +4706,10 @@
         <v>13</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>38461.0</v>
+        <v>312933.0</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>12</v>
@@ -4906,10 +4909,10 @@
         <v>13</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>9757.0</v>
+        <v>38461.0</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>12</v>
@@ -4932,13 +4935,13 @@
         <v>55</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>13050.0</v>
+        <v>43267.0</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>12</v>
@@ -4964,10 +4967,10 @@
         <v>13</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>312933.0</v>
+        <v>325679.0</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>12</v>
@@ -4990,13 +4993,13 @@
         <v>55</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>1746.0</v>
+        <v>13050.0</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>12</v>
@@ -5022,10 +5025,10 @@
         <v>13</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>325679.0</v>
+        <v>21698.0</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>12</v>
@@ -5225,10 +5228,10 @@
         <v>30</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>112939.0</v>
+        <v>152007.0</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>12</v>
@@ -5254,10 +5257,10 @@
         <v>30</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>36540.0</v>
+        <v>112939.0</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>12</v>
@@ -5283,10 +5286,10 @@
         <v>30</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>31845.0</v>
+        <v>36540.0</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>12</v>
@@ -5309,13 +5312,13 @@
         <v>55</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>21698.0</v>
+        <v>31845.0</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>12</v>
@@ -5338,13 +5341,13 @@
         <v>55</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>152007.0</v>
+        <v>1746.0</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>12</v>
@@ -6530,16 +6533,16 @@
         <v>30</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>264473.0</v>
+        <v>9109.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F205" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>57</v>
@@ -6559,10 +6562,10 @@
         <v>30</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>9109.0</v>
+        <v>210.0</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>12</v>
@@ -6588,10 +6591,10 @@
         <v>30</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>210.0</v>
+        <v>28338.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6617,16 +6620,16 @@
         <v>30</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>28338.0</v>
+        <v>264473.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F208" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F208" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>57</v>
@@ -6675,10 +6678,10 @@
         <v>30</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>49095.0</v>
+        <v>83141.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6701,13 +6704,13 @@
         <v>57</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>83141.0</v>
+        <v>43423.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6733,10 +6736,10 @@
         <v>13</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>43423.0</v>
+        <v>1573.0</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>12</v>
@@ -6762,10 +6765,10 @@
         <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>1573.0</v>
+        <v>28802.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6788,13 +6791,13 @@
         <v>57</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>28802.0</v>
+        <v>49095.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6878,10 +6881,10 @@
         <v>13</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>2938.0</v>
+        <v>400774.0</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>12</v>
@@ -6965,16 +6968,16 @@
         <v>13</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>1087.0</v>
+        <v>8125.0</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F220" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F220" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>58</v>
@@ -7052,16 +7055,16 @@
         <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>8125.0</v>
+        <v>570723.0</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F223" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>58</v>
@@ -7081,10 +7084,10 @@
         <v>13</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>400774.0</v>
+        <v>17602.0</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>12</v>
@@ -7110,16 +7113,16 @@
         <v>13</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>570723.0</v>
+        <v>1087.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F225" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>58</v>
@@ -7139,10 +7142,10 @@
         <v>13</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>17602.0</v>
+        <v>13953.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7168,10 +7171,10 @@
         <v>13</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>13953.0</v>
+        <v>2938.0</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
@@ -7194,13 +7197,13 @@
         <v>58</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>37213.0</v>
+        <v>196510.0</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>12</v>
@@ -7223,13 +7226,13 @@
         <v>58</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>196510.0</v>
+        <v>8052.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7252,13 +7255,13 @@
         <v>58</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>8052.0</v>
+        <v>52019.0</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>12</v>
@@ -7281,13 +7284,13 @@
         <v>58</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>52019.0</v>
+        <v>2847.0</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>12</v>
@@ -7313,10 +7316,10 @@
         <v>10</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>74089.0</v>
+        <v>586581.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>12</v>
@@ -7342,10 +7345,10 @@
         <v>10</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>2847.0</v>
+        <v>37213.0</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>12</v>
@@ -7371,16 +7374,16 @@
         <v>10</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>586581.0</v>
+        <v>65877.0</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F234" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F234" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>58</v>
@@ -7400,16 +7403,16 @@
         <v>10</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>65877.0</v>
+        <v>74089.0</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F235" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G235" s="8" t="s">
         <v>58</v>
@@ -7458,10 +7461,10 @@
         <v>30</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>515691.0</v>
+        <v>61111.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7487,10 +7490,10 @@
         <v>30</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>61111.0</v>
+        <v>77697.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7516,10 +7519,10 @@
         <v>30</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>77697.0</v>
+        <v>7771.0</v>
       </c>
       <c r="E239" s="7" t="s">
         <v>12</v>
@@ -7545,16 +7548,16 @@
         <v>30</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>7771.0</v>
+        <v>118765.0</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F240" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F240" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G240" s="8" t="s">
         <v>58</v>
@@ -7574,16 +7577,16 @@
         <v>30</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>118765.0</v>
+        <v>515691.0</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F241" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>58</v>
@@ -7748,16 +7751,16 @@
         <v>13</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>371730.0</v>
+        <v>33073.0</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F247" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>59</v>
@@ -7864,10 +7867,10 @@
         <v>13</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>33073.0</v>
+        <v>3296.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>12</v>
@@ -7893,10 +7896,10 @@
         <v>13</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>3296.0</v>
+        <v>160.0</v>
       </c>
       <c r="E252" s="7" t="s">
         <v>12</v>
@@ -7922,10 +7925,10 @@
         <v>13</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>160.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E253" s="7" t="s">
         <v>12</v>
@@ -7980,16 +7983,16 @@
         <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>5458.0</v>
+        <v>371730.0</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F255" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F255" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G255" s="8" t="s">
         <v>59</v>
@@ -8035,13 +8038,13 @@
         <v>59</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>790.0</v>
+        <v>302914.0</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>12</v>
@@ -8064,13 +8067,13 @@
         <v>59</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>27683.0</v>
+        <v>31570.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8096,10 +8099,10 @@
         <v>10</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>31570.0</v>
+        <v>566118.0</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>12</v>
@@ -8125,10 +8128,10 @@
         <v>10</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>566118.0</v>
+        <v>25241.0</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>12</v>
@@ -8154,10 +8157,10 @@
         <v>10</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>25241.0</v>
+        <v>32891.0</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>12</v>
@@ -8183,10 +8186,10 @@
         <v>10</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>32891.0</v>
+        <v>790.0</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>12</v>
@@ -8241,10 +8244,10 @@
         <v>30</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>302914.0</v>
+        <v>10553.0</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>12</v>
@@ -8270,10 +8273,10 @@
         <v>30</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>150.0</v>
+        <v>160020.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8299,10 +8302,10 @@
         <v>30</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>6744.0</v>
+        <v>150.0</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>12</v>
@@ -8328,10 +8331,10 @@
         <v>30</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>47292.0</v>
+        <v>27683.0</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>12</v>
@@ -8386,10 +8389,10 @@
         <v>30</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>160020.0</v>
+        <v>6744.0</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>12</v>
@@ -8415,10 +8418,10 @@
         <v>30</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>10553.0</v>
+        <v>47292.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8589,10 +8592,10 @@
         <v>13</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D276" s="6" t="n">
-        <v>220465.0</v>
+        <v>26381.0</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>12</v>
@@ -8618,10 +8621,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>170.0</v>
+        <v>115.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8676,10 +8679,10 @@
         <v>13</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D279" s="6" t="n">
-        <v>115.0</v>
+        <v>3979.0</v>
       </c>
       <c r="E279" s="7" t="s">
         <v>12</v>
@@ -8705,10 +8708,10 @@
         <v>13</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>3979.0</v>
+        <v>96105.0</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>12</v>
@@ -8734,10 +8737,10 @@
         <v>13</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>96105.0</v>
+        <v>38472.0</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>12</v>
@@ -8763,10 +8766,10 @@
         <v>13</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>38472.0</v>
+        <v>2731.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8792,10 +8795,10 @@
         <v>13</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>2731.0</v>
+        <v>35463.0</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>12</v>
@@ -8821,10 +8824,10 @@
         <v>13</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>35463.0</v>
+        <v>170.0</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>12</v>
@@ -8850,10 +8853,10 @@
         <v>13</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>26381.0</v>
+        <v>20130.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8879,16 +8882,16 @@
         <v>13</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>168847.0</v>
+        <v>220465.0</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F286" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G286" s="8" t="s">
         <v>60</v>
@@ -8934,13 +8937,13 @@
         <v>60</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>20130.0</v>
+        <v>1308.0</v>
       </c>
       <c r="E288" s="7" t="s">
         <v>12</v>
@@ -8963,19 +8966,19 @@
         <v>60</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>1308.0</v>
+        <v>168847.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F289" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F289" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>60</v>
@@ -9311,13 +9314,13 @@
         <v>61</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>4517.0</v>
+        <v>1798.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9430,16 +9433,16 @@
         <v>13</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>414833.0</v>
+        <v>4517.0</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F305" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G305" s="8" t="s">
         <v>61</v>
@@ -9459,10 +9462,10 @@
         <v>13</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>10887.0</v>
+        <v>18161.0</v>
       </c>
       <c r="E306" s="7" t="s">
         <v>12</v>
@@ -9488,10 +9491,10 @@
         <v>13</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>49827.0</v>
+        <v>10887.0</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>12</v>
@@ -9517,10 +9520,10 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>18161.0</v>
+        <v>49827.0</v>
       </c>
       <c r="E308" s="7" t="s">
         <v>12</v>
@@ -9546,10 +9549,10 @@
         <v>13</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>5125.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>12</v>
@@ -9572,19 +9575,19 @@
         <v>61</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>1798.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E310" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F310" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F310" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G310" s="8" t="s">
         <v>61</v>
@@ -9604,10 +9607,10 @@
         <v>13</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>49079.0</v>
+        <v>5125.0</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>12</v>
@@ -9633,10 +9636,10 @@
         <v>13</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>16117.0</v>
+        <v>49079.0</v>
       </c>
       <c r="E312" s="7" t="s">
         <v>12</v>
@@ -9659,13 +9662,13 @@
         <v>61</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>3372.0</v>
+        <v>2152.0</v>
       </c>
       <c r="E313" s="7" t="s">
         <v>12</v>
@@ -9688,13 +9691,13 @@
         <v>61</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D314" s="6" t="n">
-        <v>2153.0</v>
+        <v>3372.0</v>
       </c>
       <c r="E314" s="7" t="s">
         <v>12</v>
@@ -9720,10 +9723,10 @@
         <v>10</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D315" s="6" t="n">
-        <v>7578.0</v>
+        <v>2153.0</v>
       </c>
       <c r="E315" s="7" t="s">
         <v>12</v>
@@ -9746,19 +9749,19 @@
         <v>61</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>191.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F316" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F316" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G316" s="8" t="s">
         <v>61</v>
@@ -9778,10 +9781,10 @@
         <v>10</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D317" s="6" t="n">
-        <v>19353.0</v>
+        <v>7578.0</v>
       </c>
       <c r="E317" s="7" t="s">
         <v>12</v>
@@ -9807,10 +9810,10 @@
         <v>10</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D318" s="6" t="n">
-        <v>25684.0</v>
+        <v>560394.0</v>
       </c>
       <c r="E318" s="7" t="s">
         <v>16</v>
@@ -9836,16 +9839,16 @@
         <v>10</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D319" s="6" t="n">
-        <v>560394.0</v>
+        <v>19353.0</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F319" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G319" s="8" t="s">
         <v>61</v>
@@ -9862,13 +9865,13 @@
         <v>61</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>3475.0</v>
+        <v>191.0</v>
       </c>
       <c r="E320" s="7" t="s">
         <v>12</v>
@@ -9894,10 +9897,10 @@
         <v>10</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D321" s="6" t="n">
-        <v>2152.0</v>
+        <v>3475.0</v>
       </c>
       <c r="E321" s="7" t="s">
         <v>12</v>
@@ -9923,10 +9926,10 @@
         <v>30</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>400544.0</v>
+        <v>17918.0</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>12</v>
@@ -9952,10 +9955,10 @@
         <v>30</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>17918.0</v>
+        <v>7822.0</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>12</v>
@@ -9981,10 +9984,10 @@
         <v>30</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>7822.0</v>
+        <v>32300.0</v>
       </c>
       <c r="E324" s="7" t="s">
         <v>12</v>
@@ -10010,10 +10013,10 @@
         <v>30</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D325" s="6" t="n">
-        <v>32300.0</v>
+        <v>400544.0</v>
       </c>
       <c r="E325" s="7" t="s">
         <v>12</v>
@@ -10039,16 +10042,16 @@
         <v>13</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>288195.0</v>
+        <v>240445.0</v>
       </c>
       <c r="E326" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F326" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G326" s="8" t="s">
         <v>62</v>
@@ -10068,16 +10071,16 @@
         <v>13</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D327" s="6" t="n">
-        <v>1049.0</v>
+        <v>288195.0</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F327" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F327" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G327" s="8" t="s">
         <v>62</v>
@@ -10097,10 +10100,10 @@
         <v>13</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D328" s="6" t="n">
-        <v>373443.0</v>
+        <v>1049.0</v>
       </c>
       <c r="E328" s="7" t="s">
         <v>12</v>
@@ -10126,16 +10129,16 @@
         <v>13</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D329" s="6" t="n">
-        <v>177177.0</v>
+        <v>373443.0</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F329" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>62</v>
@@ -10155,16 +10158,16 @@
         <v>13</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D330" s="6" t="n">
-        <v>15369.0</v>
+        <v>177177.0</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F330" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F330" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G330" s="8" t="s">
         <v>62</v>
@@ -10184,10 +10187,10 @@
         <v>13</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D331" s="6" t="n">
-        <v>25040.0</v>
+        <v>15369.0</v>
       </c>
       <c r="E331" s="7" t="s">
         <v>12</v>
@@ -10213,10 +10216,10 @@
         <v>13</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D332" s="6" t="n">
-        <v>16196.0</v>
+        <v>25040.0</v>
       </c>
       <c r="E332" s="7" t="s">
         <v>12</v>
@@ -10242,10 +10245,10 @@
         <v>13</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D333" s="6" t="n">
-        <v>28904.0</v>
+        <v>16196.0</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>12</v>
@@ -10329,10 +10332,10 @@
         <v>13</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>39009.0</v>
+        <v>28904.0</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>12</v>
@@ -10358,16 +10361,16 @@
         <v>13</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D337" s="6" t="n">
-        <v>240445.0</v>
+        <v>39009.0</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F337" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F337" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G337" s="8" t="s">
         <v>62</v>
@@ -10384,13 +10387,13 @@
         <v>62</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>21302.0</v>
+        <v>38261.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10413,13 +10416,13 @@
         <v>62</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>182371.0</v>
+        <v>866.0</v>
       </c>
       <c r="E339" s="7" t="s">
         <v>12</v>
@@ -10445,10 +10448,10 @@
         <v>30</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D340" s="6" t="n">
-        <v>177268.0</v>
+        <v>256566.0</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>12</v>
@@ -10474,10 +10477,10 @@
         <v>30</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D341" s="6" t="n">
-        <v>15943.0</v>
+        <v>6148.0</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>12</v>
@@ -10503,10 +10506,10 @@
         <v>30</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>38261.0</v>
+        <v>1449.0</v>
       </c>
       <c r="E342" s="7" t="s">
         <v>12</v>
@@ -10529,19 +10532,19 @@
         <v>62</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D343" s="6" t="n">
-        <v>1449.0</v>
+        <v>488224.0</v>
       </c>
       <c r="E343" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F343" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F343" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G343" s="8" t="s">
         <v>62</v>
@@ -10561,10 +10564,10 @@
         <v>30</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D344" s="6" t="n">
-        <v>6148.0</v>
+        <v>15943.0</v>
       </c>
       <c r="E344" s="7" t="s">
         <v>12</v>
@@ -10590,10 +10593,10 @@
         <v>30</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D345" s="6" t="n">
-        <v>256566.0</v>
+        <v>177268.0</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>12</v>
@@ -10616,19 +10619,19 @@
         <v>62</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>488224.0</v>
+        <v>182371.0</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F346" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F346" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G346" s="8" t="s">
         <v>62</v>
@@ -10648,10 +10651,10 @@
         <v>13</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D347" s="6" t="n">
-        <v>866.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E347" s="7" t="s">
         <v>12</v>
@@ -10677,10 +10680,10 @@
         <v>13</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D348" s="6" t="n">
-        <v>14390.0</v>
+        <v>69412.0</v>
       </c>
       <c r="E348" s="7" t="s">
         <v>12</v>
@@ -10706,10 +10709,10 @@
         <v>13</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D349" s="6" t="n">
-        <v>9380.0</v>
+        <v>7560.0</v>
       </c>
       <c r="E349" s="7" t="s">
         <v>12</v>
@@ -10735,10 +10738,10 @@
         <v>13</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D350" s="6" t="n">
-        <v>185.0</v>
+        <v>805776.0</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>12</v>
@@ -10764,10 +10767,10 @@
         <v>13</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D351" s="6" t="n">
-        <v>7510.0</v>
+        <v>14289.0</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>12</v>
@@ -10793,10 +10796,10 @@
         <v>13</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D352" s="6" t="n">
-        <v>15854.0</v>
+        <v>62866.0</v>
       </c>
       <c r="E352" s="7" t="s">
         <v>12</v>
@@ -10851,10 +10854,10 @@
         <v>13</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D354" s="6" t="n">
-        <v>62866.0</v>
+        <v>14390.0</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>12</v>
@@ -10880,10 +10883,10 @@
         <v>13</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D355" s="6" t="n">
-        <v>14289.0</v>
+        <v>7510.0</v>
       </c>
       <c r="E355" s="7" t="s">
         <v>12</v>
@@ -10909,10 +10912,10 @@
         <v>13</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D356" s="6" t="n">
-        <v>805776.0</v>
+        <v>185.0</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>12</v>
@@ -10938,10 +10941,10 @@
         <v>13</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D357" s="6" t="n">
-        <v>7560.0</v>
+        <v>9380.0</v>
       </c>
       <c r="E357" s="7" t="s">
         <v>12</v>
@@ -10993,19 +10996,19 @@
         <v>63</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>69412.0</v>
+        <v>96851.0</v>
       </c>
       <c r="E359" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F359" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F359" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G359" s="8" t="s">
         <v>63</v>
@@ -11022,13 +11025,13 @@
         <v>63</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D360" s="6" t="n">
-        <v>42515.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>12</v>
@@ -11109,19 +11112,19 @@
         <v>63</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D363" s="6" t="n">
-        <v>419250.0</v>
+        <v>42515.0</v>
       </c>
       <c r="E363" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F363" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G363" s="8" t="s">
         <v>63</v>
@@ -11141,16 +11144,16 @@
         <v>10</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D364" s="6" t="n">
-        <v>96851.0</v>
+        <v>419250.0</v>
       </c>
       <c r="E364" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F364" s="7" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>63</v>
@@ -11373,10 +11376,10 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>3681.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E372" s="7" t="s">
         <v>12</v>
@@ -11489,10 +11492,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>91385.0</v>
+        <v>228939.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11518,10 +11521,10 @@
         <v>13</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D377" s="6" t="n">
-        <v>228939.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E377" s="7" t="s">
         <v>12</v>
@@ -11547,10 +11550,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>5337.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11576,10 +11579,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>3142.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11605,10 +11608,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>102275.0</v>
+        <v>4119.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11634,10 +11637,10 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>96052.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E381" s="7" t="s">
         <v>12</v>
@@ -11663,10 +11666,10 @@
         <v>13</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D382" s="6" t="n">
-        <v>4119.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E382" s="7" t="s">
         <v>12</v>
@@ -11689,13 +11692,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>8817.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11721,10 +11724,10 @@
         <v>10</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>14304.0</v>
+        <v>3572.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11750,16 +11753,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D385" s="6" t="n">
-        <v>69259.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E385" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F385" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F385" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G385" s="8" t="s">
         <v>64</v>
@@ -11776,13 +11779,13 @@
         <v>64</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D386" s="6" t="n">
-        <v>25352.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E386" s="7" t="s">
         <v>12</v>
@@ -11892,13 +11895,13 @@
         <v>64</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>3572.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E390" s="7" t="s">
         <v>12</v>
@@ -11924,10 +11927,10 @@
         <v>30</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D391" s="6" t="n">
-        <v>7380.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E391" s="7" t="s">
         <v>12</v>
@@ -11953,10 +11956,10 @@
         <v>30</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D392" s="6" t="n">
-        <v>13204.0</v>
+        <v>7380.0</v>
       </c>
       <c r="E392" s="7" t="s">
         <v>12</v>
@@ -11982,10 +11985,10 @@
         <v>30</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D393" s="6" t="n">
-        <v>42128.0</v>
+        <v>13204.0</v>
       </c>
       <c r="E393" s="7" t="s">
         <v>12</v>
@@ -12011,10 +12014,10 @@
         <v>30</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D394" s="6" t="n">
-        <v>12024.0</v>
+        <v>42128.0</v>
       </c>
       <c r="E394" s="7" t="s">
         <v>12</v>
@@ -12040,16 +12043,16 @@
         <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>252681.0</v>
+        <v>12024.0</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F395" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F395" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G395" s="8" t="s">
         <v>64</v>
@@ -12098,10 +12101,10 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D397" s="6" t="n">
-        <v>5282.0</v>
+        <v>2360.0</v>
       </c>
       <c r="E397" s="7" t="s">
         <v>12</v>
@@ -12127,10 +12130,10 @@
         <v>13</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D398" s="6" t="n">
-        <v>5080.0</v>
+        <v>5282.0</v>
       </c>
       <c r="E398" s="7" t="s">
         <v>12</v>
@@ -12214,16 +12217,16 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>9750.0</v>
+        <v>728271.0</v>
       </c>
       <c r="E401" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F401" s="7" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>65</v>
@@ -12301,16 +12304,16 @@
         <v>13</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D404" s="6" t="n">
-        <v>728271.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E404" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F404" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G404" s="8" t="s">
         <v>65</v>
@@ -12388,16 +12391,16 @@
         <v>13</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D407" s="6" t="n">
-        <v>2360.0</v>
+        <v>9750.0</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F407" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F407" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G407" s="8" t="s">
         <v>65</v>
@@ -12414,13 +12417,13 @@
         <v>65</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>217102.0</v>
+        <v>5080.0</v>
       </c>
       <c r="E408" s="7" t="s">
         <v>12</v>
@@ -12446,16 +12449,16 @@
         <v>13</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D409" s="6" t="n">
-        <v>65752.0</v>
+        <v>73210.0</v>
       </c>
       <c r="E409" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F409" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F409" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G409" s="8" t="s">
         <v>65</v>
@@ -12501,13 +12504,13 @@
         <v>65</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D411" s="6" t="n">
-        <v>73210.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E411" s="7" t="s">
         <v>12</v>
@@ -12530,19 +12533,19 @@
         <v>65</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D412" s="6" t="n">
-        <v>285268.0</v>
+        <v>4067.0</v>
       </c>
       <c r="E412" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F412" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F412" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G412" s="8" t="s">
         <v>65</v>
@@ -12562,16 +12565,16 @@
         <v>10</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>160813.0</v>
+        <v>285268.0</v>
       </c>
       <c r="E413" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F413" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F413" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G413" s="8" t="s">
         <v>65</v>
@@ -12591,10 +12594,10 @@
         <v>10</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D414" s="6" t="n">
-        <v>60.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E414" s="7" t="s">
         <v>12</v>
@@ -12617,13 +12620,13 @@
         <v>65</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>35159.0</v>
+        <v>60.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12649,10 +12652,10 @@
         <v>30</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D416" s="6" t="n">
-        <v>548.0</v>
+        <v>35159.0</v>
       </c>
       <c r="E416" s="7" t="s">
         <v>12</v>
@@ -12678,10 +12681,10 @@
         <v>30</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D417" s="6" t="n">
-        <v>126986.0</v>
+        <v>548.0</v>
       </c>
       <c r="E417" s="7" t="s">
         <v>12</v>
@@ -12707,10 +12710,10 @@
         <v>30</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D418" s="6" t="n">
-        <v>7149.0</v>
+        <v>126986.0</v>
       </c>
       <c r="E418" s="7" t="s">
         <v>12</v>
@@ -12736,16 +12739,16 @@
         <v>30</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D419" s="6" t="n">
-        <v>594911.0</v>
+        <v>7149.0</v>
       </c>
       <c r="E419" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F419" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F419" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G419" s="8" t="s">
         <v>65</v>
@@ -12765,16 +12768,16 @@
         <v>30</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D420" s="6" t="n">
-        <v>39117.0</v>
+        <v>594911.0</v>
       </c>
       <c r="E420" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F420" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F420" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G420" s="8" t="s">
         <v>65</v>
@@ -12791,13 +12794,13 @@
         <v>65</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>4067.0</v>
+        <v>39117.0</v>
       </c>
       <c r="E421" s="7" t="s">
         <v>12</v>
@@ -12823,10 +12826,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>784.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12968,10 +12971,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>5605.0</v>
+        <v>784.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -12997,10 +13000,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>1359.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13226,13 +13229,13 @@
         <v>66</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D436" s="6" t="n">
-        <v>398394.0</v>
+        <v>5730.0</v>
       </c>
       <c r="E436" s="7" t="s">
         <v>12</v>
@@ -13287,10 +13290,10 @@
         <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>5730.0</v>
+        <v>9349.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13345,16 +13348,16 @@
         <v>10</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>3803.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E440" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F440" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F440" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G440" s="8" t="s">
         <v>66</v>
@@ -13374,16 +13377,16 @@
         <v>10</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>210756.0</v>
+        <v>209762.0</v>
       </c>
       <c r="E441" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F441" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F441" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G441" s="8" t="s">
         <v>66</v>
@@ -13403,10 +13406,10 @@
         <v>10</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D442" s="6" t="n">
-        <v>209762.0</v>
+        <v>4524.0</v>
       </c>
       <c r="E442" s="7" t="s">
         <v>12</v>
@@ -13432,10 +13435,10 @@
         <v>10</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>4524.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E443" s="7" t="s">
         <v>12</v>
@@ -13458,13 +13461,13 @@
         <v>66</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D444" s="6" t="n">
-        <v>108610.0</v>
+        <v>31883.0</v>
       </c>
       <c r="E444" s="7" t="s">
         <v>12</v>
@@ -13487,13 +13490,13 @@
         <v>66</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>9349.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13548,10 +13551,10 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>1412.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E447" s="7" t="s">
         <v>12</v>
@@ -13574,19 +13577,19 @@
         <v>66</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>94352.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E448" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F448" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F448" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G448" s="8" t="s">
         <v>66</v>
@@ -13606,16 +13609,16 @@
         <v>30</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D449" s="6" t="n">
-        <v>1503.0</v>
+        <v>94352.0</v>
       </c>
       <c r="E449" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F449" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F449" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G449" s="8" t="s">
         <v>66</v>
@@ -13635,10 +13638,10 @@
         <v>30</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D450" s="6" t="n">
-        <v>31883.0</v>
+        <v>1412.0</v>
       </c>
       <c r="E450" s="7" t="s">
         <v>12</v>
@@ -13664,10 +13667,10 @@
         <v>13</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D451" s="6" t="n">
-        <v>4957.0</v>
+        <v>872.0</v>
       </c>
       <c r="E451" s="7" t="s">
         <v>12</v>
@@ -13693,16 +13696,16 @@
         <v>13</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D452" s="6" t="n">
-        <v>78020.0</v>
+        <v>420532.0</v>
       </c>
       <c r="E452" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F452" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F452" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G452" s="8" t="s">
         <v>67</v>
@@ -13722,10 +13725,10 @@
         <v>13</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D453" s="6" t="n">
-        <v>2727.0</v>
+        <v>175.0</v>
       </c>
       <c r="E453" s="7" t="s">
         <v>12</v>
@@ -13751,10 +13754,10 @@
         <v>13</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D454" s="6" t="n">
-        <v>1522.0</v>
+        <v>47101.0</v>
       </c>
       <c r="E454" s="7" t="s">
         <v>12</v>
@@ -13780,10 +13783,10 @@
         <v>13</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D455" s="6" t="n">
-        <v>936.0</v>
+        <v>57845.0</v>
       </c>
       <c r="E455" s="7" t="s">
         <v>12</v>
@@ -13809,16 +13812,16 @@
         <v>13</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D456" s="6" t="n">
-        <v>792.0</v>
+        <v>357258.0</v>
       </c>
       <c r="E456" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F456" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F456" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G456" s="8" t="s">
         <v>67</v>
@@ -13838,16 +13841,16 @@
         <v>13</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D457" s="6" t="n">
-        <v>357258.0</v>
+        <v>4957.0</v>
       </c>
       <c r="E457" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F457" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F457" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G457" s="8" t="s">
         <v>67</v>
@@ -13867,10 +13870,10 @@
         <v>13</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D458" s="6" t="n">
-        <v>57845.0</v>
+        <v>936.0</v>
       </c>
       <c r="E458" s="7" t="s">
         <v>12</v>
@@ -13896,10 +13899,10 @@
         <v>13</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D459" s="6" t="n">
-        <v>175.0</v>
+        <v>1522.0</v>
       </c>
       <c r="E459" s="7" t="s">
         <v>12</v>
@@ -13925,10 +13928,10 @@
         <v>13</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D460" s="6" t="n">
-        <v>420532.0</v>
+        <v>2727.0</v>
       </c>
       <c r="E460" s="7" t="s">
         <v>12</v>
@@ -13954,16 +13957,16 @@
         <v>13</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D461" s="6" t="n">
-        <v>47101.0</v>
+        <v>78020.0</v>
       </c>
       <c r="E461" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F461" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F461" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G461" s="8" t="s">
         <v>67</v>
@@ -14012,10 +14015,10 @@
         <v>13</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D463" s="6" t="n">
-        <v>872.0</v>
+        <v>792.0</v>
       </c>
       <c r="E463" s="7" t="s">
         <v>12</v>
@@ -14041,10 +14044,10 @@
         <v>13</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D464" s="6" t="n">
-        <v>13052.0</v>
+        <v>64823.0</v>
       </c>
       <c r="E464" s="7" t="s">
         <v>12</v>
@@ -14067,13 +14070,13 @@
         <v>67</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D465" s="6" t="n">
-        <v>3363.0</v>
+        <v>13052.0</v>
       </c>
       <c r="E465" s="7" t="s">
         <v>12</v>
@@ -14096,13 +14099,13 @@
         <v>67</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D466" s="6" t="n">
-        <v>64823.0</v>
+        <v>74709.0</v>
       </c>
       <c r="E466" s="7" t="s">
         <v>12</v>
@@ -14125,13 +14128,13 @@
         <v>67</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>245670.0</v>
+        <v>6691.0</v>
       </c>
       <c r="E467" s="7" t="s">
         <v>12</v>
@@ -14157,10 +14160,10 @@
         <v>10</v>
       </c>
       <c r="C468" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D468" s="6" t="n">
-        <v>122605.0</v>
+        <v>245670.0</v>
       </c>
       <c r="E468" s="7" t="s">
         <v>12</v>
@@ -14186,10 +14189,10 @@
         <v>10</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D469" s="6" t="n">
-        <v>3174.0</v>
+        <v>122605.0</v>
       </c>
       <c r="E469" s="7" t="s">
         <v>12</v>
@@ -14212,13 +14215,13 @@
         <v>67</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D470" s="6" t="n">
-        <v>74709.0</v>
+        <v>3174.0</v>
       </c>
       <c r="E470" s="7" t="s">
         <v>12</v>
@@ -14273,10 +14276,10 @@
         <v>30</v>
       </c>
       <c r="C472" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D472" s="6" t="n">
-        <v>646.0</v>
+        <v>3363.0</v>
       </c>
       <c r="E472" s="7" t="s">
         <v>12</v>
@@ -14302,10 +14305,10 @@
         <v>30</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D473" s="6" t="n">
-        <v>8245.0</v>
+        <v>199283.0</v>
       </c>
       <c r="E473" s="7" t="s">
         <v>12</v>
@@ -14331,10 +14334,10 @@
         <v>30</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D474" s="6" t="n">
-        <v>207867.0</v>
+        <v>8245.0</v>
       </c>
       <c r="E474" s="7" t="s">
         <v>12</v>
@@ -14360,10 +14363,10 @@
         <v>30</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D475" s="6" t="n">
-        <v>6920.0</v>
+        <v>207867.0</v>
       </c>
       <c r="E475" s="7" t="s">
         <v>12</v>
@@ -14386,13 +14389,13 @@
         <v>67</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D476" s="6" t="n">
-        <v>6691.0</v>
+        <v>6920.0</v>
       </c>
       <c r="E476" s="7" t="s">
         <v>12</v>
@@ -14418,10 +14421,10 @@
         <v>30</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D477" s="6" t="n">
-        <v>199283.0</v>
+        <v>646.0</v>
       </c>
       <c r="E477" s="7" t="s">
         <v>12</v>
@@ -14447,10 +14450,10 @@
         <v>13</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D478" s="6" t="n">
-        <v>4818.0</v>
+        <v>158897.0</v>
       </c>
       <c r="E478" s="7" t="s">
         <v>12</v>
@@ -14476,10 +14479,10 @@
         <v>13</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D479" s="6" t="n">
-        <v>692.0</v>
+        <v>3849.0</v>
       </c>
       <c r="E479" s="7" t="s">
         <v>12</v>
@@ -14505,10 +14508,10 @@
         <v>13</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D480" s="6" t="n">
-        <v>3849.0</v>
+        <v>8962.0</v>
       </c>
       <c r="E480" s="7" t="s">
         <v>12</v>
@@ -14534,10 +14537,10 @@
         <v>13</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D481" s="6" t="n">
-        <v>8962.0</v>
+        <v>1252.0</v>
       </c>
       <c r="E481" s="7" t="s">
         <v>12</v>
@@ -14563,10 +14566,10 @@
         <v>13</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D482" s="6" t="n">
-        <v>1252.0</v>
+        <v>4818.0</v>
       </c>
       <c r="E482" s="7" t="s">
         <v>12</v>
@@ -14592,10 +14595,10 @@
         <v>13</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D483" s="6" t="n">
-        <v>4118.0</v>
+        <v>549073.0</v>
       </c>
       <c r="E483" s="7" t="s">
         <v>12</v>
@@ -14621,10 +14624,10 @@
         <v>13</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D484" s="6" t="n">
-        <v>158897.0</v>
+        <v>20516.0</v>
       </c>
       <c r="E484" s="7" t="s">
         <v>12</v>
@@ -14650,10 +14653,10 @@
         <v>13</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D485" s="6" t="n">
-        <v>20516.0</v>
+        <v>4118.0</v>
       </c>
       <c r="E485" s="7" t="s">
         <v>12</v>
@@ -14679,10 +14682,10 @@
         <v>13</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D486" s="6" t="n">
-        <v>549073.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E486" s="7" t="s">
         <v>12</v>
@@ -14708,10 +14711,10 @@
         <v>13</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D487" s="6" t="n">
-        <v>2658.0</v>
+        <v>791.0</v>
       </c>
       <c r="E487" s="7" t="s">
         <v>12</v>
@@ -14737,16 +14740,16 @@
         <v>13</v>
       </c>
       <c r="C488" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D488" s="6" t="n">
-        <v>791.0</v>
+        <v>108623.0</v>
       </c>
       <c r="E488" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F488" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F488" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G488" s="8" t="s">
         <v>68</v>
@@ -14766,16 +14769,16 @@
         <v>13</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D489" s="6" t="n">
-        <v>108623.0</v>
+        <v>692.0</v>
       </c>
       <c r="E489" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F489" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F489" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G489" s="8" t="s">
         <v>68</v>
@@ -14795,16 +14798,16 @@
         <v>13</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D490" s="6" t="n">
-        <v>70327.0</v>
+        <v>96503.0</v>
       </c>
       <c r="E490" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F490" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F490" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G490" s="8" t="s">
         <v>68</v>
@@ -14821,13 +14824,13 @@
         <v>68</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D491" s="6" t="n">
-        <v>96503.0</v>
+        <v>107735.0</v>
       </c>
       <c r="E491" s="7" t="s">
         <v>16</v>
@@ -14850,13 +14853,13 @@
         <v>68</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D492" s="6" t="n">
-        <v>15334.0</v>
+        <v>54343.0</v>
       </c>
       <c r="E492" s="7" t="s">
         <v>12</v>
@@ -14882,10 +14885,10 @@
         <v>13</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D493" s="6" t="n">
-        <v>8296.0</v>
+        <v>70327.0</v>
       </c>
       <c r="E493" s="7" t="s">
         <v>12</v>
@@ -14911,16 +14914,16 @@
         <v>10</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D494" s="6" t="n">
-        <v>107735.0</v>
+        <v>296618.0</v>
       </c>
       <c r="E494" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F494" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F494" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G494" s="8" t="s">
         <v>68</v>
@@ -14940,10 +14943,10 @@
         <v>10</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D495" s="6" t="n">
-        <v>296618.0</v>
+        <v>170208.0</v>
       </c>
       <c r="E495" s="7" t="s">
         <v>12</v>
@@ -14969,10 +14972,10 @@
         <v>10</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D496" s="6" t="n">
-        <v>170208.0</v>
+        <v>13403.0</v>
       </c>
       <c r="E496" s="7" t="s">
         <v>12</v>
@@ -14998,10 +15001,10 @@
         <v>10</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D497" s="6" t="n">
-        <v>13403.0</v>
+        <v>15334.0</v>
       </c>
       <c r="E497" s="7" t="s">
         <v>12</v>
@@ -15027,10 +15030,10 @@
         <v>30</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D498" s="6" t="n">
-        <v>54343.0</v>
+        <v>4041.0</v>
       </c>
       <c r="E498" s="7" t="s">
         <v>12</v>
@@ -15056,16 +15059,16 @@
         <v>30</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D499" s="6" t="n">
-        <v>4041.0</v>
+        <v>190807.0</v>
       </c>
       <c r="E499" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F499" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F499" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G499" s="8" t="s">
         <v>68</v>
@@ -15085,16 +15088,16 @@
         <v>30</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D500" s="6" t="n">
-        <v>190807.0</v>
+        <v>206053.0</v>
       </c>
       <c r="E500" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F500" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F500" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G500" s="8" t="s">
         <v>68</v>
@@ -15114,10 +15117,10 @@
         <v>30</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D501" s="6" t="n">
-        <v>206053.0</v>
+        <v>5306.0</v>
       </c>
       <c r="E501" s="7" t="s">
         <v>12</v>
@@ -15140,13 +15143,13 @@
         <v>68</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C502" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D502" s="6" t="n">
-        <v>5306.0</v>
+        <v>14544.0</v>
       </c>
       <c r="E502" s="7" t="s">
         <v>12</v>
@@ -15172,10 +15175,10 @@
         <v>13</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D503" s="6" t="n">
-        <v>14544.0</v>
+        <v>8296.0</v>
       </c>
       <c r="E503" s="7" t="s">
         <v>12</v>
@@ -15346,16 +15349,16 @@
         <v>13</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D509" s="6" t="n">
-        <v>908897.0</v>
+        <v>30675.0</v>
       </c>
       <c r="E509" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F509" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F509" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G509" s="8" t="s">
         <v>69</v>
@@ -15404,10 +15407,10 @@
         <v>13</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D511" s="6" t="n">
-        <v>30675.0</v>
+        <v>201113.0</v>
       </c>
       <c r="E511" s="7" t="s">
         <v>12</v>
@@ -15433,10 +15436,10 @@
         <v>13</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D512" s="6" t="n">
-        <v>201113.0</v>
+        <v>5181.0</v>
       </c>
       <c r="E512" s="7" t="s">
         <v>12</v>
@@ -15462,10 +15465,10 @@
         <v>13</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D513" s="6" t="n">
-        <v>5181.0</v>
+        <v>18261.0</v>
       </c>
       <c r="E513" s="7" t="s">
         <v>12</v>
@@ -15491,10 +15494,10 @@
         <v>13</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D514" s="6" t="n">
-        <v>18261.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E514" s="7" t="s">
         <v>12</v>
@@ -15520,16 +15523,16 @@
         <v>13</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D515" s="6" t="n">
-        <v>1519.0</v>
+        <v>908897.0</v>
       </c>
       <c r="E515" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F515" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F515" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G515" s="8" t="s">
         <v>69</v>
@@ -15578,10 +15581,10 @@
         <v>10</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D517" s="6" t="n">
-        <v>1408.0</v>
+        <v>44.0</v>
       </c>
       <c r="E517" s="7" t="s">
         <v>12</v>
@@ -15636,10 +15639,10 @@
         <v>10</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D519" s="6" t="n">
-        <v>42853.0</v>
+        <v>1408.0</v>
       </c>
       <c r="E519" s="7" t="s">
         <v>12</v>
@@ -15694,10 +15697,10 @@
         <v>10</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D521" s="6" t="n">
-        <v>162695.0</v>
+        <v>372386.0</v>
       </c>
       <c r="E521" s="7" t="s">
         <v>12</v>
@@ -15723,10 +15726,10 @@
         <v>10</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D522" s="6" t="n">
-        <v>44.0</v>
+        <v>162639.0</v>
       </c>
       <c r="E522" s="7" t="s">
         <v>12</v>
@@ -15752,10 +15755,10 @@
         <v>10</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D523" s="6" t="n">
-        <v>372386.0</v>
+        <v>162695.0</v>
       </c>
       <c r="E523" s="7" t="s">
         <v>12</v>
@@ -15781,10 +15784,10 @@
         <v>10</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D524" s="6" t="n">
-        <v>162639.0</v>
+        <v>42853.0</v>
       </c>
       <c r="E524" s="7" t="s">
         <v>12</v>
@@ -15984,10 +15987,10 @@
         <v>13</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D531" s="6" t="n">
-        <v>133084.0</v>
+        <v>8250.0</v>
       </c>
       <c r="E531" s="7" t="s">
         <v>12</v>
@@ -16013,10 +16016,10 @@
         <v>13</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D532" s="6" t="n">
-        <v>2394.0</v>
+        <v>17644.0</v>
       </c>
       <c r="E532" s="7" t="s">
         <v>12</v>
@@ -16042,10 +16045,10 @@
         <v>13</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D533" s="6" t="n">
-        <v>8250.0</v>
+        <v>249.0</v>
       </c>
       <c r="E533" s="7" t="s">
         <v>12</v>
@@ -16071,10 +16074,10 @@
         <v>13</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D534" s="6" t="n">
-        <v>249.0</v>
+        <v>11404.0</v>
       </c>
       <c r="E534" s="7" t="s">
         <v>12</v>
@@ -16100,10 +16103,10 @@
         <v>13</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D535" s="6" t="n">
-        <v>11404.0</v>
+        <v>133084.0</v>
       </c>
       <c r="E535" s="7" t="s">
         <v>12</v>
@@ -16277,7 +16280,7 @@
         <v>19</v>
       </c>
       <c r="D541" s="6" t="n">
-        <v>349507.0</v>
+        <v>357059.0</v>
       </c>
       <c r="E541" s="7" t="s">
         <v>12</v>
@@ -16332,10 +16335,10 @@
         <v>13</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D543" s="6" t="n">
-        <v>178087.0</v>
+        <v>155751.0</v>
       </c>
       <c r="E543" s="7" t="s">
         <v>12</v>
@@ -16361,10 +16364,10 @@
         <v>13</v>
       </c>
       <c r="C544" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D544" s="6" t="n">
-        <v>155449.0</v>
+        <v>2394.0</v>
       </c>
       <c r="E544" s="7" t="s">
         <v>12</v>
@@ -16387,13 +16390,13 @@
         <v>70</v>
       </c>
       <c r="B545" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D545" s="6" t="n">
-        <v>17644.0</v>
+        <v>9668.0</v>
       </c>
       <c r="E545" s="7" t="s">
         <v>12</v>
@@ -16419,10 +16422,10 @@
         <v>13</v>
       </c>
       <c r="C546" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D546" s="6" t="n">
-        <v>61145.0</v>
+        <v>180673.0</v>
       </c>
       <c r="E546" s="7" t="s">
         <v>12</v>
@@ -16451,7 +16454,7 @@
         <v>35</v>
       </c>
       <c r="D547" s="6" t="n">
-        <v>97563.0</v>
+        <v>98434.0</v>
       </c>
       <c r="E547" s="7" t="s">
         <v>12</v>
@@ -16477,10 +16480,10 @@
         <v>13</v>
       </c>
       <c r="C548" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D548" s="6" t="n">
-        <v>833.0</v>
+        <v>61145.0</v>
       </c>
       <c r="E548" s="7" t="s">
         <v>12</v>
@@ -16506,10 +16509,10 @@
         <v>10</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D549" s="6" t="n">
-        <v>49096.0</v>
+        <v>445652.0</v>
       </c>
       <c r="E549" s="7" t="s">
         <v>12</v>
@@ -16535,10 +16538,10 @@
         <v>10</v>
       </c>
       <c r="C550" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D550" s="6" t="n">
-        <v>445516.0</v>
+        <v>68846.0</v>
       </c>
       <c r="E550" s="7" t="s">
         <v>12</v>
@@ -16622,10 +16625,10 @@
         <v>10</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D553" s="6" t="n">
-        <v>68846.0</v>
+        <v>49132.0</v>
       </c>
       <c r="E553" s="7" t="s">
         <v>12</v>
@@ -16680,10 +16683,10 @@
         <v>30</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D555" s="6" t="n">
-        <v>9668.0</v>
+        <v>16624.0</v>
       </c>
       <c r="E555" s="7" t="s">
         <v>12</v>
@@ -16709,10 +16712,10 @@
         <v>30</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D556" s="6" t="n">
-        <v>167261.0</v>
+        <v>146605.0</v>
       </c>
       <c r="E556" s="7" t="s">
         <v>12</v>
@@ -16738,10 +16741,10 @@
         <v>30</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D557" s="6" t="n">
-        <v>16365.0</v>
+        <v>24743.0</v>
       </c>
       <c r="E557" s="7" t="s">
         <v>12</v>
@@ -16764,13 +16767,13 @@
         <v>70</v>
       </c>
       <c r="B558" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D558" s="6" t="n">
-        <v>146605.0</v>
+        <v>17014.0</v>
       </c>
       <c r="E558" s="7" t="s">
         <v>12</v>
@@ -16793,13 +16796,13 @@
         <v>70</v>
       </c>
       <c r="B559" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D559" s="6" t="n">
-        <v>24743.0</v>
+        <v>833.0</v>
       </c>
       <c r="E559" s="7" t="s">
         <v>12</v>
@@ -16822,13 +16825,13 @@
         <v>70</v>
       </c>
       <c r="B560" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C560" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D560" s="6" t="n">
-        <v>17014.0</v>
+        <v>167261.0</v>
       </c>
       <c r="E560" s="7" t="s">
         <v>12</v>
@@ -16854,10 +16857,10 @@
         <v>13</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D561" s="6" t="n">
-        <v>37838.0</v>
+        <v>1147.0</v>
       </c>
       <c r="E561" s="7" t="s">
         <v>12</v>
@@ -16883,10 +16886,10 @@
         <v>13</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D562" s="6" t="n">
-        <v>54.0</v>
+        <v>50267.0</v>
       </c>
       <c r="E562" s="7" t="s">
         <v>12</v>
@@ -16912,10 +16915,10 @@
         <v>13</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D563" s="6" t="n">
-        <v>24394.0</v>
+        <v>103167.0</v>
       </c>
       <c r="E563" s="7" t="s">
         <v>12</v>
@@ -16941,10 +16944,10 @@
         <v>13</v>
       </c>
       <c r="C564" s="5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D564" s="6" t="n">
-        <v>62902.0</v>
+        <v>388.0</v>
       </c>
       <c r="E564" s="7" t="s">
         <v>12</v>
@@ -16970,10 +16973,10 @@
         <v>13</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D565" s="6" t="n">
-        <v>1163.0</v>
+        <v>4205.0</v>
       </c>
       <c r="E565" s="7" t="s">
         <v>12</v>
@@ -16999,10 +17002,10 @@
         <v>13</v>
       </c>
       <c r="C566" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D566" s="6" t="n">
-        <v>25799.0</v>
+        <v>54.0</v>
       </c>
       <c r="E566" s="7" t="s">
         <v>12</v>
@@ -17028,10 +17031,10 @@
         <v>13</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D567" s="6" t="n">
-        <v>44867.0</v>
+        <v>5640.0</v>
       </c>
       <c r="E567" s="7" t="s">
         <v>12</v>
@@ -17057,10 +17060,10 @@
         <v>13</v>
       </c>
       <c r="C568" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D568" s="6" t="n">
-        <v>14066.0</v>
+        <v>147017.0</v>
       </c>
       <c r="E568" s="7" t="s">
         <v>12</v>
@@ -17086,10 +17089,10 @@
         <v>13</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D569" s="6" t="n">
-        <v>3016.0</v>
+        <v>46194.0</v>
       </c>
       <c r="E569" s="7" t="s">
         <v>12</v>
@@ -17112,13 +17115,13 @@
         <v>71</v>
       </c>
       <c r="B570" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C570" s="5" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D570" s="6" t="n">
-        <v>3681.0</v>
+        <v>9716.0</v>
       </c>
       <c r="E570" s="7" t="s">
         <v>12</v>
@@ -17144,16 +17147,16 @@
         <v>13</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D571" s="6" t="n">
-        <v>2199.0</v>
+        <v>697083.0</v>
       </c>
       <c r="E571" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F571" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F571" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G571" s="8" t="s">
         <v>71</v>
@@ -17170,13 +17173,13 @@
         <v>71</v>
       </c>
       <c r="B572" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C572" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D572" s="6" t="n">
-        <v>8074.0</v>
+        <v>499.0</v>
       </c>
       <c r="E572" s="7" t="s">
         <v>12</v>
@@ -17199,13 +17202,13 @@
         <v>71</v>
       </c>
       <c r="B573" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D573" s="6" t="n">
-        <v>95045.0</v>
+        <v>73411.0</v>
       </c>
       <c r="E573" s="7" t="s">
         <v>12</v>
@@ -17228,13 +17231,13 @@
         <v>71</v>
       </c>
       <c r="B574" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C574" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D574" s="6" t="n">
-        <v>7943.0</v>
+        <v>3016.0</v>
       </c>
       <c r="E574" s="7" t="s">
         <v>12</v>
@@ -17257,13 +17260,13 @@
         <v>71</v>
       </c>
       <c r="B575" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D575" s="6" t="n">
-        <v>65641.0</v>
+        <v>135115.0</v>
       </c>
       <c r="E575" s="7" t="s">
         <v>12</v>
@@ -17286,13 +17289,13 @@
         <v>71</v>
       </c>
       <c r="B576" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C576" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D576" s="6" t="n">
-        <v>3492.0</v>
+        <v>11348.0</v>
       </c>
       <c r="E576" s="7" t="s">
         <v>12</v>
@@ -17315,13 +17318,13 @@
         <v>71</v>
       </c>
       <c r="B577" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D577" s="6" t="n">
-        <v>21702.0</v>
+        <v>649.0</v>
       </c>
       <c r="E577" s="7" t="s">
         <v>12</v>
@@ -17344,13 +17347,13 @@
         <v>71</v>
       </c>
       <c r="B578" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C578" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D578" s="6" t="n">
-        <v>11782.0</v>
+        <v>30577.0</v>
       </c>
       <c r="E578" s="7" t="s">
         <v>12</v>
@@ -17376,10 +17379,10 @@
         <v>10</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D579" s="6" t="n">
-        <v>116078.0</v>
+        <v>132880.0</v>
       </c>
       <c r="E579" s="7" t="s">
         <v>12</v>
@@ -17405,10 +17408,10 @@
         <v>10</v>
       </c>
       <c r="C580" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D580" s="6" t="n">
-        <v>33155.0</v>
+        <v>4412.0</v>
       </c>
       <c r="E580" s="7" t="s">
         <v>12</v>
@@ -17431,19 +17434,19 @@
         <v>71</v>
       </c>
       <c r="B581" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D581" s="6" t="n">
-        <v>296328.0</v>
+        <v>30784.0</v>
       </c>
       <c r="E581" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F581" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F581" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G581" s="8" t="s">
         <v>71</v>
@@ -17452,6 +17455,876 @@
         <v>71</v>
       </c>
       <c r="I581" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B582" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C582" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D582" s="6" t="n">
+        <v>17930.0</v>
+      </c>
+      <c r="E582" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F582" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G582" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H582" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I582" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B583" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C583" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D583" s="6" t="n">
+        <v>369907.0</v>
+      </c>
+      <c r="E583" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F583" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G583" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H583" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I583" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B584" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C584" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D584" s="6" t="n">
+        <v>5930.0</v>
+      </c>
+      <c r="E584" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F584" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G584" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H584" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I584" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B585" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C585" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D585" s="6" t="n">
+        <v>160983.0</v>
+      </c>
+      <c r="E585" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F585" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G585" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H585" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I585" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B586" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C586" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D586" s="6" t="n">
+        <v>3492.0</v>
+      </c>
+      <c r="E586" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F586" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G586" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H586" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I586" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B587" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C587" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D587" s="6" t="n">
+        <v>267.0</v>
+      </c>
+      <c r="E587" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F587" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G587" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H587" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I587" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B588" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C588" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D588" s="6" t="n">
+        <v>245314.0</v>
+      </c>
+      <c r="E588" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F588" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G588" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H588" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I588" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B589" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C589" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D589" s="6" t="n">
+        <v>10813.0</v>
+      </c>
+      <c r="E589" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F589" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G589" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H589" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I589" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B590" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C590" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D590" s="6" t="n">
+        <v>215594.0</v>
+      </c>
+      <c r="E590" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F590" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G590" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H590" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I590" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B591" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C591" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D591" s="6" t="n">
+        <v>25445.0</v>
+      </c>
+      <c r="E591" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F591" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G591" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H591" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I591" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B592" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C592" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D592" s="6" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="E592" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F592" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G592" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H592" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I592" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B593" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C593" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D593" s="6" t="n">
+        <v>46550.0</v>
+      </c>
+      <c r="E593" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F593" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G593" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H593" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I593" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B594" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C594" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D594" s="6" t="n">
+        <v>110968.0</v>
+      </c>
+      <c r="E594" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F594" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G594" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H594" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I594" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B595" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C595" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D595" s="6" t="n">
+        <v>1855.0</v>
+      </c>
+      <c r="E595" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F595" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G595" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H595" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I595" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B596" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C596" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D596" s="6" t="n">
+        <v>17402.0</v>
+      </c>
+      <c r="E596" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F596" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G596" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H596" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I596" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B597" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C597" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D597" s="6" t="n">
+        <v>4826.0</v>
+      </c>
+      <c r="E597" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F597" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G597" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H597" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I597" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B598" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C598" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D598" s="6" t="n">
+        <v>270175.0</v>
+      </c>
+      <c r="E598" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F598" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G598" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H598" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I598" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B599" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C599" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D599" s="6" t="n">
+        <v>50148.0</v>
+      </c>
+      <c r="E599" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F599" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G599" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H599" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I599" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B600" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C600" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D600" s="6" t="n">
+        <v>435.0</v>
+      </c>
+      <c r="E600" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F600" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G600" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H600" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I600" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B601" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C601" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D601" s="6" t="n">
+        <v>11787.0</v>
+      </c>
+      <c r="E601" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F601" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G601" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H601" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I601" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B602" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C602" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D602" s="6" t="n">
+        <v>4538.0</v>
+      </c>
+      <c r="E602" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F602" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G602" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H602" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I602" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B603" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C603" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D603" s="6" t="n">
+        <v>36202.0</v>
+      </c>
+      <c r="E603" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F603" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G603" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H603" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I603" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B604" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C604" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D604" s="6" t="n">
+        <v>148242.0</v>
+      </c>
+      <c r="E604" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F604" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G604" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H604" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I604" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B605" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D605" s="6" t="n">
+        <v>2065.0</v>
+      </c>
+      <c r="E605" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F605" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G605" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H605" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I605" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B606" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C606" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D606" s="6" t="n">
+        <v>236929.0</v>
+      </c>
+      <c r="E606" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F606" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G606" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H606" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I606" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B607" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C607" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D607" s="6" t="n">
+        <v>28201.0</v>
+      </c>
+      <c r="E607" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F607" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G607" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H607" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I607" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B608" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C608" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D608" s="6" t="n">
+        <v>48677.0</v>
+      </c>
+      <c r="E608" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F608" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G608" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H608" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I608" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B609" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C609" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D609" s="6" t="n">
+        <v>201801.0</v>
+      </c>
+      <c r="E609" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F609" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G609" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H609" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I609" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B610" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C610" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D610" s="6" t="n">
+        <v>113095.0</v>
+      </c>
+      <c r="E610" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F610" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G610" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H610" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I610" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B611" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C611" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D611" s="6" t="n">
+        <v>318112.0</v>
+      </c>
+      <c r="E611" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F611" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G611" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H611" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I611" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4808" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5226" uniqueCount="75">
   <si>
     <t>Ngày</t>
   </si>
@@ -149,19 +149,19 @@
     <t>2026-08-02</t>
   </si>
   <si>
+    <t>120253483200380712</t>
+  </si>
+  <si>
     <t>120253483200390712</t>
   </si>
   <si>
     <t>120253483628540712</t>
   </si>
   <si>
-    <t>120253483200380712</t>
+    <t>120252922477470712</t>
   </si>
   <si>
     <t>120252922477480712</t>
-  </si>
-  <si>
-    <t>120252922477470712</t>
   </si>
   <si>
     <t>120253417262500712</t>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
   </si>
 </sst>
 </file>
@@ -594,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I611"/>
+  <dimension ref="A1:I664"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -1519,7 +1525,7 @@
         <v>45</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2747.0</v>
+        <v>1510.0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>12</v>
@@ -1545,16 +1551,16 @@
         <v>13</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>65819.0</v>
+        <v>2747.0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>44</v>
@@ -1574,16 +1580,16 @@
         <v>13</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>102721.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>44</v>
@@ -1603,7 +1609,7 @@
         <v>13</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>470.0</v>
@@ -1774,13 +1780,13 @@
         <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>35805.0</v>
+        <v>430.0</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>12</v>
@@ -1806,10 +1812,10 @@
         <v>13</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>1510.0</v>
+        <v>35805.0</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>12</v>
@@ -1832,13 +1838,13 @@
         <v>44</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>5790.0</v>
+        <v>102721.0</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>12</v>
@@ -1864,10 +1870,10 @@
         <v>30</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>430.0</v>
+        <v>573.0</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
@@ -1919,19 +1925,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>498079.0</v>
+        <v>157090.0</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>44</v>
@@ -1948,13 +1954,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>573.0</v>
+        <v>111418.0</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>12</v>
@@ -1980,10 +1986,10 @@
         <v>10</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>111418.0</v>
+        <v>35215.0</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>12</v>
@@ -2012,7 +2018,7 @@
         <v>49</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>35215.0</v>
+        <v>5790.0</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>12</v>
@@ -2093,19 +2099,19 @@
         <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>3585.0</v>
+        <v>498079.0</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>44</v>
@@ -2125,10 +2131,10 @@
         <v>30</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>487.0</v>
+        <v>3585.0</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>12</v>
@@ -2154,10 +2160,10 @@
         <v>30</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>283422.0</v>
+        <v>487.0</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>12</v>
@@ -2183,10 +2189,10 @@
         <v>30</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>157090.0</v>
+        <v>283422.0</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>12</v>
@@ -2241,10 +2247,10 @@
         <v>13</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>3486.0</v>
+        <v>83.0</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>12</v>
@@ -2386,10 +2392,10 @@
         <v>13</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>831603.0</v>
+        <v>5532.0</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>12</v>
@@ -2415,10 +2421,10 @@
         <v>13</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1721.0</v>
+        <v>3486.0</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>12</v>
@@ -2444,10 +2450,10 @@
         <v>13</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>5532.0</v>
+        <v>1721.0</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>12</v>
@@ -2473,10 +2479,10 @@
         <v>13</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>10890.0</v>
+        <v>831603.0</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>12</v>
@@ -2502,10 +2508,10 @@
         <v>13</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>378256.0</v>
+        <v>10890.0</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>12</v>
@@ -2531,10 +2537,10 @@
         <v>13</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>17497.0</v>
+        <v>378256.0</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>12</v>
@@ -2560,7 +2566,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>14414.0</v>
@@ -2589,10 +2595,10 @@
         <v>13</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>83.0</v>
+        <v>17497.0</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>12</v>
@@ -2644,19 +2650,19 @@
         <v>51</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>85165.0</v>
+        <v>8487.0</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F71" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G71" s="8" t="s">
         <v>51</v>
@@ -2673,13 +2679,13 @@
         <v>51</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>100851.0</v>
+        <v>3300.0</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>12</v>
@@ -2705,10 +2711,10 @@
         <v>10</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>373138.0</v>
+        <v>256233.0</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>12</v>
@@ -2734,10 +2740,10 @@
         <v>10</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>61630.0</v>
+        <v>100851.0</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>12</v>
@@ -2763,10 +2769,10 @@
         <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>8487.0</v>
+        <v>373138.0</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>12</v>
@@ -2789,13 +2795,13 @@
         <v>51</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>3300.0</v>
+        <v>61630.0</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>12</v>
@@ -2821,16 +2827,16 @@
         <v>30</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>5448.0</v>
+        <v>85165.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>51</v>
@@ -2850,10 +2856,10 @@
         <v>30</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>669.0</v>
+        <v>5448.0</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>12</v>
@@ -2879,10 +2885,10 @@
         <v>30</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>351708.0</v>
+        <v>669.0</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>12</v>
@@ -2908,16 +2914,16 @@
         <v>30</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>187504.0</v>
+        <v>351708.0</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F80" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>51</v>
@@ -2937,16 +2943,16 @@
         <v>30</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>4349.0</v>
+        <v>187504.0</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>51</v>
@@ -2963,13 +2969,13 @@
         <v>51</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>256233.0</v>
+        <v>4349.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
@@ -2995,10 +3001,10 @@
         <v>13</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>2226.0</v>
+        <v>14080.0</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>12</v>
@@ -3024,16 +3030,16 @@
         <v>13</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>152212.0</v>
+        <v>1645.0</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F84" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>53</v>
@@ -3053,10 +3059,10 @@
         <v>13</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>1645.0</v>
+        <v>2497.0</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>12</v>
@@ -3082,10 +3088,10 @@
         <v>13</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>2497.0</v>
+        <v>112.0</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>12</v>
@@ -3111,10 +3117,10 @@
         <v>13</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>112.0</v>
+        <v>2226.0</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>12</v>
@@ -3140,10 +3146,10 @@
         <v>13</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>20121.0</v>
+        <v>45437.0</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -3169,10 +3175,10 @@
         <v>13</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>14080.0</v>
+        <v>4645.0</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>12</v>
@@ -3198,16 +3204,16 @@
         <v>13</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>4645.0</v>
+        <v>309962.0</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>53</v>
@@ -3227,16 +3233,16 @@
         <v>13</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>309962.0</v>
+        <v>20121.0</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F91" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>53</v>
@@ -3314,10 +3320,10 @@
         <v>13</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>4423.0</v>
+        <v>19856.0</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>12</v>
@@ -3343,16 +3349,16 @@
         <v>13</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>45437.0</v>
+        <v>152212.0</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>53</v>
@@ -3369,13 +3375,13 @@
         <v>53</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>19856.0</v>
+        <v>38896.0</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>12</v>
@@ -3401,10 +3407,10 @@
         <v>13</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>122.0</v>
+        <v>4423.0</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>12</v>
@@ -3430,16 +3436,16 @@
         <v>10</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>2580.0</v>
+        <v>98382.0</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>53</v>
@@ -3459,10 +3465,10 @@
         <v>13</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>4782.0</v>
+        <v>122.0</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>12</v>
@@ -3488,16 +3494,16 @@
         <v>10</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>8698.0</v>
+        <v>294779.0</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>53</v>
@@ -3517,10 +3523,10 @@
         <v>10</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>294779.0</v>
+        <v>66166.0</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>16</v>
@@ -3549,13 +3555,13 @@
         <v>49</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>66166.0</v>
+        <v>2384.0</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G102" s="8" t="s">
         <v>53</v>
@@ -3575,10 +3581,10 @@
         <v>10</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>2384.0</v>
+        <v>2580.0</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>12</v>
@@ -3604,16 +3610,16 @@
         <v>10</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>98382.0</v>
+        <v>8698.0</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G104" s="8" t="s">
         <v>53</v>
@@ -3630,19 +3636,19 @@
         <v>53</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>38896.0</v>
+        <v>115599.0</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>53</v>
@@ -3662,10 +3668,10 @@
         <v>30</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>1375.0</v>
+        <v>202034.0</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>12</v>
@@ -3691,10 +3697,10 @@
         <v>30</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>202034.0</v>
+        <v>183435.0</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>12</v>
@@ -3720,10 +3726,10 @@
         <v>30</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>183435.0</v>
+        <v>21260.0</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>12</v>
@@ -3746,13 +3752,13 @@
         <v>53</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>21260.0</v>
+        <v>4782.0</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>12</v>
@@ -3778,16 +3784,16 @@
         <v>30</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>115599.0</v>
+        <v>1375.0</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F110" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>53</v>
@@ -3894,7 +3900,7 @@
         <v>13</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D114" s="6" t="n">
         <v>290.0</v>
@@ -4097,16 +4103,16 @@
         <v>13</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>109034.0</v>
+        <v>1325.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F121" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>54</v>
@@ -4126,7 +4132,7 @@
         <v>13</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>20525.0</v>
@@ -4155,16 +4161,16 @@
         <v>13</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>26515.0</v>
+        <v>109034.0</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>54</v>
@@ -4184,10 +4190,10 @@
         <v>13</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>1325.0</v>
+        <v>26515.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
@@ -4329,7 +4335,7 @@
         <v>10</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D129" s="6" t="n">
         <v>3016.0</v>
@@ -4358,7 +4364,7 @@
         <v>10</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D130" s="6" t="n">
         <v>119.0</v>
@@ -4561,10 +4567,10 @@
         <v>13</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>480065.0</v>
+        <v>43267.0</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>12</v>
@@ -4706,10 +4712,10 @@
         <v>13</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>312933.0</v>
+        <v>69.0</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>12</v>
@@ -4735,10 +4741,10 @@
         <v>13</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>42366.0</v>
+        <v>480065.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>12</v>
@@ -4764,10 +4770,10 @@
         <v>13</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>832.0</v>
+        <v>42366.0</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>12</v>
@@ -4793,10 +4799,10 @@
         <v>13</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>1882.0</v>
+        <v>832.0</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>12</v>
@@ -4822,10 +4828,10 @@
         <v>13</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>25102.0</v>
+        <v>1882.0</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>12</v>
@@ -4851,16 +4857,16 @@
         <v>13</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>47872.0</v>
+        <v>25102.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F147" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>55</v>
@@ -4880,16 +4886,16 @@
         <v>13</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>69.0</v>
+        <v>47872.0</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F148" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G148" s="8" t="s">
         <v>55</v>
@@ -4938,10 +4944,10 @@
         <v>13</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>43267.0</v>
+        <v>325679.0</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>12</v>
@@ -4967,10 +4973,10 @@
         <v>13</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>325679.0</v>
+        <v>312933.0</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>12</v>
@@ -4996,10 +5002,10 @@
         <v>30</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>13050.0</v>
+        <v>28884.0</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>12</v>
@@ -5022,13 +5028,13 @@
         <v>55</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>21698.0</v>
+        <v>1746.0</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>12</v>
@@ -5051,13 +5057,13 @@
         <v>55</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>576515.0</v>
+        <v>21698.0</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>12</v>
@@ -5083,10 +5089,10 @@
         <v>10</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>328.0</v>
+        <v>143.0</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>12</v>
@@ -5109,19 +5115,19 @@
         <v>55</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>250155.0</v>
+        <v>328.0</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F156" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>55</v>
@@ -5141,16 +5147,16 @@
         <v>30</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>28884.0</v>
+        <v>250155.0</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F157" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F157" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G157" s="8" t="s">
         <v>55</v>
@@ -5170,10 +5176,10 @@
         <v>10</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>143.0</v>
+        <v>576515.0</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>12</v>
@@ -5199,10 +5205,10 @@
         <v>30</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>37534.0</v>
+        <v>13050.0</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>12</v>
@@ -5341,13 +5347,13 @@
         <v>55</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>1746.0</v>
+        <v>37534.0</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>12</v>
@@ -5460,7 +5466,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D168" s="6" t="n">
         <v>6378.0</v>
@@ -5634,7 +5640,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D174" s="6" t="n">
         <v>10115.0</v>
@@ -5663,7 +5669,7 @@
         <v>13</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D175" s="6" t="n">
         <v>35065.0</v>
@@ -5689,19 +5695,19 @@
         <v>56</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>115261.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F176" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G176" s="8" t="s">
         <v>56</v>
@@ -5837,7 +5843,7 @@
         <v>10</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D181" s="6" t="n">
         <v>6519.0</v>
@@ -5866,10 +5872,10 @@
         <v>10</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>1182.0</v>
+        <v>24571.0</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>12</v>
@@ -5892,19 +5898,19 @@
         <v>56</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>24571.0</v>
+        <v>115261.0</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F183" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F183" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G183" s="8" t="s">
         <v>56</v>
@@ -6414,13 +6420,13 @@
         <v>57</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>476600.0</v>
+        <v>365576.0</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>16</v>
@@ -6443,19 +6449,19 @@
         <v>57</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>365576.0</v>
+        <v>28338.0</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F202" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>57</v>
@@ -6472,13 +6478,13 @@
         <v>57</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>13066.0</v>
+        <v>28802.0</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>12</v>
@@ -6504,10 +6510,10 @@
         <v>13</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>195553.0</v>
+        <v>1573.0</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>12</v>
@@ -6530,13 +6536,13 @@
         <v>57</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>9109.0</v>
+        <v>43423.0</v>
       </c>
       <c r="E205" s="7" t="s">
         <v>12</v>
@@ -6562,10 +6568,10 @@
         <v>30</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>210.0</v>
+        <v>83141.0</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>12</v>
@@ -6591,10 +6597,10 @@
         <v>30</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>28338.0</v>
+        <v>49095.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6620,16 +6626,16 @@
         <v>30</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>264473.0</v>
+        <v>74588.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>57</v>
@@ -6649,10 +6655,10 @@
         <v>30</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>74588.0</v>
+        <v>13066.0</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>12</v>
@@ -6678,10 +6684,10 @@
         <v>30</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>83141.0</v>
+        <v>210.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6704,13 +6710,13 @@
         <v>57</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>43423.0</v>
+        <v>9109.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6733,19 +6739,19 @@
         <v>57</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>1573.0</v>
+        <v>264473.0</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F212" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F212" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G212" s="8" t="s">
         <v>57</v>
@@ -6765,10 +6771,10 @@
         <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>28802.0</v>
+        <v>195553.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6791,19 +6797,19 @@
         <v>57</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>49095.0</v>
+        <v>476600.0</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F214" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F214" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G214" s="8" t="s">
         <v>57</v>
@@ -6823,10 +6829,10 @@
         <v>13</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>28745.0</v>
+        <v>2938.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6852,10 +6858,10 @@
         <v>13</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>8204.0</v>
+        <v>21893.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
@@ -6910,10 +6916,10 @@
         <v>13</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>21893.0</v>
+        <v>8204.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6939,10 +6945,10 @@
         <v>13</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>47108.0</v>
+        <v>28745.0</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>12</v>
@@ -6968,16 +6974,16 @@
         <v>13</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>8125.0</v>
+        <v>47108.0</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F220" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>58</v>
@@ -6997,10 +7003,10 @@
         <v>13</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>142958.0</v>
+        <v>1087.0</v>
       </c>
       <c r="E221" s="7" t="s">
         <v>12</v>
@@ -7026,16 +7032,16 @@
         <v>13</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>55407.0</v>
+        <v>142958.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F222" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>58</v>
@@ -7055,10 +7061,10 @@
         <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>570723.0</v>
+        <v>55407.0</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>16</v>
@@ -7084,16 +7090,16 @@
         <v>13</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>17602.0</v>
+        <v>8125.0</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F224" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F224" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>58</v>
@@ -7113,16 +7119,16 @@
         <v>13</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>1087.0</v>
+        <v>570723.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F225" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>58</v>
@@ -7142,10 +7148,10 @@
         <v>13</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>13953.0</v>
+        <v>17602.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7171,10 +7177,10 @@
         <v>13</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>2938.0</v>
+        <v>13953.0</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
@@ -7197,13 +7203,13 @@
         <v>58</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>196510.0</v>
+        <v>2847.0</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>12</v>
@@ -7226,13 +7232,13 @@
         <v>58</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>8052.0</v>
+        <v>196510.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7255,13 +7261,13 @@
         <v>58</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>52019.0</v>
+        <v>8052.0</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>12</v>
@@ -7284,13 +7290,13 @@
         <v>58</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>2847.0</v>
+        <v>52019.0</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>12</v>
@@ -7316,10 +7322,10 @@
         <v>10</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>586581.0</v>
+        <v>74089.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>12</v>
@@ -7345,10 +7351,10 @@
         <v>10</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>37213.0</v>
+        <v>586581.0</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>12</v>
@@ -7377,13 +7383,13 @@
         <v>48</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>65877.0</v>
+        <v>37213.0</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F234" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>58</v>
@@ -7403,16 +7409,16 @@
         <v>10</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>74089.0</v>
+        <v>65877.0</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F235" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F235" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G235" s="8" t="s">
         <v>58</v>
@@ -7461,10 +7467,10 @@
         <v>30</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>61111.0</v>
+        <v>515691.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7490,10 +7496,10 @@
         <v>30</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>77697.0</v>
+        <v>61111.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7519,10 +7525,10 @@
         <v>30</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>7771.0</v>
+        <v>77697.0</v>
       </c>
       <c r="E239" s="7" t="s">
         <v>12</v>
@@ -7548,16 +7554,16 @@
         <v>30</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>118765.0</v>
+        <v>7771.0</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F240" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G240" s="8" t="s">
         <v>58</v>
@@ -7577,16 +7583,16 @@
         <v>30</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>515691.0</v>
+        <v>118765.0</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F241" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F241" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>58</v>
@@ -7635,16 +7641,16 @@
         <v>13</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D243" s="6" t="n">
-        <v>118119.0</v>
+        <v>27632.0</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F243" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F243" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>59</v>
@@ -7664,16 +7670,16 @@
         <v>13</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D244" s="6" t="n">
-        <v>284471.0</v>
+        <v>118119.0</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F244" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>59</v>
@@ -7693,16 +7699,16 @@
         <v>13</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D245" s="6" t="n">
-        <v>5434.0</v>
+        <v>284471.0</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F245" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F245" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G245" s="8" t="s">
         <v>59</v>
@@ -7722,10 +7728,10 @@
         <v>13</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D246" s="6" t="n">
-        <v>1388.0</v>
+        <v>5434.0</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>12</v>
@@ -7751,10 +7757,10 @@
         <v>13</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>33073.0</v>
+        <v>1388.0</v>
       </c>
       <c r="E247" s="7" t="s">
         <v>12</v>
@@ -7780,16 +7786,16 @@
         <v>13</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>509.0</v>
+        <v>371730.0</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F248" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F248" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>59</v>
@@ -7809,10 +7815,10 @@
         <v>13</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>23722.0</v>
+        <v>509.0</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>12</v>
@@ -7838,10 +7844,10 @@
         <v>13</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>279499.0</v>
+        <v>23722.0</v>
       </c>
       <c r="E250" s="7" t="s">
         <v>12</v>
@@ -7867,10 +7873,10 @@
         <v>13</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>3296.0</v>
+        <v>279499.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>12</v>
@@ -7896,10 +7902,10 @@
         <v>13</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>160.0</v>
+        <v>33073.0</v>
       </c>
       <c r="E252" s="7" t="s">
         <v>12</v>
@@ -7925,10 +7931,10 @@
         <v>13</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>5458.0</v>
+        <v>3296.0</v>
       </c>
       <c r="E253" s="7" t="s">
         <v>12</v>
@@ -7954,10 +7960,10 @@
         <v>13</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>27632.0</v>
+        <v>160.0</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>12</v>
@@ -7983,16 +7989,16 @@
         <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>371730.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F255" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G255" s="8" t="s">
         <v>59</v>
@@ -8041,10 +8047,10 @@
         <v>30</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>302914.0</v>
+        <v>27683.0</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>12</v>
@@ -8070,10 +8076,10 @@
         <v>10</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>31570.0</v>
+        <v>790.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8096,13 +8102,13 @@
         <v>59</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>566118.0</v>
+        <v>160020.0</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>12</v>
@@ -8128,10 +8134,10 @@
         <v>10</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>25241.0</v>
+        <v>3186.0</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>12</v>
@@ -8157,10 +8163,10 @@
         <v>10</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>32891.0</v>
+        <v>31570.0</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>12</v>
@@ -8186,10 +8192,10 @@
         <v>10</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>790.0</v>
+        <v>566118.0</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>12</v>
@@ -8215,10 +8221,10 @@
         <v>10</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>3186.0</v>
+        <v>32891.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8241,13 +8247,13 @@
         <v>59</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>10553.0</v>
+        <v>25241.0</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>12</v>
@@ -8273,10 +8279,10 @@
         <v>30</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>160020.0</v>
+        <v>302914.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8302,10 +8308,10 @@
         <v>30</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>150.0</v>
+        <v>10553.0</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>12</v>
@@ -8331,10 +8337,10 @@
         <v>30</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>27683.0</v>
+        <v>150.0</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>12</v>
@@ -8360,10 +8366,10 @@
         <v>30</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D268" s="6" t="n">
-        <v>7698.0</v>
+        <v>6744.0</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>12</v>
@@ -8389,10 +8395,10 @@
         <v>30</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>6744.0</v>
+        <v>47292.0</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>12</v>
@@ -8418,10 +8424,10 @@
         <v>30</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>47292.0</v>
+        <v>7698.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8476,7 +8482,7 @@
         <v>13</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D272" s="6" t="n">
         <v>15.0</v>
@@ -8621,10 +8627,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>115.0</v>
+        <v>2731.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8679,10 +8685,10 @@
         <v>13</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D279" s="6" t="n">
-        <v>3979.0</v>
+        <v>115.0</v>
       </c>
       <c r="E279" s="7" t="s">
         <v>12</v>
@@ -8708,10 +8714,10 @@
         <v>13</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>96105.0</v>
+        <v>170.0</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>12</v>
@@ -8737,10 +8743,10 @@
         <v>13</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>38472.0</v>
+        <v>96105.0</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>12</v>
@@ -8766,10 +8772,10 @@
         <v>13</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>2731.0</v>
+        <v>38472.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8795,10 +8801,10 @@
         <v>13</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>35463.0</v>
+        <v>220465.0</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>12</v>
@@ -8824,10 +8830,10 @@
         <v>13</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>170.0</v>
+        <v>35463.0</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>12</v>
@@ -8853,10 +8859,10 @@
         <v>13</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>20130.0</v>
+        <v>3979.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8882,16 +8888,16 @@
         <v>13</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>220465.0</v>
+        <v>168847.0</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F286" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F286" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G286" s="8" t="s">
         <v>60</v>
@@ -8937,13 +8943,13 @@
         <v>60</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>1308.0</v>
+        <v>20130.0</v>
       </c>
       <c r="E288" s="7" t="s">
         <v>12</v>
@@ -8966,19 +8972,19 @@
         <v>60</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>168847.0</v>
+        <v>1308.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F289" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>60</v>
@@ -8998,7 +9004,7 @@
         <v>10</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D290" s="6" t="n">
         <v>6706.0</v>
@@ -9027,7 +9033,7 @@
         <v>10</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D291" s="6" t="n">
         <v>4451.0</v>
@@ -9230,16 +9236,16 @@
         <v>30</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>87988.0</v>
+        <v>18189.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F298" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F298" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>60</v>
@@ -9259,16 +9265,16 @@
         <v>30</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>18189.0</v>
+        <v>87988.0</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F299" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G299" s="8" t="s">
         <v>60</v>
@@ -9314,13 +9320,13 @@
         <v>61</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>1798.0</v>
+        <v>4517.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9346,7 +9352,7 @@
         <v>13</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D302" s="6" t="n">
         <v>32243.0</v>
@@ -9433,10 +9439,10 @@
         <v>13</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>4517.0</v>
+        <v>18161.0</v>
       </c>
       <c r="E305" s="7" t="s">
         <v>12</v>
@@ -9462,10 +9468,10 @@
         <v>13</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>18161.0</v>
+        <v>10887.0</v>
       </c>
       <c r="E306" s="7" t="s">
         <v>12</v>
@@ -9491,10 +9497,10 @@
         <v>13</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>10887.0</v>
+        <v>49827.0</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>12</v>
@@ -9520,10 +9526,10 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>49827.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E308" s="7" t="s">
         <v>12</v>
@@ -9549,16 +9555,16 @@
         <v>13</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>16117.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E309" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F309" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F309" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G309" s="8" t="s">
         <v>61</v>
@@ -9578,16 +9584,16 @@
         <v>13</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>414833.0</v>
+        <v>5125.0</v>
       </c>
       <c r="E310" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F310" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G310" s="8" t="s">
         <v>61</v>
@@ -9604,13 +9610,13 @@
         <v>61</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>5125.0</v>
+        <v>1798.0</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>12</v>
@@ -9662,13 +9668,13 @@
         <v>61</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>2152.0</v>
+        <v>32300.0</v>
       </c>
       <c r="E313" s="7" t="s">
         <v>12</v>
@@ -9723,7 +9729,7 @@
         <v>10</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D315" s="6" t="n">
         <v>2153.0</v>
@@ -9749,19 +9755,19 @@
         <v>61</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>25684.0</v>
+        <v>191.0</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F316" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F316" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G316" s="8" t="s">
         <v>61</v>
@@ -9839,7 +9845,7 @@
         <v>10</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D319" s="6" t="n">
         <v>19353.0</v>
@@ -9865,19 +9871,19 @@
         <v>61</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>191.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F320" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F320" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G320" s="8" t="s">
         <v>61</v>
@@ -9923,13 +9929,13 @@
         <v>61</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>17918.0</v>
+        <v>2152.0</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>12</v>
@@ -9955,10 +9961,10 @@
         <v>30</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>7822.0</v>
+        <v>400544.0</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>12</v>
@@ -9984,10 +9990,10 @@
         <v>30</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>32300.0</v>
+        <v>17918.0</v>
       </c>
       <c r="E324" s="7" t="s">
         <v>12</v>
@@ -10013,10 +10019,10 @@
         <v>30</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D325" s="6" t="n">
-        <v>400544.0</v>
+        <v>7822.0</v>
       </c>
       <c r="E325" s="7" t="s">
         <v>12</v>
@@ -10042,16 +10048,16 @@
         <v>13</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>240445.0</v>
+        <v>288195.0</v>
       </c>
       <c r="E326" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F326" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G326" s="8" t="s">
         <v>62</v>
@@ -10071,16 +10077,16 @@
         <v>13</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D327" s="6" t="n">
-        <v>288195.0</v>
+        <v>1049.0</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F327" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G327" s="8" t="s">
         <v>62</v>
@@ -10100,10 +10106,10 @@
         <v>13</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D328" s="6" t="n">
-        <v>1049.0</v>
+        <v>373443.0</v>
       </c>
       <c r="E328" s="7" t="s">
         <v>12</v>
@@ -10129,16 +10135,16 @@
         <v>13</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D329" s="6" t="n">
-        <v>373443.0</v>
+        <v>177177.0</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F329" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F329" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>62</v>
@@ -10158,16 +10164,16 @@
         <v>13</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D330" s="6" t="n">
-        <v>177177.0</v>
+        <v>15369.0</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F330" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G330" s="8" t="s">
         <v>62</v>
@@ -10187,10 +10193,10 @@
         <v>13</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D331" s="6" t="n">
-        <v>15369.0</v>
+        <v>25040.0</v>
       </c>
       <c r="E331" s="7" t="s">
         <v>12</v>
@@ -10216,10 +10222,10 @@
         <v>13</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D332" s="6" t="n">
-        <v>25040.0</v>
+        <v>16196.0</v>
       </c>
       <c r="E332" s="7" t="s">
         <v>12</v>
@@ -10245,10 +10251,10 @@
         <v>13</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D333" s="6" t="n">
-        <v>16196.0</v>
+        <v>155203.0</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>12</v>
@@ -10274,10 +10280,10 @@
         <v>13</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D334" s="6" t="n">
-        <v>7928.0</v>
+        <v>28904.0</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>12</v>
@@ -10303,10 +10309,10 @@
         <v>13</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D335" s="6" t="n">
-        <v>155203.0</v>
+        <v>7928.0</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>12</v>
@@ -10329,13 +10335,13 @@
         <v>62</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>28904.0</v>
+        <v>182371.0</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>12</v>
@@ -10361,16 +10367,16 @@
         <v>13</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D337" s="6" t="n">
-        <v>39009.0</v>
+        <v>240445.0</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F337" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F337" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G337" s="8" t="s">
         <v>62</v>
@@ -10390,10 +10396,10 @@
         <v>30</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>38261.0</v>
+        <v>1449.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10416,19 +10422,19 @@
         <v>62</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>866.0</v>
+        <v>488224.0</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F339" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F339" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G339" s="8" t="s">
         <v>62</v>
@@ -10503,13 +10509,13 @@
         <v>62</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>1449.0</v>
+        <v>39009.0</v>
       </c>
       <c r="E342" s="7" t="s">
         <v>12</v>
@@ -10532,19 +10538,19 @@
         <v>62</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D343" s="6" t="n">
-        <v>488224.0</v>
+        <v>38261.0</v>
       </c>
       <c r="E343" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F343" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G343" s="8" t="s">
         <v>62</v>
@@ -10619,13 +10625,13 @@
         <v>62</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>182371.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E346" s="7" t="s">
         <v>12</v>
@@ -10651,10 +10657,10 @@
         <v>13</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D347" s="6" t="n">
-        <v>21302.0</v>
+        <v>866.0</v>
       </c>
       <c r="E347" s="7" t="s">
         <v>12</v>
@@ -10996,19 +11002,19 @@
         <v>63</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>96851.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E359" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F359" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F359" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G359" s="8" t="s">
         <v>63</v>
@@ -11025,13 +11031,13 @@
         <v>63</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D360" s="6" t="n">
-        <v>15854.0</v>
+        <v>837.0</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>12</v>
@@ -11054,19 +11060,19 @@
         <v>63</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D361" s="6" t="n">
-        <v>1766.0</v>
+        <v>303397.0</v>
       </c>
       <c r="E361" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F361" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F361" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G361" s="8" t="s">
         <v>63</v>
@@ -11083,13 +11089,13 @@
         <v>63</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D362" s="6" t="n">
-        <v>103343.0</v>
+        <v>82520.0</v>
       </c>
       <c r="E362" s="7" t="s">
         <v>12</v>
@@ -11115,10 +11121,10 @@
         <v>30</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D363" s="6" t="n">
-        <v>42515.0</v>
+        <v>2331.0</v>
       </c>
       <c r="E363" s="7" t="s">
         <v>12</v>
@@ -11141,19 +11147,19 @@
         <v>63</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D364" s="6" t="n">
-        <v>419250.0</v>
+        <v>111759.0</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F364" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>63</v>
@@ -11173,10 +11179,10 @@
         <v>10</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D365" s="6" t="n">
-        <v>2365.0</v>
+        <v>5088.0</v>
       </c>
       <c r="E365" s="7" t="s">
         <v>12</v>
@@ -11202,10 +11208,10 @@
         <v>10</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D366" s="6" t="n">
-        <v>837.0</v>
+        <v>1766.0</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>12</v>
@@ -11231,10 +11237,10 @@
         <v>10</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D367" s="6" t="n">
-        <v>5088.0</v>
+        <v>2365.0</v>
       </c>
       <c r="E367" s="7" t="s">
         <v>12</v>
@@ -11257,19 +11263,19 @@
         <v>63</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D368" s="6" t="n">
-        <v>111759.0</v>
+        <v>96851.0</v>
       </c>
       <c r="E368" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F368" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F368" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G368" s="8" t="s">
         <v>63</v>
@@ -11286,19 +11292,19 @@
         <v>63</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D369" s="6" t="n">
-        <v>2331.0</v>
+        <v>419250.0</v>
       </c>
       <c r="E369" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F369" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F369" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G369" s="8" t="s">
         <v>63</v>
@@ -11318,10 +11324,10 @@
         <v>30</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D370" s="6" t="n">
-        <v>82520.0</v>
+        <v>42515.0</v>
       </c>
       <c r="E370" s="7" t="s">
         <v>12</v>
@@ -11344,19 +11350,19 @@
         <v>63</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D371" s="6" t="n">
-        <v>303397.0</v>
+        <v>103343.0</v>
       </c>
       <c r="E371" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F371" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G371" s="8" t="s">
         <v>63</v>
@@ -11376,10 +11382,10 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>8817.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E372" s="7" t="s">
         <v>12</v>
@@ -11405,16 +11411,16 @@
         <v>13</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D373" s="6" t="n">
-        <v>404269.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E373" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F373" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G373" s="8" t="s">
         <v>64</v>
@@ -11434,10 +11440,10 @@
         <v>13</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D374" s="6" t="n">
-        <v>894.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>12</v>
@@ -11463,10 +11469,10 @@
         <v>13</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D375" s="6" t="n">
-        <v>815.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E375" s="7" t="s">
         <v>12</v>
@@ -11492,10 +11498,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>228939.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11521,10 +11527,10 @@
         <v>13</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D377" s="6" t="n">
-        <v>5337.0</v>
+        <v>228939.0</v>
       </c>
       <c r="E377" s="7" t="s">
         <v>12</v>
@@ -11550,10 +11556,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>102275.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11579,10 +11585,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>96052.0</v>
+        <v>815.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11608,10 +11614,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>4119.0</v>
+        <v>894.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11637,16 +11643,16 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>3681.0</v>
+        <v>404269.0</v>
       </c>
       <c r="E381" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F381" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F381" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>64</v>
@@ -11666,10 +11672,10 @@
         <v>13</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D382" s="6" t="n">
-        <v>91385.0</v>
+        <v>4119.0</v>
       </c>
       <c r="E382" s="7" t="s">
         <v>12</v>
@@ -11692,13 +11698,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>25352.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11721,13 +11727,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>3572.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11753,16 +11759,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D385" s="6" t="n">
-        <v>252681.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E385" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F385" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F385" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G385" s="8" t="s">
         <v>64</v>
@@ -11779,13 +11785,13 @@
         <v>64</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D386" s="6" t="n">
-        <v>14304.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E386" s="7" t="s">
         <v>12</v>
@@ -11869,7 +11875,7 @@
         <v>10</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D389" s="6" t="n">
         <v>18087.0</v>
@@ -11895,13 +11901,13 @@
         <v>64</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>3142.0</v>
+        <v>3572.0</v>
       </c>
       <c r="E390" s="7" t="s">
         <v>12</v>
@@ -11927,10 +11933,10 @@
         <v>30</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D391" s="6" t="n">
-        <v>69259.0</v>
+        <v>7380.0</v>
       </c>
       <c r="E391" s="7" t="s">
         <v>12</v>
@@ -11956,10 +11962,10 @@
         <v>30</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D392" s="6" t="n">
-        <v>7380.0</v>
+        <v>13204.0</v>
       </c>
       <c r="E392" s="7" t="s">
         <v>12</v>
@@ -11985,10 +11991,10 @@
         <v>30</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D393" s="6" t="n">
-        <v>13204.0</v>
+        <v>42128.0</v>
       </c>
       <c r="E393" s="7" t="s">
         <v>12</v>
@@ -12014,10 +12020,10 @@
         <v>30</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D394" s="6" t="n">
-        <v>42128.0</v>
+        <v>12024.0</v>
       </c>
       <c r="E394" s="7" t="s">
         <v>12</v>
@@ -12043,16 +12049,16 @@
         <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>12024.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F395" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F395" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G395" s="8" t="s">
         <v>64</v>
@@ -12217,16 +12223,16 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>728271.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E401" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F401" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>65</v>
@@ -12304,16 +12310,16 @@
         <v>13</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D404" s="6" t="n">
-        <v>65752.0</v>
+        <v>728271.0</v>
       </c>
       <c r="E404" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F404" s="7" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G404" s="8" t="s">
         <v>65</v>
@@ -12504,13 +12510,13 @@
         <v>65</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D411" s="6" t="n">
-        <v>160813.0</v>
+        <v>4067.0</v>
       </c>
       <c r="E411" s="7" t="s">
         <v>12</v>
@@ -12533,19 +12539,19 @@
         <v>65</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D412" s="6" t="n">
-        <v>4067.0</v>
+        <v>285268.0</v>
       </c>
       <c r="E412" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F412" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F412" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G412" s="8" t="s">
         <v>65</v>
@@ -12565,16 +12571,16 @@
         <v>10</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>285268.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E413" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F413" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F413" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G413" s="8" t="s">
         <v>65</v>
@@ -12594,10 +12600,10 @@
         <v>10</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D414" s="6" t="n">
-        <v>217102.0</v>
+        <v>60.0</v>
       </c>
       <c r="E414" s="7" t="s">
         <v>12</v>
@@ -12620,13 +12626,13 @@
         <v>65</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>60.0</v>
+        <v>35159.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12652,10 +12658,10 @@
         <v>30</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D416" s="6" t="n">
-        <v>35159.0</v>
+        <v>548.0</v>
       </c>
       <c r="E416" s="7" t="s">
         <v>12</v>
@@ -12681,10 +12687,10 @@
         <v>30</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D417" s="6" t="n">
-        <v>548.0</v>
+        <v>126986.0</v>
       </c>
       <c r="E417" s="7" t="s">
         <v>12</v>
@@ -12710,10 +12716,10 @@
         <v>30</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D418" s="6" t="n">
-        <v>126986.0</v>
+        <v>7149.0</v>
       </c>
       <c r="E418" s="7" t="s">
         <v>12</v>
@@ -12736,13 +12742,13 @@
         <v>65</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D419" s="6" t="n">
-        <v>7149.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E419" s="7" t="s">
         <v>12</v>
@@ -12826,10 +12832,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>1359.0</v>
+        <v>784.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12942,7 +12948,7 @@
         <v>13</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D426" s="6" t="n">
         <v>210.0</v>
@@ -12971,10 +12977,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>784.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -13000,10 +13006,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>5605.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13145,16 +13151,16 @@
         <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>510218.0</v>
+        <v>35061.0</v>
       </c>
       <c r="E433" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F433" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G433" s="8" t="s">
         <v>66</v>
@@ -13174,10 +13180,10 @@
         <v>13</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D434" s="6" t="n">
-        <v>35061.0</v>
+        <v>1355.0</v>
       </c>
       <c r="E434" s="7" t="s">
         <v>12</v>
@@ -13203,16 +13209,16 @@
         <v>13</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>1355.0</v>
+        <v>510218.0</v>
       </c>
       <c r="E435" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F435" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F435" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G435" s="8" t="s">
         <v>66</v>
@@ -13229,13 +13235,13 @@
         <v>66</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D436" s="6" t="n">
-        <v>5730.0</v>
+        <v>4083.0</v>
       </c>
       <c r="E436" s="7" t="s">
         <v>12</v>
@@ -13258,13 +13264,13 @@
         <v>66</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D437" s="6" t="n">
-        <v>4083.0</v>
+        <v>9349.0</v>
       </c>
       <c r="E437" s="7" t="s">
         <v>12</v>
@@ -13290,10 +13296,10 @@
         <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>9349.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13316,19 +13322,19 @@
         <v>66</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>2197.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E439" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F439" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F439" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G439" s="8" t="s">
         <v>66</v>
@@ -13348,16 +13354,16 @@
         <v>10</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>210756.0</v>
+        <v>209762.0</v>
       </c>
       <c r="E440" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F440" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F440" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G440" s="8" t="s">
         <v>66</v>
@@ -13380,7 +13386,7 @@
         <v>49</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>209762.0</v>
+        <v>4524.0</v>
       </c>
       <c r="E441" s="7" t="s">
         <v>12</v>
@@ -13406,10 +13412,10 @@
         <v>10</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D442" s="6" t="n">
-        <v>4524.0</v>
+        <v>5730.0</v>
       </c>
       <c r="E442" s="7" t="s">
         <v>12</v>
@@ -13493,10 +13499,10 @@
         <v>30</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>1503.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13551,10 +13557,10 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>398394.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E447" s="7" t="s">
         <v>12</v>
@@ -13577,13 +13583,13 @@
         <v>66</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>3803.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E448" s="7" t="s">
         <v>12</v>
@@ -13667,10 +13673,10 @@
         <v>13</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D451" s="6" t="n">
-        <v>872.0</v>
+        <v>47101.0</v>
       </c>
       <c r="E451" s="7" t="s">
         <v>12</v>
@@ -13696,10 +13702,10 @@
         <v>13</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D452" s="6" t="n">
-        <v>420532.0</v>
+        <v>872.0</v>
       </c>
       <c r="E452" s="7" t="s">
         <v>12</v>
@@ -13725,10 +13731,10 @@
         <v>13</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D453" s="6" t="n">
-        <v>175.0</v>
+        <v>420532.0</v>
       </c>
       <c r="E453" s="7" t="s">
         <v>12</v>
@@ -13754,10 +13760,10 @@
         <v>13</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D454" s="6" t="n">
-        <v>47101.0</v>
+        <v>175.0</v>
       </c>
       <c r="E454" s="7" t="s">
         <v>12</v>
@@ -14044,7 +14050,7 @@
         <v>13</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D464" s="6" t="n">
         <v>64823.0</v>
@@ -14073,7 +14079,7 @@
         <v>13</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D465" s="6" t="n">
         <v>13052.0</v>
@@ -14189,7 +14195,7 @@
         <v>10</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D469" s="6" t="n">
         <v>122605.0</v>
@@ -14450,10 +14456,10 @@
         <v>13</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D478" s="6" t="n">
-        <v>158897.0</v>
+        <v>4818.0</v>
       </c>
       <c r="E478" s="7" t="s">
         <v>12</v>
@@ -14479,10 +14485,10 @@
         <v>13</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D479" s="6" t="n">
-        <v>3849.0</v>
+        <v>692.0</v>
       </c>
       <c r="E479" s="7" t="s">
         <v>12</v>
@@ -14508,10 +14514,10 @@
         <v>13</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D480" s="6" t="n">
-        <v>8962.0</v>
+        <v>3849.0</v>
       </c>
       <c r="E480" s="7" t="s">
         <v>12</v>
@@ -14537,10 +14543,10 @@
         <v>13</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D481" s="6" t="n">
-        <v>1252.0</v>
+        <v>8962.0</v>
       </c>
       <c r="E481" s="7" t="s">
         <v>12</v>
@@ -14566,10 +14572,10 @@
         <v>13</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D482" s="6" t="n">
-        <v>4818.0</v>
+        <v>1252.0</v>
       </c>
       <c r="E482" s="7" t="s">
         <v>12</v>
@@ -14595,10 +14601,10 @@
         <v>13</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D483" s="6" t="n">
-        <v>549073.0</v>
+        <v>4118.0</v>
       </c>
       <c r="E483" s="7" t="s">
         <v>12</v>
@@ -14624,10 +14630,10 @@
         <v>13</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D484" s="6" t="n">
-        <v>20516.0</v>
+        <v>158897.0</v>
       </c>
       <c r="E484" s="7" t="s">
         <v>12</v>
@@ -14653,10 +14659,10 @@
         <v>13</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D485" s="6" t="n">
-        <v>4118.0</v>
+        <v>20516.0</v>
       </c>
       <c r="E485" s="7" t="s">
         <v>12</v>
@@ -14682,16 +14688,16 @@
         <v>13</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D486" s="6" t="n">
-        <v>2658.0</v>
+        <v>96503.0</v>
       </c>
       <c r="E486" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F486" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F486" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G486" s="8" t="s">
         <v>68</v>
@@ -14711,10 +14717,10 @@
         <v>13</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D487" s="6" t="n">
-        <v>791.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E487" s="7" t="s">
         <v>12</v>
@@ -14740,16 +14746,16 @@
         <v>13</v>
       </c>
       <c r="C488" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D488" s="6" t="n">
-        <v>108623.0</v>
+        <v>791.0</v>
       </c>
       <c r="E488" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F488" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F488" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G488" s="8" t="s">
         <v>68</v>
@@ -14769,16 +14775,16 @@
         <v>13</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D489" s="6" t="n">
-        <v>692.0</v>
+        <v>108623.0</v>
       </c>
       <c r="E489" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F489" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F489" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G489" s="8" t="s">
         <v>68</v>
@@ -14798,16 +14804,16 @@
         <v>13</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D490" s="6" t="n">
-        <v>96503.0</v>
+        <v>549073.0</v>
       </c>
       <c r="E490" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F490" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F490" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G490" s="8" t="s">
         <v>68</v>
@@ -14824,19 +14830,19 @@
         <v>68</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D491" s="6" t="n">
-        <v>107735.0</v>
+        <v>70327.0</v>
       </c>
       <c r="E491" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F491" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F491" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G491" s="8" t="s">
         <v>68</v>
@@ -14853,13 +14859,13 @@
         <v>68</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D492" s="6" t="n">
-        <v>54343.0</v>
+        <v>15334.0</v>
       </c>
       <c r="E492" s="7" t="s">
         <v>12</v>
@@ -14885,10 +14891,10 @@
         <v>13</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D493" s="6" t="n">
-        <v>70327.0</v>
+        <v>8296.0</v>
       </c>
       <c r="E493" s="7" t="s">
         <v>12</v>
@@ -14943,7 +14949,7 @@
         <v>10</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D495" s="6" t="n">
         <v>170208.0</v>
@@ -14972,7 +14978,7 @@
         <v>10</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D496" s="6" t="n">
         <v>13403.0</v>
@@ -15001,16 +15007,16 @@
         <v>10</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D497" s="6" t="n">
-        <v>15334.0</v>
+        <v>107735.0</v>
       </c>
       <c r="E497" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F497" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F497" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G497" s="8" t="s">
         <v>68</v>
@@ -15030,10 +15036,10 @@
         <v>30</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D498" s="6" t="n">
-        <v>4041.0</v>
+        <v>54343.0</v>
       </c>
       <c r="E498" s="7" t="s">
         <v>12</v>
@@ -15172,13 +15178,13 @@
         <v>68</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D503" s="6" t="n">
-        <v>8296.0</v>
+        <v>4041.0</v>
       </c>
       <c r="E503" s="7" t="s">
         <v>12</v>
@@ -15204,10 +15210,10 @@
         <v>13</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D504" s="6" t="n">
-        <v>248.0</v>
+        <v>4716.0</v>
       </c>
       <c r="E504" s="7" t="s">
         <v>12</v>
@@ -15233,16 +15239,16 @@
         <v>13</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D505" s="6" t="n">
-        <v>72938.0</v>
+        <v>144021.0</v>
       </c>
       <c r="E505" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F505" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F505" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G505" s="8" t="s">
         <v>69</v>
@@ -15262,16 +15268,16 @@
         <v>13</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D506" s="6" t="n">
-        <v>144021.0</v>
+        <v>62084.0</v>
       </c>
       <c r="E506" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F506" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F506" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G506" s="8" t="s">
         <v>69</v>
@@ -15291,10 +15297,10 @@
         <v>13</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D507" s="6" t="n">
-        <v>62084.0</v>
+        <v>123.0</v>
       </c>
       <c r="E507" s="7" t="s">
         <v>12</v>
@@ -15320,10 +15326,10 @@
         <v>13</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D508" s="6" t="n">
-        <v>123.0</v>
+        <v>248.0</v>
       </c>
       <c r="E508" s="7" t="s">
         <v>12</v>
@@ -15349,10 +15355,10 @@
         <v>13</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D509" s="6" t="n">
-        <v>30675.0</v>
+        <v>18261.0</v>
       </c>
       <c r="E509" s="7" t="s">
         <v>12</v>
@@ -15378,10 +15384,10 @@
         <v>13</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D510" s="6" t="n">
-        <v>4716.0</v>
+        <v>201113.0</v>
       </c>
       <c r="E510" s="7" t="s">
         <v>12</v>
@@ -15407,10 +15413,10 @@
         <v>13</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D511" s="6" t="n">
-        <v>201113.0</v>
+        <v>5181.0</v>
       </c>
       <c r="E511" s="7" t="s">
         <v>12</v>
@@ -15436,10 +15442,10 @@
         <v>13</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D512" s="6" t="n">
-        <v>5181.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E512" s="7" t="s">
         <v>12</v>
@@ -15465,16 +15471,16 @@
         <v>13</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D513" s="6" t="n">
-        <v>18261.0</v>
+        <v>908897.0</v>
       </c>
       <c r="E513" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F513" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F513" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G513" s="8" t="s">
         <v>69</v>
@@ -15494,10 +15500,10 @@
         <v>13</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D514" s="6" t="n">
-        <v>1519.0</v>
+        <v>2898.0</v>
       </c>
       <c r="E514" s="7" t="s">
         <v>12</v>
@@ -15523,16 +15529,16 @@
         <v>13</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D515" s="6" t="n">
-        <v>908897.0</v>
+        <v>72938.0</v>
       </c>
       <c r="E515" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F515" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F515" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G515" s="8" t="s">
         <v>69</v>
@@ -15555,7 +15561,7 @@
         <v>45</v>
       </c>
       <c r="D516" s="6" t="n">
-        <v>2898.0</v>
+        <v>30675.0</v>
       </c>
       <c r="E516" s="7" t="s">
         <v>12</v>
@@ -15578,13 +15584,13 @@
         <v>69</v>
       </c>
       <c r="B517" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D517" s="6" t="n">
-        <v>44.0</v>
+        <v>12907.0</v>
       </c>
       <c r="E517" s="7" t="s">
         <v>12</v>
@@ -15607,13 +15613,13 @@
         <v>69</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D518" s="6" t="n">
-        <v>12907.0</v>
+        <v>1195.0</v>
       </c>
       <c r="E518" s="7" t="s">
         <v>12</v>
@@ -15639,10 +15645,10 @@
         <v>10</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D519" s="6" t="n">
-        <v>1408.0</v>
+        <v>44.0</v>
       </c>
       <c r="E519" s="7" t="s">
         <v>12</v>
@@ -15665,19 +15671,19 @@
         <v>69</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D520" s="6" t="n">
-        <v>366304.0</v>
+        <v>372386.0</v>
       </c>
       <c r="E520" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F520" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F520" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G520" s="8" t="s">
         <v>69</v>
@@ -15697,10 +15703,10 @@
         <v>10</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D521" s="6" t="n">
-        <v>372386.0</v>
+        <v>162639.0</v>
       </c>
       <c r="E521" s="7" t="s">
         <v>12</v>
@@ -15729,7 +15735,7 @@
         <v>49</v>
       </c>
       <c r="D522" s="6" t="n">
-        <v>162639.0</v>
+        <v>42853.0</v>
       </c>
       <c r="E522" s="7" t="s">
         <v>12</v>
@@ -15755,10 +15761,10 @@
         <v>10</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D523" s="6" t="n">
-        <v>162695.0</v>
+        <v>1408.0</v>
       </c>
       <c r="E523" s="7" t="s">
         <v>12</v>
@@ -15784,10 +15790,10 @@
         <v>10</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D524" s="6" t="n">
-        <v>42853.0</v>
+        <v>162695.0</v>
       </c>
       <c r="E524" s="7" t="s">
         <v>12</v>
@@ -15810,13 +15816,13 @@
         <v>69</v>
       </c>
       <c r="B525" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D525" s="6" t="n">
-        <v>1195.0</v>
+        <v>77128.0</v>
       </c>
       <c r="E525" s="7" t="s">
         <v>12</v>
@@ -15842,10 +15848,10 @@
         <v>30</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D526" s="6" t="n">
-        <v>77128.0</v>
+        <v>1733.0</v>
       </c>
       <c r="E526" s="7" t="s">
         <v>12</v>
@@ -15871,10 +15877,10 @@
         <v>30</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D527" s="6" t="n">
-        <v>7684.0</v>
+        <v>284063.0</v>
       </c>
       <c r="E527" s="7" t="s">
         <v>12</v>
@@ -15900,10 +15906,10 @@
         <v>30</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D528" s="6" t="n">
-        <v>1733.0</v>
+        <v>26286.0</v>
       </c>
       <c r="E528" s="7" t="s">
         <v>12</v>
@@ -15929,16 +15935,16 @@
         <v>30</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D529" s="6" t="n">
-        <v>284063.0</v>
+        <v>366304.0</v>
       </c>
       <c r="E529" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F529" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F529" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G529" s="8" t="s">
         <v>69</v>
@@ -15958,10 +15964,10 @@
         <v>30</v>
       </c>
       <c r="C530" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D530" s="6" t="n">
-        <v>26286.0</v>
+        <v>7684.0</v>
       </c>
       <c r="E530" s="7" t="s">
         <v>12</v>
@@ -15987,10 +15993,10 @@
         <v>13</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D531" s="6" t="n">
-        <v>8250.0</v>
+        <v>36834.0</v>
       </c>
       <c r="E531" s="7" t="s">
         <v>12</v>
@@ -16016,10 +16022,10 @@
         <v>13</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D532" s="6" t="n">
-        <v>17644.0</v>
+        <v>8250.0</v>
       </c>
       <c r="E532" s="7" t="s">
         <v>12</v>
@@ -16045,10 +16051,10 @@
         <v>13</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D533" s="6" t="n">
-        <v>249.0</v>
+        <v>17644.0</v>
       </c>
       <c r="E533" s="7" t="s">
         <v>12</v>
@@ -16074,10 +16080,10 @@
         <v>13</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D534" s="6" t="n">
-        <v>11404.0</v>
+        <v>249.0</v>
       </c>
       <c r="E534" s="7" t="s">
         <v>12</v>
@@ -16103,10 +16109,10 @@
         <v>13</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D535" s="6" t="n">
-        <v>133084.0</v>
+        <v>11404.0</v>
       </c>
       <c r="E535" s="7" t="s">
         <v>12</v>
@@ -16132,10 +16138,10 @@
         <v>13</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D536" s="6" t="n">
-        <v>712.0</v>
+        <v>133084.0</v>
       </c>
       <c r="E536" s="7" t="s">
         <v>12</v>
@@ -16161,10 +16167,10 @@
         <v>13</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D537" s="6" t="n">
-        <v>36834.0</v>
+        <v>2797.0</v>
       </c>
       <c r="E537" s="7" t="s">
         <v>12</v>
@@ -16248,10 +16254,10 @@
         <v>13</v>
       </c>
       <c r="C540" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D540" s="6" t="n">
-        <v>2797.0</v>
+        <v>357059.0</v>
       </c>
       <c r="E540" s="7" t="s">
         <v>12</v>
@@ -16277,10 +16283,10 @@
         <v>13</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D541" s="6" t="n">
-        <v>357059.0</v>
+        <v>6031.0</v>
       </c>
       <c r="E541" s="7" t="s">
         <v>12</v>
@@ -16306,10 +16312,10 @@
         <v>13</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D542" s="6" t="n">
-        <v>6031.0</v>
+        <v>712.0</v>
       </c>
       <c r="E542" s="7" t="s">
         <v>12</v>
@@ -16390,13 +16396,13 @@
         <v>70</v>
       </c>
       <c r="B545" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D545" s="6" t="n">
-        <v>9668.0</v>
+        <v>68846.0</v>
       </c>
       <c r="E545" s="7" t="s">
         <v>12</v>
@@ -16451,10 +16457,10 @@
         <v>30</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D547" s="6" t="n">
-        <v>98434.0</v>
+        <v>8609.0</v>
       </c>
       <c r="E547" s="7" t="s">
         <v>12</v>
@@ -16477,13 +16483,13 @@
         <v>70</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C548" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D548" s="6" t="n">
-        <v>61145.0</v>
+        <v>49132.0</v>
       </c>
       <c r="E548" s="7" t="s">
         <v>12</v>
@@ -16506,13 +16512,13 @@
         <v>70</v>
       </c>
       <c r="B549" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D549" s="6" t="n">
-        <v>445652.0</v>
+        <v>61145.0</v>
       </c>
       <c r="E549" s="7" t="s">
         <v>12</v>
@@ -16541,7 +16547,7 @@
         <v>49</v>
       </c>
       <c r="D550" s="6" t="n">
-        <v>68846.0</v>
+        <v>5446.0</v>
       </c>
       <c r="E550" s="7" t="s">
         <v>12</v>
@@ -16567,10 +16573,10 @@
         <v>10</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D551" s="6" t="n">
-        <v>5446.0</v>
+        <v>184.0</v>
       </c>
       <c r="E551" s="7" t="s">
         <v>12</v>
@@ -16593,13 +16599,13 @@
         <v>70</v>
       </c>
       <c r="B552" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C552" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D552" s="6" t="n">
-        <v>184.0</v>
+        <v>98434.0</v>
       </c>
       <c r="E552" s="7" t="s">
         <v>12</v>
@@ -16625,10 +16631,10 @@
         <v>10</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D553" s="6" t="n">
-        <v>49132.0</v>
+        <v>445652.0</v>
       </c>
       <c r="E553" s="7" t="s">
         <v>12</v>
@@ -16654,10 +16660,10 @@
         <v>30</v>
       </c>
       <c r="C554" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D554" s="6" t="n">
-        <v>8609.0</v>
+        <v>9668.0</v>
       </c>
       <c r="E554" s="7" t="s">
         <v>12</v>
@@ -16770,10 +16776,10 @@
         <v>13</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D558" s="6" t="n">
-        <v>17014.0</v>
+        <v>833.0</v>
       </c>
       <c r="E558" s="7" t="s">
         <v>12</v>
@@ -16799,10 +16805,10 @@
         <v>13</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D559" s="6" t="n">
-        <v>833.0</v>
+        <v>17014.0</v>
       </c>
       <c r="E559" s="7" t="s">
         <v>12</v>
@@ -16886,10 +16892,10 @@
         <v>13</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D562" s="6" t="n">
-        <v>50267.0</v>
+        <v>135115.0</v>
       </c>
       <c r="E562" s="7" t="s">
         <v>12</v>
@@ -16944,7 +16950,7 @@
         <v>13</v>
       </c>
       <c r="C564" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D564" s="6" t="n">
         <v>388.0</v>
@@ -17205,7 +17211,7 @@
         <v>13</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D573" s="6" t="n">
         <v>73411.0</v>
@@ -17234,7 +17240,7 @@
         <v>13</v>
       </c>
       <c r="C574" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D574" s="6" t="n">
         <v>3016.0</v>
@@ -17263,10 +17269,10 @@
         <v>13</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D575" s="6" t="n">
-        <v>135115.0</v>
+        <v>50267.0</v>
       </c>
       <c r="E575" s="7" t="s">
         <v>12</v>
@@ -17408,10 +17414,10 @@
         <v>10</v>
       </c>
       <c r="C580" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D580" s="6" t="n">
-        <v>4412.0</v>
+        <v>369966.0</v>
       </c>
       <c r="E580" s="7" t="s">
         <v>12</v>
@@ -17437,7 +17443,7 @@
         <v>10</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D581" s="6" t="n">
         <v>30784.0</v>
@@ -17466,7 +17472,7 @@
         <v>10</v>
       </c>
       <c r="C582" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D582" s="6" t="n">
         <v>17930.0</v>
@@ -17495,10 +17501,10 @@
         <v>10</v>
       </c>
       <c r="C583" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D583" s="6" t="n">
-        <v>369907.0</v>
+        <v>4412.0</v>
       </c>
       <c r="E583" s="7" t="s">
         <v>12</v>
@@ -17553,10 +17559,10 @@
         <v>30</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D585" s="6" t="n">
-        <v>160983.0</v>
+        <v>3492.0</v>
       </c>
       <c r="E585" s="7" t="s">
         <v>12</v>
@@ -17582,10 +17588,10 @@
         <v>30</v>
       </c>
       <c r="C586" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D586" s="6" t="n">
-        <v>3492.0</v>
+        <v>267.0</v>
       </c>
       <c r="E586" s="7" t="s">
         <v>12</v>
@@ -17611,16 +17617,16 @@
         <v>30</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D587" s="6" t="n">
-        <v>267.0</v>
+        <v>245314.0</v>
       </c>
       <c r="E587" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F587" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F587" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G587" s="8" t="s">
         <v>71</v>
@@ -17640,16 +17646,16 @@
         <v>30</v>
       </c>
       <c r="C588" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D588" s="6" t="n">
-        <v>245314.0</v>
+        <v>10813.0</v>
       </c>
       <c r="E588" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F588" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F588" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G588" s="8" t="s">
         <v>71</v>
@@ -17669,10 +17675,10 @@
         <v>30</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D589" s="6" t="n">
-        <v>10813.0</v>
+        <v>215594.0</v>
       </c>
       <c r="E589" s="7" t="s">
         <v>12</v>
@@ -17698,10 +17704,10 @@
         <v>30</v>
       </c>
       <c r="C590" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D590" s="6" t="n">
-        <v>215594.0</v>
+        <v>160983.0</v>
       </c>
       <c r="E590" s="7" t="s">
         <v>12</v>
@@ -17727,16 +17733,16 @@
         <v>13</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D591" s="6" t="n">
-        <v>25445.0</v>
+        <v>154891.0</v>
       </c>
       <c r="E591" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F591" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F591" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G591" s="8" t="s">
         <v>72</v>
@@ -17756,16 +17762,16 @@
         <v>13</v>
       </c>
       <c r="C592" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D592" s="6" t="n">
-        <v>46.0</v>
+        <v>481367.0</v>
       </c>
       <c r="E592" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F592" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F592" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G592" s="8" t="s">
         <v>72</v>
@@ -17785,10 +17791,10 @@
         <v>13</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D593" s="6" t="n">
-        <v>46550.0</v>
+        <v>5871.0</v>
       </c>
       <c r="E593" s="7" t="s">
         <v>12</v>
@@ -17814,10 +17820,10 @@
         <v>13</v>
       </c>
       <c r="C594" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D594" s="6" t="n">
-        <v>110968.0</v>
+        <v>21078.0</v>
       </c>
       <c r="E594" s="7" t="s">
         <v>12</v>
@@ -17846,7 +17852,7 @@
         <v>28</v>
       </c>
       <c r="D595" s="6" t="n">
-        <v>1855.0</v>
+        <v>30056.0</v>
       </c>
       <c r="E595" s="7" t="s">
         <v>12</v>
@@ -17872,10 +17878,10 @@
         <v>13</v>
       </c>
       <c r="C596" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D596" s="6" t="n">
-        <v>17402.0</v>
+        <v>3386.0</v>
       </c>
       <c r="E596" s="7" t="s">
         <v>12</v>
@@ -17901,16 +17907,16 @@
         <v>13</v>
       </c>
       <c r="C597" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D597" s="6" t="n">
-        <v>4826.0</v>
+        <v>84215.0</v>
       </c>
       <c r="E597" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F597" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F597" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G597" s="8" t="s">
         <v>72</v>
@@ -17930,16 +17936,16 @@
         <v>13</v>
       </c>
       <c r="C598" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D598" s="6" t="n">
-        <v>270175.0</v>
+        <v>1973.0</v>
       </c>
       <c r="E598" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F598" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F598" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G598" s="8" t="s">
         <v>72</v>
@@ -17959,10 +17965,10 @@
         <v>13</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D599" s="6" t="n">
-        <v>50148.0</v>
+        <v>1132.0</v>
       </c>
       <c r="E599" s="7" t="s">
         <v>12</v>
@@ -17985,19 +17991,19 @@
         <v>72</v>
       </c>
       <c r="B600" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C600" s="5" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D600" s="6" t="n">
-        <v>435.0</v>
+        <v>538223.0</v>
       </c>
       <c r="E600" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F600" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F600" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G600" s="8" t="s">
         <v>72</v>
@@ -18017,16 +18023,16 @@
         <v>13</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D601" s="6" t="n">
-        <v>11787.0</v>
+        <v>60893.0</v>
       </c>
       <c r="E601" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F601" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F601" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G601" s="8" t="s">
         <v>72</v>
@@ -18046,10 +18052,10 @@
         <v>13</v>
       </c>
       <c r="C602" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D602" s="6" t="n">
-        <v>4538.0</v>
+        <v>138808.0</v>
       </c>
       <c r="E602" s="7" t="s">
         <v>12</v>
@@ -18072,13 +18078,13 @@
         <v>72</v>
       </c>
       <c r="B603" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D603" s="6" t="n">
-        <v>36202.0</v>
+        <v>17195.0</v>
       </c>
       <c r="E603" s="7" t="s">
         <v>12</v>
@@ -18101,19 +18107,19 @@
         <v>72</v>
       </c>
       <c r="B604" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C604" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D604" s="6" t="n">
-        <v>148242.0</v>
+        <v>31.0</v>
       </c>
       <c r="E604" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F604" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F604" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G604" s="8" t="s">
         <v>72</v>
@@ -18133,10 +18139,10 @@
         <v>30</v>
       </c>
       <c r="C605" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D605" s="6" t="n">
-        <v>2065.0</v>
+        <v>96.0</v>
       </c>
       <c r="E605" s="7" t="s">
         <v>12</v>
@@ -18159,19 +18165,19 @@
         <v>72</v>
       </c>
       <c r="B606" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C606" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D606" s="6" t="n">
-        <v>236929.0</v>
+        <v>199612.0</v>
       </c>
       <c r="E606" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F606" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F606" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G606" s="8" t="s">
         <v>72</v>
@@ -18188,19 +18194,19 @@
         <v>72</v>
       </c>
       <c r="B607" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D607" s="6" t="n">
-        <v>28201.0</v>
+        <v>413992.0</v>
       </c>
       <c r="E607" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F607" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F607" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G607" s="8" t="s">
         <v>72</v>
@@ -18220,10 +18226,10 @@
         <v>10</v>
       </c>
       <c r="C608" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D608" s="6" t="n">
-        <v>48677.0</v>
+        <v>69940.0</v>
       </c>
       <c r="E608" s="7" t="s">
         <v>12</v>
@@ -18249,10 +18255,10 @@
         <v>10</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D609" s="6" t="n">
-        <v>201801.0</v>
+        <v>4681.0</v>
       </c>
       <c r="E609" s="7" t="s">
         <v>12</v>
@@ -18275,13 +18281,13 @@
         <v>72</v>
       </c>
       <c r="B610" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C610" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D610" s="6" t="n">
-        <v>113095.0</v>
+        <v>76271.0</v>
       </c>
       <c r="E610" s="7" t="s">
         <v>12</v>
@@ -18304,13 +18310,13 @@
         <v>72</v>
       </c>
       <c r="B611" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D611" s="6" t="n">
-        <v>318112.0</v>
+        <v>11956.0</v>
       </c>
       <c r="E611" s="7" t="s">
         <v>12</v>
@@ -18325,6 +18331,1543 @@
         <v>72</v>
       </c>
       <c r="I611" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B612" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C612" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D612" s="6" t="n">
+        <v>393940.0</v>
+      </c>
+      <c r="E612" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F612" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G612" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H612" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I612" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B613" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C613" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D613" s="6" t="n">
+        <v>10252.0</v>
+      </c>
+      <c r="E613" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F613" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G613" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H613" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I613" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B614" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C614" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D614" s="6" t="n">
+        <v>219512.0</v>
+      </c>
+      <c r="E614" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F614" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G614" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H614" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I614" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B615" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D615" s="6" t="n">
+        <v>45738.0</v>
+      </c>
+      <c r="E615" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F615" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G615" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H615" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I615" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B616" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C616" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D616" s="6" t="n">
+        <v>10263.0</v>
+      </c>
+      <c r="E616" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F616" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G616" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H616" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I616" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B617" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C617" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D617" s="6" t="n">
+        <v>681.0</v>
+      </c>
+      <c r="E617" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F617" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G617" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H617" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I617" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B618" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C618" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D618" s="6" t="n">
+        <v>250858.0</v>
+      </c>
+      <c r="E618" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F618" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G618" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H618" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I618" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B619" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C619" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D619" s="6" t="n">
+        <v>597.0</v>
+      </c>
+      <c r="E619" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F619" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G619" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H619" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I619" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B620" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C620" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D620" s="6" t="n">
+        <v>1345.0</v>
+      </c>
+      <c r="E620" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F620" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G620" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H620" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I620" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B621" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C621" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D621" s="6" t="n">
+        <v>3953.0</v>
+      </c>
+      <c r="E621" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F621" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G621" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H621" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I621" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B622" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C622" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D622" s="6" t="n">
+        <v>2658.0</v>
+      </c>
+      <c r="E622" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F622" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G622" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H622" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I622" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B623" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C623" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D623" s="6" t="n">
+        <v>4371.0</v>
+      </c>
+      <c r="E623" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F623" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G623" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H623" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I623" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B624" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C624" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D624" s="6" t="n">
+        <v>83909.0</v>
+      </c>
+      <c r="E624" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F624" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G624" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H624" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I624" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B625" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C625" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D625" s="6" t="n">
+        <v>84856.0</v>
+      </c>
+      <c r="E625" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F625" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G625" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H625" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I625" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B626" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C626" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D626" s="6" t="n">
+        <v>4464.0</v>
+      </c>
+      <c r="E626" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F626" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G626" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H626" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I626" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B627" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C627" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D627" s="6" t="n">
+        <v>386333.0</v>
+      </c>
+      <c r="E627" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F627" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G627" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H627" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I627" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B628" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C628" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D628" s="6" t="n">
+        <v>54493.0</v>
+      </c>
+      <c r="E628" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F628" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G628" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H628" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I628" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B629" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C629" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D629" s="6" t="n">
+        <v>129190.0</v>
+      </c>
+      <c r="E629" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F629" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G629" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H629" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I629" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B630" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C630" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D630" s="6" t="n">
+        <v>139458.0</v>
+      </c>
+      <c r="E630" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F630" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G630" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H630" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I630" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B631" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C631" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D631" s="6" t="n">
+        <v>5327.0</v>
+      </c>
+      <c r="E631" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F631" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G631" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H631" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I631" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B632" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C632" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D632" s="6" t="n">
+        <v>1660.0</v>
+      </c>
+      <c r="E632" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F632" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G632" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H632" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I632" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B633" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C633" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D633" s="6" t="n">
+        <v>6983.0</v>
+      </c>
+      <c r="E633" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F633" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G633" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H633" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I633" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B634" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C634" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D634" s="6" t="n">
+        <v>191571.0</v>
+      </c>
+      <c r="E634" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F634" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G634" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H634" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I634" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B635" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C635" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D635" s="6" t="n">
+        <v>65422.0</v>
+      </c>
+      <c r="E635" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F635" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G635" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H635" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I635" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B636" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C636" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D636" s="6" t="n">
+        <v>511.0</v>
+      </c>
+      <c r="E636" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F636" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G636" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H636" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I636" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B637" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C637" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D637" s="6" t="n">
+        <v>274615.0</v>
+      </c>
+      <c r="E637" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F637" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G637" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H637" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I637" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B638" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C638" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D638" s="6" t="n">
+        <v>43435.0</v>
+      </c>
+      <c r="E638" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F638" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G638" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H638" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I638" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B639" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C639" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D639" s="6" t="n">
+        <v>5387.0</v>
+      </c>
+      <c r="E639" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F639" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G639" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H639" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I639" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B640" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C640" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D640" s="6" t="n">
+        <v>321927.0</v>
+      </c>
+      <c r="E640" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F640" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G640" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H640" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I640" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B641" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C641" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D641" s="6" t="n">
+        <v>107.0</v>
+      </c>
+      <c r="E641" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F641" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G641" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H641" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I641" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B642" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C642" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D642" s="6" t="n">
+        <v>220179.0</v>
+      </c>
+      <c r="E642" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F642" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G642" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H642" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I642" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B643" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C643" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D643" s="6" t="n">
+        <v>28519.0</v>
+      </c>
+      <c r="E643" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F643" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G643" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H643" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I643" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B644" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C644" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D644" s="6" t="n">
+        <v>276.0</v>
+      </c>
+      <c r="E644" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F644" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G644" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H644" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I644" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B645" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C645" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D645" s="6" t="n">
+        <v>9855.0</v>
+      </c>
+      <c r="E645" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F645" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G645" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H645" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I645" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B646" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C646" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D646" s="6" t="n">
+        <v>2352.0</v>
+      </c>
+      <c r="E646" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F646" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G646" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H646" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I646" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B647" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D647" s="6" t="n">
+        <v>31948.0</v>
+      </c>
+      <c r="E647" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F647" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G647" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H647" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I647" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B648" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C648" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D648" s="6" t="n">
+        <v>40742.0</v>
+      </c>
+      <c r="E648" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F648" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G648" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H648" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I648" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B649" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C649" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D649" s="6" t="n">
+        <v>728.0</v>
+      </c>
+      <c r="E649" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F649" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G649" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H649" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I649" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B650" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C650" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D650" s="6" t="n">
+        <v>157451.0</v>
+      </c>
+      <c r="E650" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F650" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G650" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H650" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I650" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B651" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D651" s="6" t="n">
+        <v>34568.0</v>
+      </c>
+      <c r="E651" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F651" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G651" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H651" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I651" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B652" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C652" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D652" s="6" t="n">
+        <v>19733.0</v>
+      </c>
+      <c r="E652" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F652" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G652" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H652" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I652" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B653" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D653" s="6" t="n">
+        <v>7631.0</v>
+      </c>
+      <c r="E653" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F653" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G653" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H653" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I653" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B654" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C654" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D654" s="6" t="n">
+        <v>4299.0</v>
+      </c>
+      <c r="E654" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F654" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G654" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H654" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I654" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B655" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D655" s="6" t="n">
+        <v>875.0</v>
+      </c>
+      <c r="E655" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F655" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G655" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H655" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I655" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B656" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C656" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D656" s="6" t="n">
+        <v>67027.0</v>
+      </c>
+      <c r="E656" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F656" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G656" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H656" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I656" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B657" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D657" s="6" t="n">
+        <v>2608.0</v>
+      </c>
+      <c r="E657" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F657" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G657" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H657" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I657" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B658" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C658" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D658" s="6" t="n">
+        <v>92663.0</v>
+      </c>
+      <c r="E658" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F658" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G658" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H658" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I658" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B659" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C659" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D659" s="6" t="n">
+        <v>3247.0</v>
+      </c>
+      <c r="E659" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F659" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G659" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H659" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I659" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B660" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C660" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D660" s="6" t="n">
+        <v>44991.0</v>
+      </c>
+      <c r="E660" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F660" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G660" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H660" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I660" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B661" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C661" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D661" s="6" t="n">
+        <v>19955.0</v>
+      </c>
+      <c r="E661" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F661" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G661" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H661" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I661" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B662" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C662" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D662" s="6" t="n">
+        <v>118275.0</v>
+      </c>
+      <c r="E662" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F662" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G662" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H662" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I662" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B663" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C663" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D663" s="6" t="n">
+        <v>60517.0</v>
+      </c>
+      <c r="E663" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F663" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G663" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H663" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I663" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B664" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C664" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D664" s="6" t="n">
+        <v>234255.0</v>
+      </c>
+      <c r="E664" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F664" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G664" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H664" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I664" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5226" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5488" uniqueCount="81">
   <si>
     <t>Ngày</t>
   </si>
@@ -237,6 +237,24 @@
   </si>
   <si>
     <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>120254199946640712</t>
+  </si>
+  <si>
+    <t>120254199946650712</t>
+  </si>
+  <si>
+    <t>120254199946660712</t>
+  </si>
+  <si>
+    <t>120254199840830712</t>
+  </si>
+  <si>
+    <t>120254199840840712</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
   </si>
 </sst>
 </file>
@@ -600,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I664"/>
+  <dimension ref="A1:I697"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -5408,10 +5426,10 @@
         <v>13</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>171781.0</v>
+        <v>35065.0</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
@@ -5640,10 +5658,10 @@
         <v>13</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>10115.0</v>
+        <v>39617.0</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>12</v>
@@ -5669,10 +5687,10 @@
         <v>13</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>35065.0</v>
+        <v>10115.0</v>
       </c>
       <c r="E175" s="7" t="s">
         <v>12</v>
@@ -5695,13 +5713,13 @@
         <v>56</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>1182.0</v>
+        <v>171781.0</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>12</v>
@@ -5724,19 +5742,19 @@
         <v>56</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>39617.0</v>
+        <v>115261.0</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F177" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F177" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>56</v>
@@ -5872,10 +5890,10 @@
         <v>10</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>24571.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>12</v>
@@ -5901,16 +5919,16 @@
         <v>30</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>115261.0</v>
+        <v>275877.0</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F183" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G183" s="8" t="s">
         <v>56</v>
@@ -5985,13 +6003,13 @@
         <v>56</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>8022.0</v>
+        <v>24571.0</v>
       </c>
       <c r="E186" s="7" t="s">
         <v>12</v>
@@ -6017,16 +6035,16 @@
         <v>30</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>275877.0</v>
+        <v>8022.0</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F187" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G187" s="8" t="s">
         <v>56</v>
@@ -6449,19 +6467,19 @@
         <v>57</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>28338.0</v>
+        <v>476600.0</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F202" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F202" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>57</v>
@@ -6478,13 +6496,13 @@
         <v>57</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>28802.0</v>
+        <v>13066.0</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>12</v>
@@ -6510,10 +6528,10 @@
         <v>13</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>1573.0</v>
+        <v>195553.0</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>12</v>
@@ -6536,19 +6554,19 @@
         <v>57</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>43423.0</v>
+        <v>264473.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F205" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>57</v>
@@ -6568,10 +6586,10 @@
         <v>30</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>83141.0</v>
+        <v>9109.0</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>12</v>
@@ -6597,10 +6615,10 @@
         <v>30</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>49095.0</v>
+        <v>210.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6626,10 +6644,10 @@
         <v>30</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>74588.0</v>
+        <v>28338.0</v>
       </c>
       <c r="E208" s="7" t="s">
         <v>12</v>
@@ -6655,10 +6673,10 @@
         <v>30</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>13066.0</v>
+        <v>74588.0</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>12</v>
@@ -6684,10 +6702,10 @@
         <v>30</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>210.0</v>
+        <v>49095.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6713,10 +6731,10 @@
         <v>30</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>9109.0</v>
+        <v>83141.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6739,19 +6757,19 @@
         <v>57</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>264473.0</v>
+        <v>43423.0</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F212" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G212" s="8" t="s">
         <v>57</v>
@@ -6771,10 +6789,10 @@
         <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>195553.0</v>
+        <v>1573.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6797,19 +6815,19 @@
         <v>57</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>476600.0</v>
+        <v>28802.0</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F214" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F214" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G214" s="8" t="s">
         <v>57</v>
@@ -6829,10 +6847,10 @@
         <v>13</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>2938.0</v>
+        <v>28745.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6858,10 +6876,10 @@
         <v>13</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>21893.0</v>
+        <v>8204.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
@@ -6887,10 +6905,10 @@
         <v>13</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>400774.0</v>
+        <v>2938.0</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>12</v>
@@ -6916,10 +6934,10 @@
         <v>13</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>8204.0</v>
+        <v>21893.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6945,10 +6963,10 @@
         <v>13</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>28745.0</v>
+        <v>47108.0</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>12</v>
@@ -6974,10 +6992,10 @@
         <v>13</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>47108.0</v>
+        <v>400774.0</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>12</v>
@@ -7003,10 +7021,10 @@
         <v>13</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>1087.0</v>
+        <v>142958.0</v>
       </c>
       <c r="E221" s="7" t="s">
         <v>12</v>
@@ -7032,16 +7050,16 @@
         <v>13</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>142958.0</v>
+        <v>55407.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F222" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F222" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>58</v>
@@ -7061,16 +7079,16 @@
         <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>55407.0</v>
+        <v>8125.0</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F223" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>58</v>
@@ -7090,16 +7108,16 @@
         <v>13</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>8125.0</v>
+        <v>570723.0</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F224" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>58</v>
@@ -7119,16 +7137,16 @@
         <v>13</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>570723.0</v>
+        <v>17602.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F225" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>58</v>
@@ -7148,10 +7166,10 @@
         <v>13</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>17602.0</v>
+        <v>1087.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7290,13 +7308,13 @@
         <v>58</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>52019.0</v>
+        <v>74089.0</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>12</v>
@@ -7319,13 +7337,13 @@
         <v>58</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>74089.0</v>
+        <v>52019.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>12</v>
@@ -7641,16 +7659,16 @@
         <v>13</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D243" s="6" t="n">
-        <v>27632.0</v>
+        <v>118119.0</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F243" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F243" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>59</v>
@@ -7670,16 +7688,16 @@
         <v>13</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D244" s="6" t="n">
-        <v>118119.0</v>
+        <v>284471.0</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F244" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>59</v>
@@ -7699,16 +7717,16 @@
         <v>13</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D245" s="6" t="n">
-        <v>284471.0</v>
+        <v>5434.0</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F245" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F245" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G245" s="8" t="s">
         <v>59</v>
@@ -7728,10 +7746,10 @@
         <v>13</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D246" s="6" t="n">
-        <v>5434.0</v>
+        <v>1388.0</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>12</v>
@@ -7757,16 +7775,16 @@
         <v>13</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>1388.0</v>
+        <v>371730.0</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F247" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F247" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>59</v>
@@ -7786,16 +7804,16 @@
         <v>13</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>371730.0</v>
+        <v>509.0</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F248" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>59</v>
@@ -7815,10 +7833,10 @@
         <v>13</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>509.0</v>
+        <v>23722.0</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>12</v>
@@ -7844,10 +7862,10 @@
         <v>13</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>23722.0</v>
+        <v>279499.0</v>
       </c>
       <c r="E250" s="7" t="s">
         <v>12</v>
@@ -7873,10 +7891,10 @@
         <v>13</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>279499.0</v>
+        <v>33073.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>12</v>
@@ -7902,10 +7920,10 @@
         <v>13</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>33073.0</v>
+        <v>160.0</v>
       </c>
       <c r="E252" s="7" t="s">
         <v>12</v>
@@ -7931,10 +7949,10 @@
         <v>13</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>3296.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E253" s="7" t="s">
         <v>12</v>
@@ -7960,10 +7978,10 @@
         <v>13</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>160.0</v>
+        <v>27632.0</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>12</v>
@@ -7989,10 +8007,10 @@
         <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>5458.0</v>
+        <v>3296.0</v>
       </c>
       <c r="E255" s="7" t="s">
         <v>12</v>
@@ -8044,13 +8062,13 @@
         <v>59</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>27683.0</v>
+        <v>790.0</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>12</v>
@@ -8073,13 +8091,13 @@
         <v>59</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>790.0</v>
+        <v>27683.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8102,13 +8120,13 @@
         <v>59</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>160020.0</v>
+        <v>31570.0</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>12</v>
@@ -8134,10 +8152,10 @@
         <v>10</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>3186.0</v>
+        <v>566118.0</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>12</v>
@@ -8163,10 +8181,10 @@
         <v>10</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>31570.0</v>
+        <v>25241.0</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>12</v>
@@ -8192,10 +8210,10 @@
         <v>10</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>566118.0</v>
+        <v>32891.0</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>12</v>
@@ -8221,10 +8239,10 @@
         <v>10</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>32891.0</v>
+        <v>3186.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8247,13 +8265,13 @@
         <v>59</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>25241.0</v>
+        <v>302914.0</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>12</v>
@@ -8279,10 +8297,10 @@
         <v>30</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>302914.0</v>
+        <v>150.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8308,10 +8326,10 @@
         <v>30</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>10553.0</v>
+        <v>6744.0</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>12</v>
@@ -8337,10 +8355,10 @@
         <v>30</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>150.0</v>
+        <v>47292.0</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>12</v>
@@ -8366,10 +8384,10 @@
         <v>30</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D268" s="6" t="n">
-        <v>6744.0</v>
+        <v>7698.0</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>12</v>
@@ -8395,10 +8413,10 @@
         <v>30</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>47292.0</v>
+        <v>160020.0</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>12</v>
@@ -8424,10 +8442,10 @@
         <v>30</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>7698.0</v>
+        <v>10553.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8453,10 +8471,10 @@
         <v>13</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D271" s="6" t="n">
-        <v>233437.0</v>
+        <v>40129.0</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>12</v>
@@ -8482,10 +8500,10 @@
         <v>13</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D272" s="6" t="n">
-        <v>15.0</v>
+        <v>20732.0</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>12</v>
@@ -8511,10 +8529,10 @@
         <v>13</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D273" s="6" t="n">
-        <v>20732.0</v>
+        <v>6937.0</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>12</v>
@@ -8540,10 +8558,10 @@
         <v>13</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D274" s="6" t="n">
-        <v>6937.0</v>
+        <v>15068.0</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>12</v>
@@ -8569,10 +8587,10 @@
         <v>13</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D275" s="6" t="n">
-        <v>15068.0</v>
+        <v>26381.0</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>12</v>
@@ -8598,10 +8616,10 @@
         <v>13</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D276" s="6" t="n">
-        <v>26381.0</v>
+        <v>233437.0</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>12</v>
@@ -8627,10 +8645,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>2731.0</v>
+        <v>96105.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8656,10 +8674,10 @@
         <v>13</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D278" s="6" t="n">
-        <v>40129.0</v>
+        <v>115.0</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>12</v>
@@ -8685,10 +8703,10 @@
         <v>13</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D279" s="6" t="n">
-        <v>115.0</v>
+        <v>3979.0</v>
       </c>
       <c r="E279" s="7" t="s">
         <v>12</v>
@@ -8743,10 +8761,10 @@
         <v>13</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>96105.0</v>
+        <v>38472.0</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>12</v>
@@ -8772,10 +8790,10 @@
         <v>13</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>38472.0</v>
+        <v>2731.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8801,10 +8819,10 @@
         <v>13</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>220465.0</v>
+        <v>35463.0</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>12</v>
@@ -8830,10 +8848,10 @@
         <v>13</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>35463.0</v>
+        <v>15.0</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>12</v>
@@ -8859,10 +8877,10 @@
         <v>13</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>3979.0</v>
+        <v>20130.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8888,16 +8906,16 @@
         <v>13</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>168847.0</v>
+        <v>220465.0</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F286" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G286" s="8" t="s">
         <v>60</v>
@@ -8914,19 +8932,19 @@
         <v>60</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D287" s="6" t="n">
-        <v>1780.0</v>
+        <v>318547.0</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F287" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F287" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G287" s="8" t="s">
         <v>60</v>
@@ -8943,13 +8961,13 @@
         <v>60</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>20130.0</v>
+        <v>1308.0</v>
       </c>
       <c r="E288" s="7" t="s">
         <v>12</v>
@@ -8975,16 +8993,16 @@
         <v>10</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>1308.0</v>
+        <v>621367.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F289" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F289" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>60</v>
@@ -9001,19 +9019,19 @@
         <v>60</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>6706.0</v>
+        <v>168847.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F290" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F290" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>60</v>
@@ -9091,16 +9109,16 @@
         <v>10</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>621367.0</v>
+        <v>1780.0</v>
       </c>
       <c r="E293" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F293" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F293" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G293" s="8" t="s">
         <v>60</v>
@@ -9117,19 +9135,19 @@
         <v>60</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>318547.0</v>
+        <v>6706.0</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F294" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F294" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G294" s="8" t="s">
         <v>60</v>
@@ -9149,10 +9167,10 @@
         <v>30</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>11792.0</v>
+        <v>27356.0</v>
       </c>
       <c r="E295" s="7" t="s">
         <v>12</v>
@@ -9236,16 +9254,16 @@
         <v>30</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>18189.0</v>
+        <v>87988.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F298" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>60</v>
@@ -9265,16 +9283,16 @@
         <v>30</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>87988.0</v>
+        <v>18189.0</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F299" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F299" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G299" s="8" t="s">
         <v>60</v>
@@ -9294,10 +9312,10 @@
         <v>30</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>27356.0</v>
+        <v>11792.0</v>
       </c>
       <c r="E300" s="7" t="s">
         <v>12</v>
@@ -9320,13 +9338,13 @@
         <v>61</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>4517.0</v>
+        <v>1798.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9439,10 +9457,10 @@
         <v>13</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>18161.0</v>
+        <v>4517.0</v>
       </c>
       <c r="E305" s="7" t="s">
         <v>12</v>
@@ -9468,10 +9486,10 @@
         <v>13</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>10887.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E306" s="7" t="s">
         <v>12</v>
@@ -9497,10 +9515,10 @@
         <v>13</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>49827.0</v>
+        <v>10887.0</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>12</v>
@@ -9526,10 +9544,10 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>16117.0</v>
+        <v>49827.0</v>
       </c>
       <c r="E308" s="7" t="s">
         <v>12</v>
@@ -9555,16 +9573,16 @@
         <v>13</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>414833.0</v>
+        <v>18161.0</v>
       </c>
       <c r="E309" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F309" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F309" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G309" s="8" t="s">
         <v>61</v>
@@ -9584,16 +9602,16 @@
         <v>13</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>5125.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E310" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F310" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F310" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G310" s="8" t="s">
         <v>61</v>
@@ -9610,13 +9628,13 @@
         <v>61</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>1798.0</v>
+        <v>5125.0</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>12</v>
@@ -9668,13 +9686,13 @@
         <v>61</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>32300.0</v>
+        <v>2152.0</v>
       </c>
       <c r="E313" s="7" t="s">
         <v>12</v>
@@ -9929,13 +9947,13 @@
         <v>61</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>2152.0</v>
+        <v>400544.0</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>12</v>
@@ -9961,10 +9979,10 @@
         <v>30</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>400544.0</v>
+        <v>17918.0</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>12</v>
@@ -9990,10 +10008,10 @@
         <v>30</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>17918.0</v>
+        <v>7822.0</v>
       </c>
       <c r="E324" s="7" t="s">
         <v>12</v>
@@ -10019,10 +10037,10 @@
         <v>30</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D325" s="6" t="n">
-        <v>7822.0</v>
+        <v>32300.0</v>
       </c>
       <c r="E325" s="7" t="s">
         <v>12</v>
@@ -10251,10 +10269,10 @@
         <v>13</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D333" s="6" t="n">
-        <v>155203.0</v>
+        <v>28904.0</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>12</v>
@@ -10280,10 +10298,10 @@
         <v>13</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D334" s="6" t="n">
-        <v>28904.0</v>
+        <v>7928.0</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>12</v>
@@ -10309,10 +10327,10 @@
         <v>13</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D335" s="6" t="n">
-        <v>7928.0</v>
+        <v>155203.0</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>12</v>
@@ -10335,13 +10353,13 @@
         <v>62</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>182371.0</v>
+        <v>39009.0</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>12</v>
@@ -10393,13 +10411,13 @@
         <v>62</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>1449.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10422,19 +10440,19 @@
         <v>62</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>488224.0</v>
+        <v>182371.0</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F339" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G339" s="8" t="s">
         <v>62</v>
@@ -10454,10 +10472,10 @@
         <v>30</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D340" s="6" t="n">
-        <v>256566.0</v>
+        <v>177268.0</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>12</v>
@@ -10483,10 +10501,10 @@
         <v>30</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D341" s="6" t="n">
-        <v>6148.0</v>
+        <v>15943.0</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>12</v>
@@ -10509,13 +10527,13 @@
         <v>62</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>39009.0</v>
+        <v>38261.0</v>
       </c>
       <c r="E342" s="7" t="s">
         <v>12</v>
@@ -10541,10 +10559,10 @@
         <v>30</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D343" s="6" t="n">
-        <v>38261.0</v>
+        <v>1449.0</v>
       </c>
       <c r="E343" s="7" t="s">
         <v>12</v>
@@ -10570,10 +10588,10 @@
         <v>30</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D344" s="6" t="n">
-        <v>15943.0</v>
+        <v>6148.0</v>
       </c>
       <c r="E344" s="7" t="s">
         <v>12</v>
@@ -10599,10 +10617,10 @@
         <v>30</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D345" s="6" t="n">
-        <v>177268.0</v>
+        <v>256566.0</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>12</v>
@@ -10625,19 +10643,19 @@
         <v>62</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>21302.0</v>
+        <v>488224.0</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F346" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F346" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G346" s="8" t="s">
         <v>62</v>
@@ -10686,10 +10704,10 @@
         <v>13</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D348" s="6" t="n">
-        <v>69412.0</v>
+        <v>14390.0</v>
       </c>
       <c r="E348" s="7" t="s">
         <v>12</v>
@@ -10715,10 +10733,10 @@
         <v>13</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D349" s="6" t="n">
-        <v>7560.0</v>
+        <v>9380.0</v>
       </c>
       <c r="E349" s="7" t="s">
         <v>12</v>
@@ -10744,10 +10762,10 @@
         <v>13</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D350" s="6" t="n">
-        <v>805776.0</v>
+        <v>185.0</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>12</v>
@@ -10773,10 +10791,10 @@
         <v>13</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D351" s="6" t="n">
-        <v>14289.0</v>
+        <v>7510.0</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>12</v>
@@ -10802,10 +10820,10 @@
         <v>13</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D352" s="6" t="n">
-        <v>62866.0</v>
+        <v>7560.0</v>
       </c>
       <c r="E352" s="7" t="s">
         <v>12</v>
@@ -10860,10 +10878,10 @@
         <v>13</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D354" s="6" t="n">
-        <v>14390.0</v>
+        <v>62866.0</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>12</v>
@@ -10889,10 +10907,10 @@
         <v>13</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D355" s="6" t="n">
-        <v>7510.0</v>
+        <v>14289.0</v>
       </c>
       <c r="E355" s="7" t="s">
         <v>12</v>
@@ -10918,10 +10936,10 @@
         <v>13</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D356" s="6" t="n">
-        <v>185.0</v>
+        <v>69412.0</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>12</v>
@@ -10947,10 +10965,10 @@
         <v>13</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D357" s="6" t="n">
-        <v>9380.0</v>
+        <v>805776.0</v>
       </c>
       <c r="E357" s="7" t="s">
         <v>12</v>
@@ -11002,19 +11020,19 @@
         <v>63</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>15854.0</v>
+        <v>419250.0</v>
       </c>
       <c r="E359" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F359" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F359" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G359" s="8" t="s">
         <v>63</v>
@@ -11031,13 +11049,13 @@
         <v>63</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D360" s="6" t="n">
-        <v>837.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>12</v>
@@ -11060,19 +11078,19 @@
         <v>63</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D361" s="6" t="n">
-        <v>303397.0</v>
+        <v>1766.0</v>
       </c>
       <c r="E361" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F361" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G361" s="8" t="s">
         <v>63</v>
@@ -11092,10 +11110,10 @@
         <v>30</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D362" s="6" t="n">
-        <v>82520.0</v>
+        <v>42515.0</v>
       </c>
       <c r="E362" s="7" t="s">
         <v>12</v>
@@ -11118,13 +11136,13 @@
         <v>63</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D363" s="6" t="n">
-        <v>2331.0</v>
+        <v>837.0</v>
       </c>
       <c r="E363" s="7" t="s">
         <v>12</v>
@@ -11147,19 +11165,19 @@
         <v>63</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D364" s="6" t="n">
-        <v>111759.0</v>
+        <v>96851.0</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F364" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F364" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>63</v>
@@ -11179,10 +11197,10 @@
         <v>10</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D365" s="6" t="n">
-        <v>5088.0</v>
+        <v>2365.0</v>
       </c>
       <c r="E365" s="7" t="s">
         <v>12</v>
@@ -11208,10 +11226,10 @@
         <v>10</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D366" s="6" t="n">
-        <v>1766.0</v>
+        <v>103343.0</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>12</v>
@@ -11237,10 +11255,10 @@
         <v>10</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D367" s="6" t="n">
-        <v>2365.0</v>
+        <v>5088.0</v>
       </c>
       <c r="E367" s="7" t="s">
         <v>12</v>
@@ -11263,19 +11281,19 @@
         <v>63</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D368" s="6" t="n">
-        <v>96851.0</v>
+        <v>111759.0</v>
       </c>
       <c r="E368" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F368" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G368" s="8" t="s">
         <v>63</v>
@@ -11292,19 +11310,19 @@
         <v>63</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D369" s="6" t="n">
-        <v>419250.0</v>
+        <v>2331.0</v>
       </c>
       <c r="E369" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F369" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G369" s="8" t="s">
         <v>63</v>
@@ -11324,10 +11342,10 @@
         <v>30</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D370" s="6" t="n">
-        <v>42515.0</v>
+        <v>82520.0</v>
       </c>
       <c r="E370" s="7" t="s">
         <v>12</v>
@@ -11350,19 +11368,19 @@
         <v>63</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D371" s="6" t="n">
-        <v>103343.0</v>
+        <v>303397.0</v>
       </c>
       <c r="E371" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F371" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F371" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G371" s="8" t="s">
         <v>63</v>
@@ -11382,10 +11400,10 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>5337.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E372" s="7" t="s">
         <v>12</v>
@@ -11411,16 +11429,16 @@
         <v>13</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D373" s="6" t="n">
-        <v>96052.0</v>
+        <v>404269.0</v>
       </c>
       <c r="E373" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F373" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F373" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G373" s="8" t="s">
         <v>64</v>
@@ -11440,10 +11458,10 @@
         <v>13</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D374" s="6" t="n">
-        <v>102275.0</v>
+        <v>894.0</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>12</v>
@@ -11469,10 +11487,10 @@
         <v>13</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D375" s="6" t="n">
-        <v>3142.0</v>
+        <v>815.0</v>
       </c>
       <c r="E375" s="7" t="s">
         <v>12</v>
@@ -11498,10 +11516,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>3681.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11556,10 +11574,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>91385.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11585,10 +11603,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>815.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11614,10 +11632,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>894.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11643,16 +11661,16 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>404269.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E381" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F381" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F381" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>64</v>
@@ -11698,13 +11716,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>14304.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11727,13 +11745,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>8817.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -12107,10 +12125,10 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D397" s="6" t="n">
-        <v>2360.0</v>
+        <v>5282.0</v>
       </c>
       <c r="E397" s="7" t="s">
         <v>12</v>
@@ -12136,10 +12154,10 @@
         <v>13</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D398" s="6" t="n">
-        <v>5282.0</v>
+        <v>5080.0</v>
       </c>
       <c r="E398" s="7" t="s">
         <v>12</v>
@@ -12223,10 +12241,10 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>65752.0</v>
+        <v>9750.0</v>
       </c>
       <c r="E401" s="7" t="s">
         <v>16</v>
@@ -12397,16 +12415,16 @@
         <v>13</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D407" s="6" t="n">
-        <v>9750.0</v>
+        <v>2360.0</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F407" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G407" s="8" t="s">
         <v>65</v>
@@ -12423,19 +12441,19 @@
         <v>65</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>5080.0</v>
+        <v>285268.0</v>
       </c>
       <c r="E408" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F408" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F408" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G408" s="8" t="s">
         <v>65</v>
@@ -12455,16 +12473,16 @@
         <v>13</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D409" s="6" t="n">
-        <v>73210.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E409" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F409" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F409" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G409" s="8" t="s">
         <v>65</v>
@@ -12513,10 +12531,10 @@
         <v>13</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D411" s="6" t="n">
-        <v>4067.0</v>
+        <v>73210.0</v>
       </c>
       <c r="E411" s="7" t="s">
         <v>12</v>
@@ -12542,16 +12560,16 @@
         <v>10</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D412" s="6" t="n">
-        <v>285268.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E412" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F412" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F412" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G412" s="8" t="s">
         <v>65</v>
@@ -12571,10 +12589,10 @@
         <v>10</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>217102.0</v>
+        <v>60.0</v>
       </c>
       <c r="E413" s="7" t="s">
         <v>12</v>
@@ -12597,13 +12615,13 @@
         <v>65</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D414" s="6" t="n">
-        <v>60.0</v>
+        <v>35159.0</v>
       </c>
       <c r="E414" s="7" t="s">
         <v>12</v>
@@ -12626,13 +12644,13 @@
         <v>65</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>35159.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12687,10 +12705,10 @@
         <v>30</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D417" s="6" t="n">
-        <v>126986.0</v>
+        <v>7149.0</v>
       </c>
       <c r="E417" s="7" t="s">
         <v>12</v>
@@ -12716,16 +12734,16 @@
         <v>30</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D418" s="6" t="n">
-        <v>7149.0</v>
+        <v>594911.0</v>
       </c>
       <c r="E418" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F418" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F418" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G418" s="8" t="s">
         <v>65</v>
@@ -12742,13 +12760,13 @@
         <v>65</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D419" s="6" t="n">
-        <v>160813.0</v>
+        <v>39117.0</v>
       </c>
       <c r="E419" s="7" t="s">
         <v>12</v>
@@ -12771,19 +12789,19 @@
         <v>65</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D420" s="6" t="n">
-        <v>594911.0</v>
+        <v>4067.0</v>
       </c>
       <c r="E420" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F420" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F420" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G420" s="8" t="s">
         <v>65</v>
@@ -12803,10 +12821,10 @@
         <v>30</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>39117.0</v>
+        <v>126986.0</v>
       </c>
       <c r="E421" s="7" t="s">
         <v>12</v>
@@ -12832,10 +12850,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>784.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12861,10 +12879,10 @@
         <v>13</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D423" s="6" t="n">
-        <v>44956.0</v>
+        <v>58027.0</v>
       </c>
       <c r="E423" s="7" t="s">
         <v>12</v>
@@ -12890,10 +12908,10 @@
         <v>13</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D424" s="6" t="n">
-        <v>58027.0</v>
+        <v>8420.0</v>
       </c>
       <c r="E424" s="7" t="s">
         <v>12</v>
@@ -12919,10 +12937,10 @@
         <v>13</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D425" s="6" t="n">
-        <v>8420.0</v>
+        <v>210.0</v>
       </c>
       <c r="E425" s="7" t="s">
         <v>12</v>
@@ -12948,10 +12966,10 @@
         <v>13</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D426" s="6" t="n">
-        <v>210.0</v>
+        <v>784.0</v>
       </c>
       <c r="E426" s="7" t="s">
         <v>12</v>
@@ -12977,10 +12995,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>5605.0</v>
+        <v>4241.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -13006,10 +13024,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>1359.0</v>
+        <v>8146.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13035,10 +13053,10 @@
         <v>13</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D429" s="6" t="n">
-        <v>8146.0</v>
+        <v>261758.0</v>
       </c>
       <c r="E429" s="7" t="s">
         <v>12</v>
@@ -13064,10 +13082,10 @@
         <v>13</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D430" s="6" t="n">
-        <v>261758.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E430" s="7" t="s">
         <v>12</v>
@@ -13093,16 +13111,16 @@
         <v>13</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>70064.0</v>
+        <v>510218.0</v>
       </c>
       <c r="E431" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F431" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F431" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G431" s="8" t="s">
         <v>66</v>
@@ -13122,10 +13140,10 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>4241.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E432" s="7" t="s">
         <v>12</v>
@@ -13180,10 +13198,10 @@
         <v>13</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D434" s="6" t="n">
-        <v>1355.0</v>
+        <v>44956.0</v>
       </c>
       <c r="E434" s="7" t="s">
         <v>12</v>
@@ -13209,16 +13227,16 @@
         <v>13</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>510218.0</v>
+        <v>1355.0</v>
       </c>
       <c r="E435" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F435" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F435" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G435" s="8" t="s">
         <v>66</v>
@@ -13293,13 +13311,13 @@
         <v>66</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>3803.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13325,16 +13343,16 @@
         <v>10</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>210756.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E439" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F439" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F439" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G439" s="8" t="s">
         <v>66</v>
@@ -13441,16 +13459,16 @@
         <v>10</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>108610.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E443" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F443" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F443" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G443" s="8" t="s">
         <v>66</v>
@@ -13499,10 +13517,10 @@
         <v>30</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>398394.0</v>
+        <v>1412.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13528,16 +13546,16 @@
         <v>30</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D446" s="6" t="n">
-        <v>105.0</v>
+        <v>94352.0</v>
       </c>
       <c r="E446" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F446" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F446" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G446" s="8" t="s">
         <v>66</v>
@@ -13557,10 +13575,10 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>2197.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E447" s="7" t="s">
         <v>12</v>
@@ -13586,10 +13604,10 @@
         <v>30</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>1503.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E448" s="7" t="s">
         <v>12</v>
@@ -13612,19 +13630,19 @@
         <v>66</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D449" s="6" t="n">
-        <v>94352.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E449" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F449" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F449" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G449" s="8" t="s">
         <v>66</v>
@@ -13644,10 +13662,10 @@
         <v>30</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D450" s="6" t="n">
-        <v>1412.0</v>
+        <v>105.0</v>
       </c>
       <c r="E450" s="7" t="s">
         <v>12</v>
@@ -13673,10 +13691,10 @@
         <v>13</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D451" s="6" t="n">
-        <v>47101.0</v>
+        <v>4957.0</v>
       </c>
       <c r="E451" s="7" t="s">
         <v>12</v>
@@ -13702,16 +13720,16 @@
         <v>13</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D452" s="6" t="n">
-        <v>872.0</v>
+        <v>78020.0</v>
       </c>
       <c r="E452" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F452" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F452" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G452" s="8" t="s">
         <v>67</v>
@@ -13731,10 +13749,10 @@
         <v>13</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D453" s="6" t="n">
-        <v>420532.0</v>
+        <v>2727.0</v>
       </c>
       <c r="E453" s="7" t="s">
         <v>12</v>
@@ -13760,10 +13778,10 @@
         <v>13</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D454" s="6" t="n">
-        <v>175.0</v>
+        <v>1522.0</v>
       </c>
       <c r="E454" s="7" t="s">
         <v>12</v>
@@ -13789,10 +13807,10 @@
         <v>13</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D455" s="6" t="n">
-        <v>57845.0</v>
+        <v>936.0</v>
       </c>
       <c r="E455" s="7" t="s">
         <v>12</v>
@@ -13818,16 +13836,16 @@
         <v>13</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D456" s="6" t="n">
-        <v>357258.0</v>
+        <v>175.0</v>
       </c>
       <c r="E456" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F456" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F456" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G456" s="8" t="s">
         <v>67</v>
@@ -13847,16 +13865,16 @@
         <v>13</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D457" s="6" t="n">
-        <v>4957.0</v>
+        <v>357258.0</v>
       </c>
       <c r="E457" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F457" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F457" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G457" s="8" t="s">
         <v>67</v>
@@ -13876,10 +13894,10 @@
         <v>13</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D458" s="6" t="n">
-        <v>936.0</v>
+        <v>57845.0</v>
       </c>
       <c r="E458" s="7" t="s">
         <v>12</v>
@@ -13905,10 +13923,10 @@
         <v>13</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D459" s="6" t="n">
-        <v>1522.0</v>
+        <v>792.0</v>
       </c>
       <c r="E459" s="7" t="s">
         <v>12</v>
@@ -13934,10 +13952,10 @@
         <v>13</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D460" s="6" t="n">
-        <v>2727.0</v>
+        <v>872.0</v>
       </c>
       <c r="E460" s="7" t="s">
         <v>12</v>
@@ -13963,16 +13981,16 @@
         <v>13</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D461" s="6" t="n">
-        <v>78020.0</v>
+        <v>47101.0</v>
       </c>
       <c r="E461" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F461" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F461" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G461" s="8" t="s">
         <v>67</v>
@@ -14021,10 +14039,10 @@
         <v>13</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D463" s="6" t="n">
-        <v>792.0</v>
+        <v>420532.0</v>
       </c>
       <c r="E463" s="7" t="s">
         <v>12</v>
@@ -14050,10 +14068,10 @@
         <v>13</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D464" s="6" t="n">
-        <v>64823.0</v>
+        <v>13052.0</v>
       </c>
       <c r="E464" s="7" t="s">
         <v>12</v>
@@ -14076,13 +14094,13 @@
         <v>67</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D465" s="6" t="n">
-        <v>13052.0</v>
+        <v>3363.0</v>
       </c>
       <c r="E465" s="7" t="s">
         <v>12</v>
@@ -14105,13 +14123,13 @@
         <v>67</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D466" s="6" t="n">
-        <v>74709.0</v>
+        <v>64823.0</v>
       </c>
       <c r="E466" s="7" t="s">
         <v>12</v>
@@ -14134,13 +14152,13 @@
         <v>67</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>6691.0</v>
+        <v>245670.0</v>
       </c>
       <c r="E467" s="7" t="s">
         <v>12</v>
@@ -14166,10 +14184,10 @@
         <v>10</v>
       </c>
       <c r="C468" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D468" s="6" t="n">
-        <v>245670.0</v>
+        <v>122605.0</v>
       </c>
       <c r="E468" s="7" t="s">
         <v>12</v>
@@ -14195,10 +14213,10 @@
         <v>10</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D469" s="6" t="n">
-        <v>122605.0</v>
+        <v>3174.0</v>
       </c>
       <c r="E469" s="7" t="s">
         <v>12</v>
@@ -14221,13 +14239,13 @@
         <v>67</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D470" s="6" t="n">
-        <v>3174.0</v>
+        <v>74709.0</v>
       </c>
       <c r="E470" s="7" t="s">
         <v>12</v>
@@ -14282,10 +14300,10 @@
         <v>30</v>
       </c>
       <c r="C472" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D472" s="6" t="n">
-        <v>3363.0</v>
+        <v>646.0</v>
       </c>
       <c r="E472" s="7" t="s">
         <v>12</v>
@@ -14311,10 +14329,10 @@
         <v>30</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D473" s="6" t="n">
-        <v>199283.0</v>
+        <v>8245.0</v>
       </c>
       <c r="E473" s="7" t="s">
         <v>12</v>
@@ -14340,10 +14358,10 @@
         <v>30</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D474" s="6" t="n">
-        <v>8245.0</v>
+        <v>207867.0</v>
       </c>
       <c r="E474" s="7" t="s">
         <v>12</v>
@@ -14369,10 +14387,10 @@
         <v>30</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D475" s="6" t="n">
-        <v>207867.0</v>
+        <v>6920.0</v>
       </c>
       <c r="E475" s="7" t="s">
         <v>12</v>
@@ -14395,13 +14413,13 @@
         <v>67</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D476" s="6" t="n">
-        <v>6920.0</v>
+        <v>6691.0</v>
       </c>
       <c r="E476" s="7" t="s">
         <v>12</v>
@@ -14427,10 +14445,10 @@
         <v>30</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D477" s="6" t="n">
-        <v>646.0</v>
+        <v>199283.0</v>
       </c>
       <c r="E477" s="7" t="s">
         <v>12</v>
@@ -14688,16 +14706,16 @@
         <v>13</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D486" s="6" t="n">
-        <v>96503.0</v>
+        <v>549073.0</v>
       </c>
       <c r="E486" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F486" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F486" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G486" s="8" t="s">
         <v>68</v>
@@ -14804,10 +14822,10 @@
         <v>13</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D490" s="6" t="n">
-        <v>549073.0</v>
+        <v>70327.0</v>
       </c>
       <c r="E490" s="7" t="s">
         <v>12</v>
@@ -14833,16 +14851,16 @@
         <v>13</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D491" s="6" t="n">
-        <v>70327.0</v>
+        <v>96503.0</v>
       </c>
       <c r="E491" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F491" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F491" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G491" s="8" t="s">
         <v>68</v>
@@ -15210,10 +15228,10 @@
         <v>13</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D504" s="6" t="n">
-        <v>4716.0</v>
+        <v>248.0</v>
       </c>
       <c r="E504" s="7" t="s">
         <v>12</v>
@@ -15239,16 +15257,16 @@
         <v>13</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D505" s="6" t="n">
-        <v>144021.0</v>
+        <v>72938.0</v>
       </c>
       <c r="E505" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F505" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F505" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G505" s="8" t="s">
         <v>69</v>
@@ -15268,16 +15286,16 @@
         <v>13</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D506" s="6" t="n">
-        <v>62084.0</v>
+        <v>144021.0</v>
       </c>
       <c r="E506" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F506" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F506" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G506" s="8" t="s">
         <v>69</v>
@@ -15297,10 +15315,10 @@
         <v>13</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D507" s="6" t="n">
-        <v>123.0</v>
+        <v>62084.0</v>
       </c>
       <c r="E507" s="7" t="s">
         <v>12</v>
@@ -15326,10 +15344,10 @@
         <v>13</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D508" s="6" t="n">
-        <v>248.0</v>
+        <v>123.0</v>
       </c>
       <c r="E508" s="7" t="s">
         <v>12</v>
@@ -15355,10 +15373,10 @@
         <v>13</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D509" s="6" t="n">
-        <v>18261.0</v>
+        <v>5181.0</v>
       </c>
       <c r="E509" s="7" t="s">
         <v>12</v>
@@ -15384,10 +15402,10 @@
         <v>13</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D510" s="6" t="n">
-        <v>201113.0</v>
+        <v>4716.0</v>
       </c>
       <c r="E510" s="7" t="s">
         <v>12</v>
@@ -15413,10 +15431,10 @@
         <v>13</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D511" s="6" t="n">
-        <v>5181.0</v>
+        <v>201113.0</v>
       </c>
       <c r="E511" s="7" t="s">
         <v>12</v>
@@ -15442,10 +15460,10 @@
         <v>13</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D512" s="6" t="n">
-        <v>1519.0</v>
+        <v>18261.0</v>
       </c>
       <c r="E512" s="7" t="s">
         <v>12</v>
@@ -15471,16 +15489,16 @@
         <v>13</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D513" s="6" t="n">
-        <v>908897.0</v>
+        <v>30675.0</v>
       </c>
       <c r="E513" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F513" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F513" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G513" s="8" t="s">
         <v>69</v>
@@ -15500,16 +15518,16 @@
         <v>13</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D514" s="6" t="n">
-        <v>2898.0</v>
+        <v>908897.0</v>
       </c>
       <c r="E514" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F514" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F514" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G514" s="8" t="s">
         <v>69</v>
@@ -15529,10 +15547,10 @@
         <v>13</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D515" s="6" t="n">
-        <v>72938.0</v>
+        <v>2898.0</v>
       </c>
       <c r="E515" s="7" t="s">
         <v>12</v>
@@ -15558,10 +15576,10 @@
         <v>13</v>
       </c>
       <c r="C516" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D516" s="6" t="n">
-        <v>30675.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E516" s="7" t="s">
         <v>12</v>
@@ -15616,10 +15634,10 @@
         <v>10</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D518" s="6" t="n">
-        <v>1195.0</v>
+        <v>1408.0</v>
       </c>
       <c r="E518" s="7" t="s">
         <v>12</v>
@@ -15645,10 +15663,10 @@
         <v>10</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D519" s="6" t="n">
-        <v>44.0</v>
+        <v>162695.0</v>
       </c>
       <c r="E519" s="7" t="s">
         <v>12</v>
@@ -15674,10 +15692,10 @@
         <v>10</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D520" s="6" t="n">
-        <v>372386.0</v>
+        <v>44.0</v>
       </c>
       <c r="E520" s="7" t="s">
         <v>12</v>
@@ -15703,10 +15721,10 @@
         <v>10</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D521" s="6" t="n">
-        <v>162639.0</v>
+        <v>372386.0</v>
       </c>
       <c r="E521" s="7" t="s">
         <v>12</v>
@@ -15732,10 +15750,10 @@
         <v>10</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D522" s="6" t="n">
-        <v>42853.0</v>
+        <v>162639.0</v>
       </c>
       <c r="E522" s="7" t="s">
         <v>12</v>
@@ -15761,10 +15779,10 @@
         <v>10</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D523" s="6" t="n">
-        <v>1408.0</v>
+        <v>42853.0</v>
       </c>
       <c r="E523" s="7" t="s">
         <v>12</v>
@@ -15787,19 +15805,19 @@
         <v>69</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D524" s="6" t="n">
-        <v>162695.0</v>
+        <v>366304.0</v>
       </c>
       <c r="E524" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F524" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F524" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G524" s="8" t="s">
         <v>69</v>
@@ -15816,13 +15834,13 @@
         <v>69</v>
       </c>
       <c r="B525" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D525" s="6" t="n">
-        <v>77128.0</v>
+        <v>1195.0</v>
       </c>
       <c r="E525" s="7" t="s">
         <v>12</v>
@@ -15848,10 +15866,10 @@
         <v>30</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D526" s="6" t="n">
-        <v>1733.0</v>
+        <v>7684.0</v>
       </c>
       <c r="E526" s="7" t="s">
         <v>12</v>
@@ -15877,10 +15895,10 @@
         <v>30</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D527" s="6" t="n">
-        <v>284063.0</v>
+        <v>1733.0</v>
       </c>
       <c r="E527" s="7" t="s">
         <v>12</v>
@@ -15906,10 +15924,10 @@
         <v>30</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D528" s="6" t="n">
-        <v>26286.0</v>
+        <v>284063.0</v>
       </c>
       <c r="E528" s="7" t="s">
         <v>12</v>
@@ -15935,16 +15953,16 @@
         <v>30</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D529" s="6" t="n">
-        <v>366304.0</v>
+        <v>26286.0</v>
       </c>
       <c r="E529" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F529" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F529" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G529" s="8" t="s">
         <v>69</v>
@@ -15964,10 +15982,10 @@
         <v>30</v>
       </c>
       <c r="C530" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D530" s="6" t="n">
-        <v>7684.0</v>
+        <v>77128.0</v>
       </c>
       <c r="E530" s="7" t="s">
         <v>12</v>
@@ -15993,10 +16011,10 @@
         <v>13</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D531" s="6" t="n">
-        <v>36834.0</v>
+        <v>133084.0</v>
       </c>
       <c r="E531" s="7" t="s">
         <v>12</v>
@@ -16022,10 +16040,10 @@
         <v>13</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D532" s="6" t="n">
-        <v>8250.0</v>
+        <v>2394.0</v>
       </c>
       <c r="E532" s="7" t="s">
         <v>12</v>
@@ -16051,10 +16069,10 @@
         <v>13</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D533" s="6" t="n">
-        <v>17644.0</v>
+        <v>8250.0</v>
       </c>
       <c r="E533" s="7" t="s">
         <v>12</v>
@@ -16080,10 +16098,10 @@
         <v>13</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D534" s="6" t="n">
-        <v>249.0</v>
+        <v>17644.0</v>
       </c>
       <c r="E534" s="7" t="s">
         <v>12</v>
@@ -16109,10 +16127,10 @@
         <v>13</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D535" s="6" t="n">
-        <v>11404.0</v>
+        <v>249.0</v>
       </c>
       <c r="E535" s="7" t="s">
         <v>12</v>
@@ -16138,10 +16156,10 @@
         <v>13</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D536" s="6" t="n">
-        <v>133084.0</v>
+        <v>11404.0</v>
       </c>
       <c r="E536" s="7" t="s">
         <v>12</v>
@@ -16167,10 +16185,10 @@
         <v>13</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D537" s="6" t="n">
-        <v>2797.0</v>
+        <v>658.0</v>
       </c>
       <c r="E537" s="7" t="s">
         <v>12</v>
@@ -16196,10 +16214,10 @@
         <v>13</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D538" s="6" t="n">
-        <v>1287.0</v>
+        <v>36834.0</v>
       </c>
       <c r="E538" s="7" t="s">
         <v>12</v>
@@ -16225,10 +16243,10 @@
         <v>13</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D539" s="6" t="n">
-        <v>658.0</v>
+        <v>1287.0</v>
       </c>
       <c r="E539" s="7" t="s">
         <v>12</v>
@@ -16254,10 +16272,10 @@
         <v>13</v>
       </c>
       <c r="C540" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D540" s="6" t="n">
-        <v>357059.0</v>
+        <v>2797.0</v>
       </c>
       <c r="E540" s="7" t="s">
         <v>12</v>
@@ -16283,10 +16301,10 @@
         <v>13</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D541" s="6" t="n">
-        <v>6031.0</v>
+        <v>357059.0</v>
       </c>
       <c r="E541" s="7" t="s">
         <v>12</v>
@@ -16312,10 +16330,10 @@
         <v>13</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D542" s="6" t="n">
-        <v>712.0</v>
+        <v>6031.0</v>
       </c>
       <c r="E542" s="7" t="s">
         <v>12</v>
@@ -16341,10 +16359,10 @@
         <v>13</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D543" s="6" t="n">
-        <v>155751.0</v>
+        <v>180673.0</v>
       </c>
       <c r="E543" s="7" t="s">
         <v>12</v>
@@ -16370,10 +16388,10 @@
         <v>13</v>
       </c>
       <c r="C544" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D544" s="6" t="n">
-        <v>2394.0</v>
+        <v>155751.0</v>
       </c>
       <c r="E544" s="7" t="s">
         <v>12</v>
@@ -16396,13 +16414,13 @@
         <v>70</v>
       </c>
       <c r="B545" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="D545" s="6" t="n">
-        <v>68846.0</v>
+        <v>712.0</v>
       </c>
       <c r="E545" s="7" t="s">
         <v>12</v>
@@ -16428,10 +16446,10 @@
         <v>13</v>
       </c>
       <c r="C546" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D546" s="6" t="n">
-        <v>180673.0</v>
+        <v>61145.0</v>
       </c>
       <c r="E546" s="7" t="s">
         <v>12</v>
@@ -16486,10 +16504,10 @@
         <v>10</v>
       </c>
       <c r="C548" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D548" s="6" t="n">
-        <v>49132.0</v>
+        <v>445652.0</v>
       </c>
       <c r="E548" s="7" t="s">
         <v>12</v>
@@ -16512,13 +16530,13 @@
         <v>70</v>
       </c>
       <c r="B549" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D549" s="6" t="n">
-        <v>61145.0</v>
+        <v>68846.0</v>
       </c>
       <c r="E549" s="7" t="s">
         <v>12</v>
@@ -16631,10 +16649,10 @@
         <v>10</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D553" s="6" t="n">
-        <v>445652.0</v>
+        <v>49132.0</v>
       </c>
       <c r="E553" s="7" t="s">
         <v>12</v>
@@ -16686,13 +16704,13 @@
         <v>70</v>
       </c>
       <c r="B555" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D555" s="6" t="n">
-        <v>16624.0</v>
+        <v>17014.0</v>
       </c>
       <c r="E555" s="7" t="s">
         <v>12</v>
@@ -16718,10 +16736,10 @@
         <v>30</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D556" s="6" t="n">
-        <v>146605.0</v>
+        <v>167261.0</v>
       </c>
       <c r="E556" s="7" t="s">
         <v>12</v>
@@ -16744,13 +16762,13 @@
         <v>70</v>
       </c>
       <c r="B557" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D557" s="6" t="n">
-        <v>24743.0</v>
+        <v>833.0</v>
       </c>
       <c r="E557" s="7" t="s">
         <v>12</v>
@@ -16773,13 +16791,13 @@
         <v>70</v>
       </c>
       <c r="B558" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D558" s="6" t="n">
-        <v>833.0</v>
+        <v>24743.0</v>
       </c>
       <c r="E558" s="7" t="s">
         <v>12</v>
@@ -16802,13 +16820,13 @@
         <v>70</v>
       </c>
       <c r="B559" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D559" s="6" t="n">
-        <v>17014.0</v>
+        <v>16624.0</v>
       </c>
       <c r="E559" s="7" t="s">
         <v>12</v>
@@ -16834,10 +16852,10 @@
         <v>30</v>
       </c>
       <c r="C560" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D560" s="6" t="n">
-        <v>167261.0</v>
+        <v>146605.0</v>
       </c>
       <c r="E560" s="7" t="s">
         <v>12</v>
@@ -16892,10 +16910,10 @@
         <v>13</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D562" s="6" t="n">
-        <v>135115.0</v>
+        <v>50267.0</v>
       </c>
       <c r="E562" s="7" t="s">
         <v>12</v>
@@ -16921,10 +16939,10 @@
         <v>13</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D563" s="6" t="n">
-        <v>103167.0</v>
+        <v>135115.0</v>
       </c>
       <c r="E563" s="7" t="s">
         <v>12</v>
@@ -16950,10 +16968,10 @@
         <v>13</v>
       </c>
       <c r="C564" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D564" s="6" t="n">
-        <v>388.0</v>
+        <v>103167.0</v>
       </c>
       <c r="E564" s="7" t="s">
         <v>12</v>
@@ -16979,10 +16997,10 @@
         <v>13</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D565" s="6" t="n">
-        <v>4205.0</v>
+        <v>388.0</v>
       </c>
       <c r="E565" s="7" t="s">
         <v>12</v>
@@ -17008,10 +17026,10 @@
         <v>13</v>
       </c>
       <c r="C566" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D566" s="6" t="n">
-        <v>54.0</v>
+        <v>4205.0</v>
       </c>
       <c r="E566" s="7" t="s">
         <v>12</v>
@@ -17037,10 +17055,10 @@
         <v>13</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D567" s="6" t="n">
-        <v>5640.0</v>
+        <v>147017.0</v>
       </c>
       <c r="E567" s="7" t="s">
         <v>12</v>
@@ -17066,10 +17084,10 @@
         <v>13</v>
       </c>
       <c r="C568" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D568" s="6" t="n">
-        <v>147017.0</v>
+        <v>5640.0</v>
       </c>
       <c r="E568" s="7" t="s">
         <v>12</v>
@@ -17211,10 +17229,10 @@
         <v>13</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D573" s="6" t="n">
-        <v>73411.0</v>
+        <v>3016.0</v>
       </c>
       <c r="E573" s="7" t="s">
         <v>12</v>
@@ -17240,10 +17258,10 @@
         <v>13</v>
       </c>
       <c r="C574" s="5" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D574" s="6" t="n">
-        <v>3016.0</v>
+        <v>54.0</v>
       </c>
       <c r="E574" s="7" t="s">
         <v>12</v>
@@ -17266,13 +17284,13 @@
         <v>71</v>
       </c>
       <c r="B575" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D575" s="6" t="n">
-        <v>50267.0</v>
+        <v>30577.0</v>
       </c>
       <c r="E575" s="7" t="s">
         <v>12</v>
@@ -17298,10 +17316,10 @@
         <v>13</v>
       </c>
       <c r="C576" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D576" s="6" t="n">
-        <v>11348.0</v>
+        <v>73411.0</v>
       </c>
       <c r="E576" s="7" t="s">
         <v>12</v>
@@ -17353,13 +17371,13 @@
         <v>71</v>
       </c>
       <c r="B578" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C578" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D578" s="6" t="n">
-        <v>30577.0</v>
+        <v>132880.0</v>
       </c>
       <c r="E578" s="7" t="s">
         <v>12</v>
@@ -17382,13 +17400,13 @@
         <v>71</v>
       </c>
       <c r="B579" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D579" s="6" t="n">
-        <v>132880.0</v>
+        <v>11348.0</v>
       </c>
       <c r="E579" s="7" t="s">
         <v>12</v>
@@ -17733,10 +17751,10 @@
         <v>13</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D591" s="6" t="n">
-        <v>154891.0</v>
+        <v>30056.0</v>
       </c>
       <c r="E591" s="7" t="s">
         <v>12</v>
@@ -17762,16 +17780,16 @@
         <v>13</v>
       </c>
       <c r="C592" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D592" s="6" t="n">
-        <v>481367.0</v>
+        <v>138808.0</v>
       </c>
       <c r="E592" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F592" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F592" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G592" s="8" t="s">
         <v>72</v>
@@ -17791,10 +17809,10 @@
         <v>13</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D593" s="6" t="n">
-        <v>5871.0</v>
+        <v>31.0</v>
       </c>
       <c r="E593" s="7" t="s">
         <v>12</v>
@@ -17820,10 +17838,10 @@
         <v>13</v>
       </c>
       <c r="C594" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D594" s="6" t="n">
-        <v>21078.0</v>
+        <v>5871.0</v>
       </c>
       <c r="E594" s="7" t="s">
         <v>12</v>
@@ -17849,10 +17867,10 @@
         <v>13</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D595" s="6" t="n">
-        <v>30056.0</v>
+        <v>21078.0</v>
       </c>
       <c r="E595" s="7" t="s">
         <v>12</v>
@@ -17878,10 +17896,10 @@
         <v>13</v>
       </c>
       <c r="C596" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D596" s="6" t="n">
-        <v>3386.0</v>
+        <v>1132.0</v>
       </c>
       <c r="E596" s="7" t="s">
         <v>12</v>
@@ -17907,16 +17925,16 @@
         <v>13</v>
       </c>
       <c r="C597" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D597" s="6" t="n">
-        <v>84215.0</v>
+        <v>154891.0</v>
       </c>
       <c r="E597" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F597" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F597" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G597" s="8" t="s">
         <v>72</v>
@@ -17936,16 +17954,16 @@
         <v>13</v>
       </c>
       <c r="C598" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D598" s="6" t="n">
-        <v>1973.0</v>
+        <v>84215.0</v>
       </c>
       <c r="E598" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F598" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F598" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G598" s="8" t="s">
         <v>72</v>
@@ -17965,10 +17983,10 @@
         <v>13</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D599" s="6" t="n">
-        <v>1132.0</v>
+        <v>1973.0</v>
       </c>
       <c r="E599" s="7" t="s">
         <v>12</v>
@@ -17994,16 +18012,16 @@
         <v>13</v>
       </c>
       <c r="C600" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D600" s="6" t="n">
-        <v>538223.0</v>
+        <v>3386.0</v>
       </c>
       <c r="E600" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F600" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F600" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G600" s="8" t="s">
         <v>72</v>
@@ -18023,16 +18041,16 @@
         <v>13</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D601" s="6" t="n">
-        <v>60893.0</v>
+        <v>538223.0</v>
       </c>
       <c r="E601" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F601" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G601" s="8" t="s">
         <v>72</v>
@@ -18052,16 +18070,16 @@
         <v>13</v>
       </c>
       <c r="C602" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D602" s="6" t="n">
-        <v>138808.0</v>
+        <v>60893.0</v>
       </c>
       <c r="E602" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F602" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F602" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G602" s="8" t="s">
         <v>72</v>
@@ -18081,16 +18099,16 @@
         <v>13</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D603" s="6" t="n">
-        <v>17195.0</v>
+        <v>481367.0</v>
       </c>
       <c r="E603" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F603" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F603" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G603" s="8" t="s">
         <v>72</v>
@@ -18110,10 +18128,10 @@
         <v>13</v>
       </c>
       <c r="C604" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D604" s="6" t="n">
-        <v>31.0</v>
+        <v>17195.0</v>
       </c>
       <c r="E604" s="7" t="s">
         <v>12</v>
@@ -18139,10 +18157,10 @@
         <v>30</v>
       </c>
       <c r="C605" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D605" s="6" t="n">
-        <v>96.0</v>
+        <v>76271.0</v>
       </c>
       <c r="E605" s="7" t="s">
         <v>12</v>
@@ -18165,13 +18183,13 @@
         <v>72</v>
       </c>
       <c r="B606" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C606" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D606" s="6" t="n">
-        <v>199612.0</v>
+        <v>10263.0</v>
       </c>
       <c r="E606" s="7" t="s">
         <v>12</v>
@@ -18200,7 +18218,7 @@
         <v>32</v>
       </c>
       <c r="D607" s="6" t="n">
-        <v>413992.0</v>
+        <v>414009.0</v>
       </c>
       <c r="E607" s="7" t="s">
         <v>16</v>
@@ -18281,13 +18299,13 @@
         <v>72</v>
       </c>
       <c r="B610" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C610" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D610" s="6" t="n">
-        <v>76271.0</v>
+        <v>199612.0</v>
       </c>
       <c r="E610" s="7" t="s">
         <v>12</v>
@@ -18313,10 +18331,10 @@
         <v>30</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D611" s="6" t="n">
-        <v>11956.0</v>
+        <v>96.0</v>
       </c>
       <c r="E611" s="7" t="s">
         <v>12</v>
@@ -18455,13 +18473,13 @@
         <v>72</v>
       </c>
       <c r="B616" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C616" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D616" s="6" t="n">
-        <v>10263.0</v>
+        <v>11956.0</v>
       </c>
       <c r="E616" s="7" t="s">
         <v>12</v>
@@ -18487,10 +18505,10 @@
         <v>13</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D617" s="6" t="n">
-        <v>681.0</v>
+        <v>4371.0</v>
       </c>
       <c r="E617" s="7" t="s">
         <v>12</v>
@@ -18516,10 +18534,10 @@
         <v>13</v>
       </c>
       <c r="C618" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D618" s="6" t="n">
-        <v>250858.0</v>
+        <v>597.0</v>
       </c>
       <c r="E618" s="7" t="s">
         <v>12</v>
@@ -18545,10 +18563,10 @@
         <v>13</v>
       </c>
       <c r="C619" s="5" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D619" s="6" t="n">
-        <v>597.0</v>
+        <v>1345.0</v>
       </c>
       <c r="E619" s="7" t="s">
         <v>12</v>
@@ -18574,10 +18592,10 @@
         <v>13</v>
       </c>
       <c r="C620" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D620" s="6" t="n">
-        <v>1345.0</v>
+        <v>3953.0</v>
       </c>
       <c r="E620" s="7" t="s">
         <v>12</v>
@@ -18603,10 +18621,10 @@
         <v>13</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D621" s="6" t="n">
-        <v>3953.0</v>
+        <v>681.0</v>
       </c>
       <c r="E621" s="7" t="s">
         <v>12</v>
@@ -18632,10 +18650,10 @@
         <v>13</v>
       </c>
       <c r="C622" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D622" s="6" t="n">
-        <v>2658.0</v>
+        <v>4464.0</v>
       </c>
       <c r="E622" s="7" t="s">
         <v>12</v>
@@ -18661,10 +18679,10 @@
         <v>13</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D623" s="6" t="n">
-        <v>4371.0</v>
+        <v>83909.0</v>
       </c>
       <c r="E623" s="7" t="s">
         <v>12</v>
@@ -18690,10 +18708,10 @@
         <v>13</v>
       </c>
       <c r="C624" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D624" s="6" t="n">
-        <v>83909.0</v>
+        <v>84856.0</v>
       </c>
       <c r="E624" s="7" t="s">
         <v>12</v>
@@ -18719,10 +18737,10 @@
         <v>13</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D625" s="6" t="n">
-        <v>84856.0</v>
+        <v>386333.0</v>
       </c>
       <c r="E625" s="7" t="s">
         <v>12</v>
@@ -18748,10 +18766,10 @@
         <v>13</v>
       </c>
       <c r="C626" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D626" s="6" t="n">
-        <v>4464.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E626" s="7" t="s">
         <v>12</v>
@@ -18777,16 +18795,16 @@
         <v>13</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D627" s="6" t="n">
-        <v>386333.0</v>
+        <v>129190.0</v>
       </c>
       <c r="E627" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F627" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F627" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G627" s="8" t="s">
         <v>73</v>
@@ -18806,10 +18824,10 @@
         <v>13</v>
       </c>
       <c r="C628" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D628" s="6" t="n">
-        <v>54493.0</v>
+        <v>251598.0</v>
       </c>
       <c r="E628" s="7" t="s">
         <v>12</v>
@@ -18835,16 +18853,16 @@
         <v>13</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D629" s="6" t="n">
-        <v>129190.0</v>
+        <v>54493.0</v>
       </c>
       <c r="E629" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F629" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F629" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G629" s="8" t="s">
         <v>73</v>
@@ -18861,13 +18879,13 @@
         <v>73</v>
       </c>
       <c r="B630" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C630" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D630" s="6" t="n">
-        <v>139458.0</v>
+        <v>5327.0</v>
       </c>
       <c r="E630" s="7" t="s">
         <v>12</v>
@@ -18890,13 +18908,13 @@
         <v>73</v>
       </c>
       <c r="B631" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C631" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D631" s="6" t="n">
-        <v>5327.0</v>
+        <v>43478.0</v>
       </c>
       <c r="E631" s="7" t="s">
         <v>12</v>
@@ -18922,10 +18940,10 @@
         <v>10</v>
       </c>
       <c r="C632" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D632" s="6" t="n">
-        <v>1660.0</v>
+        <v>276686.0</v>
       </c>
       <c r="E632" s="7" t="s">
         <v>12</v>
@@ -18948,13 +18966,13 @@
         <v>73</v>
       </c>
       <c r="B633" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C633" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D633" s="6" t="n">
-        <v>6983.0</v>
+        <v>65439.0</v>
       </c>
       <c r="E633" s="7" t="s">
         <v>12</v>
@@ -18980,16 +18998,16 @@
         <v>10</v>
       </c>
       <c r="C634" s="5" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D634" s="6" t="n">
-        <v>191571.0</v>
+        <v>139458.0</v>
       </c>
       <c r="E634" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F634" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F634" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G634" s="8" t="s">
         <v>73</v>
@@ -19009,16 +19027,16 @@
         <v>10</v>
       </c>
       <c r="C635" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D635" s="6" t="n">
-        <v>65422.0</v>
+        <v>191571.0</v>
       </c>
       <c r="E635" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F635" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F635" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G635" s="8" t="s">
         <v>73</v>
@@ -19038,10 +19056,10 @@
         <v>10</v>
       </c>
       <c r="C636" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D636" s="6" t="n">
-        <v>511.0</v>
+        <v>1660.0</v>
       </c>
       <c r="E636" s="7" t="s">
         <v>12</v>
@@ -19067,10 +19085,10 @@
         <v>10</v>
       </c>
       <c r="C637" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D637" s="6" t="n">
-        <v>274615.0</v>
+        <v>511.0</v>
       </c>
       <c r="E637" s="7" t="s">
         <v>12</v>
@@ -19096,10 +19114,10 @@
         <v>30</v>
       </c>
       <c r="C638" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D638" s="6" t="n">
-        <v>43435.0</v>
+        <v>5387.0</v>
       </c>
       <c r="E638" s="7" t="s">
         <v>12</v>
@@ -19125,16 +19143,16 @@
         <v>30</v>
       </c>
       <c r="C639" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D639" s="6" t="n">
-        <v>5387.0</v>
+        <v>322311.0</v>
       </c>
       <c r="E639" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F639" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F639" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G639" s="8" t="s">
         <v>73</v>
@@ -19154,16 +19172,16 @@
         <v>30</v>
       </c>
       <c r="C640" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D640" s="6" t="n">
-        <v>321927.0</v>
+        <v>107.0</v>
       </c>
       <c r="E640" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F640" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F640" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G640" s="8" t="s">
         <v>73</v>
@@ -19183,10 +19201,10 @@
         <v>30</v>
       </c>
       <c r="C641" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D641" s="6" t="n">
-        <v>107.0</v>
+        <v>220179.0</v>
       </c>
       <c r="E641" s="7" t="s">
         <v>12</v>
@@ -19212,10 +19230,10 @@
         <v>30</v>
       </c>
       <c r="C642" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D642" s="6" t="n">
-        <v>220179.0</v>
+        <v>28519.0</v>
       </c>
       <c r="E642" s="7" t="s">
         <v>12</v>
@@ -19238,13 +19256,13 @@
         <v>73</v>
       </c>
       <c r="B643" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C643" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D643" s="6" t="n">
-        <v>28519.0</v>
+        <v>6983.0</v>
       </c>
       <c r="E643" s="7" t="s">
         <v>12</v>
@@ -19270,10 +19288,10 @@
         <v>13</v>
       </c>
       <c r="C644" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D644" s="6" t="n">
-        <v>276.0</v>
+        <v>337691.0</v>
       </c>
       <c r="E644" s="7" t="s">
         <v>12</v>
@@ -19299,10 +19317,10 @@
         <v>13</v>
       </c>
       <c r="C645" s="5" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D645" s="6" t="n">
-        <v>9855.0</v>
+        <v>422.0</v>
       </c>
       <c r="E645" s="7" t="s">
         <v>12</v>
@@ -19328,10 +19346,10 @@
         <v>13</v>
       </c>
       <c r="C646" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D646" s="6" t="n">
-        <v>2352.0</v>
+        <v>3992.0</v>
       </c>
       <c r="E646" s="7" t="s">
         <v>12</v>
@@ -19357,16 +19375,16 @@
         <v>13</v>
       </c>
       <c r="C647" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D647" s="6" t="n">
-        <v>31948.0</v>
+        <v>85944.0</v>
       </c>
       <c r="E647" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F647" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F647" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G647" s="8" t="s">
         <v>74</v>
@@ -19386,10 +19404,10 @@
         <v>13</v>
       </c>
       <c r="C648" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D648" s="6" t="n">
-        <v>40742.0</v>
+        <v>125172.0</v>
       </c>
       <c r="E648" s="7" t="s">
         <v>12</v>
@@ -19415,10 +19433,10 @@
         <v>13</v>
       </c>
       <c r="C649" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D649" s="6" t="n">
-        <v>728.0</v>
+        <v>2352.0</v>
       </c>
       <c r="E649" s="7" t="s">
         <v>12</v>
@@ -19441,13 +19459,13 @@
         <v>74</v>
       </c>
       <c r="B650" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C650" s="5" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="D650" s="6" t="n">
-        <v>157451.0</v>
+        <v>4304.0</v>
       </c>
       <c r="E650" s="7" t="s">
         <v>12</v>
@@ -19473,10 +19491,10 @@
         <v>13</v>
       </c>
       <c r="C651" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D651" s="6" t="n">
-        <v>34568.0</v>
+        <v>13457.0</v>
       </c>
       <c r="E651" s="7" t="s">
         <v>12</v>
@@ -19502,10 +19520,10 @@
         <v>13</v>
       </c>
       <c r="C652" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D652" s="6" t="n">
-        <v>19733.0</v>
+        <v>506974.0</v>
       </c>
       <c r="E652" s="7" t="s">
         <v>12</v>
@@ -19528,13 +19546,13 @@
         <v>74</v>
       </c>
       <c r="B653" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C653" s="5" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D653" s="6" t="n">
-        <v>7631.0</v>
+        <v>2106.0</v>
       </c>
       <c r="E653" s="7" t="s">
         <v>12</v>
@@ -19557,13 +19575,13 @@
         <v>74</v>
       </c>
       <c r="B654" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C654" s="5" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="D654" s="6" t="n">
-        <v>4299.0</v>
+        <v>4268.0</v>
       </c>
       <c r="E654" s="7" t="s">
         <v>12</v>
@@ -19586,13 +19604,13 @@
         <v>74</v>
       </c>
       <c r="B655" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C655" s="5" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D655" s="6" t="n">
-        <v>875.0</v>
+        <v>21715.0</v>
       </c>
       <c r="E655" s="7" t="s">
         <v>12</v>
@@ -19615,13 +19633,13 @@
         <v>74</v>
       </c>
       <c r="B656" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C656" s="5" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="D656" s="6" t="n">
-        <v>67027.0</v>
+        <v>1953.0</v>
       </c>
       <c r="E656" s="7" t="s">
         <v>12</v>
@@ -19644,13 +19662,13 @@
         <v>74</v>
       </c>
       <c r="B657" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C657" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D657" s="6" t="n">
-        <v>2608.0</v>
+        <v>52273.0</v>
       </c>
       <c r="E657" s="7" t="s">
         <v>12</v>
@@ -19673,19 +19691,19 @@
         <v>74</v>
       </c>
       <c r="B658" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C658" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D658" s="6" t="n">
-        <v>92663.0</v>
+        <v>126794.0</v>
       </c>
       <c r="E658" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F658" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F658" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G658" s="8" t="s">
         <v>74</v>
@@ -19705,10 +19723,10 @@
         <v>30</v>
       </c>
       <c r="C659" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D659" s="6" t="n">
-        <v>3247.0</v>
+        <v>1356.0</v>
       </c>
       <c r="E659" s="7" t="s">
         <v>12</v>
@@ -19731,13 +19749,13 @@
         <v>74</v>
       </c>
       <c r="B660" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C660" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D660" s="6" t="n">
-        <v>44991.0</v>
+        <v>1843.0</v>
       </c>
       <c r="E660" s="7" t="s">
         <v>12</v>
@@ -19763,10 +19781,10 @@
         <v>10</v>
       </c>
       <c r="C661" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D661" s="6" t="n">
-        <v>19955.0</v>
+        <v>3706.0</v>
       </c>
       <c r="E661" s="7" t="s">
         <v>12</v>
@@ -19789,13 +19807,13 @@
         <v>74</v>
       </c>
       <c r="B662" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C662" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D662" s="6" t="n">
-        <v>118275.0</v>
+        <v>11491.0</v>
       </c>
       <c r="E662" s="7" t="s">
         <v>12</v>
@@ -19824,7 +19842,7 @@
         <v>11</v>
       </c>
       <c r="D663" s="6" t="n">
-        <v>60517.0</v>
+        <v>118438.0</v>
       </c>
       <c r="E663" s="7" t="s">
         <v>12</v>
@@ -19847,13 +19865,13 @@
         <v>74</v>
       </c>
       <c r="B664" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C664" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D664" s="6" t="n">
-        <v>234255.0</v>
+        <v>6817.0</v>
       </c>
       <c r="E664" s="7" t="s">
         <v>12</v>
@@ -19868,6 +19886,963 @@
         <v>74</v>
       </c>
       <c r="I664" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B665" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C665" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D665" s="6" t="n">
+        <v>34079.0</v>
+      </c>
+      <c r="E665" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F665" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G665" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H665" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I665" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B666" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C666" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D666" s="6" t="n">
+        <v>115323.0</v>
+      </c>
+      <c r="E666" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F666" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G666" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H666" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I666" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B667" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C667" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D667" s="6" t="n">
+        <v>179290.0</v>
+      </c>
+      <c r="E667" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F667" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G667" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H667" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I667" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B668" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C668" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D668" s="6" t="n">
+        <v>36007.0</v>
+      </c>
+      <c r="E668" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F668" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G668" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H668" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I668" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B669" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C669" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D669" s="6" t="n">
+        <v>10437.0</v>
+      </c>
+      <c r="E669" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F669" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G669" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H669" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I669" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B670" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C670" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D670" s="6" t="n">
+        <v>347664.0</v>
+      </c>
+      <c r="E670" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F670" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G670" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H670" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I670" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B671" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C671" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D671" s="6" t="n">
+        <v>2655.0</v>
+      </c>
+      <c r="E671" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F671" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G671" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H671" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I671" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B672" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C672" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D672" s="6" t="n">
+        <v>196855.0</v>
+      </c>
+      <c r="E672" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F672" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G672" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H672" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I672" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B673" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D673" s="6" t="n">
+        <v>2286.0</v>
+      </c>
+      <c r="E673" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F673" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G673" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H673" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I673" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B674" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C674" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D674" s="6" t="n">
+        <v>3560.0</v>
+      </c>
+      <c r="E674" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F674" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G674" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H674" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I674" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B675" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C675" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D675" s="6" t="n">
+        <v>483.0</v>
+      </c>
+      <c r="E675" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F675" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G675" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H675" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I675" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B676" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C676" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D676" s="6" t="n">
+        <v>816.0</v>
+      </c>
+      <c r="E676" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F676" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G676" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H676" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I676" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B677" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D677" s="6" t="n">
+        <v>148689.0</v>
+      </c>
+      <c r="E677" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F677" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G677" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H677" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I677" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B678" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D678" s="6" t="n">
+        <v>7587.0</v>
+      </c>
+      <c r="E678" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F678" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G678" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H678" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I678" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B679" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D679" s="6" t="n">
+        <v>29656.0</v>
+      </c>
+      <c r="E679" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F679" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G679" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H679" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I679" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B680" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C680" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D680" s="6" t="n">
+        <v>8480.0</v>
+      </c>
+      <c r="E680" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F680" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G680" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H680" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I680" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B681" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D681" s="6" t="n">
+        <v>18784.0</v>
+      </c>
+      <c r="E681" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F681" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G681" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H681" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I681" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B682" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C682" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D682" s="6" t="n">
+        <v>1869.0</v>
+      </c>
+      <c r="E682" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F682" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G682" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H682" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I682" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B683" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D683" s="6" t="n">
+        <v>34128.0</v>
+      </c>
+      <c r="E683" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F683" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G683" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H683" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I683" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B684" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C684" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D684" s="6" t="n">
+        <v>98043.0</v>
+      </c>
+      <c r="E684" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F684" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G684" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H684" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I684" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B685" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D685" s="6" t="n">
+        <v>6588.0</v>
+      </c>
+      <c r="E685" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F685" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G685" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H685" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I685" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B686" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C686" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D686" s="6" t="n">
+        <v>14785.0</v>
+      </c>
+      <c r="E686" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F686" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G686" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H686" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I686" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B687" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C687" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D687" s="6" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="E687" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F687" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G687" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H687" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I687" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B688" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C688" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D688" s="6" t="n">
+        <v>3258.0</v>
+      </c>
+      <c r="E688" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F688" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G688" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H688" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I688" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B689" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C689" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D689" s="6" t="n">
+        <v>195.0</v>
+      </c>
+      <c r="E689" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F689" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G689" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H689" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I689" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B690" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C690" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D690" s="6" t="n">
+        <v>30384.0</v>
+      </c>
+      <c r="E690" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F690" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G690" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H690" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I690" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B691" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C691" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D691" s="6" t="n">
+        <v>76393.0</v>
+      </c>
+      <c r="E691" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F691" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G691" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H691" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I691" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B692" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C692" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D692" s="6" t="n">
+        <v>8735.0</v>
+      </c>
+      <c r="E692" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F692" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G692" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H692" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I692" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B693" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C693" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D693" s="6" t="n">
+        <v>1752.0</v>
+      </c>
+      <c r="E693" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F693" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G693" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H693" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I693" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B694" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C694" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D694" s="6" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="E694" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F694" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G694" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H694" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I694" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B695" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C695" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D695" s="6" t="n">
+        <v>125852.0</v>
+      </c>
+      <c r="E695" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F695" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G695" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H695" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I695" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B696" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C696" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D696" s="6" t="n">
+        <v>75334.0</v>
+      </c>
+      <c r="E696" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F696" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G696" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H696" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I696" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B697" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C697" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D697" s="6" t="n">
+        <v>12407.0</v>
+      </c>
+      <c r="E697" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F697" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G697" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H697" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I697" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5488" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5524" uniqueCount="81">
   <si>
     <t>Ngày</t>
   </si>
@@ -239,6 +239,9 @@
     <t>2026-08-25</t>
   </si>
   <si>
+    <t>120254199840840712</t>
+  </si>
+  <si>
     <t>120254199946640712</t>
   </si>
   <si>
@@ -249,9 +252,6 @@
   </si>
   <si>
     <t>120254199840830712</t>
-  </si>
-  <si>
-    <t>120254199840840712</t>
   </si>
   <si>
     <t>2026-08-26</t>
@@ -618,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I697"/>
+  <dimension ref="A1:I702"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -10878,10 +10878,10 @@
         <v>13</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D354" s="6" t="n">
-        <v>62866.0</v>
+        <v>69412.0</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>12</v>
@@ -10907,10 +10907,10 @@
         <v>13</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D355" s="6" t="n">
-        <v>14289.0</v>
+        <v>62866.0</v>
       </c>
       <c r="E355" s="7" t="s">
         <v>12</v>
@@ -10936,10 +10936,10 @@
         <v>13</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D356" s="6" t="n">
-        <v>69412.0</v>
+        <v>14289.0</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>12</v>
@@ -11023,16 +11023,16 @@
         <v>10</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>419250.0</v>
+        <v>2365.0</v>
       </c>
       <c r="E359" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F359" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F359" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G359" s="8" t="s">
         <v>63</v>
@@ -11168,16 +11168,16 @@
         <v>10</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D364" s="6" t="n">
-        <v>96851.0</v>
+        <v>419250.0</v>
       </c>
       <c r="E364" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F364" s="7" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>63</v>
@@ -11197,16 +11197,16 @@
         <v>10</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D365" s="6" t="n">
-        <v>2365.0</v>
+        <v>96851.0</v>
       </c>
       <c r="E365" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F365" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F365" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G365" s="8" t="s">
         <v>63</v>
@@ -12125,10 +12125,10 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D397" s="6" t="n">
-        <v>5282.0</v>
+        <v>2360.0</v>
       </c>
       <c r="E397" s="7" t="s">
         <v>12</v>
@@ -12241,10 +12241,10 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>9750.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E401" s="7" t="s">
         <v>16</v>
@@ -12415,16 +12415,16 @@
         <v>13</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D407" s="6" t="n">
-        <v>2360.0</v>
+        <v>9750.0</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F407" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F407" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G407" s="8" t="s">
         <v>65</v>
@@ -12441,19 +12441,19 @@
         <v>65</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>285268.0</v>
+        <v>5282.0</v>
       </c>
       <c r="E408" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F408" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F408" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G408" s="8" t="s">
         <v>65</v>
@@ -12473,16 +12473,16 @@
         <v>13</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D409" s="6" t="n">
-        <v>65752.0</v>
+        <v>73210.0</v>
       </c>
       <c r="E409" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F409" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F409" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G409" s="8" t="s">
         <v>65</v>
@@ -12531,10 +12531,10 @@
         <v>13</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D411" s="6" t="n">
-        <v>73210.0</v>
+        <v>4067.0</v>
       </c>
       <c r="E411" s="7" t="s">
         <v>12</v>
@@ -12560,16 +12560,16 @@
         <v>10</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D412" s="6" t="n">
-        <v>217102.0</v>
+        <v>285268.0</v>
       </c>
       <c r="E412" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F412" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F412" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G412" s="8" t="s">
         <v>65</v>
@@ -12589,10 +12589,10 @@
         <v>10</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>60.0</v>
+        <v>217102.0</v>
       </c>
       <c r="E413" s="7" t="s">
         <v>12</v>
@@ -12615,13 +12615,13 @@
         <v>65</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D414" s="6" t="n">
-        <v>35159.0</v>
+        <v>60.0</v>
       </c>
       <c r="E414" s="7" t="s">
         <v>12</v>
@@ -12644,13 +12644,13 @@
         <v>65</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>160813.0</v>
+        <v>35159.0</v>
       </c>
       <c r="E415" s="7" t="s">
         <v>12</v>
@@ -12705,10 +12705,10 @@
         <v>30</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D417" s="6" t="n">
-        <v>7149.0</v>
+        <v>126986.0</v>
       </c>
       <c r="E417" s="7" t="s">
         <v>12</v>
@@ -12734,16 +12734,16 @@
         <v>30</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D418" s="6" t="n">
-        <v>594911.0</v>
+        <v>7149.0</v>
       </c>
       <c r="E418" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F418" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F418" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G418" s="8" t="s">
         <v>65</v>
@@ -12763,16 +12763,16 @@
         <v>30</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D419" s="6" t="n">
-        <v>39117.0</v>
+        <v>594911.0</v>
       </c>
       <c r="E419" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F419" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F419" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G419" s="8" t="s">
         <v>65</v>
@@ -12789,13 +12789,13 @@
         <v>65</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D420" s="6" t="n">
-        <v>4067.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E420" s="7" t="s">
         <v>12</v>
@@ -12821,10 +12821,10 @@
         <v>30</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>126986.0</v>
+        <v>39117.0</v>
       </c>
       <c r="E421" s="7" t="s">
         <v>12</v>
@@ -12850,10 +12850,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>1359.0</v>
+        <v>784.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12879,10 +12879,10 @@
         <v>13</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D423" s="6" t="n">
-        <v>58027.0</v>
+        <v>1355.0</v>
       </c>
       <c r="E423" s="7" t="s">
         <v>12</v>
@@ -12908,10 +12908,10 @@
         <v>13</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D424" s="6" t="n">
-        <v>8420.0</v>
+        <v>44956.0</v>
       </c>
       <c r="E424" s="7" t="s">
         <v>12</v>
@@ -12937,10 +12937,10 @@
         <v>13</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D425" s="6" t="n">
-        <v>210.0</v>
+        <v>58027.0</v>
       </c>
       <c r="E425" s="7" t="s">
         <v>12</v>
@@ -12966,10 +12966,10 @@
         <v>13</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D426" s="6" t="n">
-        <v>784.0</v>
+        <v>8420.0</v>
       </c>
       <c r="E426" s="7" t="s">
         <v>12</v>
@@ -12995,10 +12995,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>4241.0</v>
+        <v>210.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -13024,10 +13024,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>8146.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13053,10 +13053,10 @@
         <v>13</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D429" s="6" t="n">
-        <v>261758.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E429" s="7" t="s">
         <v>12</v>
@@ -13082,10 +13082,10 @@
         <v>13</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D430" s="6" t="n">
-        <v>70064.0</v>
+        <v>8146.0</v>
       </c>
       <c r="E430" s="7" t="s">
         <v>12</v>
@@ -13111,16 +13111,16 @@
         <v>13</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>510218.0</v>
+        <v>261758.0</v>
       </c>
       <c r="E431" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F431" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F431" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G431" s="8" t="s">
         <v>66</v>
@@ -13140,10 +13140,10 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>5605.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E432" s="7" t="s">
         <v>12</v>
@@ -13169,10 +13169,10 @@
         <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>35061.0</v>
+        <v>4241.0</v>
       </c>
       <c r="E433" s="7" t="s">
         <v>12</v>
@@ -13198,16 +13198,16 @@
         <v>13</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D434" s="6" t="n">
-        <v>44956.0</v>
+        <v>510218.0</v>
       </c>
       <c r="E434" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F434" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F434" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G434" s="8" t="s">
         <v>66</v>
@@ -13227,10 +13227,10 @@
         <v>13</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>1355.0</v>
+        <v>35061.0</v>
       </c>
       <c r="E435" s="7" t="s">
         <v>12</v>
@@ -13282,13 +13282,13 @@
         <v>66</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D437" s="6" t="n">
-        <v>9349.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E437" s="7" t="s">
         <v>12</v>
@@ -13311,13 +13311,13 @@
         <v>66</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>2197.0</v>
+        <v>5730.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13340,13 +13340,13 @@
         <v>66</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>3803.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E439" s="7" t="s">
         <v>12</v>
@@ -13372,10 +13372,10 @@
         <v>10</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>209762.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E440" s="7" t="s">
         <v>12</v>
@@ -13401,16 +13401,16 @@
         <v>10</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>4524.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E441" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F441" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F441" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G441" s="8" t="s">
         <v>66</v>
@@ -13430,10 +13430,10 @@
         <v>10</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D442" s="6" t="n">
-        <v>5730.0</v>
+        <v>209762.0</v>
       </c>
       <c r="E442" s="7" t="s">
         <v>12</v>
@@ -13459,16 +13459,16 @@
         <v>10</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>210756.0</v>
+        <v>4524.0</v>
       </c>
       <c r="E443" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F443" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F443" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G443" s="8" t="s">
         <v>66</v>
@@ -13485,13 +13485,13 @@
         <v>66</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D444" s="6" t="n">
-        <v>31883.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E444" s="7" t="s">
         <v>12</v>
@@ -13514,13 +13514,13 @@
         <v>66</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>1412.0</v>
+        <v>9349.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13546,16 +13546,16 @@
         <v>30</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D446" s="6" t="n">
-        <v>94352.0</v>
+        <v>105.0</v>
       </c>
       <c r="E446" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F446" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F446" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G446" s="8" t="s">
         <v>66</v>
@@ -13575,10 +13575,10 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>1503.0</v>
+        <v>1412.0</v>
       </c>
       <c r="E447" s="7" t="s">
         <v>12</v>
@@ -13604,16 +13604,16 @@
         <v>30</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>398394.0</v>
+        <v>94352.0</v>
       </c>
       <c r="E448" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F448" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F448" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G448" s="8" t="s">
         <v>66</v>
@@ -13630,13 +13630,13 @@
         <v>66</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D449" s="6" t="n">
-        <v>108610.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E449" s="7" t="s">
         <v>12</v>
@@ -13662,10 +13662,10 @@
         <v>30</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D450" s="6" t="n">
-        <v>105.0</v>
+        <v>31883.0</v>
       </c>
       <c r="E450" s="7" t="s">
         <v>12</v>
@@ -13952,10 +13952,10 @@
         <v>13</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D460" s="6" t="n">
-        <v>872.0</v>
+        <v>420532.0</v>
       </c>
       <c r="E460" s="7" t="s">
         <v>12</v>
@@ -13981,10 +13981,10 @@
         <v>13</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D461" s="6" t="n">
-        <v>47101.0</v>
+        <v>872.0</v>
       </c>
       <c r="E461" s="7" t="s">
         <v>12</v>
@@ -14010,10 +14010,10 @@
         <v>13</v>
       </c>
       <c r="C462" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D462" s="6" t="n">
-        <v>106406.0</v>
+        <v>47101.0</v>
       </c>
       <c r="E462" s="7" t="s">
         <v>12</v>
@@ -14039,10 +14039,10 @@
         <v>13</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D463" s="6" t="n">
-        <v>420532.0</v>
+        <v>106406.0</v>
       </c>
       <c r="E463" s="7" t="s">
         <v>12</v>
@@ -14065,13 +14065,13 @@
         <v>67</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D464" s="6" t="n">
-        <v>13052.0</v>
+        <v>245670.0</v>
       </c>
       <c r="E464" s="7" t="s">
         <v>12</v>
@@ -14094,13 +14094,13 @@
         <v>67</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D465" s="6" t="n">
-        <v>3363.0</v>
+        <v>13052.0</v>
       </c>
       <c r="E465" s="7" t="s">
         <v>12</v>
@@ -14123,13 +14123,13 @@
         <v>67</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D466" s="6" t="n">
-        <v>64823.0</v>
+        <v>3363.0</v>
       </c>
       <c r="E466" s="7" t="s">
         <v>12</v>
@@ -14152,13 +14152,13 @@
         <v>67</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>245670.0</v>
+        <v>64823.0</v>
       </c>
       <c r="E467" s="7" t="s">
         <v>12</v>
@@ -14474,10 +14474,10 @@
         <v>13</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D478" s="6" t="n">
-        <v>4818.0</v>
+        <v>158897.0</v>
       </c>
       <c r="E478" s="7" t="s">
         <v>12</v>
@@ -14503,10 +14503,10 @@
         <v>13</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D479" s="6" t="n">
-        <v>692.0</v>
+        <v>3849.0</v>
       </c>
       <c r="E479" s="7" t="s">
         <v>12</v>
@@ -14532,10 +14532,10 @@
         <v>13</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D480" s="6" t="n">
-        <v>3849.0</v>
+        <v>8962.0</v>
       </c>
       <c r="E480" s="7" t="s">
         <v>12</v>
@@ -14561,10 +14561,10 @@
         <v>13</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D481" s="6" t="n">
-        <v>8962.0</v>
+        <v>1252.0</v>
       </c>
       <c r="E481" s="7" t="s">
         <v>12</v>
@@ -14590,10 +14590,10 @@
         <v>13</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D482" s="6" t="n">
-        <v>1252.0</v>
+        <v>4818.0</v>
       </c>
       <c r="E482" s="7" t="s">
         <v>12</v>
@@ -14619,10 +14619,10 @@
         <v>13</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D483" s="6" t="n">
-        <v>4118.0</v>
+        <v>549073.0</v>
       </c>
       <c r="E483" s="7" t="s">
         <v>12</v>
@@ -14648,10 +14648,10 @@
         <v>13</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D484" s="6" t="n">
-        <v>158897.0</v>
+        <v>20516.0</v>
       </c>
       <c r="E484" s="7" t="s">
         <v>12</v>
@@ -14677,10 +14677,10 @@
         <v>13</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D485" s="6" t="n">
-        <v>20516.0</v>
+        <v>4118.0</v>
       </c>
       <c r="E485" s="7" t="s">
         <v>12</v>
@@ -14706,10 +14706,10 @@
         <v>13</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D486" s="6" t="n">
-        <v>549073.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E486" s="7" t="s">
         <v>12</v>
@@ -14735,10 +14735,10 @@
         <v>13</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D487" s="6" t="n">
-        <v>2658.0</v>
+        <v>791.0</v>
       </c>
       <c r="E487" s="7" t="s">
         <v>12</v>
@@ -14764,16 +14764,16 @@
         <v>13</v>
       </c>
       <c r="C488" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D488" s="6" t="n">
-        <v>791.0</v>
+        <v>108623.0</v>
       </c>
       <c r="E488" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F488" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F488" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G488" s="8" t="s">
         <v>68</v>
@@ -14793,16 +14793,16 @@
         <v>13</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D489" s="6" t="n">
-        <v>108623.0</v>
+        <v>692.0</v>
       </c>
       <c r="E489" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F489" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F489" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G489" s="8" t="s">
         <v>68</v>
@@ -14822,16 +14822,16 @@
         <v>13</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D490" s="6" t="n">
-        <v>70327.0</v>
+        <v>96503.0</v>
       </c>
       <c r="E490" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F490" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F490" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G490" s="8" t="s">
         <v>68</v>
@@ -14848,19 +14848,19 @@
         <v>68</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D491" s="6" t="n">
-        <v>96503.0</v>
+        <v>15334.0</v>
       </c>
       <c r="E491" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F491" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F491" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G491" s="8" t="s">
         <v>68</v>
@@ -14877,13 +14877,13 @@
         <v>68</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D492" s="6" t="n">
-        <v>15334.0</v>
+        <v>8296.0</v>
       </c>
       <c r="E492" s="7" t="s">
         <v>12</v>
@@ -14909,10 +14909,10 @@
         <v>13</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D493" s="6" t="n">
-        <v>8296.0</v>
+        <v>14544.0</v>
       </c>
       <c r="E493" s="7" t="s">
         <v>12</v>
@@ -14935,13 +14935,13 @@
         <v>68</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D494" s="6" t="n">
-        <v>296618.0</v>
+        <v>5306.0</v>
       </c>
       <c r="E494" s="7" t="s">
         <v>12</v>
@@ -14964,13 +14964,13 @@
         <v>68</v>
       </c>
       <c r="B495" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D495" s="6" t="n">
-        <v>170208.0</v>
+        <v>206053.0</v>
       </c>
       <c r="E495" s="7" t="s">
         <v>12</v>
@@ -14993,19 +14993,19 @@
         <v>68</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D496" s="6" t="n">
-        <v>13403.0</v>
+        <v>190807.0</v>
       </c>
       <c r="E496" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F496" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F496" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G496" s="8" t="s">
         <v>68</v>
@@ -15022,19 +15022,19 @@
         <v>68</v>
       </c>
       <c r="B497" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D497" s="6" t="n">
-        <v>107735.0</v>
+        <v>4041.0</v>
       </c>
       <c r="E497" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F497" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F497" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G497" s="8" t="s">
         <v>68</v>
@@ -15080,19 +15080,19 @@
         <v>68</v>
       </c>
       <c r="B499" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D499" s="6" t="n">
-        <v>190807.0</v>
+        <v>13403.0</v>
       </c>
       <c r="E499" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F499" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F499" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G499" s="8" t="s">
         <v>68</v>
@@ -15109,13 +15109,13 @@
         <v>68</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D500" s="6" t="n">
-        <v>206053.0</v>
+        <v>170208.0</v>
       </c>
       <c r="E500" s="7" t="s">
         <v>12</v>
@@ -15138,13 +15138,13 @@
         <v>68</v>
       </c>
       <c r="B501" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D501" s="6" t="n">
-        <v>5306.0</v>
+        <v>296618.0</v>
       </c>
       <c r="E501" s="7" t="s">
         <v>12</v>
@@ -15170,10 +15170,10 @@
         <v>13</v>
       </c>
       <c r="C502" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D502" s="6" t="n">
-        <v>14544.0</v>
+        <v>70327.0</v>
       </c>
       <c r="E502" s="7" t="s">
         <v>12</v>
@@ -15196,19 +15196,19 @@
         <v>68</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D503" s="6" t="n">
-        <v>4041.0</v>
+        <v>107735.0</v>
       </c>
       <c r="E503" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F503" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F503" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G503" s="8" t="s">
         <v>68</v>
@@ -15228,16 +15228,16 @@
         <v>13</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D504" s="6" t="n">
-        <v>248.0</v>
+        <v>144021.0</v>
       </c>
       <c r="E504" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F504" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F504" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G504" s="8" t="s">
         <v>69</v>
@@ -15257,10 +15257,10 @@
         <v>13</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D505" s="6" t="n">
-        <v>72938.0</v>
+        <v>62084.0</v>
       </c>
       <c r="E505" s="7" t="s">
         <v>12</v>
@@ -15286,16 +15286,16 @@
         <v>13</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D506" s="6" t="n">
-        <v>144021.0</v>
+        <v>30675.0</v>
       </c>
       <c r="E506" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F506" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F506" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G506" s="8" t="s">
         <v>69</v>
@@ -15315,10 +15315,10 @@
         <v>13</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D507" s="6" t="n">
-        <v>62084.0</v>
+        <v>72938.0</v>
       </c>
       <c r="E507" s="7" t="s">
         <v>12</v>
@@ -15344,10 +15344,10 @@
         <v>13</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D508" s="6" t="n">
-        <v>123.0</v>
+        <v>248.0</v>
       </c>
       <c r="E508" s="7" t="s">
         <v>12</v>
@@ -15373,10 +15373,10 @@
         <v>13</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D509" s="6" t="n">
-        <v>5181.0</v>
+        <v>123.0</v>
       </c>
       <c r="E509" s="7" t="s">
         <v>12</v>
@@ -15402,16 +15402,16 @@
         <v>13</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D510" s="6" t="n">
-        <v>4716.0</v>
+        <v>908897.0</v>
       </c>
       <c r="E510" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F510" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F510" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G510" s="8" t="s">
         <v>69</v>
@@ -15431,10 +15431,10 @@
         <v>13</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D511" s="6" t="n">
-        <v>201113.0</v>
+        <v>4716.0</v>
       </c>
       <c r="E511" s="7" t="s">
         <v>12</v>
@@ -15460,10 +15460,10 @@
         <v>13</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D512" s="6" t="n">
-        <v>18261.0</v>
+        <v>201113.0</v>
       </c>
       <c r="E512" s="7" t="s">
         <v>12</v>
@@ -15489,10 +15489,10 @@
         <v>13</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D513" s="6" t="n">
-        <v>30675.0</v>
+        <v>5181.0</v>
       </c>
       <c r="E513" s="7" t="s">
         <v>12</v>
@@ -15518,16 +15518,16 @@
         <v>13</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D514" s="6" t="n">
-        <v>908897.0</v>
+        <v>18261.0</v>
       </c>
       <c r="E514" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F514" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F514" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G514" s="8" t="s">
         <v>69</v>
@@ -15547,10 +15547,10 @@
         <v>13</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D515" s="6" t="n">
-        <v>2898.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E515" s="7" t="s">
         <v>12</v>
@@ -15576,10 +15576,10 @@
         <v>13</v>
       </c>
       <c r="C516" s="5" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D516" s="6" t="n">
-        <v>1519.0</v>
+        <v>2898.0</v>
       </c>
       <c r="E516" s="7" t="s">
         <v>12</v>
@@ -15602,13 +15602,13 @@
         <v>69</v>
       </c>
       <c r="B517" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D517" s="6" t="n">
-        <v>12907.0</v>
+        <v>44.0</v>
       </c>
       <c r="E517" s="7" t="s">
         <v>12</v>
@@ -15631,13 +15631,13 @@
         <v>69</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D518" s="6" t="n">
-        <v>1408.0</v>
+        <v>12907.0</v>
       </c>
       <c r="E518" s="7" t="s">
         <v>12</v>
@@ -15663,10 +15663,10 @@
         <v>10</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D519" s="6" t="n">
-        <v>162695.0</v>
+        <v>1408.0</v>
       </c>
       <c r="E519" s="7" t="s">
         <v>12</v>
@@ -15689,19 +15689,19 @@
         <v>69</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D520" s="6" t="n">
-        <v>44.0</v>
+        <v>366304.0</v>
       </c>
       <c r="E520" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F520" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F520" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G520" s="8" t="s">
         <v>69</v>
@@ -15721,10 +15721,10 @@
         <v>10</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D521" s="6" t="n">
-        <v>372386.0</v>
+        <v>162695.0</v>
       </c>
       <c r="E521" s="7" t="s">
         <v>12</v>
@@ -15750,10 +15750,10 @@
         <v>10</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D522" s="6" t="n">
-        <v>162639.0</v>
+        <v>372386.0</v>
       </c>
       <c r="E522" s="7" t="s">
         <v>12</v>
@@ -15779,10 +15779,10 @@
         <v>10</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D523" s="6" t="n">
-        <v>42853.0</v>
+        <v>162639.0</v>
       </c>
       <c r="E523" s="7" t="s">
         <v>12</v>
@@ -15805,19 +15805,19 @@
         <v>69</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D524" s="6" t="n">
-        <v>366304.0</v>
+        <v>42853.0</v>
       </c>
       <c r="E524" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F524" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F524" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G524" s="8" t="s">
         <v>69</v>
@@ -15866,10 +15866,10 @@
         <v>30</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D526" s="6" t="n">
-        <v>7684.0</v>
+        <v>77128.0</v>
       </c>
       <c r="E526" s="7" t="s">
         <v>12</v>
@@ -15895,10 +15895,10 @@
         <v>30</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D527" s="6" t="n">
-        <v>1733.0</v>
+        <v>7684.0</v>
       </c>
       <c r="E527" s="7" t="s">
         <v>12</v>
@@ -15924,10 +15924,10 @@
         <v>30</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D528" s="6" t="n">
-        <v>284063.0</v>
+        <v>1733.0</v>
       </c>
       <c r="E528" s="7" t="s">
         <v>12</v>
@@ -15953,10 +15953,10 @@
         <v>30</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D529" s="6" t="n">
-        <v>26286.0</v>
+        <v>284063.0</v>
       </c>
       <c r="E529" s="7" t="s">
         <v>12</v>
@@ -15982,10 +15982,10 @@
         <v>30</v>
       </c>
       <c r="C530" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D530" s="6" t="n">
-        <v>77128.0</v>
+        <v>26286.0</v>
       </c>
       <c r="E530" s="7" t="s">
         <v>12</v>
@@ -16011,10 +16011,10 @@
         <v>13</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D531" s="6" t="n">
-        <v>133084.0</v>
+        <v>36834.0</v>
       </c>
       <c r="E531" s="7" t="s">
         <v>12</v>
@@ -16040,10 +16040,10 @@
         <v>13</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D532" s="6" t="n">
-        <v>2394.0</v>
+        <v>8250.0</v>
       </c>
       <c r="E532" s="7" t="s">
         <v>12</v>
@@ -16069,10 +16069,10 @@
         <v>13</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D533" s="6" t="n">
-        <v>8250.0</v>
+        <v>17644.0</v>
       </c>
       <c r="E533" s="7" t="s">
         <v>12</v>
@@ -16098,10 +16098,10 @@
         <v>13</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D534" s="6" t="n">
-        <v>17644.0</v>
+        <v>249.0</v>
       </c>
       <c r="E534" s="7" t="s">
         <v>12</v>
@@ -16127,10 +16127,10 @@
         <v>13</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D535" s="6" t="n">
-        <v>249.0</v>
+        <v>11404.0</v>
       </c>
       <c r="E535" s="7" t="s">
         <v>12</v>
@@ -16156,10 +16156,10 @@
         <v>13</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D536" s="6" t="n">
-        <v>11404.0</v>
+        <v>133084.0</v>
       </c>
       <c r="E536" s="7" t="s">
         <v>12</v>
@@ -16185,10 +16185,10 @@
         <v>13</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D537" s="6" t="n">
-        <v>658.0</v>
+        <v>155751.0</v>
       </c>
       <c r="E537" s="7" t="s">
         <v>12</v>
@@ -16214,10 +16214,10 @@
         <v>13</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D538" s="6" t="n">
-        <v>36834.0</v>
+        <v>1287.0</v>
       </c>
       <c r="E538" s="7" t="s">
         <v>12</v>
@@ -16243,10 +16243,10 @@
         <v>13</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D539" s="6" t="n">
-        <v>1287.0</v>
+        <v>658.0</v>
       </c>
       <c r="E539" s="7" t="s">
         <v>12</v>
@@ -16359,10 +16359,10 @@
         <v>13</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D543" s="6" t="n">
-        <v>180673.0</v>
+        <v>712.0</v>
       </c>
       <c r="E543" s="7" t="s">
         <v>12</v>
@@ -16388,10 +16388,10 @@
         <v>13</v>
       </c>
       <c r="C544" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D544" s="6" t="n">
-        <v>155751.0</v>
+        <v>2394.0</v>
       </c>
       <c r="E544" s="7" t="s">
         <v>12</v>
@@ -16414,13 +16414,13 @@
         <v>70</v>
       </c>
       <c r="B545" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D545" s="6" t="n">
-        <v>712.0</v>
+        <v>49132.0</v>
       </c>
       <c r="E545" s="7" t="s">
         <v>12</v>
@@ -16446,10 +16446,10 @@
         <v>13</v>
       </c>
       <c r="C546" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D546" s="6" t="n">
-        <v>61145.0</v>
+        <v>180673.0</v>
       </c>
       <c r="E546" s="7" t="s">
         <v>12</v>
@@ -16501,13 +16501,13 @@
         <v>70</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C548" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D548" s="6" t="n">
-        <v>445652.0</v>
+        <v>61145.0</v>
       </c>
       <c r="E548" s="7" t="s">
         <v>12</v>
@@ -16649,10 +16649,10 @@
         <v>10</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D553" s="6" t="n">
-        <v>49132.0</v>
+        <v>445652.0</v>
       </c>
       <c r="E553" s="7" t="s">
         <v>12</v>
@@ -16704,13 +16704,13 @@
         <v>70</v>
       </c>
       <c r="B555" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D555" s="6" t="n">
-        <v>17014.0</v>
+        <v>16624.0</v>
       </c>
       <c r="E555" s="7" t="s">
         <v>12</v>
@@ -16736,10 +16736,10 @@
         <v>30</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D556" s="6" t="n">
-        <v>167261.0</v>
+        <v>146605.0</v>
       </c>
       <c r="E556" s="7" t="s">
         <v>12</v>
@@ -16762,13 +16762,13 @@
         <v>70</v>
       </c>
       <c r="B557" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D557" s="6" t="n">
-        <v>833.0</v>
+        <v>24743.0</v>
       </c>
       <c r="E557" s="7" t="s">
         <v>12</v>
@@ -16791,13 +16791,13 @@
         <v>70</v>
       </c>
       <c r="B558" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D558" s="6" t="n">
-        <v>24743.0</v>
+        <v>17014.0</v>
       </c>
       <c r="E558" s="7" t="s">
         <v>12</v>
@@ -16820,13 +16820,13 @@
         <v>70</v>
       </c>
       <c r="B559" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D559" s="6" t="n">
-        <v>16624.0</v>
+        <v>833.0</v>
       </c>
       <c r="E559" s="7" t="s">
         <v>12</v>
@@ -16852,10 +16852,10 @@
         <v>30</v>
       </c>
       <c r="C560" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D560" s="6" t="n">
-        <v>146605.0</v>
+        <v>167261.0</v>
       </c>
       <c r="E560" s="7" t="s">
         <v>12</v>
@@ -17055,10 +17055,10 @@
         <v>13</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D567" s="6" t="n">
-        <v>147017.0</v>
+        <v>54.0</v>
       </c>
       <c r="E567" s="7" t="s">
         <v>12</v>
@@ -17113,10 +17113,10 @@
         <v>13</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D569" s="6" t="n">
-        <v>46194.0</v>
+        <v>147017.0</v>
       </c>
       <c r="E569" s="7" t="s">
         <v>12</v>
@@ -17142,10 +17142,10 @@
         <v>13</v>
       </c>
       <c r="C570" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D570" s="6" t="n">
-        <v>9716.0</v>
+        <v>46194.0</v>
       </c>
       <c r="E570" s="7" t="s">
         <v>12</v>
@@ -17229,10 +17229,10 @@
         <v>13</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D573" s="6" t="n">
-        <v>3016.0</v>
+        <v>73411.0</v>
       </c>
       <c r="E573" s="7" t="s">
         <v>12</v>
@@ -17258,10 +17258,10 @@
         <v>13</v>
       </c>
       <c r="C574" s="5" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D574" s="6" t="n">
-        <v>54.0</v>
+        <v>3016.0</v>
       </c>
       <c r="E574" s="7" t="s">
         <v>12</v>
@@ -17284,13 +17284,13 @@
         <v>71</v>
       </c>
       <c r="B575" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D575" s="6" t="n">
-        <v>30577.0</v>
+        <v>9716.0</v>
       </c>
       <c r="E575" s="7" t="s">
         <v>12</v>
@@ -17316,10 +17316,10 @@
         <v>13</v>
       </c>
       <c r="C576" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D576" s="6" t="n">
-        <v>73411.0</v>
+        <v>11348.0</v>
       </c>
       <c r="E576" s="7" t="s">
         <v>12</v>
@@ -17374,10 +17374,10 @@
         <v>10</v>
       </c>
       <c r="C578" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D578" s="6" t="n">
-        <v>132880.0</v>
+        <v>4412.0</v>
       </c>
       <c r="E578" s="7" t="s">
         <v>12</v>
@@ -17400,13 +17400,13 @@
         <v>71</v>
       </c>
       <c r="B579" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D579" s="6" t="n">
-        <v>11348.0</v>
+        <v>30577.0</v>
       </c>
       <c r="E579" s="7" t="s">
         <v>12</v>
@@ -17432,10 +17432,10 @@
         <v>10</v>
       </c>
       <c r="C580" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D580" s="6" t="n">
-        <v>369966.0</v>
+        <v>132880.0</v>
       </c>
       <c r="E580" s="7" t="s">
         <v>12</v>
@@ -17519,10 +17519,10 @@
         <v>10</v>
       </c>
       <c r="C583" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D583" s="6" t="n">
-        <v>4412.0</v>
+        <v>369966.0</v>
       </c>
       <c r="E583" s="7" t="s">
         <v>12</v>
@@ -17809,16 +17809,16 @@
         <v>13</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D593" s="6" t="n">
-        <v>31.0</v>
+        <v>481367.0</v>
       </c>
       <c r="E593" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F593" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F593" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G593" s="8" t="s">
         <v>72</v>
@@ -18099,16 +18099,16 @@
         <v>13</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D603" s="6" t="n">
-        <v>481367.0</v>
+        <v>17195.0</v>
       </c>
       <c r="E603" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F603" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F603" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G603" s="8" t="s">
         <v>72</v>
@@ -18128,10 +18128,10 @@
         <v>13</v>
       </c>
       <c r="C604" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D604" s="6" t="n">
-        <v>17195.0</v>
+        <v>31.0</v>
       </c>
       <c r="E604" s="7" t="s">
         <v>12</v>
@@ -18215,16 +18215,16 @@
         <v>10</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D607" s="6" t="n">
-        <v>414009.0</v>
+        <v>199612.0</v>
       </c>
       <c r="E607" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F607" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F607" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G607" s="8" t="s">
         <v>72</v>
@@ -18244,16 +18244,16 @@
         <v>10</v>
       </c>
       <c r="C608" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D608" s="6" t="n">
-        <v>69940.0</v>
+        <v>414009.0</v>
       </c>
       <c r="E608" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F608" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F608" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G608" s="8" t="s">
         <v>72</v>
@@ -18273,10 +18273,10 @@
         <v>10</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D609" s="6" t="n">
-        <v>4681.0</v>
+        <v>69940.0</v>
       </c>
       <c r="E609" s="7" t="s">
         <v>12</v>
@@ -18302,10 +18302,10 @@
         <v>10</v>
       </c>
       <c r="C610" s="5" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D610" s="6" t="n">
-        <v>199612.0</v>
+        <v>4681.0</v>
       </c>
       <c r="E610" s="7" t="s">
         <v>12</v>
@@ -18360,16 +18360,16 @@
         <v>30</v>
       </c>
       <c r="C612" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D612" s="6" t="n">
-        <v>393940.0</v>
+        <v>11956.0</v>
       </c>
       <c r="E612" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F612" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F612" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G612" s="8" t="s">
         <v>72</v>
@@ -18389,16 +18389,16 @@
         <v>30</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D613" s="6" t="n">
-        <v>10252.0</v>
+        <v>393940.0</v>
       </c>
       <c r="E613" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F613" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F613" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G613" s="8" t="s">
         <v>72</v>
@@ -18418,16 +18418,16 @@
         <v>30</v>
       </c>
       <c r="C614" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D614" s="6" t="n">
-        <v>219512.0</v>
+        <v>10252.0</v>
       </c>
       <c r="E614" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F614" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F614" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G614" s="8" t="s">
         <v>72</v>
@@ -18447,16 +18447,16 @@
         <v>30</v>
       </c>
       <c r="C615" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D615" s="6" t="n">
-        <v>45738.0</v>
+        <v>219512.0</v>
       </c>
       <c r="E615" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F615" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F615" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G615" s="8" t="s">
         <v>72</v>
@@ -18476,10 +18476,10 @@
         <v>30</v>
       </c>
       <c r="C616" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D616" s="6" t="n">
-        <v>11956.0</v>
+        <v>45738.0</v>
       </c>
       <c r="E616" s="7" t="s">
         <v>12</v>
@@ -18505,10 +18505,10 @@
         <v>13</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D617" s="6" t="n">
-        <v>4371.0</v>
+        <v>54493.0</v>
       </c>
       <c r="E617" s="7" t="s">
         <v>12</v>
@@ -18534,10 +18534,10 @@
         <v>13</v>
       </c>
       <c r="C618" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D618" s="6" t="n">
-        <v>597.0</v>
+        <v>251598.0</v>
       </c>
       <c r="E618" s="7" t="s">
         <v>12</v>
@@ -18563,10 +18563,10 @@
         <v>13</v>
       </c>
       <c r="C619" s="5" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D619" s="6" t="n">
-        <v>1345.0</v>
+        <v>597.0</v>
       </c>
       <c r="E619" s="7" t="s">
         <v>12</v>
@@ -18592,10 +18592,10 @@
         <v>13</v>
       </c>
       <c r="C620" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D620" s="6" t="n">
-        <v>3953.0</v>
+        <v>1345.0</v>
       </c>
       <c r="E620" s="7" t="s">
         <v>12</v>
@@ -18621,10 +18621,10 @@
         <v>13</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D621" s="6" t="n">
-        <v>681.0</v>
+        <v>3953.0</v>
       </c>
       <c r="E621" s="7" t="s">
         <v>12</v>
@@ -18650,10 +18650,10 @@
         <v>13</v>
       </c>
       <c r="C622" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D622" s="6" t="n">
-        <v>4464.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E622" s="7" t="s">
         <v>12</v>
@@ -18679,10 +18679,10 @@
         <v>13</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D623" s="6" t="n">
-        <v>83909.0</v>
+        <v>681.0</v>
       </c>
       <c r="E623" s="7" t="s">
         <v>12</v>
@@ -18708,10 +18708,10 @@
         <v>13</v>
       </c>
       <c r="C624" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D624" s="6" t="n">
-        <v>84856.0</v>
+        <v>4371.0</v>
       </c>
       <c r="E624" s="7" t="s">
         <v>12</v>
@@ -18737,10 +18737,10 @@
         <v>13</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D625" s="6" t="n">
-        <v>386333.0</v>
+        <v>83909.0</v>
       </c>
       <c r="E625" s="7" t="s">
         <v>12</v>
@@ -18766,10 +18766,10 @@
         <v>13</v>
       </c>
       <c r="C626" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D626" s="6" t="n">
-        <v>2658.0</v>
+        <v>84856.0</v>
       </c>
       <c r="E626" s="7" t="s">
         <v>12</v>
@@ -18795,16 +18795,16 @@
         <v>13</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D627" s="6" t="n">
-        <v>129190.0</v>
+        <v>4464.0</v>
       </c>
       <c r="E627" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F627" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F627" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G627" s="8" t="s">
         <v>73</v>
@@ -18824,10 +18824,10 @@
         <v>13</v>
       </c>
       <c r="C628" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D628" s="6" t="n">
-        <v>251598.0</v>
+        <v>386333.0</v>
       </c>
       <c r="E628" s="7" t="s">
         <v>12</v>
@@ -18853,16 +18853,16 @@
         <v>13</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D629" s="6" t="n">
-        <v>54493.0</v>
+        <v>129190.0</v>
       </c>
       <c r="E629" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F629" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F629" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G629" s="8" t="s">
         <v>73</v>
@@ -18879,13 +18879,13 @@
         <v>73</v>
       </c>
       <c r="B630" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C630" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D630" s="6" t="n">
-        <v>5327.0</v>
+        <v>5387.0</v>
       </c>
       <c r="E630" s="7" t="s">
         <v>12</v>
@@ -18908,13 +18908,13 @@
         <v>73</v>
       </c>
       <c r="B631" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C631" s="5" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D631" s="6" t="n">
-        <v>43478.0</v>
+        <v>5327.0</v>
       </c>
       <c r="E631" s="7" t="s">
         <v>12</v>
@@ -18940,10 +18940,10 @@
         <v>10</v>
       </c>
       <c r="C632" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D632" s="6" t="n">
-        <v>276686.0</v>
+        <v>511.0</v>
       </c>
       <c r="E632" s="7" t="s">
         <v>12</v>
@@ -18969,16 +18969,16 @@
         <v>10</v>
       </c>
       <c r="C633" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D633" s="6" t="n">
-        <v>65439.0</v>
+        <v>191571.0</v>
       </c>
       <c r="E633" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F633" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F633" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G633" s="8" t="s">
         <v>73</v>
@@ -18998,10 +18998,10 @@
         <v>10</v>
       </c>
       <c r="C634" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D634" s="6" t="n">
-        <v>139458.0</v>
+        <v>276686.0</v>
       </c>
       <c r="E634" s="7" t="s">
         <v>12</v>
@@ -19027,16 +19027,16 @@
         <v>10</v>
       </c>
       <c r="C635" s="5" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D635" s="6" t="n">
-        <v>191571.0</v>
+        <v>65439.0</v>
       </c>
       <c r="E635" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F635" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F635" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G635" s="8" t="s">
         <v>73</v>
@@ -19053,13 +19053,13 @@
         <v>73</v>
       </c>
       <c r="B636" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C636" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D636" s="6" t="n">
-        <v>1660.0</v>
+        <v>6983.0</v>
       </c>
       <c r="E636" s="7" t="s">
         <v>12</v>
@@ -19085,10 +19085,10 @@
         <v>10</v>
       </c>
       <c r="C637" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D637" s="6" t="n">
-        <v>511.0</v>
+        <v>139458.0</v>
       </c>
       <c r="E637" s="7" t="s">
         <v>12</v>
@@ -19111,13 +19111,13 @@
         <v>73</v>
       </c>
       <c r="B638" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C638" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D638" s="6" t="n">
-        <v>5387.0</v>
+        <v>1660.0</v>
       </c>
       <c r="E638" s="7" t="s">
         <v>12</v>
@@ -19143,16 +19143,16 @@
         <v>30</v>
       </c>
       <c r="C639" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D639" s="6" t="n">
-        <v>322311.0</v>
+        <v>43478.0</v>
       </c>
       <c r="E639" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F639" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F639" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G639" s="8" t="s">
         <v>73</v>
@@ -19172,16 +19172,16 @@
         <v>30</v>
       </c>
       <c r="C640" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D640" s="6" t="n">
-        <v>107.0</v>
+        <v>322311.0</v>
       </c>
       <c r="E640" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F640" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F640" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G640" s="8" t="s">
         <v>73</v>
@@ -19201,10 +19201,10 @@
         <v>30</v>
       </c>
       <c r="C641" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D641" s="6" t="n">
-        <v>220179.0</v>
+        <v>107.0</v>
       </c>
       <c r="E641" s="7" t="s">
         <v>12</v>
@@ -19230,10 +19230,10 @@
         <v>30</v>
       </c>
       <c r="C642" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D642" s="6" t="n">
-        <v>28519.0</v>
+        <v>220179.0</v>
       </c>
       <c r="E642" s="7" t="s">
         <v>12</v>
@@ -19256,13 +19256,13 @@
         <v>73</v>
       </c>
       <c r="B643" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C643" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D643" s="6" t="n">
-        <v>6983.0</v>
+        <v>28519.0</v>
       </c>
       <c r="E643" s="7" t="s">
         <v>12</v>
@@ -19291,7 +19291,7 @@
         <v>29</v>
       </c>
       <c r="D644" s="6" t="n">
-        <v>337691.0</v>
+        <v>337771.0</v>
       </c>
       <c r="E644" s="7" t="s">
         <v>12</v>
@@ -19433,10 +19433,10 @@
         <v>13</v>
       </c>
       <c r="C649" s="5" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="D649" s="6" t="n">
-        <v>2352.0</v>
+        <v>1953.0</v>
       </c>
       <c r="E649" s="7" t="s">
         <v>12</v>
@@ -19459,13 +19459,13 @@
         <v>74</v>
       </c>
       <c r="B650" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C650" s="5" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="D650" s="6" t="n">
-        <v>4304.0</v>
+        <v>13457.0</v>
       </c>
       <c r="E650" s="7" t="s">
         <v>12</v>
@@ -19491,10 +19491,10 @@
         <v>13</v>
       </c>
       <c r="C651" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D651" s="6" t="n">
-        <v>13457.0</v>
+        <v>507249.0</v>
       </c>
       <c r="E651" s="7" t="s">
         <v>12</v>
@@ -19517,13 +19517,13 @@
         <v>74</v>
       </c>
       <c r="B652" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C652" s="5" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="D652" s="6" t="n">
-        <v>506974.0</v>
+        <v>4304.0</v>
       </c>
       <c r="E652" s="7" t="s">
         <v>12</v>
@@ -19549,7 +19549,7 @@
         <v>10</v>
       </c>
       <c r="C653" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D653" s="6" t="n">
         <v>2106.0</v>
@@ -19578,7 +19578,7 @@
         <v>10</v>
       </c>
       <c r="C654" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D654" s="6" t="n">
         <v>4268.0</v>
@@ -19607,7 +19607,7 @@
         <v>13</v>
       </c>
       <c r="C655" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D655" s="6" t="n">
         <v>21715.0</v>
@@ -19636,10 +19636,10 @@
         <v>13</v>
       </c>
       <c r="C656" s="5" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="D656" s="6" t="n">
-        <v>1953.0</v>
+        <v>52273.0</v>
       </c>
       <c r="E656" s="7" t="s">
         <v>12</v>
@@ -19665,16 +19665,16 @@
         <v>13</v>
       </c>
       <c r="C657" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D657" s="6" t="n">
-        <v>52273.0</v>
+        <v>126794.0</v>
       </c>
       <c r="E657" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F657" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F657" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G657" s="8" t="s">
         <v>74</v>
@@ -19694,16 +19694,16 @@
         <v>13</v>
       </c>
       <c r="C658" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D658" s="6" t="n">
-        <v>126794.0</v>
+        <v>2352.0</v>
       </c>
       <c r="E658" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F658" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F658" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G658" s="8" t="s">
         <v>74</v>
@@ -19720,13 +19720,13 @@
         <v>74</v>
       </c>
       <c r="B659" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C659" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D659" s="6" t="n">
-        <v>1356.0</v>
+        <v>1843.0</v>
       </c>
       <c r="E659" s="7" t="s">
         <v>12</v>
@@ -19749,13 +19749,13 @@
         <v>74</v>
       </c>
       <c r="B660" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C660" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D660" s="6" t="n">
-        <v>1843.0</v>
+        <v>36007.0</v>
       </c>
       <c r="E660" s="7" t="s">
         <v>12</v>
@@ -19778,13 +19778,13 @@
         <v>74</v>
       </c>
       <c r="B661" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C661" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D661" s="6" t="n">
-        <v>3706.0</v>
+        <v>11491.0</v>
       </c>
       <c r="E661" s="7" t="s">
         <v>12</v>
@@ -19807,13 +19807,13 @@
         <v>74</v>
       </c>
       <c r="B662" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C662" s="5" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D662" s="6" t="n">
-        <v>11491.0</v>
+        <v>118438.0</v>
       </c>
       <c r="E662" s="7" t="s">
         <v>12</v>
@@ -19839,10 +19839,10 @@
         <v>10</v>
       </c>
       <c r="C663" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D663" s="6" t="n">
-        <v>118438.0</v>
+        <v>179290.0</v>
       </c>
       <c r="E663" s="7" t="s">
         <v>12</v>
@@ -19868,10 +19868,10 @@
         <v>10</v>
       </c>
       <c r="C664" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D664" s="6" t="n">
-        <v>6817.0</v>
+        <v>34079.0</v>
       </c>
       <c r="E664" s="7" t="s">
         <v>12</v>
@@ -19897,10 +19897,10 @@
         <v>10</v>
       </c>
       <c r="C665" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D665" s="6" t="n">
-        <v>34079.0</v>
+        <v>115323.0</v>
       </c>
       <c r="E665" s="7" t="s">
         <v>12</v>
@@ -19926,10 +19926,10 @@
         <v>10</v>
       </c>
       <c r="C666" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D666" s="6" t="n">
-        <v>115323.0</v>
+        <v>3706.0</v>
       </c>
       <c r="E666" s="7" t="s">
         <v>12</v>
@@ -19955,10 +19955,10 @@
         <v>10</v>
       </c>
       <c r="C667" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D667" s="6" t="n">
-        <v>179290.0</v>
+        <v>6817.0</v>
       </c>
       <c r="E667" s="7" t="s">
         <v>12</v>
@@ -19984,10 +19984,10 @@
         <v>30</v>
       </c>
       <c r="C668" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D668" s="6" t="n">
-        <v>36007.0</v>
+        <v>1356.0</v>
       </c>
       <c r="E668" s="7" t="s">
         <v>12</v>
@@ -20045,7 +20045,7 @@
         <v>38</v>
       </c>
       <c r="D670" s="6" t="n">
-        <v>347664.0</v>
+        <v>347974.0</v>
       </c>
       <c r="E670" s="7" t="s">
         <v>12</v>
@@ -20103,7 +20103,7 @@
         <v>39</v>
       </c>
       <c r="D672" s="6" t="n">
-        <v>196855.0</v>
+        <v>197199.0</v>
       </c>
       <c r="E672" s="7" t="s">
         <v>12</v>
@@ -20187,16 +20187,16 @@
         <v>13</v>
       </c>
       <c r="C675" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D675" s="6" t="n">
-        <v>483.0</v>
+        <v>12320.0</v>
       </c>
       <c r="E675" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F675" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F675" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G675" s="8" t="s">
         <v>80</v>
@@ -20216,10 +20216,10 @@
         <v>13</v>
       </c>
       <c r="C676" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D676" s="6" t="n">
-        <v>816.0</v>
+        <v>3618.0</v>
       </c>
       <c r="E676" s="7" t="s">
         <v>12</v>
@@ -20245,10 +20245,10 @@
         <v>13</v>
       </c>
       <c r="C677" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D677" s="6" t="n">
-        <v>148689.0</v>
+        <v>816.0</v>
       </c>
       <c r="E677" s="7" t="s">
         <v>12</v>
@@ -20274,10 +20274,10 @@
         <v>13</v>
       </c>
       <c r="C678" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D678" s="6" t="n">
-        <v>7587.0</v>
+        <v>6529.0</v>
       </c>
       <c r="E678" s="7" t="s">
         <v>12</v>
@@ -20303,10 +20303,10 @@
         <v>13</v>
       </c>
       <c r="C679" s="5" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="D679" s="6" t="n">
-        <v>29656.0</v>
+        <v>292434.0</v>
       </c>
       <c r="E679" s="7" t="s">
         <v>12</v>
@@ -20335,7 +20335,7 @@
         <v>76</v>
       </c>
       <c r="D680" s="6" t="n">
-        <v>8480.0</v>
+        <v>17699.0</v>
       </c>
       <c r="E680" s="7" t="s">
         <v>12</v>
@@ -20358,13 +20358,13 @@
         <v>80</v>
       </c>
       <c r="B681" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C681" s="5" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="D681" s="6" t="n">
-        <v>18784.0</v>
+        <v>9667.0</v>
       </c>
       <c r="E681" s="7" t="s">
         <v>12</v>
@@ -20390,10 +20390,10 @@
         <v>13</v>
       </c>
       <c r="C682" s="5" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D682" s="6" t="n">
-        <v>1869.0</v>
+        <v>6317.0</v>
       </c>
       <c r="E682" s="7" t="s">
         <v>12</v>
@@ -20416,13 +20416,13 @@
         <v>80</v>
       </c>
       <c r="B683" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C683" s="5" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="D683" s="6" t="n">
-        <v>34128.0</v>
+        <v>13138.0</v>
       </c>
       <c r="E683" s="7" t="s">
         <v>12</v>
@@ -20445,13 +20445,13 @@
         <v>80</v>
       </c>
       <c r="B684" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C684" s="5" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="D684" s="6" t="n">
-        <v>98043.0</v>
+        <v>30128.0</v>
       </c>
       <c r="E684" s="7" t="s">
         <v>12</v>
@@ -20474,19 +20474,19 @@
         <v>80</v>
       </c>
       <c r="B685" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C685" s="5" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="D685" s="6" t="n">
-        <v>6588.0</v>
+        <v>49711.0</v>
       </c>
       <c r="E685" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F685" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F685" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G685" s="8" t="s">
         <v>80</v>
@@ -20506,10 +20506,10 @@
         <v>13</v>
       </c>
       <c r="C686" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D686" s="6" t="n">
-        <v>14785.0</v>
+        <v>2762.0</v>
       </c>
       <c r="E686" s="7" t="s">
         <v>12</v>
@@ -20535,10 +20535,10 @@
         <v>13</v>
       </c>
       <c r="C687" s="5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D687" s="6" t="n">
-        <v>47.0</v>
+        <v>4039.0</v>
       </c>
       <c r="E687" s="7" t="s">
         <v>12</v>
@@ -20561,19 +20561,19 @@
         <v>80</v>
       </c>
       <c r="B688" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C688" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D688" s="6" t="n">
-        <v>3258.0</v>
+        <v>254917.0</v>
       </c>
       <c r="E688" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F688" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F688" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G688" s="8" t="s">
         <v>80</v>
@@ -20590,13 +20590,13 @@
         <v>80</v>
       </c>
       <c r="B689" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D689" s="6" t="n">
-        <v>195.0</v>
+        <v>211683.0</v>
       </c>
       <c r="E689" s="7" t="s">
         <v>12</v>
@@ -20619,13 +20619,13 @@
         <v>80</v>
       </c>
       <c r="B690" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C690" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D690" s="6" t="n">
-        <v>30384.0</v>
+        <v>108287.0</v>
       </c>
       <c r="E690" s="7" t="s">
         <v>12</v>
@@ -20648,19 +20648,19 @@
         <v>80</v>
       </c>
       <c r="B691" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C691" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D691" s="6" t="n">
-        <v>76393.0</v>
+        <v>66696.0</v>
       </c>
       <c r="E691" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F691" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F691" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G691" s="8" t="s">
         <v>80</v>
@@ -20677,13 +20677,13 @@
         <v>80</v>
       </c>
       <c r="B692" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C692" s="5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D692" s="6" t="n">
-        <v>8735.0</v>
+        <v>8637.0</v>
       </c>
       <c r="E692" s="7" t="s">
         <v>12</v>
@@ -20706,13 +20706,13 @@
         <v>80</v>
       </c>
       <c r="B693" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C693" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D693" s="6" t="n">
-        <v>1752.0</v>
+        <v>25353.0</v>
       </c>
       <c r="E693" s="7" t="s">
         <v>12</v>
@@ -20735,13 +20735,13 @@
         <v>80</v>
       </c>
       <c r="B694" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C694" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D694" s="6" t="n">
-        <v>70.0</v>
+        <v>12692.0</v>
       </c>
       <c r="E694" s="7" t="s">
         <v>12</v>
@@ -20764,13 +20764,13 @@
         <v>80</v>
       </c>
       <c r="B695" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C695" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D695" s="6" t="n">
-        <v>125852.0</v>
+        <v>97697.0</v>
       </c>
       <c r="E695" s="7" t="s">
         <v>12</v>
@@ -20793,13 +20793,13 @@
         <v>80</v>
       </c>
       <c r="B696" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C696" s="5" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D696" s="6" t="n">
-        <v>75334.0</v>
+        <v>8735.0</v>
       </c>
       <c r="E696" s="7" t="s">
         <v>12</v>
@@ -20822,13 +20822,13 @@
         <v>80</v>
       </c>
       <c r="B697" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C697" s="5" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D697" s="6" t="n">
-        <v>12407.0</v>
+        <v>29847.0</v>
       </c>
       <c r="E697" s="7" t="s">
         <v>12</v>
@@ -20843,6 +20843,151 @@
         <v>80</v>
       </c>
       <c r="I697" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B698" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C698" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D698" s="6" t="n">
+        <v>1752.0</v>
+      </c>
+      <c r="E698" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F698" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G698" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H698" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I698" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B699" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C699" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D699" s="6" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="E699" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F699" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G699" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H699" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I699" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B700" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C700" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D700" s="6" t="n">
+        <v>293933.0</v>
+      </c>
+      <c r="E700" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F700" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G700" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H700" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I700" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B701" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C701" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D701" s="6" t="n">
+        <v>154761.0</v>
+      </c>
+      <c r="E701" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F701" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G701" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H701" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I701" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B702" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C702" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D702" s="6" t="n">
+        <v>7858.0</v>
+      </c>
+      <c r="E702" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F702" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G702" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H702" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I702" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5524" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5708" uniqueCount="82">
   <si>
     <t>Ngày</t>
   </si>
@@ -239,13 +239,10 @@
     <t>2026-08-25</t>
   </si>
   <si>
-    <t>120254199840840712</t>
+    <t>120254199946650712</t>
   </si>
   <si>
     <t>120254199946640712</t>
-  </si>
-  <si>
-    <t>120254199946650712</t>
   </si>
   <si>
     <t>120254199946660712</t>
@@ -254,7 +251,13 @@
     <t>120254199840830712</t>
   </si>
   <si>
+    <t>120254199840840712</t>
+  </si>
+  <si>
     <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
   </si>
 </sst>
 </file>
@@ -618,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I702"/>
+  <dimension ref="A1:I725"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -10704,10 +10707,10 @@
         <v>13</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D348" s="6" t="n">
-        <v>14390.0</v>
+        <v>7510.0</v>
       </c>
       <c r="E348" s="7" t="s">
         <v>12</v>
@@ -10733,16 +10736,16 @@
         <v>13</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D349" s="6" t="n">
-        <v>9380.0</v>
+        <v>104026.0</v>
       </c>
       <c r="E349" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F349" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F349" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G349" s="8" t="s">
         <v>63</v>
@@ -10762,10 +10765,10 @@
         <v>13</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D350" s="6" t="n">
-        <v>185.0</v>
+        <v>9380.0</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>12</v>
@@ -10791,10 +10794,10 @@
         <v>13</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D351" s="6" t="n">
-        <v>7510.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>12</v>
@@ -10849,10 +10852,10 @@
         <v>13</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D353" s="6" t="n">
-        <v>89540.0</v>
+        <v>14390.0</v>
       </c>
       <c r="E353" s="7" t="s">
         <v>12</v>
@@ -10878,10 +10881,10 @@
         <v>13</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D354" s="6" t="n">
-        <v>69412.0</v>
+        <v>89540.0</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>12</v>
@@ -10994,16 +10997,16 @@
         <v>13</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D358" s="6" t="n">
-        <v>104026.0</v>
+        <v>69412.0</v>
       </c>
       <c r="E358" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F358" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F358" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G358" s="8" t="s">
         <v>63</v>
@@ -11020,13 +11023,13 @@
         <v>63</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>2365.0</v>
+        <v>185.0</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>12</v>
@@ -11049,13 +11052,13 @@
         <v>63</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D360" s="6" t="n">
-        <v>15854.0</v>
+        <v>42515.0</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>12</v>
@@ -11081,10 +11084,10 @@
         <v>10</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D361" s="6" t="n">
-        <v>1766.0</v>
+        <v>2365.0</v>
       </c>
       <c r="E361" s="7" t="s">
         <v>12</v>
@@ -11110,16 +11113,16 @@
         <v>30</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D362" s="6" t="n">
-        <v>42515.0</v>
+        <v>303397.0</v>
       </c>
       <c r="E362" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F362" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F362" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G362" s="8" t="s">
         <v>63</v>
@@ -11255,10 +11258,10 @@
         <v>10</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D367" s="6" t="n">
-        <v>5088.0</v>
+        <v>1766.0</v>
       </c>
       <c r="E367" s="7" t="s">
         <v>12</v>
@@ -11281,13 +11284,13 @@
         <v>63</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D368" s="6" t="n">
-        <v>111759.0</v>
+        <v>5088.0</v>
       </c>
       <c r="E368" s="7" t="s">
         <v>12</v>
@@ -11313,10 +11316,10 @@
         <v>30</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D369" s="6" t="n">
-        <v>2331.0</v>
+        <v>111759.0</v>
       </c>
       <c r="E369" s="7" t="s">
         <v>12</v>
@@ -11342,10 +11345,10 @@
         <v>30</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D370" s="6" t="n">
-        <v>82520.0</v>
+        <v>2331.0</v>
       </c>
       <c r="E370" s="7" t="s">
         <v>12</v>
@@ -11371,16 +11374,16 @@
         <v>30</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D371" s="6" t="n">
-        <v>303397.0</v>
+        <v>82520.0</v>
       </c>
       <c r="E371" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F371" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G371" s="8" t="s">
         <v>63</v>
@@ -16011,10 +16014,10 @@
         <v>13</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D531" s="6" t="n">
-        <v>36834.0</v>
+        <v>133084.0</v>
       </c>
       <c r="E531" s="7" t="s">
         <v>12</v>
@@ -16040,10 +16043,10 @@
         <v>13</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D532" s="6" t="n">
-        <v>8250.0</v>
+        <v>155751.0</v>
       </c>
       <c r="E532" s="7" t="s">
         <v>12</v>
@@ -16069,10 +16072,10 @@
         <v>13</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D533" s="6" t="n">
-        <v>17644.0</v>
+        <v>8250.0</v>
       </c>
       <c r="E533" s="7" t="s">
         <v>12</v>
@@ -16098,10 +16101,10 @@
         <v>13</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D534" s="6" t="n">
-        <v>249.0</v>
+        <v>17644.0</v>
       </c>
       <c r="E534" s="7" t="s">
         <v>12</v>
@@ -16127,10 +16130,10 @@
         <v>13</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D535" s="6" t="n">
-        <v>11404.0</v>
+        <v>249.0</v>
       </c>
       <c r="E535" s="7" t="s">
         <v>12</v>
@@ -16156,10 +16159,10 @@
         <v>13</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D536" s="6" t="n">
-        <v>133084.0</v>
+        <v>11404.0</v>
       </c>
       <c r="E536" s="7" t="s">
         <v>12</v>
@@ -16185,10 +16188,10 @@
         <v>13</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D537" s="6" t="n">
-        <v>155751.0</v>
+        <v>712.0</v>
       </c>
       <c r="E537" s="7" t="s">
         <v>12</v>
@@ -16214,10 +16217,10 @@
         <v>13</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D538" s="6" t="n">
-        <v>1287.0</v>
+        <v>36834.0</v>
       </c>
       <c r="E538" s="7" t="s">
         <v>12</v>
@@ -16243,10 +16246,10 @@
         <v>13</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D539" s="6" t="n">
-        <v>658.0</v>
+        <v>1287.0</v>
       </c>
       <c r="E539" s="7" t="s">
         <v>12</v>
@@ -16272,10 +16275,10 @@
         <v>13</v>
       </c>
       <c r="C540" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D540" s="6" t="n">
-        <v>2797.0</v>
+        <v>658.0</v>
       </c>
       <c r="E540" s="7" t="s">
         <v>12</v>
@@ -16301,10 +16304,10 @@
         <v>13</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D541" s="6" t="n">
-        <v>357059.0</v>
+        <v>2797.0</v>
       </c>
       <c r="E541" s="7" t="s">
         <v>12</v>
@@ -16330,10 +16333,10 @@
         <v>13</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D542" s="6" t="n">
-        <v>6031.0</v>
+        <v>357059.0</v>
       </c>
       <c r="E542" s="7" t="s">
         <v>12</v>
@@ -16359,10 +16362,10 @@
         <v>13</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D543" s="6" t="n">
-        <v>712.0</v>
+        <v>6031.0</v>
       </c>
       <c r="E543" s="7" t="s">
         <v>12</v>
@@ -16414,13 +16417,13 @@
         <v>70</v>
       </c>
       <c r="B545" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D545" s="6" t="n">
-        <v>49132.0</v>
+        <v>17014.0</v>
       </c>
       <c r="E545" s="7" t="s">
         <v>12</v>
@@ -16475,10 +16478,10 @@
         <v>30</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D547" s="6" t="n">
-        <v>8609.0</v>
+        <v>98434.0</v>
       </c>
       <c r="E547" s="7" t="s">
         <v>12</v>
@@ -16533,10 +16536,10 @@
         <v>10</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D549" s="6" t="n">
-        <v>68846.0</v>
+        <v>445652.0</v>
       </c>
       <c r="E549" s="7" t="s">
         <v>12</v>
@@ -16562,10 +16565,10 @@
         <v>10</v>
       </c>
       <c r="C550" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D550" s="6" t="n">
-        <v>5446.0</v>
+        <v>68846.0</v>
       </c>
       <c r="E550" s="7" t="s">
         <v>12</v>
@@ -16591,10 +16594,10 @@
         <v>10</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D551" s="6" t="n">
-        <v>184.0</v>
+        <v>5446.0</v>
       </c>
       <c r="E551" s="7" t="s">
         <v>12</v>
@@ -16617,13 +16620,13 @@
         <v>70</v>
       </c>
       <c r="B552" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C552" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D552" s="6" t="n">
-        <v>98434.0</v>
+        <v>184.0</v>
       </c>
       <c r="E552" s="7" t="s">
         <v>12</v>
@@ -16649,10 +16652,10 @@
         <v>10</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D553" s="6" t="n">
-        <v>445652.0</v>
+        <v>49132.0</v>
       </c>
       <c r="E553" s="7" t="s">
         <v>12</v>
@@ -16678,10 +16681,10 @@
         <v>30</v>
       </c>
       <c r="C554" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D554" s="6" t="n">
-        <v>9668.0</v>
+        <v>8609.0</v>
       </c>
       <c r="E554" s="7" t="s">
         <v>12</v>
@@ -16707,10 +16710,10 @@
         <v>30</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D555" s="6" t="n">
-        <v>16624.0</v>
+        <v>167261.0</v>
       </c>
       <c r="E555" s="7" t="s">
         <v>12</v>
@@ -16736,10 +16739,10 @@
         <v>30</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D556" s="6" t="n">
-        <v>146605.0</v>
+        <v>16624.0</v>
       </c>
       <c r="E556" s="7" t="s">
         <v>12</v>
@@ -16765,10 +16768,10 @@
         <v>30</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D557" s="6" t="n">
-        <v>24743.0</v>
+        <v>146605.0</v>
       </c>
       <c r="E557" s="7" t="s">
         <v>12</v>
@@ -16791,13 +16794,13 @@
         <v>70</v>
       </c>
       <c r="B558" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D558" s="6" t="n">
-        <v>17014.0</v>
+        <v>24743.0</v>
       </c>
       <c r="E558" s="7" t="s">
         <v>12</v>
@@ -16852,10 +16855,10 @@
         <v>30</v>
       </c>
       <c r="C560" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D560" s="6" t="n">
-        <v>167261.0</v>
+        <v>9668.0</v>
       </c>
       <c r="E560" s="7" t="s">
         <v>12</v>
@@ -17055,10 +17058,10 @@
         <v>13</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D567" s="6" t="n">
-        <v>54.0</v>
+        <v>9716.0</v>
       </c>
       <c r="E567" s="7" t="s">
         <v>12</v>
@@ -17287,10 +17290,10 @@
         <v>13</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D575" s="6" t="n">
-        <v>9716.0</v>
+        <v>54.0</v>
       </c>
       <c r="E575" s="7" t="s">
         <v>12</v>
@@ -17345,10 +17348,10 @@
         <v>10</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D577" s="6" t="n">
-        <v>649.0</v>
+        <v>5930.0</v>
       </c>
       <c r="E577" s="7" t="s">
         <v>12</v>
@@ -17400,13 +17403,13 @@
         <v>71</v>
       </c>
       <c r="B579" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D579" s="6" t="n">
-        <v>30577.0</v>
+        <v>30784.0</v>
       </c>
       <c r="E579" s="7" t="s">
         <v>12</v>
@@ -17461,10 +17464,10 @@
         <v>10</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D581" s="6" t="n">
-        <v>30784.0</v>
+        <v>17930.0</v>
       </c>
       <c r="E581" s="7" t="s">
         <v>12</v>
@@ -17490,10 +17493,10 @@
         <v>10</v>
       </c>
       <c r="C582" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D582" s="6" t="n">
-        <v>17930.0</v>
+        <v>649.0</v>
       </c>
       <c r="E582" s="7" t="s">
         <v>12</v>
@@ -17545,13 +17548,13 @@
         <v>71</v>
       </c>
       <c r="B584" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C584" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D584" s="6" t="n">
-        <v>5930.0</v>
+        <v>160983.0</v>
       </c>
       <c r="E584" s="7" t="s">
         <v>12</v>
@@ -17577,10 +17580,10 @@
         <v>30</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D585" s="6" t="n">
-        <v>3492.0</v>
+        <v>215594.0</v>
       </c>
       <c r="E585" s="7" t="s">
         <v>12</v>
@@ -17606,10 +17609,10 @@
         <v>30</v>
       </c>
       <c r="C586" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D586" s="6" t="n">
-        <v>267.0</v>
+        <v>3492.0</v>
       </c>
       <c r="E586" s="7" t="s">
         <v>12</v>
@@ -17635,16 +17638,16 @@
         <v>30</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D587" s="6" t="n">
-        <v>245314.0</v>
+        <v>30577.0</v>
       </c>
       <c r="E587" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F587" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F587" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G587" s="8" t="s">
         <v>71</v>
@@ -17693,16 +17696,16 @@
         <v>30</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D589" s="6" t="n">
-        <v>215594.0</v>
+        <v>245314.0</v>
       </c>
       <c r="E589" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F589" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F589" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G589" s="8" t="s">
         <v>71</v>
@@ -17722,10 +17725,10 @@
         <v>30</v>
       </c>
       <c r="C590" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D590" s="6" t="n">
-        <v>160983.0</v>
+        <v>267.0</v>
       </c>
       <c r="E590" s="7" t="s">
         <v>12</v>
@@ -17751,16 +17754,16 @@
         <v>13</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D591" s="6" t="n">
-        <v>30056.0</v>
+        <v>60893.0</v>
       </c>
       <c r="E591" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F591" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F591" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G591" s="8" t="s">
         <v>72</v>
@@ -17780,16 +17783,16 @@
         <v>13</v>
       </c>
       <c r="C592" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D592" s="6" t="n">
-        <v>138808.0</v>
+        <v>538223.0</v>
       </c>
       <c r="E592" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F592" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F592" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G592" s="8" t="s">
         <v>72</v>
@@ -17809,16 +17812,16 @@
         <v>13</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D593" s="6" t="n">
-        <v>481367.0</v>
+        <v>3386.0</v>
       </c>
       <c r="E593" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F593" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F593" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G593" s="8" t="s">
         <v>72</v>
@@ -17838,10 +17841,10 @@
         <v>13</v>
       </c>
       <c r="C594" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D594" s="6" t="n">
-        <v>5871.0</v>
+        <v>1973.0</v>
       </c>
       <c r="E594" s="7" t="s">
         <v>12</v>
@@ -17867,16 +17870,16 @@
         <v>13</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D595" s="6" t="n">
-        <v>21078.0</v>
+        <v>84215.0</v>
       </c>
       <c r="E595" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F595" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F595" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G595" s="8" t="s">
         <v>72</v>
@@ -17896,10 +17899,10 @@
         <v>13</v>
       </c>
       <c r="C596" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D596" s="6" t="n">
-        <v>1132.0</v>
+        <v>154891.0</v>
       </c>
       <c r="E596" s="7" t="s">
         <v>12</v>
@@ -17925,10 +17928,10 @@
         <v>13</v>
       </c>
       <c r="C597" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D597" s="6" t="n">
-        <v>154891.0</v>
+        <v>30056.0</v>
       </c>
       <c r="E597" s="7" t="s">
         <v>12</v>
@@ -17954,16 +17957,16 @@
         <v>13</v>
       </c>
       <c r="C598" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D598" s="6" t="n">
-        <v>84215.0</v>
+        <v>21078.0</v>
       </c>
       <c r="E598" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F598" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F598" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G598" s="8" t="s">
         <v>72</v>
@@ -17983,10 +17986,10 @@
         <v>13</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D599" s="6" t="n">
-        <v>1973.0</v>
+        <v>5871.0</v>
       </c>
       <c r="E599" s="7" t="s">
         <v>12</v>
@@ -18012,16 +18015,16 @@
         <v>13</v>
       </c>
       <c r="C600" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D600" s="6" t="n">
-        <v>3386.0</v>
+        <v>481367.0</v>
       </c>
       <c r="E600" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F600" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F600" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G600" s="8" t="s">
         <v>72</v>
@@ -18041,16 +18044,16 @@
         <v>13</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D601" s="6" t="n">
-        <v>538223.0</v>
+        <v>138808.0</v>
       </c>
       <c r="E601" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F601" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F601" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G601" s="8" t="s">
         <v>72</v>
@@ -18070,16 +18073,16 @@
         <v>13</v>
       </c>
       <c r="C602" s="5" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D602" s="6" t="n">
-        <v>60893.0</v>
+        <v>1132.0</v>
       </c>
       <c r="E602" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F602" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F602" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G602" s="8" t="s">
         <v>72</v>
@@ -18099,10 +18102,10 @@
         <v>13</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D603" s="6" t="n">
-        <v>17195.0</v>
+        <v>10263.0</v>
       </c>
       <c r="E603" s="7" t="s">
         <v>12</v>
@@ -18186,10 +18189,10 @@
         <v>13</v>
       </c>
       <c r="C606" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D606" s="6" t="n">
-        <v>10263.0</v>
+        <v>17195.0</v>
       </c>
       <c r="E606" s="7" t="s">
         <v>12</v>
@@ -18215,16 +18218,16 @@
         <v>10</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D607" s="6" t="n">
-        <v>199612.0</v>
+        <v>414009.0</v>
       </c>
       <c r="E607" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F607" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F607" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G607" s="8" t="s">
         <v>72</v>
@@ -18244,16 +18247,16 @@
         <v>10</v>
       </c>
       <c r="C608" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D608" s="6" t="n">
-        <v>414009.0</v>
+        <v>69940.0</v>
       </c>
       <c r="E608" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F608" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F608" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G608" s="8" t="s">
         <v>72</v>
@@ -18273,10 +18276,10 @@
         <v>10</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D609" s="6" t="n">
-        <v>69940.0</v>
+        <v>4681.0</v>
       </c>
       <c r="E609" s="7" t="s">
         <v>12</v>
@@ -18302,10 +18305,10 @@
         <v>10</v>
       </c>
       <c r="C610" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D610" s="6" t="n">
-        <v>4681.0</v>
+        <v>199612.0</v>
       </c>
       <c r="E610" s="7" t="s">
         <v>12</v>
@@ -18360,16 +18363,16 @@
         <v>30</v>
       </c>
       <c r="C612" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D612" s="6" t="n">
-        <v>11956.0</v>
+        <v>393940.0</v>
       </c>
       <c r="E612" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F612" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F612" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G612" s="8" t="s">
         <v>72</v>
@@ -18389,16 +18392,16 @@
         <v>30</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D613" s="6" t="n">
-        <v>393940.0</v>
+        <v>10252.0</v>
       </c>
       <c r="E613" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F613" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F613" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G613" s="8" t="s">
         <v>72</v>
@@ -18418,16 +18421,16 @@
         <v>30</v>
       </c>
       <c r="C614" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D614" s="6" t="n">
-        <v>10252.0</v>
+        <v>219512.0</v>
       </c>
       <c r="E614" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F614" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F614" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G614" s="8" t="s">
         <v>72</v>
@@ -18447,16 +18450,16 @@
         <v>30</v>
       </c>
       <c r="C615" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D615" s="6" t="n">
-        <v>219512.0</v>
+        <v>45738.0</v>
       </c>
       <c r="E615" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F615" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F615" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G615" s="8" t="s">
         <v>72</v>
@@ -18476,10 +18479,10 @@
         <v>30</v>
       </c>
       <c r="C616" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D616" s="6" t="n">
-        <v>45738.0</v>
+        <v>11956.0</v>
       </c>
       <c r="E616" s="7" t="s">
         <v>12</v>
@@ -18505,10 +18508,10 @@
         <v>13</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D617" s="6" t="n">
-        <v>54493.0</v>
+        <v>681.0</v>
       </c>
       <c r="E617" s="7" t="s">
         <v>12</v>
@@ -18621,10 +18624,10 @@
         <v>13</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D621" s="6" t="n">
-        <v>3953.0</v>
+        <v>54493.0</v>
       </c>
       <c r="E621" s="7" t="s">
         <v>12</v>
@@ -18650,10 +18653,10 @@
         <v>13</v>
       </c>
       <c r="C622" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D622" s="6" t="n">
-        <v>2658.0</v>
+        <v>84856.0</v>
       </c>
       <c r="E622" s="7" t="s">
         <v>12</v>
@@ -18679,10 +18682,10 @@
         <v>13</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D623" s="6" t="n">
-        <v>681.0</v>
+        <v>4371.0</v>
       </c>
       <c r="E623" s="7" t="s">
         <v>12</v>
@@ -18708,10 +18711,10 @@
         <v>13</v>
       </c>
       <c r="C624" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D624" s="6" t="n">
-        <v>4371.0</v>
+        <v>83909.0</v>
       </c>
       <c r="E624" s="7" t="s">
         <v>12</v>
@@ -18737,10 +18740,10 @@
         <v>13</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D625" s="6" t="n">
-        <v>83909.0</v>
+        <v>4464.0</v>
       </c>
       <c r="E625" s="7" t="s">
         <v>12</v>
@@ -18766,10 +18769,10 @@
         <v>13</v>
       </c>
       <c r="C626" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D626" s="6" t="n">
-        <v>84856.0</v>
+        <v>386333.0</v>
       </c>
       <c r="E626" s="7" t="s">
         <v>12</v>
@@ -18795,10 +18798,10 @@
         <v>13</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D627" s="6" t="n">
-        <v>4464.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E627" s="7" t="s">
         <v>12</v>
@@ -18824,16 +18827,16 @@
         <v>13</v>
       </c>
       <c r="C628" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D628" s="6" t="n">
-        <v>386333.0</v>
+        <v>129190.0</v>
       </c>
       <c r="E628" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F628" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F628" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G628" s="8" t="s">
         <v>73</v>
@@ -18853,16 +18856,16 @@
         <v>13</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D629" s="6" t="n">
-        <v>129190.0</v>
+        <v>3953.0</v>
       </c>
       <c r="E629" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F629" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F629" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G629" s="8" t="s">
         <v>73</v>
@@ -18879,13 +18882,13 @@
         <v>73</v>
       </c>
       <c r="B630" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C630" s="5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D630" s="6" t="n">
-        <v>5387.0</v>
+        <v>5327.0</v>
       </c>
       <c r="E630" s="7" t="s">
         <v>12</v>
@@ -18908,13 +18911,13 @@
         <v>73</v>
       </c>
       <c r="B631" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C631" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D631" s="6" t="n">
-        <v>5327.0</v>
+        <v>1660.0</v>
       </c>
       <c r="E631" s="7" t="s">
         <v>12</v>
@@ -18940,16 +18943,16 @@
         <v>10</v>
       </c>
       <c r="C632" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D632" s="6" t="n">
-        <v>511.0</v>
+        <v>191571.0</v>
       </c>
       <c r="E632" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F632" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F632" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G632" s="8" t="s">
         <v>73</v>
@@ -18969,16 +18972,16 @@
         <v>10</v>
       </c>
       <c r="C633" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D633" s="6" t="n">
-        <v>191571.0</v>
+        <v>276686.0</v>
       </c>
       <c r="E633" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F633" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F633" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G633" s="8" t="s">
         <v>73</v>
@@ -18998,10 +19001,10 @@
         <v>10</v>
       </c>
       <c r="C634" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D634" s="6" t="n">
-        <v>276686.0</v>
+        <v>65439.0</v>
       </c>
       <c r="E634" s="7" t="s">
         <v>12</v>
@@ -19027,10 +19030,10 @@
         <v>10</v>
       </c>
       <c r="C635" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D635" s="6" t="n">
-        <v>65439.0</v>
+        <v>139458.0</v>
       </c>
       <c r="E635" s="7" t="s">
         <v>12</v>
@@ -19053,13 +19056,13 @@
         <v>73</v>
       </c>
       <c r="B636" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C636" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D636" s="6" t="n">
-        <v>6983.0</v>
+        <v>511.0</v>
       </c>
       <c r="E636" s="7" t="s">
         <v>12</v>
@@ -19082,13 +19085,13 @@
         <v>73</v>
       </c>
       <c r="B637" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C637" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D637" s="6" t="n">
-        <v>139458.0</v>
+        <v>6983.0</v>
       </c>
       <c r="E637" s="7" t="s">
         <v>12</v>
@@ -19111,13 +19114,13 @@
         <v>73</v>
       </c>
       <c r="B638" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C638" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D638" s="6" t="n">
-        <v>1660.0</v>
+        <v>43478.0</v>
       </c>
       <c r="E638" s="7" t="s">
         <v>12</v>
@@ -19143,16 +19146,16 @@
         <v>30</v>
       </c>
       <c r="C639" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D639" s="6" t="n">
-        <v>43478.0</v>
+        <v>322311.0</v>
       </c>
       <c r="E639" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F639" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F639" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G639" s="8" t="s">
         <v>73</v>
@@ -19172,16 +19175,16 @@
         <v>30</v>
       </c>
       <c r="C640" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D640" s="6" t="n">
-        <v>322311.0</v>
+        <v>107.0</v>
       </c>
       <c r="E640" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F640" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F640" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G640" s="8" t="s">
         <v>73</v>
@@ -19201,10 +19204,10 @@
         <v>30</v>
       </c>
       <c r="C641" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D641" s="6" t="n">
-        <v>107.0</v>
+        <v>220179.0</v>
       </c>
       <c r="E641" s="7" t="s">
         <v>12</v>
@@ -19230,10 +19233,10 @@
         <v>30</v>
       </c>
       <c r="C642" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D642" s="6" t="n">
-        <v>220179.0</v>
+        <v>28519.0</v>
       </c>
       <c r="E642" s="7" t="s">
         <v>12</v>
@@ -19259,10 +19262,10 @@
         <v>30</v>
       </c>
       <c r="C643" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D643" s="6" t="n">
-        <v>28519.0</v>
+        <v>5387.0</v>
       </c>
       <c r="E643" s="7" t="s">
         <v>12</v>
@@ -19288,10 +19291,10 @@
         <v>13</v>
       </c>
       <c r="C644" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D644" s="6" t="n">
-        <v>337771.0</v>
+        <v>13457.0</v>
       </c>
       <c r="E644" s="7" t="s">
         <v>12</v>
@@ -19433,10 +19436,10 @@
         <v>13</v>
       </c>
       <c r="C649" s="5" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D649" s="6" t="n">
-        <v>1953.0</v>
+        <v>2352.0</v>
       </c>
       <c r="E649" s="7" t="s">
         <v>12</v>
@@ -19459,13 +19462,13 @@
         <v>74</v>
       </c>
       <c r="B650" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C650" s="5" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="D650" s="6" t="n">
-        <v>13457.0</v>
+        <v>2106.0</v>
       </c>
       <c r="E650" s="7" t="s">
         <v>12</v>
@@ -19552,7 +19555,7 @@
         <v>77</v>
       </c>
       <c r="D653" s="6" t="n">
-        <v>2106.0</v>
+        <v>4268.0</v>
       </c>
       <c r="E653" s="7" t="s">
         <v>12</v>
@@ -19575,13 +19578,13 @@
         <v>74</v>
       </c>
       <c r="B654" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C654" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D654" s="6" t="n">
-        <v>4268.0</v>
+        <v>21715.0</v>
       </c>
       <c r="E654" s="7" t="s">
         <v>12</v>
@@ -19610,7 +19613,7 @@
         <v>79</v>
       </c>
       <c r="D655" s="6" t="n">
-        <v>21715.0</v>
+        <v>1953.0</v>
       </c>
       <c r="E655" s="7" t="s">
         <v>12</v>
@@ -19636,16 +19639,16 @@
         <v>13</v>
       </c>
       <c r="C656" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D656" s="6" t="n">
-        <v>52273.0</v>
+        <v>126794.0</v>
       </c>
       <c r="E656" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F656" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F656" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G656" s="8" t="s">
         <v>74</v>
@@ -19665,16 +19668,16 @@
         <v>13</v>
       </c>
       <c r="C657" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D657" s="6" t="n">
-        <v>126794.0</v>
+        <v>338362.0</v>
       </c>
       <c r="E657" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F657" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F657" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G657" s="8" t="s">
         <v>74</v>
@@ -19694,10 +19697,10 @@
         <v>13</v>
       </c>
       <c r="C658" s="5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D658" s="6" t="n">
-        <v>2352.0</v>
+        <v>52273.0</v>
       </c>
       <c r="E658" s="7" t="s">
         <v>12</v>
@@ -19752,10 +19755,10 @@
         <v>30</v>
       </c>
       <c r="C660" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D660" s="6" t="n">
-        <v>36007.0</v>
+        <v>1356.0</v>
       </c>
       <c r="E660" s="7" t="s">
         <v>12</v>
@@ -19778,13 +19781,13 @@
         <v>74</v>
       </c>
       <c r="B661" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C661" s="5" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D661" s="6" t="n">
-        <v>11491.0</v>
+        <v>118438.0</v>
       </c>
       <c r="E661" s="7" t="s">
         <v>12</v>
@@ -19810,10 +19813,10 @@
         <v>10</v>
       </c>
       <c r="C662" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D662" s="6" t="n">
-        <v>118438.0</v>
+        <v>179290.0</v>
       </c>
       <c r="E662" s="7" t="s">
         <v>12</v>
@@ -19839,10 +19842,10 @@
         <v>10</v>
       </c>
       <c r="C663" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D663" s="6" t="n">
-        <v>179290.0</v>
+        <v>34079.0</v>
       </c>
       <c r="E663" s="7" t="s">
         <v>12</v>
@@ -19868,10 +19871,10 @@
         <v>10</v>
       </c>
       <c r="C664" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D664" s="6" t="n">
-        <v>34079.0</v>
+        <v>115323.0</v>
       </c>
       <c r="E664" s="7" t="s">
         <v>12</v>
@@ -19897,10 +19900,10 @@
         <v>10</v>
       </c>
       <c r="C665" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D665" s="6" t="n">
-        <v>115323.0</v>
+        <v>3706.0</v>
       </c>
       <c r="E665" s="7" t="s">
         <v>12</v>
@@ -19923,13 +19926,13 @@
         <v>74</v>
       </c>
       <c r="B666" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C666" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D666" s="6" t="n">
-        <v>3706.0</v>
+        <v>36007.0</v>
       </c>
       <c r="E666" s="7" t="s">
         <v>12</v>
@@ -19984,10 +19987,10 @@
         <v>30</v>
       </c>
       <c r="C668" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D668" s="6" t="n">
-        <v>1356.0</v>
+        <v>3560.0</v>
       </c>
       <c r="E668" s="7" t="s">
         <v>12</v>
@@ -20010,13 +20013,13 @@
         <v>74</v>
       </c>
       <c r="B669" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C669" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D669" s="6" t="n">
-        <v>10437.0</v>
+        <v>2655.0</v>
       </c>
       <c r="E669" s="7" t="s">
         <v>12</v>
@@ -20042,10 +20045,10 @@
         <v>30</v>
       </c>
       <c r="C670" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D670" s="6" t="n">
-        <v>347974.0</v>
+        <v>197199.0</v>
       </c>
       <c r="E670" s="7" t="s">
         <v>12</v>
@@ -20071,10 +20074,10 @@
         <v>30</v>
       </c>
       <c r="C671" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D671" s="6" t="n">
-        <v>2655.0</v>
+        <v>2286.0</v>
       </c>
       <c r="E671" s="7" t="s">
         <v>12</v>
@@ -20097,13 +20100,13 @@
         <v>74</v>
       </c>
       <c r="B672" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C672" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D672" s="6" t="n">
-        <v>197199.0</v>
+        <v>10437.0</v>
       </c>
       <c r="E672" s="7" t="s">
         <v>12</v>
@@ -20126,13 +20129,13 @@
         <v>74</v>
       </c>
       <c r="B673" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C673" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D673" s="6" t="n">
-        <v>2286.0</v>
+        <v>11491.0</v>
       </c>
       <c r="E673" s="7" t="s">
         <v>12</v>
@@ -20158,10 +20161,10 @@
         <v>30</v>
       </c>
       <c r="C674" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D674" s="6" t="n">
-        <v>3560.0</v>
+        <v>347974.0</v>
       </c>
       <c r="E674" s="7" t="s">
         <v>12</v>
@@ -20187,16 +20190,16 @@
         <v>13</v>
       </c>
       <c r="C675" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D675" s="6" t="n">
-        <v>12320.0</v>
+        <v>337903.0</v>
       </c>
       <c r="E675" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F675" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F675" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G675" s="8" t="s">
         <v>80</v>
@@ -20216,16 +20219,16 @@
         <v>13</v>
       </c>
       <c r="C676" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D676" s="6" t="n">
-        <v>3618.0</v>
+        <v>13014.0</v>
       </c>
       <c r="E676" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F676" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F676" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G676" s="8" t="s">
         <v>80</v>
@@ -20245,10 +20248,10 @@
         <v>13</v>
       </c>
       <c r="C677" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D677" s="6" t="n">
-        <v>816.0</v>
+        <v>3718.0</v>
       </c>
       <c r="E677" s="7" t="s">
         <v>12</v>
@@ -20274,10 +20277,10 @@
         <v>13</v>
       </c>
       <c r="C678" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D678" s="6" t="n">
-        <v>6529.0</v>
+        <v>512.0</v>
       </c>
       <c r="E678" s="7" t="s">
         <v>12</v>
@@ -20303,10 +20306,10 @@
         <v>13</v>
       </c>
       <c r="C679" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D679" s="6" t="n">
-        <v>292434.0</v>
+        <v>816.0</v>
       </c>
       <c r="E679" s="7" t="s">
         <v>12</v>
@@ -20329,13 +20332,13 @@
         <v>80</v>
       </c>
       <c r="B680" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C680" s="5" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="D680" s="6" t="n">
-        <v>17699.0</v>
+        <v>8434.0</v>
       </c>
       <c r="E680" s="7" t="s">
         <v>12</v>
@@ -20358,13 +20361,13 @@
         <v>80</v>
       </c>
       <c r="B681" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C681" s="5" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="D681" s="6" t="n">
-        <v>9667.0</v>
+        <v>15441.0</v>
       </c>
       <c r="E681" s="7" t="s">
         <v>12</v>
@@ -20390,10 +20393,10 @@
         <v>13</v>
       </c>
       <c r="C682" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D682" s="6" t="n">
-        <v>6317.0</v>
+        <v>9667.0</v>
       </c>
       <c r="E682" s="7" t="s">
         <v>12</v>
@@ -20416,13 +20419,13 @@
         <v>80</v>
       </c>
       <c r="B683" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C683" s="5" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="D683" s="6" t="n">
-        <v>13138.0</v>
+        <v>6317.0</v>
       </c>
       <c r="E683" s="7" t="s">
         <v>12</v>
@@ -20448,10 +20451,10 @@
         <v>10</v>
       </c>
       <c r="C684" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D684" s="6" t="n">
-        <v>30128.0</v>
+        <v>19439.0</v>
       </c>
       <c r="E684" s="7" t="s">
         <v>12</v>
@@ -20474,19 +20477,19 @@
         <v>80</v>
       </c>
       <c r="B685" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C685" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D685" s="6" t="n">
-        <v>49711.0</v>
+        <v>33064.0</v>
       </c>
       <c r="E685" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F685" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F685" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G685" s="8" t="s">
         <v>80</v>
@@ -20506,16 +20509,16 @@
         <v>13</v>
       </c>
       <c r="C686" s="5" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="D686" s="6" t="n">
-        <v>2762.0</v>
+        <v>54550.0</v>
       </c>
       <c r="E686" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F686" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F686" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G686" s="8" t="s">
         <v>80</v>
@@ -20535,10 +20538,10 @@
         <v>13</v>
       </c>
       <c r="C687" s="5" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D687" s="6" t="n">
-        <v>4039.0</v>
+        <v>9197.0</v>
       </c>
       <c r="E687" s="7" t="s">
         <v>12</v>
@@ -20561,19 +20564,19 @@
         <v>80</v>
       </c>
       <c r="B688" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C688" s="5" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D688" s="6" t="n">
-        <v>254917.0</v>
+        <v>7892.0</v>
       </c>
       <c r="E688" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F688" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F688" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G688" s="8" t="s">
         <v>80</v>
@@ -20593,10 +20596,10 @@
         <v>13</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D689" s="6" t="n">
-        <v>211683.0</v>
+        <v>4039.0</v>
       </c>
       <c r="E689" s="7" t="s">
         <v>12</v>
@@ -20619,13 +20622,13 @@
         <v>80</v>
       </c>
       <c r="B690" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C690" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D690" s="6" t="n">
-        <v>108287.0</v>
+        <v>1752.0</v>
       </c>
       <c r="E690" s="7" t="s">
         <v>12</v>
@@ -20651,16 +20654,16 @@
         <v>13</v>
       </c>
       <c r="C691" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D691" s="6" t="n">
-        <v>66696.0</v>
+        <v>252954.0</v>
       </c>
       <c r="E691" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F691" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F691" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G691" s="8" t="s">
         <v>80</v>
@@ -20677,13 +20680,13 @@
         <v>80</v>
       </c>
       <c r="B692" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C692" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D692" s="6" t="n">
-        <v>8637.0</v>
+        <v>227.0</v>
       </c>
       <c r="E692" s="7" t="s">
         <v>12</v>
@@ -20709,10 +20712,10 @@
         <v>13</v>
       </c>
       <c r="C693" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D693" s="6" t="n">
-        <v>25353.0</v>
+        <v>120464.0</v>
       </c>
       <c r="E693" s="7" t="s">
         <v>12</v>
@@ -20735,13 +20738,13 @@
         <v>80</v>
       </c>
       <c r="B694" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C694" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D694" s="6" t="n">
-        <v>12692.0</v>
+        <v>189500.0</v>
       </c>
       <c r="E694" s="7" t="s">
         <v>12</v>
@@ -20764,13 +20767,13 @@
         <v>80</v>
       </c>
       <c r="B695" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C695" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D695" s="6" t="n">
-        <v>97697.0</v>
+        <v>310950.0</v>
       </c>
       <c r="E695" s="7" t="s">
         <v>12</v>
@@ -20796,10 +20799,10 @@
         <v>30</v>
       </c>
       <c r="C696" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D696" s="6" t="n">
-        <v>8735.0</v>
+        <v>32442.0</v>
       </c>
       <c r="E696" s="7" t="s">
         <v>12</v>
@@ -20825,10 +20828,10 @@
         <v>30</v>
       </c>
       <c r="C697" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D697" s="6" t="n">
-        <v>29847.0</v>
+        <v>8735.0</v>
       </c>
       <c r="E697" s="7" t="s">
         <v>12</v>
@@ -20854,10 +20857,10 @@
         <v>10</v>
       </c>
       <c r="C698" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D698" s="6" t="n">
-        <v>1752.0</v>
+        <v>70.0</v>
       </c>
       <c r="E698" s="7" t="s">
         <v>12</v>
@@ -20880,19 +20883,19 @@
         <v>80</v>
       </c>
       <c r="B699" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C699" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D699" s="6" t="n">
-        <v>70.0</v>
+        <v>279574.0</v>
       </c>
       <c r="E699" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F699" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F699" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G699" s="8" t="s">
         <v>80</v>
@@ -20909,13 +20912,13 @@
         <v>80</v>
       </c>
       <c r="B700" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C700" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D700" s="6" t="n">
-        <v>293933.0</v>
+        <v>1622.0</v>
       </c>
       <c r="E700" s="7" t="s">
         <v>12</v>
@@ -20938,13 +20941,13 @@
         <v>80</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C701" s="5" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D701" s="6" t="n">
-        <v>154761.0</v>
+        <v>108278.0</v>
       </c>
       <c r="E701" s="7" t="s">
         <v>12</v>
@@ -20967,13 +20970,13 @@
         <v>80</v>
       </c>
       <c r="B702" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C702" s="5" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="D702" s="6" t="n">
-        <v>7858.0</v>
+        <v>13334.0</v>
       </c>
       <c r="E702" s="7" t="s">
         <v>12</v>
@@ -20988,6 +20991,673 @@
         <v>80</v>
       </c>
       <c r="I702" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B703" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C703" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D703" s="6" t="n">
+        <v>25961.0</v>
+      </c>
+      <c r="E703" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F703" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G703" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H703" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I703" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B704" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C704" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D704" s="6" t="n">
+        <v>8705.0</v>
+      </c>
+      <c r="E704" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F704" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G704" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H704" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I704" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B705" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C705" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D705" s="6" t="n">
+        <v>79394.0</v>
+      </c>
+      <c r="E705" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F705" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G705" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H705" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I705" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B706" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C706" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D706" s="6" t="n">
+        <v>18161.0</v>
+      </c>
+      <c r="E706" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F706" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G706" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H706" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I706" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B707" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C707" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D707" s="6" t="n">
+        <v>11957.0</v>
+      </c>
+      <c r="E707" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F707" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G707" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H707" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I707" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B708" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C708" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D708" s="6" t="n">
+        <v>17602.0</v>
+      </c>
+      <c r="E708" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F708" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G708" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H708" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I708" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B709" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C709" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D709" s="6" t="n">
+        <v>1924.0</v>
+      </c>
+      <c r="E709" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F709" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G709" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H709" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I709" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B710" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C710" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D710" s="6" t="n">
+        <v>8222.0</v>
+      </c>
+      <c r="E710" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F710" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G710" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H710" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I710" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B711" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C711" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D711" s="6" t="n">
+        <v>133159.0</v>
+      </c>
+      <c r="E711" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F711" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G711" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H711" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I711" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B712" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C712" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D712" s="6" t="n">
+        <v>960.0</v>
+      </c>
+      <c r="E712" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F712" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G712" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H712" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I712" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B713" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C713" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D713" s="6" t="n">
+        <v>5279.0</v>
+      </c>
+      <c r="E713" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F713" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G713" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H713" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I713" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B714" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C714" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D714" s="6" t="n">
+        <v>132163.0</v>
+      </c>
+      <c r="E714" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F714" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G714" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H714" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I714" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B715" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C715" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D715" s="6" t="n">
+        <v>9546.0</v>
+      </c>
+      <c r="E715" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F715" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G715" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H715" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I715" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B716" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C716" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D716" s="6" t="n">
+        <v>12367.0</v>
+      </c>
+      <c r="E716" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F716" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G716" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H716" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I716" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B717" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C717" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D717" s="6" t="n">
+        <v>677.0</v>
+      </c>
+      <c r="E717" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F717" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G717" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H717" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I717" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B718" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C718" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D718" s="6" t="n">
+        <v>6396.0</v>
+      </c>
+      <c r="E718" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F718" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G718" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H718" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I718" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B719" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C719" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D719" s="6" t="n">
+        <v>15883.0</v>
+      </c>
+      <c r="E719" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F719" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G719" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H719" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I719" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B720" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C720" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D720" s="6" t="n">
+        <v>23970.0</v>
+      </c>
+      <c r="E720" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F720" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G720" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H720" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I720" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B721" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C721" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D721" s="6" t="n">
+        <v>86503.0</v>
+      </c>
+      <c r="E721" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F721" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G721" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H721" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I721" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B722" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C722" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D722" s="6" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="E722" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F722" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G722" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H722" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I722" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B723" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C723" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D723" s="6" t="n">
+        <v>54951.0</v>
+      </c>
+      <c r="E723" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F723" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G723" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H723" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I723" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B724" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C724" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D724" s="6" t="n">
+        <v>26847.0</v>
+      </c>
+      <c r="E724" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F724" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G724" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H724" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I724" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B725" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C725" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D725" s="6" t="n">
+        <v>5760.0</v>
+      </c>
+      <c r="E725" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F725" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G725" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H725" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I725" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5708" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5913" uniqueCount="83">
   <si>
     <t>Ngày</t>
   </si>
@@ -239,10 +239,13 @@
     <t>2026-08-25</t>
   </si>
   <si>
-    <t>120254199946650712</t>
+    <t>120254199840840712</t>
   </si>
   <si>
     <t>120254199946640712</t>
+  </si>
+  <si>
+    <t>120254199946650712</t>
   </si>
   <si>
     <t>120254199946660712</t>
@@ -251,13 +254,13 @@
     <t>120254199840830712</t>
   </si>
   <si>
-    <t>120254199840840712</t>
-  </si>
-  <si>
     <t>2026-08-26</t>
   </si>
   <si>
     <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
   </si>
 </sst>
 </file>
@@ -621,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I725"/>
+  <dimension ref="A1:I751"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -3051,16 +3054,16 @@
         <v>13</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>1645.0</v>
+        <v>152212.0</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>53</v>
@@ -3080,10 +3083,10 @@
         <v>13</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>2497.0</v>
+        <v>1645.0</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>12</v>
@@ -3167,10 +3170,10 @@
         <v>13</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>45437.0</v>
+        <v>4423.0</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -3370,16 +3373,16 @@
         <v>13</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>152212.0</v>
+        <v>45437.0</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F95" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>53</v>
@@ -3396,13 +3399,13 @@
         <v>53</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>38896.0</v>
+        <v>2497.0</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>12</v>
@@ -3428,10 +3431,10 @@
         <v>13</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>4423.0</v>
+        <v>122.0</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>12</v>
@@ -3457,16 +3460,16 @@
         <v>10</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>98382.0</v>
+        <v>38896.0</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>53</v>
@@ -3483,13 +3486,13 @@
         <v>53</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>122.0</v>
+        <v>8698.0</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>12</v>
@@ -3628,13 +3631,13 @@
         <v>53</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>8698.0</v>
+        <v>4782.0</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>12</v>
@@ -3715,19 +3718,19 @@
         <v>53</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>183435.0</v>
+        <v>98382.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>53</v>
@@ -3747,10 +3750,10 @@
         <v>30</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>21260.0</v>
+        <v>183435.0</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>12</v>
@@ -3773,13 +3776,13 @@
         <v>53</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>4782.0</v>
+        <v>21260.0</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>12</v>
@@ -3892,16 +3895,16 @@
         <v>13</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>299654.0</v>
+        <v>290.0</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F113" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>54</v>
@@ -3921,10 +3924,10 @@
         <v>13</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>290.0</v>
+        <v>120.0</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>12</v>
@@ -3950,10 +3953,10 @@
         <v>13</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>120.0</v>
+        <v>1127.0</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>12</v>
@@ -3979,10 +3982,10 @@
         <v>13</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>1127.0</v>
+        <v>25484.0</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>12</v>
@@ -4008,10 +4011,10 @@
         <v>13</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>25484.0</v>
+        <v>480946.0</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>12</v>
@@ -4037,10 +4040,10 @@
         <v>13</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>480946.0</v>
+        <v>1325.0</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>12</v>
@@ -4124,16 +4127,16 @@
         <v>13</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>1325.0</v>
+        <v>109034.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>54</v>
@@ -4182,16 +4185,16 @@
         <v>13</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>109034.0</v>
+        <v>299654.0</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>54</v>
@@ -4733,10 +4736,10 @@
         <v>13</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>69.0</v>
+        <v>38461.0</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>12</v>
@@ -4936,10 +4939,10 @@
         <v>13</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>38461.0</v>
+        <v>69.0</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>12</v>
@@ -4965,10 +4968,10 @@
         <v>13</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>325679.0</v>
+        <v>21698.0</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>12</v>
@@ -5081,10 +5084,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>21698.0</v>
+        <v>325679.0</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>12</v>
@@ -5400,10 +5403,10 @@
         <v>13</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>26672.0</v>
+        <v>6378.0</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>12</v>
@@ -5458,10 +5461,10 @@
         <v>13</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>404959.0</v>
+        <v>171781.0</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>12</v>
@@ -5487,10 +5490,10 @@
         <v>13</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>6378.0</v>
+        <v>404959.0</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>12</v>
@@ -5516,16 +5519,16 @@
         <v>13</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>401598.0</v>
+        <v>1334.0</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F169" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>56</v>
@@ -5545,10 +5548,10 @@
         <v>13</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>44678.0</v>
+        <v>26672.0</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>12</v>
@@ -5574,10 +5577,10 @@
         <v>13</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>621.0</v>
+        <v>44678.0</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>12</v>
@@ -5603,10 +5606,10 @@
         <v>13</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>1334.0</v>
+        <v>621.0</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>12</v>
@@ -5632,16 +5635,16 @@
         <v>13</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>23158.0</v>
+        <v>401598.0</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F173" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F173" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G173" s="8" t="s">
         <v>56</v>
@@ -5661,10 +5664,10 @@
         <v>13</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>39617.0</v>
+        <v>23158.0</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>12</v>
@@ -5716,19 +5719,19 @@
         <v>56</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>171781.0</v>
+        <v>115261.0</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F176" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F176" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G176" s="8" t="s">
         <v>56</v>
@@ -5745,19 +5748,19 @@
         <v>56</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>115261.0</v>
+        <v>39617.0</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F177" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>56</v>
@@ -5777,10 +5780,10 @@
         <v>10</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>2647.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E178" s="7" t="s">
         <v>12</v>
@@ -5803,19 +5806,19 @@
         <v>56</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>5782.0</v>
+        <v>275877.0</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F179" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F179" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G179" s="8" t="s">
         <v>56</v>
@@ -5835,16 +5838,16 @@
         <v>10</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>399954.0</v>
+        <v>24571.0</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F180" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G180" s="8" t="s">
         <v>56</v>
@@ -5864,10 +5867,10 @@
         <v>10</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>6519.0</v>
+        <v>5782.0</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>12</v>
@@ -5893,16 +5896,16 @@
         <v>10</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>1182.0</v>
+        <v>399954.0</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F182" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F182" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G182" s="8" t="s">
         <v>56</v>
@@ -5919,19 +5922,19 @@
         <v>56</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>275877.0</v>
+        <v>6519.0</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F183" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G183" s="8" t="s">
         <v>56</v>
@@ -5951,10 +5954,10 @@
         <v>10</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>2290.0</v>
+        <v>2647.0</v>
       </c>
       <c r="E184" s="7" t="s">
         <v>12</v>
@@ -5977,13 +5980,13 @@
         <v>56</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>11551.0</v>
+        <v>2290.0</v>
       </c>
       <c r="E185" s="7" t="s">
         <v>12</v>
@@ -6006,19 +6009,19 @@
         <v>56</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>24571.0</v>
+        <v>331374.0</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F186" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F186" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G186" s="8" t="s">
         <v>56</v>
@@ -6038,10 +6041,10 @@
         <v>30</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>8022.0</v>
+        <v>11551.0</v>
       </c>
       <c r="E187" s="7" t="s">
         <v>12</v>
@@ -6067,16 +6070,16 @@
         <v>30</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>331374.0</v>
+        <v>8022.0</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F188" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G188" s="8" t="s">
         <v>56</v>
@@ -6241,10 +6244,10 @@
         <v>13</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>18488.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E194" s="7" t="s">
         <v>12</v>
@@ -6328,10 +6331,10 @@
         <v>13</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>55.0</v>
+        <v>18488.0</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>12</v>
@@ -6357,10 +6360,10 @@
         <v>13</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>2314.0</v>
+        <v>55.0</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>12</v>
@@ -6386,10 +6389,10 @@
         <v>13</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>12137.0</v>
+        <v>2314.0</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>12</v>
@@ -6441,19 +6444,19 @@
         <v>57</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>365576.0</v>
+        <v>210.0</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F201" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G201" s="8" t="s">
         <v>57</v>
@@ -6470,13 +6473,13 @@
         <v>57</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>476600.0</v>
+        <v>365576.0</v>
       </c>
       <c r="E202" s="7" t="s">
         <v>16</v>
@@ -6560,16 +6563,16 @@
         <v>30</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>264473.0</v>
+        <v>9109.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F205" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>57</v>
@@ -6586,19 +6589,19 @@
         <v>57</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>9109.0</v>
+        <v>476600.0</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F206" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F206" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>57</v>
@@ -6618,10 +6621,10 @@
         <v>30</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>210.0</v>
+        <v>28338.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6647,16 +6650,16 @@
         <v>30</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>28338.0</v>
+        <v>264473.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F208" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F208" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>57</v>
@@ -6705,10 +6708,10 @@
         <v>30</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>49095.0</v>
+        <v>83141.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6731,13 +6734,13 @@
         <v>57</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>83141.0</v>
+        <v>43423.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6763,10 +6766,10 @@
         <v>13</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>43423.0</v>
+        <v>1573.0</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>12</v>
@@ -6792,10 +6795,10 @@
         <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>1573.0</v>
+        <v>28802.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6818,13 +6821,13 @@
         <v>57</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>28802.0</v>
+        <v>49095.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6850,10 +6853,10 @@
         <v>13</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>28745.0</v>
+        <v>142958.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6879,10 +6882,10 @@
         <v>13</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>8204.0</v>
+        <v>2938.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
@@ -6908,10 +6911,10 @@
         <v>13</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>2938.0</v>
+        <v>21893.0</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>12</v>
@@ -6937,10 +6940,10 @@
         <v>13</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>21893.0</v>
+        <v>47108.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6966,10 +6969,10 @@
         <v>13</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>47108.0</v>
+        <v>28745.0</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>12</v>
@@ -6995,16 +6998,16 @@
         <v>13</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>400774.0</v>
+        <v>570723.0</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F220" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F220" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>58</v>
@@ -7024,16 +7027,16 @@
         <v>13</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>142958.0</v>
+        <v>55407.0</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F221" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F221" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G221" s="8" t="s">
         <v>58</v>
@@ -7053,16 +7056,16 @@
         <v>13</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>55407.0</v>
+        <v>8125.0</v>
       </c>
       <c r="E222" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F222" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>58</v>
@@ -7082,16 +7085,16 @@
         <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>8125.0</v>
+        <v>17602.0</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F223" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>58</v>
@@ -7111,16 +7114,16 @@
         <v>13</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>570723.0</v>
+        <v>1087.0</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F224" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>58</v>
@@ -7140,10 +7143,10 @@
         <v>13</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>17602.0</v>
+        <v>13953.0</v>
       </c>
       <c r="E225" s="7" t="s">
         <v>12</v>
@@ -7169,10 +7172,10 @@
         <v>13</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>1087.0</v>
+        <v>8204.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7198,10 +7201,10 @@
         <v>13</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>13953.0</v>
+        <v>400774.0</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
@@ -7224,13 +7227,13 @@
         <v>58</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>2847.0</v>
+        <v>196510.0</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>12</v>
@@ -7253,13 +7256,13 @@
         <v>58</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>196510.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7285,10 +7288,10 @@
         <v>10</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>8052.0</v>
+        <v>2847.0</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>12</v>
@@ -7314,10 +7317,10 @@
         <v>10</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>74089.0</v>
+        <v>586581.0</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>12</v>
@@ -7340,13 +7343,13 @@
         <v>58</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>52019.0</v>
+        <v>37213.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>12</v>
@@ -7372,16 +7375,16 @@
         <v>10</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>586581.0</v>
+        <v>65877.0</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F233" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F233" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G233" s="8" t="s">
         <v>58</v>
@@ -7401,10 +7404,10 @@
         <v>10</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>37213.0</v>
+        <v>8052.0</v>
       </c>
       <c r="E234" s="7" t="s">
         <v>12</v>
@@ -7430,16 +7433,16 @@
         <v>10</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>65877.0</v>
+        <v>74089.0</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F235" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G235" s="8" t="s">
         <v>58</v>
@@ -7456,13 +7459,13 @@
         <v>58</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>3681.0</v>
+        <v>515691.0</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>12</v>
@@ -7488,10 +7491,10 @@
         <v>30</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>515691.0</v>
+        <v>77697.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7517,10 +7520,10 @@
         <v>30</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>61111.0</v>
+        <v>7771.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7546,16 +7549,16 @@
         <v>30</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>77697.0</v>
+        <v>118765.0</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F239" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F239" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>58</v>
@@ -7572,13 +7575,13 @@
         <v>58</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>7771.0</v>
+        <v>52019.0</v>
       </c>
       <c r="E240" s="7" t="s">
         <v>12</v>
@@ -7604,16 +7607,16 @@
         <v>30</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>118765.0</v>
+        <v>61111.0</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F241" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>58</v>
@@ -7633,10 +7636,10 @@
         <v>13</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D242" s="6" t="n">
-        <v>1210.0</v>
+        <v>509.0</v>
       </c>
       <c r="E242" s="7" t="s">
         <v>12</v>
@@ -7778,16 +7781,16 @@
         <v>13</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>371730.0</v>
+        <v>1210.0</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F247" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>59</v>
@@ -7807,10 +7810,10 @@
         <v>13</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>509.0</v>
+        <v>33073.0</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>12</v>
@@ -7894,10 +7897,10 @@
         <v>13</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>33073.0</v>
+        <v>3296.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>12</v>
@@ -7952,16 +7955,16 @@
         <v>13</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>5458.0</v>
+        <v>371730.0</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F253" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F253" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G253" s="8" t="s">
         <v>59</v>
@@ -7981,10 +7984,10 @@
         <v>13</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>27632.0</v>
+        <v>5458.0</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>12</v>
@@ -8010,10 +8013,10 @@
         <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>3296.0</v>
+        <v>27632.0</v>
       </c>
       <c r="E255" s="7" t="s">
         <v>12</v>
@@ -8036,13 +8039,13 @@
         <v>59</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D256" s="6" t="n">
-        <v>17105.0</v>
+        <v>31570.0</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>12</v>
@@ -8065,13 +8068,13 @@
         <v>59</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>790.0</v>
+        <v>17105.0</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>12</v>
@@ -8097,10 +8100,10 @@
         <v>30</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>27683.0</v>
+        <v>302914.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8123,13 +8126,13 @@
         <v>59</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>31570.0</v>
+        <v>27683.0</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>12</v>
@@ -8242,10 +8245,10 @@
         <v>10</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>3186.0</v>
+        <v>790.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8271,10 +8274,10 @@
         <v>30</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>302914.0</v>
+        <v>10553.0</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>12</v>
@@ -8442,13 +8445,13 @@
         <v>59</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>10553.0</v>
+        <v>3186.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8474,10 +8477,10 @@
         <v>13</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D271" s="6" t="n">
-        <v>40129.0</v>
+        <v>233437.0</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>12</v>
@@ -8503,10 +8506,10 @@
         <v>13</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D272" s="6" t="n">
-        <v>20732.0</v>
+        <v>15.0</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>12</v>
@@ -8532,10 +8535,10 @@
         <v>13</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D273" s="6" t="n">
-        <v>6937.0</v>
+        <v>20732.0</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>12</v>
@@ -8561,10 +8564,10 @@
         <v>13</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D274" s="6" t="n">
-        <v>15068.0</v>
+        <v>6937.0</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>12</v>
@@ -8590,10 +8593,10 @@
         <v>13</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D275" s="6" t="n">
-        <v>26381.0</v>
+        <v>15068.0</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>12</v>
@@ -8619,10 +8622,10 @@
         <v>13</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D276" s="6" t="n">
-        <v>233437.0</v>
+        <v>2731.0</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>12</v>
@@ -8648,10 +8651,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>96105.0</v>
+        <v>40129.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8764,10 +8767,10 @@
         <v>13</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>38472.0</v>
+        <v>96105.0</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>12</v>
@@ -8793,10 +8796,10 @@
         <v>13</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>2731.0</v>
+        <v>38472.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8822,10 +8825,10 @@
         <v>13</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>35463.0</v>
+        <v>220465.0</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>12</v>
@@ -8851,10 +8854,10 @@
         <v>13</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>15.0</v>
+        <v>35463.0</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>12</v>
@@ -8880,10 +8883,10 @@
         <v>13</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>20130.0</v>
+        <v>26381.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8909,16 +8912,16 @@
         <v>13</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>220465.0</v>
+        <v>168847.0</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F286" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F286" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G286" s="8" t="s">
         <v>60</v>
@@ -8935,19 +8938,19 @@
         <v>60</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D287" s="6" t="n">
-        <v>318547.0</v>
+        <v>1780.0</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F287" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F287" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G287" s="8" t="s">
         <v>60</v>
@@ -8964,13 +8967,13 @@
         <v>60</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>1308.0</v>
+        <v>20130.0</v>
       </c>
       <c r="E288" s="7" t="s">
         <v>12</v>
@@ -8996,16 +8999,16 @@
         <v>10</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>621367.0</v>
+        <v>1308.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F289" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>60</v>
@@ -9022,19 +9025,19 @@
         <v>60</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>168847.0</v>
+        <v>6706.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F290" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>60</v>
@@ -9112,16 +9115,16 @@
         <v>10</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>1780.0</v>
+        <v>621367.0</v>
       </c>
       <c r="E293" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F293" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F293" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G293" s="8" t="s">
         <v>60</v>
@@ -9138,19 +9141,19 @@
         <v>60</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>6706.0</v>
+        <v>318547.0</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F294" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F294" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G294" s="8" t="s">
         <v>60</v>
@@ -9170,10 +9173,10 @@
         <v>30</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>27356.0</v>
+        <v>11792.0</v>
       </c>
       <c r="E295" s="7" t="s">
         <v>12</v>
@@ -9315,10 +9318,10 @@
         <v>30</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>11792.0</v>
+        <v>27356.0</v>
       </c>
       <c r="E300" s="7" t="s">
         <v>12</v>
@@ -9341,13 +9344,13 @@
         <v>61</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>1798.0</v>
+        <v>10887.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9489,16 +9492,16 @@
         <v>13</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>16117.0</v>
+        <v>414833.0</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F306" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F306" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G306" s="8" t="s">
         <v>61</v>
@@ -9518,10 +9521,10 @@
         <v>13</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>10887.0</v>
+        <v>49827.0</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>12</v>
@@ -9547,10 +9550,10 @@
         <v>13</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>49827.0</v>
+        <v>16117.0</v>
       </c>
       <c r="E308" s="7" t="s">
         <v>12</v>
@@ -9605,16 +9608,16 @@
         <v>13</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>414833.0</v>
+        <v>5125.0</v>
       </c>
       <c r="E310" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F310" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G310" s="8" t="s">
         <v>61</v>
@@ -9631,13 +9634,13 @@
         <v>61</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>5125.0</v>
+        <v>1798.0</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>12</v>
@@ -9689,13 +9692,13 @@
         <v>61</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>2152.0</v>
+        <v>32300.0</v>
       </c>
       <c r="E313" s="7" t="s">
         <v>12</v>
@@ -9776,19 +9779,19 @@
         <v>61</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>191.0</v>
+        <v>25684.0</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F316" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F316" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G316" s="8" t="s">
         <v>61</v>
@@ -9805,13 +9808,13 @@
         <v>61</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D317" s="6" t="n">
-        <v>7578.0</v>
+        <v>191.0</v>
       </c>
       <c r="E317" s="7" t="s">
         <v>12</v>
@@ -9895,16 +9898,16 @@
         <v>10</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>25684.0</v>
+        <v>7578.0</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F320" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F320" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G320" s="8" t="s">
         <v>61</v>
@@ -9950,13 +9953,13 @@
         <v>61</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>400544.0</v>
+        <v>2152.0</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>12</v>
@@ -9982,10 +9985,10 @@
         <v>30</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>17918.0</v>
+        <v>400544.0</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>12</v>
@@ -10011,10 +10014,10 @@
         <v>30</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>7822.0</v>
+        <v>17918.0</v>
       </c>
       <c r="E324" s="7" t="s">
         <v>12</v>
@@ -10040,10 +10043,10 @@
         <v>30</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D325" s="6" t="n">
-        <v>32300.0</v>
+        <v>7822.0</v>
       </c>
       <c r="E325" s="7" t="s">
         <v>12</v>
@@ -10301,10 +10304,10 @@
         <v>13</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D334" s="6" t="n">
-        <v>7928.0</v>
+        <v>155203.0</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>12</v>
@@ -10330,10 +10333,10 @@
         <v>13</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D335" s="6" t="n">
-        <v>155203.0</v>
+        <v>7928.0</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>12</v>
@@ -10359,10 +10362,10 @@
         <v>13</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>39009.0</v>
+        <v>21302.0</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>12</v>
@@ -10417,10 +10420,10 @@
         <v>13</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>21302.0</v>
+        <v>866.0</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>12</v>
@@ -10678,10 +10681,10 @@
         <v>13</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D347" s="6" t="n">
-        <v>866.0</v>
+        <v>39009.0</v>
       </c>
       <c r="E347" s="7" t="s">
         <v>12</v>
@@ -10794,10 +10797,10 @@
         <v>13</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D351" s="6" t="n">
-        <v>15854.0</v>
+        <v>185.0</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>12</v>
@@ -11026,10 +11029,10 @@
         <v>13</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D359" s="6" t="n">
-        <v>185.0</v>
+        <v>15854.0</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>12</v>
@@ -11403,16 +11406,16 @@
         <v>13</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D372" s="6" t="n">
-        <v>3681.0</v>
+        <v>404269.0</v>
       </c>
       <c r="E372" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F372" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F372" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G372" s="8" t="s">
         <v>64</v>
@@ -11432,16 +11435,16 @@
         <v>13</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D373" s="6" t="n">
-        <v>404269.0</v>
+        <v>894.0</v>
       </c>
       <c r="E373" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F373" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G373" s="8" t="s">
         <v>64</v>
@@ -11461,10 +11464,10 @@
         <v>13</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D374" s="6" t="n">
-        <v>894.0</v>
+        <v>815.0</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>12</v>
@@ -11490,10 +11493,10 @@
         <v>13</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D375" s="6" t="n">
-        <v>815.0</v>
+        <v>91385.0</v>
       </c>
       <c r="E375" s="7" t="s">
         <v>12</v>
@@ -11519,10 +11522,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>91385.0</v>
+        <v>228939.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11548,10 +11551,10 @@
         <v>13</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D377" s="6" t="n">
-        <v>228939.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E377" s="7" t="s">
         <v>12</v>
@@ -11719,13 +11722,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>8817.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11748,13 +11751,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>14304.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11777,13 +11780,13 @@
         <v>64</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D385" s="6" t="n">
-        <v>69259.0</v>
+        <v>3572.0</v>
       </c>
       <c r="E385" s="7" t="s">
         <v>12</v>
@@ -11806,13 +11809,13 @@
         <v>64</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D386" s="6" t="n">
-        <v>25352.0</v>
+        <v>14304.0</v>
       </c>
       <c r="E386" s="7" t="s">
         <v>12</v>
@@ -11922,13 +11925,13 @@
         <v>64</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>3572.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E390" s="7" t="s">
         <v>12</v>
@@ -11983,10 +11986,10 @@
         <v>30</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D392" s="6" t="n">
-        <v>13204.0</v>
+        <v>42128.0</v>
       </c>
       <c r="E392" s="7" t="s">
         <v>12</v>
@@ -12012,10 +12015,10 @@
         <v>30</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D393" s="6" t="n">
-        <v>42128.0</v>
+        <v>12024.0</v>
       </c>
       <c r="E393" s="7" t="s">
         <v>12</v>
@@ -12041,16 +12044,16 @@
         <v>30</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D394" s="6" t="n">
-        <v>12024.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E394" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F394" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F394" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G394" s="8" t="s">
         <v>64</v>
@@ -12070,16 +12073,16 @@
         <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>252681.0</v>
+        <v>13204.0</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F395" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F395" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G395" s="8" t="s">
         <v>64</v>
@@ -12128,10 +12131,10 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D397" s="6" t="n">
-        <v>2360.0</v>
+        <v>5282.0</v>
       </c>
       <c r="E397" s="7" t="s">
         <v>12</v>
@@ -12244,16 +12247,16 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>65752.0</v>
+        <v>728271.0</v>
       </c>
       <c r="E401" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F401" s="7" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>65</v>
@@ -12331,16 +12334,16 @@
         <v>13</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D404" s="6" t="n">
-        <v>728271.0</v>
+        <v>6582.0</v>
       </c>
       <c r="E404" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F404" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F404" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G404" s="8" t="s">
         <v>65</v>
@@ -12360,10 +12363,10 @@
         <v>13</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D405" s="6" t="n">
-        <v>6582.0</v>
+        <v>48.0</v>
       </c>
       <c r="E405" s="7" t="s">
         <v>12</v>
@@ -12389,16 +12392,16 @@
         <v>13</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D406" s="6" t="n">
-        <v>48.0</v>
+        <v>9750.0</v>
       </c>
       <c r="E406" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F406" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F406" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G406" s="8" t="s">
         <v>65</v>
@@ -12418,16 +12421,16 @@
         <v>13</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D407" s="6" t="n">
-        <v>9750.0</v>
+        <v>2360.0</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F407" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G407" s="8" t="s">
         <v>65</v>
@@ -12447,16 +12450,16 @@
         <v>13</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D408" s="6" t="n">
-        <v>5282.0</v>
+        <v>65752.0</v>
       </c>
       <c r="E408" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F408" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F408" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G408" s="8" t="s">
         <v>65</v>
@@ -12473,13 +12476,13 @@
         <v>65</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D409" s="6" t="n">
-        <v>73210.0</v>
+        <v>160813.0</v>
       </c>
       <c r="E409" s="7" t="s">
         <v>12</v>
@@ -12534,10 +12537,10 @@
         <v>13</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D411" s="6" t="n">
-        <v>4067.0</v>
+        <v>73210.0</v>
       </c>
       <c r="E411" s="7" t="s">
         <v>12</v>
@@ -12792,13 +12795,13 @@
         <v>65</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D420" s="6" t="n">
-        <v>160813.0</v>
+        <v>39117.0</v>
       </c>
       <c r="E420" s="7" t="s">
         <v>12</v>
@@ -12821,13 +12824,13 @@
         <v>65</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>39117.0</v>
+        <v>4067.0</v>
       </c>
       <c r="E421" s="7" t="s">
         <v>12</v>
@@ -12853,10 +12856,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D422" s="6" t="n">
-        <v>784.0</v>
+        <v>1359.0</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>12</v>
@@ -12882,10 +12885,10 @@
         <v>13</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D423" s="6" t="n">
-        <v>1355.0</v>
+        <v>58027.0</v>
       </c>
       <c r="E423" s="7" t="s">
         <v>12</v>
@@ -12911,10 +12914,10 @@
         <v>13</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D424" s="6" t="n">
-        <v>44956.0</v>
+        <v>8420.0</v>
       </c>
       <c r="E424" s="7" t="s">
         <v>12</v>
@@ -12940,10 +12943,10 @@
         <v>13</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D425" s="6" t="n">
-        <v>58027.0</v>
+        <v>210.0</v>
       </c>
       <c r="E425" s="7" t="s">
         <v>12</v>
@@ -12969,10 +12972,10 @@
         <v>13</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D426" s="6" t="n">
-        <v>8420.0</v>
+        <v>784.0</v>
       </c>
       <c r="E426" s="7" t="s">
         <v>12</v>
@@ -12998,10 +13001,10 @@
         <v>13</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>210.0</v>
+        <v>1355.0</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>12</v>
@@ -13027,10 +13030,10 @@
         <v>13</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D428" s="6" t="n">
-        <v>5605.0</v>
+        <v>8146.0</v>
       </c>
       <c r="E428" s="7" t="s">
         <v>12</v>
@@ -13056,10 +13059,10 @@
         <v>13</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D429" s="6" t="n">
-        <v>1359.0</v>
+        <v>261758.0</v>
       </c>
       <c r="E429" s="7" t="s">
         <v>12</v>
@@ -13085,10 +13088,10 @@
         <v>13</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D430" s="6" t="n">
-        <v>8146.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E430" s="7" t="s">
         <v>12</v>
@@ -13114,10 +13117,10 @@
         <v>13</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>261758.0</v>
+        <v>4241.0</v>
       </c>
       <c r="E431" s="7" t="s">
         <v>12</v>
@@ -13143,16 +13146,16 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>70064.0</v>
+        <v>510218.0</v>
       </c>
       <c r="E432" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F432" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F432" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G432" s="8" t="s">
         <v>66</v>
@@ -13172,10 +13175,10 @@
         <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>4241.0</v>
+        <v>5605.0</v>
       </c>
       <c r="E433" s="7" t="s">
         <v>12</v>
@@ -13201,16 +13204,16 @@
         <v>13</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D434" s="6" t="n">
-        <v>510218.0</v>
+        <v>44956.0</v>
       </c>
       <c r="E434" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F434" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F434" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G434" s="8" t="s">
         <v>66</v>
@@ -13285,13 +13288,13 @@
         <v>66</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D437" s="6" t="n">
-        <v>2197.0</v>
+        <v>9349.0</v>
       </c>
       <c r="E437" s="7" t="s">
         <v>12</v>
@@ -13317,10 +13320,10 @@
         <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D438" s="6" t="n">
-        <v>5730.0</v>
+        <v>108610.0</v>
       </c>
       <c r="E438" s="7" t="s">
         <v>12</v>
@@ -13343,19 +13346,19 @@
         <v>66</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>398394.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E439" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F439" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F439" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G439" s="8" t="s">
         <v>66</v>
@@ -13375,10 +13378,10 @@
         <v>10</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D440" s="6" t="n">
-        <v>3803.0</v>
+        <v>209762.0</v>
       </c>
       <c r="E440" s="7" t="s">
         <v>12</v>
@@ -13404,16 +13407,16 @@
         <v>10</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>210756.0</v>
+        <v>4524.0</v>
       </c>
       <c r="E441" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F441" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F441" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G441" s="8" t="s">
         <v>66</v>
@@ -13433,10 +13436,10 @@
         <v>10</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D442" s="6" t="n">
-        <v>209762.0</v>
+        <v>5730.0</v>
       </c>
       <c r="E442" s="7" t="s">
         <v>12</v>
@@ -13462,10 +13465,10 @@
         <v>10</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>4524.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E443" s="7" t="s">
         <v>12</v>
@@ -13488,13 +13491,13 @@
         <v>66</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D444" s="6" t="n">
-        <v>108610.0</v>
+        <v>31883.0</v>
       </c>
       <c r="E444" s="7" t="s">
         <v>12</v>
@@ -13517,13 +13520,13 @@
         <v>66</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>9349.0</v>
+        <v>1412.0</v>
       </c>
       <c r="E445" s="7" t="s">
         <v>12</v>
@@ -13549,16 +13552,16 @@
         <v>30</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D446" s="6" t="n">
-        <v>105.0</v>
+        <v>94352.0</v>
       </c>
       <c r="E446" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F446" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F446" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G446" s="8" t="s">
         <v>66</v>
@@ -13578,10 +13581,10 @@
         <v>30</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>1412.0</v>
+        <v>1503.0</v>
       </c>
       <c r="E447" s="7" t="s">
         <v>12</v>
@@ -13607,16 +13610,16 @@
         <v>30</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D448" s="6" t="n">
-        <v>94352.0</v>
+        <v>398394.0</v>
       </c>
       <c r="E448" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F448" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F448" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G448" s="8" t="s">
         <v>66</v>
@@ -13636,10 +13639,10 @@
         <v>30</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D449" s="6" t="n">
-        <v>1503.0</v>
+        <v>2197.0</v>
       </c>
       <c r="E449" s="7" t="s">
         <v>12</v>
@@ -13665,10 +13668,10 @@
         <v>30</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D450" s="6" t="n">
-        <v>31883.0</v>
+        <v>105.0</v>
       </c>
       <c r="E450" s="7" t="s">
         <v>12</v>
@@ -14068,13 +14071,13 @@
         <v>67</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D464" s="6" t="n">
-        <v>245670.0</v>
+        <v>64823.0</v>
       </c>
       <c r="E464" s="7" t="s">
         <v>12</v>
@@ -14155,13 +14158,13 @@
         <v>67</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>64823.0</v>
+        <v>116450.0</v>
       </c>
       <c r="E467" s="7" t="s">
         <v>12</v>
@@ -14274,10 +14277,10 @@
         <v>10</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D471" s="6" t="n">
-        <v>116450.0</v>
+        <v>245670.0</v>
       </c>
       <c r="E471" s="7" t="s">
         <v>12</v>
@@ -14822,19 +14825,19 @@
         <v>68</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D490" s="6" t="n">
-        <v>96503.0</v>
+        <v>296618.0</v>
       </c>
       <c r="E490" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F490" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F490" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G490" s="8" t="s">
         <v>68</v>
@@ -14851,19 +14854,19 @@
         <v>68</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D491" s="6" t="n">
-        <v>15334.0</v>
+        <v>96503.0</v>
       </c>
       <c r="E491" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F491" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F491" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G491" s="8" t="s">
         <v>68</v>
@@ -14880,13 +14883,13 @@
         <v>68</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D492" s="6" t="n">
-        <v>8296.0</v>
+        <v>54343.0</v>
       </c>
       <c r="E492" s="7" t="s">
         <v>12</v>
@@ -14912,10 +14915,10 @@
         <v>13</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D493" s="6" t="n">
-        <v>14544.0</v>
+        <v>70327.0</v>
       </c>
       <c r="E493" s="7" t="s">
         <v>12</v>
@@ -14938,13 +14941,13 @@
         <v>68</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D494" s="6" t="n">
-        <v>5306.0</v>
+        <v>170208.0</v>
       </c>
       <c r="E494" s="7" t="s">
         <v>12</v>
@@ -14967,13 +14970,13 @@
         <v>68</v>
       </c>
       <c r="B495" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D495" s="6" t="n">
-        <v>206053.0</v>
+        <v>13403.0</v>
       </c>
       <c r="E495" s="7" t="s">
         <v>12</v>
@@ -14996,19 +14999,19 @@
         <v>68</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D496" s="6" t="n">
-        <v>190807.0</v>
+        <v>15334.0</v>
       </c>
       <c r="E496" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F496" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F496" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G496" s="8" t="s">
         <v>68</v>
@@ -15025,19 +15028,19 @@
         <v>68</v>
       </c>
       <c r="B497" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D497" s="6" t="n">
-        <v>4041.0</v>
+        <v>107735.0</v>
       </c>
       <c r="E497" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F497" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F497" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G497" s="8" t="s">
         <v>68</v>
@@ -15057,10 +15060,10 @@
         <v>30</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D498" s="6" t="n">
-        <v>54343.0</v>
+        <v>4041.0</v>
       </c>
       <c r="E498" s="7" t="s">
         <v>12</v>
@@ -15083,13 +15086,13 @@
         <v>68</v>
       </c>
       <c r="B499" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D499" s="6" t="n">
-        <v>13403.0</v>
+        <v>206053.0</v>
       </c>
       <c r="E499" s="7" t="s">
         <v>12</v>
@@ -15112,13 +15115,13 @@
         <v>68</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D500" s="6" t="n">
-        <v>170208.0</v>
+        <v>5306.0</v>
       </c>
       <c r="E500" s="7" t="s">
         <v>12</v>
@@ -15141,13 +15144,13 @@
         <v>68</v>
       </c>
       <c r="B501" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D501" s="6" t="n">
-        <v>296618.0</v>
+        <v>14544.0</v>
       </c>
       <c r="E501" s="7" t="s">
         <v>12</v>
@@ -15173,10 +15176,10 @@
         <v>13</v>
       </c>
       <c r="C502" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D502" s="6" t="n">
-        <v>70327.0</v>
+        <v>8296.0</v>
       </c>
       <c r="E502" s="7" t="s">
         <v>12</v>
@@ -15199,13 +15202,13 @@
         <v>68</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D503" s="6" t="n">
-        <v>107735.0</v>
+        <v>190807.0</v>
       </c>
       <c r="E503" s="7" t="s">
         <v>16</v>
@@ -15231,16 +15234,16 @@
         <v>13</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D504" s="6" t="n">
-        <v>144021.0</v>
+        <v>4716.0</v>
       </c>
       <c r="E504" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F504" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F504" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G504" s="8" t="s">
         <v>69</v>
@@ -15260,16 +15263,16 @@
         <v>13</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D505" s="6" t="n">
-        <v>62084.0</v>
+        <v>144021.0</v>
       </c>
       <c r="E505" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F505" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F505" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G505" s="8" t="s">
         <v>69</v>
@@ -15289,10 +15292,10 @@
         <v>13</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D506" s="6" t="n">
-        <v>30675.0</v>
+        <v>62084.0</v>
       </c>
       <c r="E506" s="7" t="s">
         <v>12</v>
@@ -15318,10 +15321,10 @@
         <v>13</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D507" s="6" t="n">
-        <v>72938.0</v>
+        <v>123.0</v>
       </c>
       <c r="E507" s="7" t="s">
         <v>12</v>
@@ -15376,10 +15379,10 @@
         <v>13</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D509" s="6" t="n">
-        <v>123.0</v>
+        <v>18261.0</v>
       </c>
       <c r="E509" s="7" t="s">
         <v>12</v>
@@ -15405,16 +15408,16 @@
         <v>13</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D510" s="6" t="n">
-        <v>908897.0</v>
+        <v>201113.0</v>
       </c>
       <c r="E510" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F510" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F510" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G510" s="8" t="s">
         <v>69</v>
@@ -15434,10 +15437,10 @@
         <v>13</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D511" s="6" t="n">
-        <v>4716.0</v>
+        <v>5181.0</v>
       </c>
       <c r="E511" s="7" t="s">
         <v>12</v>
@@ -15463,10 +15466,10 @@
         <v>13</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D512" s="6" t="n">
-        <v>201113.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E512" s="7" t="s">
         <v>12</v>
@@ -15492,16 +15495,16 @@
         <v>13</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D513" s="6" t="n">
-        <v>5181.0</v>
+        <v>908897.0</v>
       </c>
       <c r="E513" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F513" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F513" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G513" s="8" t="s">
         <v>69</v>
@@ -15521,10 +15524,10 @@
         <v>13</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D514" s="6" t="n">
-        <v>18261.0</v>
+        <v>2898.0</v>
       </c>
       <c r="E514" s="7" t="s">
         <v>12</v>
@@ -15550,10 +15553,10 @@
         <v>13</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D515" s="6" t="n">
-        <v>1519.0</v>
+        <v>72938.0</v>
       </c>
       <c r="E515" s="7" t="s">
         <v>12</v>
@@ -15579,10 +15582,10 @@
         <v>13</v>
       </c>
       <c r="C516" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D516" s="6" t="n">
-        <v>2898.0</v>
+        <v>30675.0</v>
       </c>
       <c r="E516" s="7" t="s">
         <v>12</v>
@@ -15605,13 +15608,13 @@
         <v>69</v>
       </c>
       <c r="B517" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D517" s="6" t="n">
-        <v>44.0</v>
+        <v>12907.0</v>
       </c>
       <c r="E517" s="7" t="s">
         <v>12</v>
@@ -15634,13 +15637,13 @@
         <v>69</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D518" s="6" t="n">
-        <v>12907.0</v>
+        <v>1195.0</v>
       </c>
       <c r="E518" s="7" t="s">
         <v>12</v>
@@ -15666,10 +15669,10 @@
         <v>10</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D519" s="6" t="n">
-        <v>1408.0</v>
+        <v>162695.0</v>
       </c>
       <c r="E519" s="7" t="s">
         <v>12</v>
@@ -15692,19 +15695,19 @@
         <v>69</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D520" s="6" t="n">
-        <v>366304.0</v>
+        <v>44.0</v>
       </c>
       <c r="E520" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F520" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F520" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G520" s="8" t="s">
         <v>69</v>
@@ -15724,10 +15727,10 @@
         <v>10</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D521" s="6" t="n">
-        <v>162695.0</v>
+        <v>372386.0</v>
       </c>
       <c r="E521" s="7" t="s">
         <v>12</v>
@@ -15753,10 +15756,10 @@
         <v>10</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D522" s="6" t="n">
-        <v>372386.0</v>
+        <v>162639.0</v>
       </c>
       <c r="E522" s="7" t="s">
         <v>12</v>
@@ -15782,10 +15785,10 @@
         <v>10</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D523" s="6" t="n">
-        <v>162639.0</v>
+        <v>1408.0</v>
       </c>
       <c r="E523" s="7" t="s">
         <v>12</v>
@@ -15837,13 +15840,13 @@
         <v>69</v>
       </c>
       <c r="B525" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D525" s="6" t="n">
-        <v>1195.0</v>
+        <v>77128.0</v>
       </c>
       <c r="E525" s="7" t="s">
         <v>12</v>
@@ -15869,10 +15872,10 @@
         <v>30</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D526" s="6" t="n">
-        <v>77128.0</v>
+        <v>7684.0</v>
       </c>
       <c r="E526" s="7" t="s">
         <v>12</v>
@@ -15898,10 +15901,10 @@
         <v>30</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D527" s="6" t="n">
-        <v>7684.0</v>
+        <v>1733.0</v>
       </c>
       <c r="E527" s="7" t="s">
         <v>12</v>
@@ -15927,10 +15930,10 @@
         <v>30</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D528" s="6" t="n">
-        <v>1733.0</v>
+        <v>284063.0</v>
       </c>
       <c r="E528" s="7" t="s">
         <v>12</v>
@@ -15956,10 +15959,10 @@
         <v>30</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D529" s="6" t="n">
-        <v>284063.0</v>
+        <v>26286.0</v>
       </c>
       <c r="E529" s="7" t="s">
         <v>12</v>
@@ -15985,16 +15988,16 @@
         <v>30</v>
       </c>
       <c r="C530" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D530" s="6" t="n">
-        <v>26286.0</v>
+        <v>366304.0</v>
       </c>
       <c r="E530" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F530" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F530" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G530" s="8" t="s">
         <v>69</v>
@@ -16014,10 +16017,10 @@
         <v>13</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D531" s="6" t="n">
-        <v>133084.0</v>
+        <v>36834.0</v>
       </c>
       <c r="E531" s="7" t="s">
         <v>12</v>
@@ -16043,10 +16046,10 @@
         <v>13</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D532" s="6" t="n">
-        <v>155751.0</v>
+        <v>8250.0</v>
       </c>
       <c r="E532" s="7" t="s">
         <v>12</v>
@@ -16072,10 +16075,10 @@
         <v>13</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D533" s="6" t="n">
-        <v>8250.0</v>
+        <v>17644.0</v>
       </c>
       <c r="E533" s="7" t="s">
         <v>12</v>
@@ -16101,10 +16104,10 @@
         <v>13</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D534" s="6" t="n">
-        <v>17644.0</v>
+        <v>249.0</v>
       </c>
       <c r="E534" s="7" t="s">
         <v>12</v>
@@ -16130,10 +16133,10 @@
         <v>13</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D535" s="6" t="n">
-        <v>249.0</v>
+        <v>11404.0</v>
       </c>
       <c r="E535" s="7" t="s">
         <v>12</v>
@@ -16159,10 +16162,10 @@
         <v>13</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D536" s="6" t="n">
-        <v>11404.0</v>
+        <v>133084.0</v>
       </c>
       <c r="E536" s="7" t="s">
         <v>12</v>
@@ -16217,10 +16220,10 @@
         <v>13</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D538" s="6" t="n">
-        <v>36834.0</v>
+        <v>1287.0</v>
       </c>
       <c r="E538" s="7" t="s">
         <v>12</v>
@@ -16246,10 +16249,10 @@
         <v>13</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D539" s="6" t="n">
-        <v>1287.0</v>
+        <v>658.0</v>
       </c>
       <c r="E539" s="7" t="s">
         <v>12</v>
@@ -16275,10 +16278,10 @@
         <v>13</v>
       </c>
       <c r="C540" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D540" s="6" t="n">
-        <v>658.0</v>
+        <v>2797.0</v>
       </c>
       <c r="E540" s="7" t="s">
         <v>12</v>
@@ -16304,10 +16307,10 @@
         <v>13</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D541" s="6" t="n">
-        <v>2797.0</v>
+        <v>357059.0</v>
       </c>
       <c r="E541" s="7" t="s">
         <v>12</v>
@@ -16333,10 +16336,10 @@
         <v>13</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D542" s="6" t="n">
-        <v>357059.0</v>
+        <v>6031.0</v>
       </c>
       <c r="E542" s="7" t="s">
         <v>12</v>
@@ -16362,10 +16365,10 @@
         <v>13</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D543" s="6" t="n">
-        <v>6031.0</v>
+        <v>155751.0</v>
       </c>
       <c r="E543" s="7" t="s">
         <v>12</v>
@@ -16417,13 +16420,13 @@
         <v>70</v>
       </c>
       <c r="B545" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D545" s="6" t="n">
-        <v>17014.0</v>
+        <v>68846.0</v>
       </c>
       <c r="E545" s="7" t="s">
         <v>12</v>
@@ -16478,10 +16481,10 @@
         <v>30</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D547" s="6" t="n">
-        <v>98434.0</v>
+        <v>8609.0</v>
       </c>
       <c r="E547" s="7" t="s">
         <v>12</v>
@@ -16565,10 +16568,10 @@
         <v>10</v>
       </c>
       <c r="C550" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D550" s="6" t="n">
-        <v>68846.0</v>
+        <v>5446.0</v>
       </c>
       <c r="E550" s="7" t="s">
         <v>12</v>
@@ -16594,10 +16597,10 @@
         <v>10</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D551" s="6" t="n">
-        <v>5446.0</v>
+        <v>184.0</v>
       </c>
       <c r="E551" s="7" t="s">
         <v>12</v>
@@ -16620,13 +16623,13 @@
         <v>70</v>
       </c>
       <c r="B552" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C552" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D552" s="6" t="n">
-        <v>184.0</v>
+        <v>98434.0</v>
       </c>
       <c r="E552" s="7" t="s">
         <v>12</v>
@@ -16681,10 +16684,10 @@
         <v>30</v>
       </c>
       <c r="C554" s="5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D554" s="6" t="n">
-        <v>8609.0</v>
+        <v>9668.0</v>
       </c>
       <c r="E554" s="7" t="s">
         <v>12</v>
@@ -16710,10 +16713,10 @@
         <v>30</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D555" s="6" t="n">
-        <v>167261.0</v>
+        <v>16624.0</v>
       </c>
       <c r="E555" s="7" t="s">
         <v>12</v>
@@ -16739,10 +16742,10 @@
         <v>30</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D556" s="6" t="n">
-        <v>16624.0</v>
+        <v>146605.0</v>
       </c>
       <c r="E556" s="7" t="s">
         <v>12</v>
@@ -16768,10 +16771,10 @@
         <v>30</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D557" s="6" t="n">
-        <v>146605.0</v>
+        <v>24743.0</v>
       </c>
       <c r="E557" s="7" t="s">
         <v>12</v>
@@ -16794,13 +16797,13 @@
         <v>70</v>
       </c>
       <c r="B558" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D558" s="6" t="n">
-        <v>24743.0</v>
+        <v>17014.0</v>
       </c>
       <c r="E558" s="7" t="s">
         <v>12</v>
@@ -16855,10 +16858,10 @@
         <v>30</v>
       </c>
       <c r="C560" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D560" s="6" t="n">
-        <v>9668.0</v>
+        <v>167261.0</v>
       </c>
       <c r="E560" s="7" t="s">
         <v>12</v>
@@ -16884,10 +16887,10 @@
         <v>13</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D561" s="6" t="n">
-        <v>1147.0</v>
+        <v>3016.0</v>
       </c>
       <c r="E561" s="7" t="s">
         <v>12</v>
@@ -16913,10 +16916,10 @@
         <v>13</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D562" s="6" t="n">
-        <v>50267.0</v>
+        <v>135115.0</v>
       </c>
       <c r="E562" s="7" t="s">
         <v>12</v>
@@ -16942,10 +16945,10 @@
         <v>13</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D563" s="6" t="n">
-        <v>135115.0</v>
+        <v>103167.0</v>
       </c>
       <c r="E563" s="7" t="s">
         <v>12</v>
@@ -16971,10 +16974,10 @@
         <v>13</v>
       </c>
       <c r="C564" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D564" s="6" t="n">
-        <v>103167.0</v>
+        <v>388.0</v>
       </c>
       <c r="E564" s="7" t="s">
         <v>12</v>
@@ -17000,10 +17003,10 @@
         <v>13</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D565" s="6" t="n">
-        <v>388.0</v>
+        <v>4205.0</v>
       </c>
       <c r="E565" s="7" t="s">
         <v>12</v>
@@ -17029,10 +17032,10 @@
         <v>13</v>
       </c>
       <c r="C566" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D566" s="6" t="n">
-        <v>4205.0</v>
+        <v>1147.0</v>
       </c>
       <c r="E566" s="7" t="s">
         <v>12</v>
@@ -17058,10 +17061,10 @@
         <v>13</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D567" s="6" t="n">
-        <v>9716.0</v>
+        <v>54.0</v>
       </c>
       <c r="E567" s="7" t="s">
         <v>12</v>
@@ -17174,16 +17177,16 @@
         <v>13</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D571" s="6" t="n">
-        <v>697083.0</v>
+        <v>9716.0</v>
       </c>
       <c r="E571" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F571" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F571" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G571" s="8" t="s">
         <v>71</v>
@@ -17203,16 +17206,16 @@
         <v>13</v>
       </c>
       <c r="C572" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D572" s="6" t="n">
-        <v>499.0</v>
+        <v>697083.0</v>
       </c>
       <c r="E572" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F572" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F572" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G572" s="8" t="s">
         <v>71</v>
@@ -17232,10 +17235,10 @@
         <v>13</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D573" s="6" t="n">
-        <v>73411.0</v>
+        <v>499.0</v>
       </c>
       <c r="E573" s="7" t="s">
         <v>12</v>
@@ -17261,10 +17264,10 @@
         <v>13</v>
       </c>
       <c r="C574" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D574" s="6" t="n">
-        <v>3016.0</v>
+        <v>50267.0</v>
       </c>
       <c r="E574" s="7" t="s">
         <v>12</v>
@@ -17287,13 +17290,13 @@
         <v>71</v>
       </c>
       <c r="B575" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D575" s="6" t="n">
-        <v>54.0</v>
+        <v>160983.0</v>
       </c>
       <c r="E575" s="7" t="s">
         <v>12</v>
@@ -17319,10 +17322,10 @@
         <v>13</v>
       </c>
       <c r="C576" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D576" s="6" t="n">
-        <v>11348.0</v>
+        <v>73411.0</v>
       </c>
       <c r="E576" s="7" t="s">
         <v>12</v>
@@ -17348,10 +17351,10 @@
         <v>10</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D577" s="6" t="n">
-        <v>5930.0</v>
+        <v>649.0</v>
       </c>
       <c r="E577" s="7" t="s">
         <v>12</v>
@@ -17374,13 +17377,13 @@
         <v>71</v>
       </c>
       <c r="B578" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C578" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D578" s="6" t="n">
-        <v>4412.0</v>
+        <v>11348.0</v>
       </c>
       <c r="E578" s="7" t="s">
         <v>12</v>
@@ -17406,10 +17409,10 @@
         <v>10</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D579" s="6" t="n">
-        <v>30784.0</v>
+        <v>132880.0</v>
       </c>
       <c r="E579" s="7" t="s">
         <v>12</v>
@@ -17435,10 +17438,10 @@
         <v>10</v>
       </c>
       <c r="C580" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D580" s="6" t="n">
-        <v>132880.0</v>
+        <v>369966.0</v>
       </c>
       <c r="E580" s="7" t="s">
         <v>12</v>
@@ -17464,10 +17467,10 @@
         <v>10</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D581" s="6" t="n">
-        <v>17930.0</v>
+        <v>30784.0</v>
       </c>
       <c r="E581" s="7" t="s">
         <v>12</v>
@@ -17493,10 +17496,10 @@
         <v>10</v>
       </c>
       <c r="C582" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D582" s="6" t="n">
-        <v>649.0</v>
+        <v>17930.0</v>
       </c>
       <c r="E582" s="7" t="s">
         <v>12</v>
@@ -17522,10 +17525,10 @@
         <v>10</v>
       </c>
       <c r="C583" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D583" s="6" t="n">
-        <v>369966.0</v>
+        <v>4412.0</v>
       </c>
       <c r="E583" s="7" t="s">
         <v>12</v>
@@ -17548,13 +17551,13 @@
         <v>71</v>
       </c>
       <c r="B584" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C584" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D584" s="6" t="n">
-        <v>160983.0</v>
+        <v>5930.0</v>
       </c>
       <c r="E584" s="7" t="s">
         <v>12</v>
@@ -17580,10 +17583,10 @@
         <v>30</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D585" s="6" t="n">
-        <v>215594.0</v>
+        <v>267.0</v>
       </c>
       <c r="E585" s="7" t="s">
         <v>12</v>
@@ -17609,16 +17612,16 @@
         <v>30</v>
       </c>
       <c r="C586" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D586" s="6" t="n">
-        <v>3492.0</v>
+        <v>245314.0</v>
       </c>
       <c r="E586" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F586" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F586" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G586" s="8" t="s">
         <v>71</v>
@@ -17638,10 +17641,10 @@
         <v>30</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D587" s="6" t="n">
-        <v>30577.0</v>
+        <v>10813.0</v>
       </c>
       <c r="E587" s="7" t="s">
         <v>12</v>
@@ -17667,10 +17670,10 @@
         <v>30</v>
       </c>
       <c r="C588" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D588" s="6" t="n">
-        <v>10813.0</v>
+        <v>215594.0</v>
       </c>
       <c r="E588" s="7" t="s">
         <v>12</v>
@@ -17696,16 +17699,16 @@
         <v>30</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D589" s="6" t="n">
-        <v>245314.0</v>
+        <v>30577.0</v>
       </c>
       <c r="E589" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F589" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F589" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G589" s="8" t="s">
         <v>71</v>
@@ -17725,10 +17728,10 @@
         <v>30</v>
       </c>
       <c r="C590" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D590" s="6" t="n">
-        <v>267.0</v>
+        <v>3492.0</v>
       </c>
       <c r="E590" s="7" t="s">
         <v>12</v>
@@ -17754,16 +17757,16 @@
         <v>13</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D591" s="6" t="n">
-        <v>60893.0</v>
+        <v>154891.0</v>
       </c>
       <c r="E591" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F591" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F591" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G591" s="8" t="s">
         <v>72</v>
@@ -17783,10 +17786,10 @@
         <v>13</v>
       </c>
       <c r="C592" s="5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D592" s="6" t="n">
-        <v>538223.0</v>
+        <v>481367.0</v>
       </c>
       <c r="E592" s="7" t="s">
         <v>16</v>
@@ -17812,10 +17815,10 @@
         <v>13</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D593" s="6" t="n">
-        <v>3386.0</v>
+        <v>5871.0</v>
       </c>
       <c r="E593" s="7" t="s">
         <v>12</v>
@@ -17841,10 +17844,10 @@
         <v>13</v>
       </c>
       <c r="C594" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D594" s="6" t="n">
-        <v>1973.0</v>
+        <v>21078.0</v>
       </c>
       <c r="E594" s="7" t="s">
         <v>12</v>
@@ -17870,16 +17873,16 @@
         <v>13</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D595" s="6" t="n">
-        <v>84215.0</v>
+        <v>30056.0</v>
       </c>
       <c r="E595" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F595" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F595" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G595" s="8" t="s">
         <v>72</v>
@@ -17899,10 +17902,10 @@
         <v>13</v>
       </c>
       <c r="C596" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D596" s="6" t="n">
-        <v>154891.0</v>
+        <v>3386.0</v>
       </c>
       <c r="E596" s="7" t="s">
         <v>12</v>
@@ -17928,16 +17931,16 @@
         <v>13</v>
       </c>
       <c r="C597" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D597" s="6" t="n">
-        <v>30056.0</v>
+        <v>84215.0</v>
       </c>
       <c r="E597" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F597" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F597" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G597" s="8" t="s">
         <v>72</v>
@@ -17957,10 +17960,10 @@
         <v>13</v>
       </c>
       <c r="C598" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D598" s="6" t="n">
-        <v>21078.0</v>
+        <v>1973.0</v>
       </c>
       <c r="E598" s="7" t="s">
         <v>12</v>
@@ -17986,10 +17989,10 @@
         <v>13</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D599" s="6" t="n">
-        <v>5871.0</v>
+        <v>1132.0</v>
       </c>
       <c r="E599" s="7" t="s">
         <v>12</v>
@@ -18015,10 +18018,10 @@
         <v>13</v>
       </c>
       <c r="C600" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D600" s="6" t="n">
-        <v>481367.0</v>
+        <v>538223.0</v>
       </c>
       <c r="E600" s="7" t="s">
         <v>16</v>
@@ -18044,16 +18047,16 @@
         <v>13</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D601" s="6" t="n">
-        <v>138808.0</v>
+        <v>60893.0</v>
       </c>
       <c r="E601" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F601" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F601" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G601" s="8" t="s">
         <v>72</v>
@@ -18073,10 +18076,10 @@
         <v>13</v>
       </c>
       <c r="C602" s="5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D602" s="6" t="n">
-        <v>1132.0</v>
+        <v>138808.0</v>
       </c>
       <c r="E602" s="7" t="s">
         <v>12</v>
@@ -18102,10 +18105,10 @@
         <v>13</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D603" s="6" t="n">
-        <v>10263.0</v>
+        <v>17195.0</v>
       </c>
       <c r="E603" s="7" t="s">
         <v>12</v>
@@ -18160,10 +18163,10 @@
         <v>30</v>
       </c>
       <c r="C605" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D605" s="6" t="n">
-        <v>76271.0</v>
+        <v>96.0</v>
       </c>
       <c r="E605" s="7" t="s">
         <v>12</v>
@@ -18186,19 +18189,19 @@
         <v>72</v>
       </c>
       <c r="B606" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C606" s="5" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D606" s="6" t="n">
-        <v>17195.0</v>
+        <v>414009.0</v>
       </c>
       <c r="E606" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F606" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F606" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G606" s="8" t="s">
         <v>72</v>
@@ -18218,16 +18221,16 @@
         <v>10</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D607" s="6" t="n">
-        <v>414009.0</v>
+        <v>69940.0</v>
       </c>
       <c r="E607" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F607" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F607" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G607" s="8" t="s">
         <v>72</v>
@@ -18247,10 +18250,10 @@
         <v>10</v>
       </c>
       <c r="C608" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D608" s="6" t="n">
-        <v>69940.0</v>
+        <v>4681.0</v>
       </c>
       <c r="E608" s="7" t="s">
         <v>12</v>
@@ -18273,13 +18276,13 @@
         <v>72</v>
       </c>
       <c r="B609" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D609" s="6" t="n">
-        <v>4681.0</v>
+        <v>76271.0</v>
       </c>
       <c r="E609" s="7" t="s">
         <v>12</v>
@@ -18334,10 +18337,10 @@
         <v>30</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D611" s="6" t="n">
-        <v>96.0</v>
+        <v>11956.0</v>
       </c>
       <c r="E611" s="7" t="s">
         <v>12</v>
@@ -18363,16 +18366,16 @@
         <v>30</v>
       </c>
       <c r="C612" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D612" s="6" t="n">
-        <v>393940.0</v>
+        <v>10252.0</v>
       </c>
       <c r="E612" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F612" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F612" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G612" s="8" t="s">
         <v>72</v>
@@ -18392,16 +18395,16 @@
         <v>30</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D613" s="6" t="n">
-        <v>10252.0</v>
+        <v>219512.0</v>
       </c>
       <c r="E613" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F613" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F613" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G613" s="8" t="s">
         <v>72</v>
@@ -18421,16 +18424,16 @@
         <v>30</v>
       </c>
       <c r="C614" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D614" s="6" t="n">
-        <v>219512.0</v>
+        <v>45738.0</v>
       </c>
       <c r="E614" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F614" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F614" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G614" s="8" t="s">
         <v>72</v>
@@ -18447,13 +18450,13 @@
         <v>72</v>
       </c>
       <c r="B615" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C615" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D615" s="6" t="n">
-        <v>45738.0</v>
+        <v>10263.0</v>
       </c>
       <c r="E615" s="7" t="s">
         <v>12</v>
@@ -18479,16 +18482,16 @@
         <v>30</v>
       </c>
       <c r="C616" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D616" s="6" t="n">
-        <v>11956.0</v>
+        <v>393940.0</v>
       </c>
       <c r="E616" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F616" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F616" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G616" s="8" t="s">
         <v>72</v>
@@ -18624,10 +18627,10 @@
         <v>13</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D621" s="6" t="n">
-        <v>54493.0</v>
+        <v>3953.0</v>
       </c>
       <c r="E621" s="7" t="s">
         <v>12</v>
@@ -18653,10 +18656,10 @@
         <v>13</v>
       </c>
       <c r="C622" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D622" s="6" t="n">
-        <v>84856.0</v>
+        <v>4464.0</v>
       </c>
       <c r="E622" s="7" t="s">
         <v>12</v>
@@ -18740,10 +18743,10 @@
         <v>13</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D625" s="6" t="n">
-        <v>4464.0</v>
+        <v>84856.0</v>
       </c>
       <c r="E625" s="7" t="s">
         <v>12</v>
@@ -18827,16 +18830,16 @@
         <v>13</v>
       </c>
       <c r="C628" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D628" s="6" t="n">
-        <v>129190.0</v>
+        <v>54493.0</v>
       </c>
       <c r="E628" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F628" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F628" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G628" s="8" t="s">
         <v>73</v>
@@ -18856,16 +18859,16 @@
         <v>13</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D629" s="6" t="n">
-        <v>3953.0</v>
+        <v>129190.0</v>
       </c>
       <c r="E629" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F629" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F629" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G629" s="8" t="s">
         <v>73</v>
@@ -18882,19 +18885,19 @@
         <v>73</v>
       </c>
       <c r="B630" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C630" s="5" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D630" s="6" t="n">
-        <v>5327.0</v>
+        <v>191571.0</v>
       </c>
       <c r="E630" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F630" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F630" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G630" s="8" t="s">
         <v>73</v>
@@ -18911,13 +18914,13 @@
         <v>73</v>
       </c>
       <c r="B631" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C631" s="5" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D631" s="6" t="n">
-        <v>1660.0</v>
+        <v>5327.0</v>
       </c>
       <c r="E631" s="7" t="s">
         <v>12</v>
@@ -18943,16 +18946,16 @@
         <v>10</v>
       </c>
       <c r="C632" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D632" s="6" t="n">
-        <v>191571.0</v>
+        <v>1660.0</v>
       </c>
       <c r="E632" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F632" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F632" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G632" s="8" t="s">
         <v>73</v>
@@ -18969,13 +18972,13 @@
         <v>73</v>
       </c>
       <c r="B633" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C633" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D633" s="6" t="n">
-        <v>276686.0</v>
+        <v>6983.0</v>
       </c>
       <c r="E633" s="7" t="s">
         <v>12</v>
@@ -19001,10 +19004,10 @@
         <v>10</v>
       </c>
       <c r="C634" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D634" s="6" t="n">
-        <v>65439.0</v>
+        <v>276686.0</v>
       </c>
       <c r="E634" s="7" t="s">
         <v>12</v>
@@ -19030,10 +19033,10 @@
         <v>10</v>
       </c>
       <c r="C635" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D635" s="6" t="n">
-        <v>139458.0</v>
+        <v>65439.0</v>
       </c>
       <c r="E635" s="7" t="s">
         <v>12</v>
@@ -19059,10 +19062,10 @@
         <v>10</v>
       </c>
       <c r="C636" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D636" s="6" t="n">
-        <v>511.0</v>
+        <v>139458.0</v>
       </c>
       <c r="E636" s="7" t="s">
         <v>12</v>
@@ -19085,13 +19088,13 @@
         <v>73</v>
       </c>
       <c r="B637" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C637" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D637" s="6" t="n">
-        <v>6983.0</v>
+        <v>511.0</v>
       </c>
       <c r="E637" s="7" t="s">
         <v>12</v>
@@ -19146,16 +19149,16 @@
         <v>30</v>
       </c>
       <c r="C639" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D639" s="6" t="n">
-        <v>322311.0</v>
+        <v>5387.0</v>
       </c>
       <c r="E639" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F639" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F639" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G639" s="8" t="s">
         <v>73</v>
@@ -19175,16 +19178,16 @@
         <v>30</v>
       </c>
       <c r="C640" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D640" s="6" t="n">
-        <v>107.0</v>
+        <v>322311.0</v>
       </c>
       <c r="E640" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F640" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F640" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G640" s="8" t="s">
         <v>73</v>
@@ -19204,10 +19207,10 @@
         <v>30</v>
       </c>
       <c r="C641" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D641" s="6" t="n">
-        <v>220179.0</v>
+        <v>107.0</v>
       </c>
       <c r="E641" s="7" t="s">
         <v>12</v>
@@ -19233,10 +19236,10 @@
         <v>30</v>
       </c>
       <c r="C642" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D642" s="6" t="n">
-        <v>28519.0</v>
+        <v>220179.0</v>
       </c>
       <c r="E642" s="7" t="s">
         <v>12</v>
@@ -19262,10 +19265,10 @@
         <v>30</v>
       </c>
       <c r="C643" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D643" s="6" t="n">
-        <v>5387.0</v>
+        <v>28519.0</v>
       </c>
       <c r="E643" s="7" t="s">
         <v>12</v>
@@ -19291,10 +19294,10 @@
         <v>13</v>
       </c>
       <c r="C644" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D644" s="6" t="n">
-        <v>13457.0</v>
+        <v>2352.0</v>
       </c>
       <c r="E644" s="7" t="s">
         <v>12</v>
@@ -19320,10 +19323,10 @@
         <v>13</v>
       </c>
       <c r="C645" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D645" s="6" t="n">
-        <v>422.0</v>
+        <v>338362.0</v>
       </c>
       <c r="E645" s="7" t="s">
         <v>12</v>
@@ -19349,10 +19352,10 @@
         <v>13</v>
       </c>
       <c r="C646" s="5" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D646" s="6" t="n">
-        <v>3992.0</v>
+        <v>422.0</v>
       </c>
       <c r="E646" s="7" t="s">
         <v>12</v>
@@ -19378,16 +19381,16 @@
         <v>13</v>
       </c>
       <c r="C647" s="5" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D647" s="6" t="n">
-        <v>85944.0</v>
+        <v>52273.0</v>
       </c>
       <c r="E647" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F647" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F647" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G647" s="8" t="s">
         <v>74</v>
@@ -19407,16 +19410,16 @@
         <v>13</v>
       </c>
       <c r="C648" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D648" s="6" t="n">
-        <v>125172.0</v>
+        <v>85944.0</v>
       </c>
       <c r="E648" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F648" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F648" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G648" s="8" t="s">
         <v>74</v>
@@ -19436,10 +19439,10 @@
         <v>13</v>
       </c>
       <c r="C649" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D649" s="6" t="n">
-        <v>2352.0</v>
+        <v>125172.0</v>
       </c>
       <c r="E649" s="7" t="s">
         <v>12</v>
@@ -19462,13 +19465,13 @@
         <v>74</v>
       </c>
       <c r="B650" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C650" s="5" t="s">
         <v>75</v>
       </c>
       <c r="D650" s="6" t="n">
-        <v>2106.0</v>
+        <v>1953.0</v>
       </c>
       <c r="E650" s="7" t="s">
         <v>12</v>
@@ -19494,10 +19497,10 @@
         <v>13</v>
       </c>
       <c r="C651" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D651" s="6" t="n">
-        <v>507249.0</v>
+        <v>13457.0</v>
       </c>
       <c r="E651" s="7" t="s">
         <v>12</v>
@@ -19520,13 +19523,13 @@
         <v>74</v>
       </c>
       <c r="B652" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C652" s="5" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="D652" s="6" t="n">
-        <v>4304.0</v>
+        <v>507249.0</v>
       </c>
       <c r="E652" s="7" t="s">
         <v>12</v>
@@ -19552,10 +19555,10 @@
         <v>10</v>
       </c>
       <c r="C653" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D653" s="6" t="n">
-        <v>4268.0</v>
+        <v>4304.0</v>
       </c>
       <c r="E653" s="7" t="s">
         <v>12</v>
@@ -19578,13 +19581,13 @@
         <v>74</v>
       </c>
       <c r="B654" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C654" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D654" s="6" t="n">
-        <v>21715.0</v>
+        <v>2106.0</v>
       </c>
       <c r="E654" s="7" t="s">
         <v>12</v>
@@ -19607,13 +19610,13 @@
         <v>74</v>
       </c>
       <c r="B655" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C655" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D655" s="6" t="n">
-        <v>1953.0</v>
+        <v>4268.0</v>
       </c>
       <c r="E655" s="7" t="s">
         <v>12</v>
@@ -19639,16 +19642,16 @@
         <v>13</v>
       </c>
       <c r="C656" s="5" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D656" s="6" t="n">
-        <v>126794.0</v>
+        <v>21715.0</v>
       </c>
       <c r="E656" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F656" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F656" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G656" s="8" t="s">
         <v>74</v>
@@ -19668,16 +19671,16 @@
         <v>13</v>
       </c>
       <c r="C657" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D657" s="6" t="n">
-        <v>338362.0</v>
+        <v>126794.0</v>
       </c>
       <c r="E657" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F657" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F657" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G657" s="8" t="s">
         <v>74</v>
@@ -19697,10 +19700,10 @@
         <v>13</v>
       </c>
       <c r="C658" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D658" s="6" t="n">
-        <v>52273.0</v>
+        <v>3992.0</v>
       </c>
       <c r="E658" s="7" t="s">
         <v>12</v>
@@ -19755,10 +19758,10 @@
         <v>30</v>
       </c>
       <c r="C660" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D660" s="6" t="n">
-        <v>1356.0</v>
+        <v>36007.0</v>
       </c>
       <c r="E660" s="7" t="s">
         <v>12</v>
@@ -19781,13 +19784,13 @@
         <v>74</v>
       </c>
       <c r="B661" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C661" s="5" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D661" s="6" t="n">
-        <v>118438.0</v>
+        <v>11491.0</v>
       </c>
       <c r="E661" s="7" t="s">
         <v>12</v>
@@ -19813,10 +19816,10 @@
         <v>10</v>
       </c>
       <c r="C662" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D662" s="6" t="n">
-        <v>179290.0</v>
+        <v>6817.0</v>
       </c>
       <c r="E662" s="7" t="s">
         <v>12</v>
@@ -19842,10 +19845,10 @@
         <v>10</v>
       </c>
       <c r="C663" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D663" s="6" t="n">
-        <v>34079.0</v>
+        <v>179290.0</v>
       </c>
       <c r="E663" s="7" t="s">
         <v>12</v>
@@ -19871,10 +19874,10 @@
         <v>10</v>
       </c>
       <c r="C664" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D664" s="6" t="n">
-        <v>115323.0</v>
+        <v>34079.0</v>
       </c>
       <c r="E664" s="7" t="s">
         <v>12</v>
@@ -19900,10 +19903,10 @@
         <v>10</v>
       </c>
       <c r="C665" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D665" s="6" t="n">
-        <v>3706.0</v>
+        <v>115336.0</v>
       </c>
       <c r="E665" s="7" t="s">
         <v>12</v>
@@ -19926,13 +19929,13 @@
         <v>74</v>
       </c>
       <c r="B666" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C666" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D666" s="6" t="n">
-        <v>36007.0</v>
+        <v>3706.0</v>
       </c>
       <c r="E666" s="7" t="s">
         <v>12</v>
@@ -19958,10 +19961,10 @@
         <v>10</v>
       </c>
       <c r="C667" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D667" s="6" t="n">
-        <v>6817.0</v>
+        <v>118438.0</v>
       </c>
       <c r="E667" s="7" t="s">
         <v>12</v>
@@ -19987,10 +19990,10 @@
         <v>30</v>
       </c>
       <c r="C668" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D668" s="6" t="n">
-        <v>3560.0</v>
+        <v>1356.0</v>
       </c>
       <c r="E668" s="7" t="s">
         <v>12</v>
@@ -20016,10 +20019,10 @@
         <v>30</v>
       </c>
       <c r="C669" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D669" s="6" t="n">
-        <v>2655.0</v>
+        <v>347974.0</v>
       </c>
       <c r="E669" s="7" t="s">
         <v>12</v>
@@ -20045,10 +20048,10 @@
         <v>30</v>
       </c>
       <c r="C670" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D670" s="6" t="n">
-        <v>197199.0</v>
+        <v>2655.0</v>
       </c>
       <c r="E670" s="7" t="s">
         <v>12</v>
@@ -20074,10 +20077,10 @@
         <v>30</v>
       </c>
       <c r="C671" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D671" s="6" t="n">
-        <v>2286.0</v>
+        <v>197199.0</v>
       </c>
       <c r="E671" s="7" t="s">
         <v>12</v>
@@ -20100,13 +20103,13 @@
         <v>74</v>
       </c>
       <c r="B672" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C672" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D672" s="6" t="n">
-        <v>10437.0</v>
+        <v>2286.0</v>
       </c>
       <c r="E672" s="7" t="s">
         <v>12</v>
@@ -20132,10 +20135,10 @@
         <v>13</v>
       </c>
       <c r="C673" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D673" s="6" t="n">
-        <v>11491.0</v>
+        <v>10437.0</v>
       </c>
       <c r="E673" s="7" t="s">
         <v>12</v>
@@ -20161,10 +20164,10 @@
         <v>30</v>
       </c>
       <c r="C674" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D674" s="6" t="n">
-        <v>347974.0</v>
+        <v>3560.0</v>
       </c>
       <c r="E674" s="7" t="s">
         <v>12</v>
@@ -20193,7 +20196,7 @@
         <v>19</v>
       </c>
       <c r="D675" s="6" t="n">
-        <v>337903.0</v>
+        <v>338524.0</v>
       </c>
       <c r="E675" s="7" t="s">
         <v>12</v>
@@ -20364,7 +20367,7 @@
         <v>10</v>
       </c>
       <c r="C681" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D681" s="6" t="n">
         <v>15441.0</v>
@@ -20480,7 +20483,7 @@
         <v>10</v>
       </c>
       <c r="C685" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D685" s="6" t="n">
         <v>33064.0</v>
@@ -20509,7 +20512,7 @@
         <v>13</v>
       </c>
       <c r="C686" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D686" s="6" t="n">
         <v>54550.0</v>
@@ -20538,10 +20541,10 @@
         <v>13</v>
       </c>
       <c r="C687" s="5" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D687" s="6" t="n">
-        <v>9197.0</v>
+        <v>7892.0</v>
       </c>
       <c r="E687" s="7" t="s">
         <v>12</v>
@@ -20567,10 +20570,10 @@
         <v>13</v>
       </c>
       <c r="C688" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D688" s="6" t="n">
-        <v>7892.0</v>
+        <v>4039.0</v>
       </c>
       <c r="E688" s="7" t="s">
         <v>12</v>
@@ -20596,10 +20599,10 @@
         <v>13</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="D689" s="6" t="n">
-        <v>4039.0</v>
+        <v>9197.0</v>
       </c>
       <c r="E689" s="7" t="s">
         <v>12</v>
@@ -20622,13 +20625,13 @@
         <v>80</v>
       </c>
       <c r="B690" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C690" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D690" s="6" t="n">
-        <v>1752.0</v>
+        <v>252954.0</v>
       </c>
       <c r="E690" s="7" t="s">
         <v>12</v>
@@ -20651,13 +20654,13 @@
         <v>80</v>
       </c>
       <c r="B691" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C691" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="D691" s="6" t="n">
-        <v>252954.0</v>
+        <v>227.0</v>
       </c>
       <c r="E691" s="7" t="s">
         <v>12</v>
@@ -20680,13 +20683,13 @@
         <v>80</v>
       </c>
       <c r="B692" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C692" s="5" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="D692" s="6" t="n">
-        <v>227.0</v>
+        <v>189500.0</v>
       </c>
       <c r="E692" s="7" t="s">
         <v>12</v>
@@ -20709,13 +20712,13 @@
         <v>80</v>
       </c>
       <c r="B693" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C693" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D693" s="6" t="n">
-        <v>120464.0</v>
+        <v>70.0</v>
       </c>
       <c r="E693" s="7" t="s">
         <v>12</v>
@@ -20741,10 +20744,10 @@
         <v>10</v>
       </c>
       <c r="C694" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D694" s="6" t="n">
-        <v>189500.0</v>
+        <v>1752.0</v>
       </c>
       <c r="E694" s="7" t="s">
         <v>12</v>
@@ -20767,13 +20770,13 @@
         <v>80</v>
       </c>
       <c r="B695" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C695" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D695" s="6" t="n">
-        <v>310950.0</v>
+        <v>32442.0</v>
       </c>
       <c r="E695" s="7" t="s">
         <v>12</v>
@@ -20799,10 +20802,10 @@
         <v>30</v>
       </c>
       <c r="C696" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D696" s="6" t="n">
-        <v>32442.0</v>
+        <v>8735.0</v>
       </c>
       <c r="E696" s="7" t="s">
         <v>12</v>
@@ -20825,13 +20828,13 @@
         <v>80</v>
       </c>
       <c r="B697" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C697" s="5" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D697" s="6" t="n">
-        <v>8735.0</v>
+        <v>311364.0</v>
       </c>
       <c r="E697" s="7" t="s">
         <v>12</v>
@@ -20854,19 +20857,19 @@
         <v>80</v>
       </c>
       <c r="B698" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C698" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D698" s="6" t="n">
-        <v>70.0</v>
+        <v>280310.0</v>
       </c>
       <c r="E698" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F698" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F698" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G698" s="8" t="s">
         <v>80</v>
@@ -20883,19 +20886,19 @@
         <v>80</v>
       </c>
       <c r="B699" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C699" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D699" s="6" t="n">
-        <v>279574.0</v>
+        <v>8705.0</v>
       </c>
       <c r="E699" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F699" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F699" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G699" s="8" t="s">
         <v>80</v>
@@ -20941,19 +20944,19 @@
         <v>80</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C701" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D701" s="6" t="n">
-        <v>108278.0</v>
+        <v>85559.0</v>
       </c>
       <c r="E701" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F701" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F701" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G701" s="8" t="s">
         <v>80</v>
@@ -20970,13 +20973,13 @@
         <v>80</v>
       </c>
       <c r="B702" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C702" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D702" s="6" t="n">
-        <v>13334.0</v>
+        <v>120464.0</v>
       </c>
       <c r="E702" s="7" t="s">
         <v>12</v>
@@ -21028,13 +21031,13 @@
         <v>80</v>
       </c>
       <c r="B704" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C704" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D704" s="6" t="n">
-        <v>8705.0</v>
+        <v>13334.0</v>
       </c>
       <c r="E704" s="7" t="s">
         <v>12</v>
@@ -21057,19 +21060,19 @@
         <v>80</v>
       </c>
       <c r="B705" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C705" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D705" s="6" t="n">
-        <v>79394.0</v>
+        <v>108670.0</v>
       </c>
       <c r="E705" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F705" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F705" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G705" s="8" t="s">
         <v>80</v>
@@ -21092,7 +21095,7 @@
         <v>33</v>
       </c>
       <c r="D706" s="6" t="n">
-        <v>18161.0</v>
+        <v>110401.0</v>
       </c>
       <c r="E706" s="7" t="s">
         <v>12</v>
@@ -21118,10 +21121,10 @@
         <v>13</v>
       </c>
       <c r="C707" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D707" s="6" t="n">
-        <v>11957.0</v>
+        <v>19765.0</v>
       </c>
       <c r="E707" s="7" t="s">
         <v>12</v>
@@ -21144,13 +21147,13 @@
         <v>81</v>
       </c>
       <c r="B708" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C708" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D708" s="6" t="n">
-        <v>17602.0</v>
+        <v>36291.0</v>
       </c>
       <c r="E708" s="7" t="s">
         <v>12</v>
@@ -21176,10 +21179,10 @@
         <v>10</v>
       </c>
       <c r="C709" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D709" s="6" t="n">
-        <v>1924.0</v>
+        <v>6834.0</v>
       </c>
       <c r="E709" s="7" t="s">
         <v>12</v>
@@ -21208,7 +21211,7 @@
         <v>76</v>
       </c>
       <c r="D710" s="6" t="n">
-        <v>8222.0</v>
+        <v>19628.0</v>
       </c>
       <c r="E710" s="7" t="s">
         <v>12</v>
@@ -21234,10 +21237,10 @@
         <v>13</v>
       </c>
       <c r="C711" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D711" s="6" t="n">
-        <v>133159.0</v>
+        <v>1686.0</v>
       </c>
       <c r="E711" s="7" t="s">
         <v>12</v>
@@ -21263,10 +21266,10 @@
         <v>13</v>
       </c>
       <c r="C712" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D712" s="6" t="n">
-        <v>960.0</v>
+        <v>405880.0</v>
       </c>
       <c r="E712" s="7" t="s">
         <v>12</v>
@@ -21292,10 +21295,10 @@
         <v>13</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D713" s="6" t="n">
-        <v>5279.0</v>
+        <v>1063.0</v>
       </c>
       <c r="E713" s="7" t="s">
         <v>12</v>
@@ -21321,10 +21324,10 @@
         <v>13</v>
       </c>
       <c r="C714" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D714" s="6" t="n">
-        <v>132163.0</v>
+        <v>19774.0</v>
       </c>
       <c r="E714" s="7" t="s">
         <v>12</v>
@@ -21347,13 +21350,13 @@
         <v>81</v>
       </c>
       <c r="B715" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D715" s="6" t="n">
-        <v>9546.0</v>
+        <v>8648.0</v>
       </c>
       <c r="E715" s="7" t="s">
         <v>12</v>
@@ -21379,10 +21382,10 @@
         <v>13</v>
       </c>
       <c r="C716" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D716" s="6" t="n">
-        <v>12367.0</v>
+        <v>2033.0</v>
       </c>
       <c r="E716" s="7" t="s">
         <v>12</v>
@@ -21408,10 +21411,10 @@
         <v>13</v>
       </c>
       <c r="C717" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D717" s="6" t="n">
-        <v>677.0</v>
+        <v>3984.0</v>
       </c>
       <c r="E717" s="7" t="s">
         <v>12</v>
@@ -21434,13 +21437,13 @@
         <v>81</v>
       </c>
       <c r="B718" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C718" s="5" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="D718" s="6" t="n">
-        <v>6396.0</v>
+        <v>98198.0</v>
       </c>
       <c r="E718" s="7" t="s">
         <v>12</v>
@@ -21466,10 +21469,10 @@
         <v>13</v>
       </c>
       <c r="C719" s="5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D719" s="6" t="n">
-        <v>15883.0</v>
+        <v>378567.0</v>
       </c>
       <c r="E719" s="7" t="s">
         <v>12</v>
@@ -21492,13 +21495,13 @@
         <v>81</v>
       </c>
       <c r="B720" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C720" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D720" s="6" t="n">
-        <v>23970.0</v>
+        <v>78279.0</v>
       </c>
       <c r="E720" s="7" t="s">
         <v>12</v>
@@ -21524,10 +21527,10 @@
         <v>30</v>
       </c>
       <c r="C721" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D721" s="6" t="n">
-        <v>86503.0</v>
+        <v>44916.0</v>
       </c>
       <c r="E721" s="7" t="s">
         <v>12</v>
@@ -21550,13 +21553,13 @@
         <v>81</v>
       </c>
       <c r="B722" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C722" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D722" s="6" t="n">
-        <v>83.0</v>
+        <v>677.0</v>
       </c>
       <c r="E722" s="7" t="s">
         <v>12</v>
@@ -21582,10 +21585,10 @@
         <v>10</v>
       </c>
       <c r="C723" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D723" s="6" t="n">
-        <v>54951.0</v>
+        <v>145811.0</v>
       </c>
       <c r="E723" s="7" t="s">
         <v>12</v>
@@ -21611,10 +21614,10 @@
         <v>10</v>
       </c>
       <c r="C724" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D724" s="6" t="n">
-        <v>26847.0</v>
+        <v>31341.0</v>
       </c>
       <c r="E724" s="7" t="s">
         <v>12</v>
@@ -21637,13 +21640,13 @@
         <v>81</v>
       </c>
       <c r="B725" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C725" s="5" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="D725" s="6" t="n">
-        <v>5760.0</v>
+        <v>4669.0</v>
       </c>
       <c r="E725" s="7" t="s">
         <v>12</v>
@@ -21658,6 +21661,760 @@
         <v>81</v>
       </c>
       <c r="I725" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B726" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C726" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D726" s="6" t="n">
+        <v>5659.0</v>
+      </c>
+      <c r="E726" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F726" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G726" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H726" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I726" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B727" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C727" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D727" s="6" t="n">
+        <v>324440.0</v>
+      </c>
+      <c r="E727" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F727" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G727" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H727" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I727" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B728" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C728" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D728" s="6" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="E728" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F728" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G728" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H728" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I728" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B729" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C729" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D729" s="6" t="n">
+        <v>2490.0</v>
+      </c>
+      <c r="E729" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F729" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G729" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H729" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I729" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B730" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C730" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D730" s="6" t="n">
+        <v>411383.0</v>
+      </c>
+      <c r="E730" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F730" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G730" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H730" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I730" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B731" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C731" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D731" s="6" t="n">
+        <v>82638.0</v>
+      </c>
+      <c r="E731" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F731" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G731" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H731" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I731" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B732" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C732" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D732" s="6" t="n">
+        <v>57651.0</v>
+      </c>
+      <c r="E732" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F732" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G732" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H732" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I732" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B733" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C733" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D733" s="6" t="n">
+        <v>15746.0</v>
+      </c>
+      <c r="E733" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F733" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G733" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H733" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I733" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B734" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C734" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D734" s="6" t="n">
+        <v>100004.0</v>
+      </c>
+      <c r="E734" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F734" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G734" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H734" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I734" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B735" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C735" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D735" s="6" t="n">
+        <v>22629.0</v>
+      </c>
+      <c r="E735" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F735" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G735" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H735" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I735" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B736" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C736" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D736" s="6" t="n">
+        <v>7560.0</v>
+      </c>
+      <c r="E736" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F736" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G736" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H736" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I736" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B737" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C737" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D737" s="6" t="n">
+        <v>669.0</v>
+      </c>
+      <c r="E737" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F737" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G737" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H737" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I737" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B738" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C738" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D738" s="6" t="n">
+        <v>145324.0</v>
+      </c>
+      <c r="E738" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F738" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G738" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H738" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I738" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B739" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C739" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D739" s="6" t="n">
+        <v>2755.0</v>
+      </c>
+      <c r="E739" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F739" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G739" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H739" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I739" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B740" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C740" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D740" s="6" t="n">
+        <v>10157.0</v>
+      </c>
+      <c r="E740" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F740" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G740" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H740" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I740" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B741" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C741" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D741" s="6" t="n">
+        <v>290.0</v>
+      </c>
+      <c r="E741" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F741" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G741" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H741" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I741" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B742" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C742" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D742" s="6" t="n">
+        <v>14338.0</v>
+      </c>
+      <c r="E742" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F742" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G742" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H742" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I742" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B743" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C743" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D743" s="6" t="n">
+        <v>26382.0</v>
+      </c>
+      <c r="E743" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F743" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G743" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H743" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I743" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B744" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C744" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D744" s="6" t="n">
+        <v>22432.0</v>
+      </c>
+      <c r="E744" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F744" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G744" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H744" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I744" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B745" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C745" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D745" s="6" t="n">
+        <v>13948.0</v>
+      </c>
+      <c r="E745" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F745" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G745" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H745" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I745" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B746" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C746" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D746" s="6" t="n">
+        <v>1369.0</v>
+      </c>
+      <c r="E746" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F746" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G746" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H746" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I746" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B747" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C747" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D747" s="6" t="n">
+        <v>45106.0</v>
+      </c>
+      <c r="E747" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F747" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G747" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H747" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I747" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B748" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C748" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D748" s="6" t="n">
+        <v>109302.0</v>
+      </c>
+      <c r="E748" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F748" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G748" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H748" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I748" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B749" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C749" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D749" s="6" t="n">
+        <v>50815.0</v>
+      </c>
+      <c r="E749" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F749" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G749" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H749" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I749" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B750" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C750" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D750" s="6" t="n">
+        <v>75088.0</v>
+      </c>
+      <c r="E750" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F750" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G750" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H750" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I750" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B751" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C751" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D751" s="6" t="n">
+        <v>5706.0</v>
+      </c>
+      <c r="E751" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F751" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G751" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H751" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I751" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5913" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6141" uniqueCount="84">
   <si>
     <t>Ngày</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
   </si>
 </sst>
 </file>
@@ -624,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I751"/>
+  <dimension ref="A1:I780"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -11522,10 +11525,10 @@
         <v>13</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D376" s="6" t="n">
-        <v>228939.0</v>
+        <v>8817.0</v>
       </c>
       <c r="E376" s="7" t="s">
         <v>12</v>
@@ -11551,10 +11554,10 @@
         <v>13</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D377" s="6" t="n">
-        <v>3681.0</v>
+        <v>5337.0</v>
       </c>
       <c r="E377" s="7" t="s">
         <v>12</v>
@@ -11580,10 +11583,10 @@
         <v>13</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D378" s="6" t="n">
-        <v>5337.0</v>
+        <v>3142.0</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>12</v>
@@ -11609,10 +11612,10 @@
         <v>13</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D379" s="6" t="n">
-        <v>3142.0</v>
+        <v>102275.0</v>
       </c>
       <c r="E379" s="7" t="s">
         <v>12</v>
@@ -11638,10 +11641,10 @@
         <v>13</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D380" s="6" t="n">
-        <v>102275.0</v>
+        <v>96052.0</v>
       </c>
       <c r="E380" s="7" t="s">
         <v>12</v>
@@ -11667,10 +11670,10 @@
         <v>13</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D381" s="6" t="n">
-        <v>96052.0</v>
+        <v>4119.0</v>
       </c>
       <c r="E381" s="7" t="s">
         <v>12</v>
@@ -11696,10 +11699,10 @@
         <v>13</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D382" s="6" t="n">
-        <v>4119.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E382" s="7" t="s">
         <v>12</v>
@@ -11722,13 +11725,13 @@
         <v>64</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D383" s="6" t="n">
-        <v>69259.0</v>
+        <v>228939.0</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>12</v>
@@ -11751,13 +11754,13 @@
         <v>64</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D384" s="6" t="n">
-        <v>8817.0</v>
+        <v>25352.0</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>12</v>
@@ -11928,16 +11931,16 @@
         <v>30</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D390" s="6" t="n">
-        <v>25352.0</v>
+        <v>252681.0</v>
       </c>
       <c r="E390" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F390" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F390" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G390" s="8" t="s">
         <v>64</v>
@@ -11957,10 +11960,10 @@
         <v>30</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D391" s="6" t="n">
-        <v>7380.0</v>
+        <v>69259.0</v>
       </c>
       <c r="E391" s="7" t="s">
         <v>12</v>
@@ -11986,10 +11989,10 @@
         <v>30</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D392" s="6" t="n">
-        <v>42128.0</v>
+        <v>13204.0</v>
       </c>
       <c r="E392" s="7" t="s">
         <v>12</v>
@@ -12015,10 +12018,10 @@
         <v>30</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D393" s="6" t="n">
-        <v>12024.0</v>
+        <v>42128.0</v>
       </c>
       <c r="E393" s="7" t="s">
         <v>12</v>
@@ -12044,16 +12047,16 @@
         <v>30</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D394" s="6" t="n">
-        <v>252681.0</v>
+        <v>12024.0</v>
       </c>
       <c r="E394" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F394" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F394" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G394" s="8" t="s">
         <v>64</v>
@@ -12073,10 +12076,10 @@
         <v>30</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>13204.0</v>
+        <v>7380.0</v>
       </c>
       <c r="E395" s="7" t="s">
         <v>12</v>
@@ -16887,10 +16890,10 @@
         <v>13</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D561" s="6" t="n">
-        <v>3016.0</v>
+        <v>1147.0</v>
       </c>
       <c r="E561" s="7" t="s">
         <v>12</v>
@@ -16916,10 +16919,10 @@
         <v>13</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D562" s="6" t="n">
-        <v>135115.0</v>
+        <v>50267.0</v>
       </c>
       <c r="E562" s="7" t="s">
         <v>12</v>
@@ -16945,10 +16948,10 @@
         <v>13</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D563" s="6" t="n">
-        <v>103167.0</v>
+        <v>135115.0</v>
       </c>
       <c r="E563" s="7" t="s">
         <v>12</v>
@@ -16974,10 +16977,10 @@
         <v>13</v>
       </c>
       <c r="C564" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D564" s="6" t="n">
-        <v>388.0</v>
+        <v>103167.0</v>
       </c>
       <c r="E564" s="7" t="s">
         <v>12</v>
@@ -17003,10 +17006,10 @@
         <v>13</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D565" s="6" t="n">
-        <v>4205.0</v>
+        <v>388.0</v>
       </c>
       <c r="E565" s="7" t="s">
         <v>12</v>
@@ -17032,10 +17035,10 @@
         <v>13</v>
       </c>
       <c r="C566" s="5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D566" s="6" t="n">
-        <v>1147.0</v>
+        <v>73411.0</v>
       </c>
       <c r="E566" s="7" t="s">
         <v>12</v>
@@ -17264,10 +17267,10 @@
         <v>13</v>
       </c>
       <c r="C574" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D574" s="6" t="n">
-        <v>50267.0</v>
+        <v>3016.0</v>
       </c>
       <c r="E574" s="7" t="s">
         <v>12</v>
@@ -17290,13 +17293,13 @@
         <v>71</v>
       </c>
       <c r="B575" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D575" s="6" t="n">
-        <v>160983.0</v>
+        <v>4205.0</v>
       </c>
       <c r="E575" s="7" t="s">
         <v>12</v>
@@ -17322,10 +17325,10 @@
         <v>13</v>
       </c>
       <c r="C576" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D576" s="6" t="n">
-        <v>73411.0</v>
+        <v>11348.0</v>
       </c>
       <c r="E576" s="7" t="s">
         <v>12</v>
@@ -17377,13 +17380,13 @@
         <v>71</v>
       </c>
       <c r="B578" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C578" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D578" s="6" t="n">
-        <v>11348.0</v>
+        <v>30577.0</v>
       </c>
       <c r="E578" s="7" t="s">
         <v>12</v>
@@ -17583,10 +17586,10 @@
         <v>30</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D585" s="6" t="n">
-        <v>267.0</v>
+        <v>3492.0</v>
       </c>
       <c r="E585" s="7" t="s">
         <v>12</v>
@@ -17612,16 +17615,16 @@
         <v>30</v>
       </c>
       <c r="C586" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D586" s="6" t="n">
-        <v>245314.0</v>
+        <v>267.0</v>
       </c>
       <c r="E586" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F586" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F586" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G586" s="8" t="s">
         <v>71</v>
@@ -17641,16 +17644,16 @@
         <v>30</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D587" s="6" t="n">
-        <v>10813.0</v>
+        <v>245314.0</v>
       </c>
       <c r="E587" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F587" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F587" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G587" s="8" t="s">
         <v>71</v>
@@ -17670,10 +17673,10 @@
         <v>30</v>
       </c>
       <c r="C588" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D588" s="6" t="n">
-        <v>215594.0</v>
+        <v>10813.0</v>
       </c>
       <c r="E588" s="7" t="s">
         <v>12</v>
@@ -17699,10 +17702,10 @@
         <v>30</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D589" s="6" t="n">
-        <v>30577.0</v>
+        <v>215594.0</v>
       </c>
       <c r="E589" s="7" t="s">
         <v>12</v>
@@ -17728,10 +17731,10 @@
         <v>30</v>
       </c>
       <c r="C590" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D590" s="6" t="n">
-        <v>3492.0</v>
+        <v>160983.0</v>
       </c>
       <c r="E590" s="7" t="s">
         <v>12</v>
@@ -18105,10 +18108,10 @@
         <v>13</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D603" s="6" t="n">
-        <v>17195.0</v>
+        <v>10263.0</v>
       </c>
       <c r="E603" s="7" t="s">
         <v>12</v>
@@ -18192,16 +18195,16 @@
         <v>10</v>
       </c>
       <c r="C606" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D606" s="6" t="n">
-        <v>414009.0</v>
+        <v>199612.0</v>
       </c>
       <c r="E606" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F606" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F606" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G606" s="8" t="s">
         <v>72</v>
@@ -18218,13 +18221,13 @@
         <v>72</v>
       </c>
       <c r="B607" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D607" s="6" t="n">
-        <v>69940.0</v>
+        <v>17195.0</v>
       </c>
       <c r="E607" s="7" t="s">
         <v>12</v>
@@ -18250,10 +18253,10 @@
         <v>10</v>
       </c>
       <c r="C608" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D608" s="6" t="n">
-        <v>4681.0</v>
+        <v>69940.0</v>
       </c>
       <c r="E608" s="7" t="s">
         <v>12</v>
@@ -18276,13 +18279,13 @@
         <v>72</v>
       </c>
       <c r="B609" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D609" s="6" t="n">
-        <v>76271.0</v>
+        <v>4681.0</v>
       </c>
       <c r="E609" s="7" t="s">
         <v>12</v>
@@ -18305,13 +18308,13 @@
         <v>72</v>
       </c>
       <c r="B610" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C610" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D610" s="6" t="n">
-        <v>199612.0</v>
+        <v>76271.0</v>
       </c>
       <c r="E610" s="7" t="s">
         <v>12</v>
@@ -18334,19 +18337,19 @@
         <v>72</v>
       </c>
       <c r="B611" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D611" s="6" t="n">
-        <v>11956.0</v>
+        <v>414009.0</v>
       </c>
       <c r="E611" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F611" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F611" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G611" s="8" t="s">
         <v>72</v>
@@ -18366,10 +18369,10 @@
         <v>30</v>
       </c>
       <c r="C612" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D612" s="6" t="n">
-        <v>10252.0</v>
+        <v>11956.0</v>
       </c>
       <c r="E612" s="7" t="s">
         <v>12</v>
@@ -18395,16 +18398,16 @@
         <v>30</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D613" s="6" t="n">
-        <v>219512.0</v>
+        <v>10252.0</v>
       </c>
       <c r="E613" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F613" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F613" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G613" s="8" t="s">
         <v>72</v>
@@ -18424,16 +18427,16 @@
         <v>30</v>
       </c>
       <c r="C614" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D614" s="6" t="n">
-        <v>45738.0</v>
+        <v>219512.0</v>
       </c>
       <c r="E614" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F614" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F614" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G614" s="8" t="s">
         <v>72</v>
@@ -18450,13 +18453,13 @@
         <v>72</v>
       </c>
       <c r="B615" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C615" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D615" s="6" t="n">
-        <v>10263.0</v>
+        <v>45738.0</v>
       </c>
       <c r="E615" s="7" t="s">
         <v>12</v>
@@ -18511,10 +18514,10 @@
         <v>13</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D617" s="6" t="n">
-        <v>681.0</v>
+        <v>4371.0</v>
       </c>
       <c r="E617" s="7" t="s">
         <v>12</v>
@@ -18540,10 +18543,10 @@
         <v>13</v>
       </c>
       <c r="C618" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D618" s="6" t="n">
-        <v>251598.0</v>
+        <v>597.0</v>
       </c>
       <c r="E618" s="7" t="s">
         <v>12</v>
@@ -18569,10 +18572,10 @@
         <v>13</v>
       </c>
       <c r="C619" s="5" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D619" s="6" t="n">
-        <v>597.0</v>
+        <v>1345.0</v>
       </c>
       <c r="E619" s="7" t="s">
         <v>12</v>
@@ -18598,10 +18601,10 @@
         <v>13</v>
       </c>
       <c r="C620" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D620" s="6" t="n">
-        <v>1345.0</v>
+        <v>3953.0</v>
       </c>
       <c r="E620" s="7" t="s">
         <v>12</v>
@@ -18627,10 +18630,10 @@
         <v>13</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D621" s="6" t="n">
-        <v>3953.0</v>
+        <v>681.0</v>
       </c>
       <c r="E621" s="7" t="s">
         <v>12</v>
@@ -18685,10 +18688,10 @@
         <v>13</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D623" s="6" t="n">
-        <v>4371.0</v>
+        <v>83909.0</v>
       </c>
       <c r="E623" s="7" t="s">
         <v>12</v>
@@ -18714,10 +18717,10 @@
         <v>13</v>
       </c>
       <c r="C624" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D624" s="6" t="n">
-        <v>83909.0</v>
+        <v>84856.0</v>
       </c>
       <c r="E624" s="7" t="s">
         <v>12</v>
@@ -18743,10 +18746,10 @@
         <v>13</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D625" s="6" t="n">
-        <v>84856.0</v>
+        <v>386333.0</v>
       </c>
       <c r="E625" s="7" t="s">
         <v>12</v>
@@ -18772,10 +18775,10 @@
         <v>13</v>
       </c>
       <c r="C626" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D626" s="6" t="n">
-        <v>386333.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E626" s="7" t="s">
         <v>12</v>
@@ -18801,10 +18804,10 @@
         <v>13</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D627" s="6" t="n">
-        <v>2658.0</v>
+        <v>54493.0</v>
       </c>
       <c r="E627" s="7" t="s">
         <v>12</v>
@@ -18830,16 +18833,16 @@
         <v>13</v>
       </c>
       <c r="C628" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D628" s="6" t="n">
-        <v>54493.0</v>
+        <v>129190.0</v>
       </c>
       <c r="E628" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F628" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F628" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G628" s="8" t="s">
         <v>73</v>
@@ -18859,16 +18862,16 @@
         <v>13</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D629" s="6" t="n">
-        <v>129190.0</v>
+        <v>251598.0</v>
       </c>
       <c r="E629" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F629" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F629" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G629" s="8" t="s">
         <v>73</v>
@@ -18885,19 +18888,19 @@
         <v>73</v>
       </c>
       <c r="B630" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C630" s="5" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D630" s="6" t="n">
-        <v>191571.0</v>
+        <v>5327.0</v>
       </c>
       <c r="E630" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F630" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F630" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G630" s="8" t="s">
         <v>73</v>
@@ -18914,13 +18917,13 @@
         <v>73</v>
       </c>
       <c r="B631" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C631" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D631" s="6" t="n">
-        <v>5327.0</v>
+        <v>43478.0</v>
       </c>
       <c r="E631" s="7" t="s">
         <v>12</v>
@@ -18943,13 +18946,13 @@
         <v>73</v>
       </c>
       <c r="B632" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C632" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D632" s="6" t="n">
-        <v>1660.0</v>
+        <v>6983.0</v>
       </c>
       <c r="E632" s="7" t="s">
         <v>12</v>
@@ -18972,13 +18975,13 @@
         <v>73</v>
       </c>
       <c r="B633" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C633" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D633" s="6" t="n">
-        <v>6983.0</v>
+        <v>276686.0</v>
       </c>
       <c r="E633" s="7" t="s">
         <v>12</v>
@@ -19004,10 +19007,10 @@
         <v>10</v>
       </c>
       <c r="C634" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D634" s="6" t="n">
-        <v>276686.0</v>
+        <v>65439.0</v>
       </c>
       <c r="E634" s="7" t="s">
         <v>12</v>
@@ -19033,10 +19036,10 @@
         <v>10</v>
       </c>
       <c r="C635" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D635" s="6" t="n">
-        <v>65439.0</v>
+        <v>139458.0</v>
       </c>
       <c r="E635" s="7" t="s">
         <v>12</v>
@@ -19062,10 +19065,10 @@
         <v>10</v>
       </c>
       <c r="C636" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D636" s="6" t="n">
-        <v>139458.0</v>
+        <v>1660.0</v>
       </c>
       <c r="E636" s="7" t="s">
         <v>12</v>
@@ -19120,10 +19123,10 @@
         <v>30</v>
       </c>
       <c r="C638" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D638" s="6" t="n">
-        <v>43478.0</v>
+        <v>5387.0</v>
       </c>
       <c r="E638" s="7" t="s">
         <v>12</v>
@@ -19149,16 +19152,16 @@
         <v>30</v>
       </c>
       <c r="C639" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D639" s="6" t="n">
-        <v>5387.0</v>
+        <v>322311.0</v>
       </c>
       <c r="E639" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F639" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F639" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G639" s="8" t="s">
         <v>73</v>
@@ -19178,16 +19181,16 @@
         <v>30</v>
       </c>
       <c r="C640" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D640" s="6" t="n">
-        <v>322311.0</v>
+        <v>107.0</v>
       </c>
       <c r="E640" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F640" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F640" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G640" s="8" t="s">
         <v>73</v>
@@ -19207,10 +19210,10 @@
         <v>30</v>
       </c>
       <c r="C641" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D641" s="6" t="n">
-        <v>107.0</v>
+        <v>220179.0</v>
       </c>
       <c r="E641" s="7" t="s">
         <v>12</v>
@@ -19233,19 +19236,19 @@
         <v>73</v>
       </c>
       <c r="B642" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C642" s="5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D642" s="6" t="n">
-        <v>220179.0</v>
+        <v>191571.0</v>
       </c>
       <c r="E642" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F642" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F642" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G642" s="8" t="s">
         <v>73</v>
@@ -19381,10 +19384,10 @@
         <v>13</v>
       </c>
       <c r="C647" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D647" s="6" t="n">
-        <v>52273.0</v>
+        <v>3992.0</v>
       </c>
       <c r="E647" s="7" t="s">
         <v>12</v>
@@ -19700,10 +19703,10 @@
         <v>13</v>
       </c>
       <c r="C658" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D658" s="6" t="n">
-        <v>3992.0</v>
+        <v>52273.0</v>
       </c>
       <c r="E658" s="7" t="s">
         <v>12</v>
@@ -20480,13 +20483,13 @@
         <v>80</v>
       </c>
       <c r="B685" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C685" s="5" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D685" s="6" t="n">
-        <v>33064.0</v>
+        <v>7892.0</v>
       </c>
       <c r="E685" s="7" t="s">
         <v>12</v>
@@ -20509,19 +20512,19 @@
         <v>80</v>
       </c>
       <c r="B686" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C686" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D686" s="6" t="n">
-        <v>54550.0</v>
+        <v>33064.0</v>
       </c>
       <c r="E686" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F686" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F686" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G686" s="8" t="s">
         <v>80</v>
@@ -20541,16 +20544,16 @@
         <v>13</v>
       </c>
       <c r="C687" s="5" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D687" s="6" t="n">
-        <v>7892.0</v>
+        <v>54550.0</v>
       </c>
       <c r="E687" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F687" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F687" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G687" s="8" t="s">
         <v>80</v>
@@ -20570,10 +20573,10 @@
         <v>13</v>
       </c>
       <c r="C688" s="5" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="D688" s="6" t="n">
-        <v>4039.0</v>
+        <v>9197.0</v>
       </c>
       <c r="E688" s="7" t="s">
         <v>12</v>
@@ -20599,10 +20602,10 @@
         <v>13</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="D689" s="6" t="n">
-        <v>9197.0</v>
+        <v>4039.0</v>
       </c>
       <c r="E689" s="7" t="s">
         <v>12</v>
@@ -20625,13 +20628,13 @@
         <v>80</v>
       </c>
       <c r="B690" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C690" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D690" s="6" t="n">
-        <v>252954.0</v>
+        <v>1752.0</v>
       </c>
       <c r="E690" s="7" t="s">
         <v>12</v>
@@ -20654,13 +20657,13 @@
         <v>80</v>
       </c>
       <c r="B691" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C691" s="5" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D691" s="6" t="n">
-        <v>227.0</v>
+        <v>252954.0</v>
       </c>
       <c r="E691" s="7" t="s">
         <v>12</v>
@@ -20683,13 +20686,13 @@
         <v>80</v>
       </c>
       <c r="B692" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C692" s="5" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D692" s="6" t="n">
-        <v>189500.0</v>
+        <v>227.0</v>
       </c>
       <c r="E692" s="7" t="s">
         <v>12</v>
@@ -20712,13 +20715,13 @@
         <v>80</v>
       </c>
       <c r="B693" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C693" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D693" s="6" t="n">
-        <v>70.0</v>
+        <v>120464.0</v>
       </c>
       <c r="E693" s="7" t="s">
         <v>12</v>
@@ -20744,10 +20747,10 @@
         <v>10</v>
       </c>
       <c r="C694" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D694" s="6" t="n">
-        <v>1752.0</v>
+        <v>311394.0</v>
       </c>
       <c r="E694" s="7" t="s">
         <v>12</v>
@@ -20770,13 +20773,13 @@
         <v>80</v>
       </c>
       <c r="B695" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C695" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D695" s="6" t="n">
-        <v>32442.0</v>
+        <v>70.0</v>
       </c>
       <c r="E695" s="7" t="s">
         <v>12</v>
@@ -20802,10 +20805,10 @@
         <v>30</v>
       </c>
       <c r="C696" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D696" s="6" t="n">
-        <v>8735.0</v>
+        <v>32442.0</v>
       </c>
       <c r="E696" s="7" t="s">
         <v>12</v>
@@ -20828,13 +20831,13 @@
         <v>80</v>
       </c>
       <c r="B697" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C697" s="5" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D697" s="6" t="n">
-        <v>311364.0</v>
+        <v>8735.0</v>
       </c>
       <c r="E697" s="7" t="s">
         <v>12</v>
@@ -20857,19 +20860,19 @@
         <v>80</v>
       </c>
       <c r="B698" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C698" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D698" s="6" t="n">
-        <v>280310.0</v>
+        <v>189500.0</v>
       </c>
       <c r="E698" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F698" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F698" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G698" s="8" t="s">
         <v>80</v>
@@ -20886,19 +20889,19 @@
         <v>80</v>
       </c>
       <c r="B699" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C699" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D699" s="6" t="n">
-        <v>8705.0</v>
+        <v>280310.0</v>
       </c>
       <c r="E699" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F699" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F699" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G699" s="8" t="s">
         <v>80</v>
@@ -20918,10 +20921,10 @@
         <v>30</v>
       </c>
       <c r="C700" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D700" s="6" t="n">
-        <v>1622.0</v>
+        <v>108670.0</v>
       </c>
       <c r="E700" s="7" t="s">
         <v>12</v>
@@ -20944,19 +20947,19 @@
         <v>80</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C701" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D701" s="6" t="n">
-        <v>85559.0</v>
+        <v>13334.0</v>
       </c>
       <c r="E701" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F701" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F701" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G701" s="8" t="s">
         <v>80</v>
@@ -20976,10 +20979,10 @@
         <v>13</v>
       </c>
       <c r="C702" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D702" s="6" t="n">
-        <v>120464.0</v>
+        <v>25961.0</v>
       </c>
       <c r="E702" s="7" t="s">
         <v>12</v>
@@ -21005,10 +21008,10 @@
         <v>13</v>
       </c>
       <c r="C703" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D703" s="6" t="n">
-        <v>25961.0</v>
+        <v>8705.0</v>
       </c>
       <c r="E703" s="7" t="s">
         <v>12</v>
@@ -21031,19 +21034,19 @@
         <v>80</v>
       </c>
       <c r="B704" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C704" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D704" s="6" t="n">
-        <v>13334.0</v>
+        <v>85559.0</v>
       </c>
       <c r="E704" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F704" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F704" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G704" s="8" t="s">
         <v>80</v>
@@ -21063,10 +21066,10 @@
         <v>30</v>
       </c>
       <c r="C705" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D705" s="6" t="n">
-        <v>108670.0</v>
+        <v>1622.0</v>
       </c>
       <c r="E705" s="7" t="s">
         <v>12</v>
@@ -21092,10 +21095,10 @@
         <v>13</v>
       </c>
       <c r="C706" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D706" s="6" t="n">
-        <v>110401.0</v>
+        <v>406885.0</v>
       </c>
       <c r="E706" s="7" t="s">
         <v>12</v>
@@ -21121,10 +21124,10 @@
         <v>13</v>
       </c>
       <c r="C707" s="5" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="D707" s="6" t="n">
-        <v>19765.0</v>
+        <v>2176.0</v>
       </c>
       <c r="E707" s="7" t="s">
         <v>12</v>
@@ -21150,10 +21153,10 @@
         <v>13</v>
       </c>
       <c r="C708" s="5" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D708" s="6" t="n">
-        <v>36291.0</v>
+        <v>8648.0</v>
       </c>
       <c r="E708" s="7" t="s">
         <v>12</v>
@@ -21176,13 +21179,13 @@
         <v>81</v>
       </c>
       <c r="B709" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C709" s="5" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="D709" s="6" t="n">
-        <v>6834.0</v>
+        <v>19774.0</v>
       </c>
       <c r="E709" s="7" t="s">
         <v>12</v>
@@ -21205,13 +21208,13 @@
         <v>81</v>
       </c>
       <c r="B710" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C710" s="5" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="D710" s="6" t="n">
-        <v>19628.0</v>
+        <v>1063.0</v>
       </c>
       <c r="E710" s="7" t="s">
         <v>12</v>
@@ -21234,13 +21237,13 @@
         <v>81</v>
       </c>
       <c r="B711" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C711" s="5" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D711" s="6" t="n">
-        <v>1686.0</v>
+        <v>98448.0</v>
       </c>
       <c r="E711" s="7" t="s">
         <v>12</v>
@@ -21266,10 +21269,10 @@
         <v>13</v>
       </c>
       <c r="C712" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D712" s="6" t="n">
-        <v>405880.0</v>
+        <v>1686.0</v>
       </c>
       <c r="E712" s="7" t="s">
         <v>12</v>
@@ -21292,13 +21295,13 @@
         <v>81</v>
       </c>
       <c r="B713" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="D713" s="6" t="n">
-        <v>1063.0</v>
+        <v>19628.0</v>
       </c>
       <c r="E713" s="7" t="s">
         <v>12</v>
@@ -21321,13 +21324,13 @@
         <v>81</v>
       </c>
       <c r="B714" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C714" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D714" s="6" t="n">
-        <v>19774.0</v>
+        <v>6834.0</v>
       </c>
       <c r="E714" s="7" t="s">
         <v>12</v>
@@ -21353,10 +21356,10 @@
         <v>13</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="D715" s="6" t="n">
-        <v>8648.0</v>
+        <v>36291.0</v>
       </c>
       <c r="E715" s="7" t="s">
         <v>12</v>
@@ -21382,10 +21385,10 @@
         <v>13</v>
       </c>
       <c r="C716" s="5" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="D716" s="6" t="n">
-        <v>2033.0</v>
+        <v>19765.0</v>
       </c>
       <c r="E716" s="7" t="s">
         <v>12</v>
@@ -21411,10 +21414,10 @@
         <v>13</v>
       </c>
       <c r="C717" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D717" s="6" t="n">
-        <v>3984.0</v>
+        <v>379598.0</v>
       </c>
       <c r="E717" s="7" t="s">
         <v>12</v>
@@ -21437,13 +21440,13 @@
         <v>81</v>
       </c>
       <c r="B718" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C718" s="5" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D718" s="6" t="n">
-        <v>98198.0</v>
+        <v>3984.0</v>
       </c>
       <c r="E718" s="7" t="s">
         <v>12</v>
@@ -21469,10 +21472,10 @@
         <v>13</v>
       </c>
       <c r="C719" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D719" s="6" t="n">
-        <v>378567.0</v>
+        <v>78279.0</v>
       </c>
       <c r="E719" s="7" t="s">
         <v>12</v>
@@ -21498,10 +21501,10 @@
         <v>13</v>
       </c>
       <c r="C720" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D720" s="6" t="n">
-        <v>78279.0</v>
+        <v>110580.0</v>
       </c>
       <c r="E720" s="7" t="s">
         <v>12</v>
@@ -21527,10 +21530,10 @@
         <v>30</v>
       </c>
       <c r="C721" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D721" s="6" t="n">
-        <v>44916.0</v>
+        <v>83.0</v>
       </c>
       <c r="E721" s="7" t="s">
         <v>12</v>
@@ -21553,13 +21556,13 @@
         <v>81</v>
       </c>
       <c r="B722" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C722" s="5" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D722" s="6" t="n">
-        <v>677.0</v>
+        <v>145811.0</v>
       </c>
       <c r="E722" s="7" t="s">
         <v>12</v>
@@ -21585,10 +21588,10 @@
         <v>10</v>
       </c>
       <c r="C723" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D723" s="6" t="n">
-        <v>145811.0</v>
+        <v>31341.0</v>
       </c>
       <c r="E723" s="7" t="s">
         <v>12</v>
@@ -21614,16 +21617,16 @@
         <v>10</v>
       </c>
       <c r="C724" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D724" s="6" t="n">
-        <v>31341.0</v>
+        <v>338700.0</v>
       </c>
       <c r="E724" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F724" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F724" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G724" s="8" t="s">
         <v>81</v>
@@ -21669,13 +21672,13 @@
         <v>81</v>
       </c>
       <c r="B726" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C726" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D726" s="6" t="n">
-        <v>5659.0</v>
+        <v>45412.0</v>
       </c>
       <c r="E726" s="7" t="s">
         <v>12</v>
@@ -21701,16 +21704,16 @@
         <v>10</v>
       </c>
       <c r="C727" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D727" s="6" t="n">
-        <v>324440.0</v>
+        <v>5659.0</v>
       </c>
       <c r="E727" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F727" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F727" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G727" s="8" t="s">
         <v>81</v>
@@ -21730,10 +21733,10 @@
         <v>30</v>
       </c>
       <c r="C728" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D728" s="6" t="n">
-        <v>83.0</v>
+        <v>3168.0</v>
       </c>
       <c r="E728" s="7" t="s">
         <v>12</v>
@@ -21759,16 +21762,16 @@
         <v>30</v>
       </c>
       <c r="C729" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D729" s="6" t="n">
-        <v>2490.0</v>
+        <v>412779.0</v>
       </c>
       <c r="E729" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F729" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F729" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G729" s="8" t="s">
         <v>81</v>
@@ -21788,16 +21791,16 @@
         <v>30</v>
       </c>
       <c r="C730" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D730" s="6" t="n">
-        <v>411383.0</v>
+        <v>82638.0</v>
       </c>
       <c r="E730" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F730" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F730" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G730" s="8" t="s">
         <v>81</v>
@@ -21814,13 +21817,13 @@
         <v>81</v>
       </c>
       <c r="B731" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C731" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D731" s="6" t="n">
-        <v>82638.0</v>
+        <v>57651.0</v>
       </c>
       <c r="E731" s="7" t="s">
         <v>12</v>
@@ -21846,10 +21849,10 @@
         <v>13</v>
       </c>
       <c r="C732" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D732" s="6" t="n">
-        <v>57651.0</v>
+        <v>15746.0</v>
       </c>
       <c r="E732" s="7" t="s">
         <v>12</v>
@@ -21875,10 +21878,10 @@
         <v>13</v>
       </c>
       <c r="C733" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D733" s="6" t="n">
-        <v>15746.0</v>
+        <v>677.0</v>
       </c>
       <c r="E733" s="7" t="s">
         <v>12</v>
@@ -21904,16 +21907,16 @@
         <v>13</v>
       </c>
       <c r="C734" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D734" s="6" t="n">
-        <v>100004.0</v>
+        <v>340508.0</v>
       </c>
       <c r="E734" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F734" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F734" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G734" s="8" t="s">
         <v>82</v>
@@ -21930,13 +21933,13 @@
         <v>82</v>
       </c>
       <c r="B735" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C735" s="5" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="D735" s="6" t="n">
-        <v>22629.0</v>
+        <v>354.0</v>
       </c>
       <c r="E735" s="7" t="s">
         <v>12</v>
@@ -21959,13 +21962,13 @@
         <v>82</v>
       </c>
       <c r="B736" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C736" s="5" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="D736" s="6" t="n">
-        <v>7560.0</v>
+        <v>12510.0</v>
       </c>
       <c r="E736" s="7" t="s">
         <v>12</v>
@@ -21988,13 +21991,13 @@
         <v>82</v>
       </c>
       <c r="B737" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="D737" s="6" t="n">
-        <v>669.0</v>
+        <v>23079.0</v>
       </c>
       <c r="E737" s="7" t="s">
         <v>12</v>
@@ -22020,10 +22023,10 @@
         <v>13</v>
       </c>
       <c r="C738" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D738" s="6" t="n">
-        <v>145324.0</v>
+        <v>7371.0</v>
       </c>
       <c r="E738" s="7" t="s">
         <v>12</v>
@@ -22049,10 +22052,10 @@
         <v>13</v>
       </c>
       <c r="C739" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D739" s="6" t="n">
-        <v>2755.0</v>
+        <v>405.0</v>
       </c>
       <c r="E739" s="7" t="s">
         <v>12</v>
@@ -22078,10 +22081,10 @@
         <v>13</v>
       </c>
       <c r="C740" s="5" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D740" s="6" t="n">
-        <v>10157.0</v>
+        <v>583.0</v>
       </c>
       <c r="E740" s="7" t="s">
         <v>12</v>
@@ -22107,10 +22110,10 @@
         <v>13</v>
       </c>
       <c r="C741" s="5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D741" s="6" t="n">
-        <v>290.0</v>
+        <v>471.0</v>
       </c>
       <c r="E741" s="7" t="s">
         <v>12</v>
@@ -22133,13 +22136,13 @@
         <v>82</v>
       </c>
       <c r="B742" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C742" s="5" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D742" s="6" t="n">
-        <v>14338.0</v>
+        <v>19328.0</v>
       </c>
       <c r="E742" s="7" t="s">
         <v>12</v>
@@ -22162,13 +22165,13 @@
         <v>82</v>
       </c>
       <c r="B743" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C743" s="5" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="D743" s="6" t="n">
-        <v>26382.0</v>
+        <v>12595.0</v>
       </c>
       <c r="E743" s="7" t="s">
         <v>12</v>
@@ -22191,13 +22194,13 @@
         <v>82</v>
       </c>
       <c r="B744" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C744" s="5" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D744" s="6" t="n">
-        <v>22432.0</v>
+        <v>106580.0</v>
       </c>
       <c r="E744" s="7" t="s">
         <v>12</v>
@@ -22223,10 +22226,10 @@
         <v>13</v>
       </c>
       <c r="C745" s="5" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="D745" s="6" t="n">
-        <v>13948.0</v>
+        <v>26130.0</v>
       </c>
       <c r="E745" s="7" t="s">
         <v>12</v>
@@ -22249,13 +22252,13 @@
         <v>82</v>
       </c>
       <c r="B746" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C746" s="5" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D746" s="6" t="n">
-        <v>1369.0</v>
+        <v>175823.0</v>
       </c>
       <c r="E746" s="7" t="s">
         <v>12</v>
@@ -22278,13 +22281,13 @@
         <v>82</v>
       </c>
       <c r="B747" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C747" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D747" s="6" t="n">
-        <v>45106.0</v>
+        <v>15050.0</v>
       </c>
       <c r="E747" s="7" t="s">
         <v>12</v>
@@ -22307,19 +22310,19 @@
         <v>82</v>
       </c>
       <c r="B748" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C748" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D748" s="6" t="n">
-        <v>109302.0</v>
+        <v>135975.0</v>
       </c>
       <c r="E748" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F748" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F748" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G748" s="8" t="s">
         <v>82</v>
@@ -22336,13 +22339,13 @@
         <v>82</v>
       </c>
       <c r="B749" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C749" s="5" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D749" s="6" t="n">
-        <v>50815.0</v>
+        <v>180627.0</v>
       </c>
       <c r="E749" s="7" t="s">
         <v>12</v>
@@ -22365,19 +22368,19 @@
         <v>82</v>
       </c>
       <c r="B750" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C750" s="5" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D750" s="6" t="n">
-        <v>75088.0</v>
+        <v>258166.0</v>
       </c>
       <c r="E750" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F750" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F750" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G750" s="8" t="s">
         <v>82</v>
@@ -22397,10 +22400,10 @@
         <v>13</v>
       </c>
       <c r="C751" s="5" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="D751" s="6" t="n">
-        <v>5706.0</v>
+        <v>149791.0</v>
       </c>
       <c r="E751" s="7" t="s">
         <v>12</v>
@@ -22415,6 +22418,847 @@
         <v>82</v>
       </c>
       <c r="I751" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B752" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C752" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D752" s="6" t="n">
+        <v>175752.0</v>
+      </c>
+      <c r="E752" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F752" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G752" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H752" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I752" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B753" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C753" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D753" s="6" t="n">
+        <v>2800.0</v>
+      </c>
+      <c r="E753" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F753" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G753" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H753" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I753" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B754" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C754" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D754" s="6" t="n">
+        <v>5657.0</v>
+      </c>
+      <c r="E754" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F754" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G754" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H754" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I754" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B755" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C755" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D755" s="6" t="n">
+        <v>1522.0</v>
+      </c>
+      <c r="E755" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F755" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G755" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H755" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I755" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B756" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C756" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D756" s="6" t="n">
+        <v>117115.0</v>
+      </c>
+      <c r="E756" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F756" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G756" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H756" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I756" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B757" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C757" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D757" s="6" t="n">
+        <v>7306.0</v>
+      </c>
+      <c r="E757" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F757" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G757" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H757" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I757" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B758" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C758" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D758" s="6" t="n">
+        <v>157844.0</v>
+      </c>
+      <c r="E758" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F758" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G758" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H758" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I758" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B759" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C759" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D759" s="6" t="n">
+        <v>2155.0</v>
+      </c>
+      <c r="E759" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F759" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G759" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H759" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I759" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B760" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C760" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D760" s="6" t="n">
+        <v>66146.0</v>
+      </c>
+      <c r="E760" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F760" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G760" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H760" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I760" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B761" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C761" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D761" s="6" t="n">
+        <v>21209.0</v>
+      </c>
+      <c r="E761" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F761" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G761" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H761" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I761" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B762" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C762" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D762" s="6" t="n">
+        <v>16206.0</v>
+      </c>
+      <c r="E762" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F762" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G762" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H762" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I762" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B763" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C763" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D763" s="6" t="n">
+        <v>50124.0</v>
+      </c>
+      <c r="E763" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F763" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G763" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H763" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I763" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B764" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C764" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D764" s="6" t="n">
+        <v>36836.0</v>
+      </c>
+      <c r="E764" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F764" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G764" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H764" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I764" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B765" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C765" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D765" s="6" t="n">
+        <v>1642.0</v>
+      </c>
+      <c r="E765" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F765" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G765" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H765" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I765" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B766" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C766" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D766" s="6" t="n">
+        <v>4240.0</v>
+      </c>
+      <c r="E766" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F766" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G766" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H766" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I766" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B767" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C767" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D767" s="6" t="n">
+        <v>448526.0</v>
+      </c>
+      <c r="E767" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F767" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G767" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H767" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I767" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B768" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C768" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D768" s="6" t="n">
+        <v>6212.0</v>
+      </c>
+      <c r="E768" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F768" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G768" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H768" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I768" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B769" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C769" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D769" s="6" t="n">
+        <v>2236.0</v>
+      </c>
+      <c r="E769" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F769" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G769" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H769" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I769" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B770" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C770" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D770" s="6" t="n">
+        <v>202554.0</v>
+      </c>
+      <c r="E770" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F770" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G770" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H770" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I770" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B771" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C771" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D771" s="6" t="n">
+        <v>187439.0</v>
+      </c>
+      <c r="E771" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F771" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G771" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H771" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I771" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B772" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C772" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D772" s="6" t="n">
+        <v>28729.0</v>
+      </c>
+      <c r="E772" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F772" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G772" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H772" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I772" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B773" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C773" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D773" s="6" t="n">
+        <v>9834.0</v>
+      </c>
+      <c r="E773" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F773" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G773" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H773" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I773" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B774" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C774" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D774" s="6" t="n">
+        <v>62640.0</v>
+      </c>
+      <c r="E774" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F774" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G774" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H774" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I774" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B775" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C775" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D775" s="6" t="n">
+        <v>276071.0</v>
+      </c>
+      <c r="E775" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F775" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G775" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H775" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I775" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B776" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C776" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D776" s="6" t="n">
+        <v>21840.0</v>
+      </c>
+      <c r="E776" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F776" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G776" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H776" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I776" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B777" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C777" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D777" s="6" t="n">
+        <v>3781.0</v>
+      </c>
+      <c r="E777" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F777" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G777" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H777" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I777" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B778" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C778" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D778" s="6" t="n">
+        <v>2938.0</v>
+      </c>
+      <c r="E778" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F778" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G778" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H778" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I778" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B779" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C779" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D779" s="6" t="n">
+        <v>115239.0</v>
+      </c>
+      <c r="E779" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F779" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G779" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H779" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I779" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B780" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C780" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D780" s="6" t="n">
+        <v>5565.0</v>
+      </c>
+      <c r="E780" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F780" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G780" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H780" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I780" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
+++ b/DATA-CĐ-Tệp-Trung-805265852439209.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6651" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6681" uniqueCount="86">
   <si>
     <t>Ngày</t>
   </si>
@@ -633,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I845"/>
+  <dimension ref="A1:I849"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -13126,10 +13126,10 @@
         <v>13</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>70064.0</v>
+        <v>35061.0</v>
       </c>
       <c r="E431" s="7" t="s">
         <v>12</v>
@@ -13155,10 +13155,10 @@
         <v>13</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D432" s="6" t="n">
-        <v>4241.0</v>
+        <v>70064.0</v>
       </c>
       <c r="E432" s="7" t="s">
         <v>12</v>
@@ -13184,10 +13184,10 @@
         <v>13</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>35061.0</v>
+        <v>4241.0</v>
       </c>
       <c r="E433" s="7" t="s">
         <v>12</v>
@@ -13271,16 +13271,16 @@
         <v>10</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D436" s="6" t="n">
-        <v>210756.0</v>
+        <v>4524.0</v>
       </c>
       <c r="E436" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F436" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F436" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G436" s="8" t="s">
         <v>66</v>
@@ -13416,16 +13416,16 @@
         <v>10</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>209762.0</v>
+        <v>210756.0</v>
       </c>
       <c r="E441" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F441" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F441" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G441" s="8" t="s">
         <v>66</v>
@@ -13445,10 +13445,10 @@
         <v>10</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D442" s="6" t="n">
-        <v>4524.0</v>
+        <v>209762.0</v>
       </c>
       <c r="E442" s="7" t="s">
         <v>12</v>
@@ -18752,10 +18752,10 @@
         <v>13</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D625" s="6" t="n">
-        <v>54493.0</v>
+        <v>4464.0</v>
       </c>
       <c r="E625" s="7" t="s">
         <v>12</v>
@@ -18810,10 +18810,10 @@
         <v>13</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D627" s="6" t="n">
-        <v>2658.0</v>
+        <v>54493.0</v>
       </c>
       <c r="E627" s="7" t="s">
         <v>12</v>
@@ -18868,10 +18868,10 @@
         <v>13</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D629" s="6" t="n">
-        <v>4464.0</v>
+        <v>2658.0</v>
       </c>
       <c r="E629" s="7" t="s">
         <v>12</v>
@@ -21565,10 +21565,10 @@
         <v>10</v>
       </c>
       <c r="C722" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D722" s="6" t="n">
-        <v>145811.0</v>
+        <v>31341.0</v>
       </c>
       <c r="E722" s="7" t="s">
         <v>12</v>
@@ -21594,16 +21594,16 @@
         <v>10</v>
       </c>
       <c r="C723" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D723" s="6" t="n">
-        <v>31341.0</v>
+        <v>338700.0</v>
       </c>
       <c r="E723" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F723" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F723" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G723" s="8" t="s">
         <v>81</v>
@@ -21623,16 +21623,16 @@
         <v>10</v>
       </c>
       <c r="C724" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D724" s="6" t="n">
-        <v>338700.0</v>
+        <v>4669.0</v>
       </c>
       <c r="E724" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F724" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F724" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G724" s="8" t="s">
         <v>81</v>
@@ -21652,10 +21652,10 @@
         <v>10</v>
       </c>
       <c r="C725" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D725" s="6" t="n">
-        <v>4669.0</v>
+        <v>145811.0</v>
       </c>
       <c r="E725" s="7" t="s">
         <v>12</v>
@@ -21913,16 +21913,16 @@
         <v>13</v>
       </c>
       <c r="C734" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D734" s="6" t="n">
-        <v>342233.0</v>
+        <v>354.0</v>
       </c>
       <c r="E734" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F734" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F734" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G734" s="8" t="s">
         <v>82</v>
@@ -21942,10 +21942,10 @@
         <v>13</v>
       </c>
       <c r="C735" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D735" s="6" t="n">
-        <v>354.0</v>
+        <v>12510.0</v>
       </c>
       <c r="E735" s="7" t="s">
         <v>12</v>
@@ -21971,10 +21971,10 @@
         <v>13</v>
       </c>
       <c r="C736" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D736" s="6" t="n">
-        <v>12510.0</v>
+        <v>23079.0</v>
       </c>
       <c r="E736" s="7" t="s">
         <v>12</v>
@@ -22000,10 +22000,10 @@
         <v>13</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D737" s="6" t="n">
-        <v>23079.0</v>
+        <v>7371.0</v>
       </c>
       <c r="E737" s="7" t="s">
         <v>12</v>
@@ -22029,10 +22029,10 @@
         <v>13</v>
       </c>
       <c r="C738" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D738" s="6" t="n">
-        <v>7371.0</v>
+        <v>405.0</v>
       </c>
       <c r="E738" s="7" t="s">
         <v>12</v>
@@ -22058,16 +22058,16 @@
         <v>13</v>
       </c>
       <c r="C739" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D739" s="6" t="n">
-        <v>405.0</v>
+        <v>342233.0</v>
       </c>
       <c r="E739" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F739" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F739" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G739" s="8" t="s">
         <v>82</v>
@@ -22319,16 +22319,16 @@
         <v>30</v>
       </c>
       <c r="C748" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D748" s="6" t="n">
-        <v>5657.0</v>
+        <v>258340.0</v>
       </c>
       <c r="E748" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F748" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F748" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G748" s="8" t="s">
         <v>82</v>
@@ -22377,16 +22377,16 @@
         <v>30</v>
       </c>
       <c r="C750" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D750" s="6" t="n">
-        <v>258340.0</v>
+        <v>1522.0</v>
       </c>
       <c r="E750" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F750" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F750" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G750" s="8" t="s">
         <v>82</v>
@@ -22522,10 +22522,10 @@
         <v>30</v>
       </c>
       <c r="C755" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D755" s="6" t="n">
-        <v>1522.0</v>
+        <v>5657.0</v>
       </c>
       <c r="E755" s="7" t="s">
         <v>12</v>
@@ -23418,19 +23418,19 @@
         <v>83</v>
       </c>
       <c r="B786" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C786" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D786" s="6" t="n">
-        <v>127976.0</v>
+        <v>1676.0</v>
       </c>
       <c r="E786" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F786" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F786" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G786" s="8" t="s">
         <v>83</v>
@@ -23447,13 +23447,13 @@
         <v>83</v>
       </c>
       <c r="B787" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C787" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D787" s="6" t="n">
-        <v>1676.0</v>
+        <v>27344.0</v>
       </c>
       <c r="E787" s="7" t="s">
         <v>12</v>
@@ -23479,10 +23479,10 @@
         <v>13</v>
       </c>
       <c r="C788" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D788" s="6" t="n">
-        <v>27344.0</v>
+        <v>96073.0</v>
       </c>
       <c r="E788" s="7" t="s">
         <v>12</v>
@@ -23508,16 +23508,16 @@
         <v>13</v>
       </c>
       <c r="C789" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D789" s="6" t="n">
-        <v>96073.0</v>
+        <v>127976.0</v>
       </c>
       <c r="E789" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F789" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F789" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G789" s="8" t="s">
         <v>83</v>
@@ -23566,10 +23566,10 @@
         <v>13</v>
       </c>
       <c r="C791" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D791" s="6" t="n">
-        <v>30.0</v>
+        <v>613077.0</v>
       </c>
       <c r="E791" s="7" t="s">
         <v>12</v>
@@ -23595,10 +23595,10 @@
         <v>13</v>
       </c>
       <c r="C792" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D792" s="6" t="n">
-        <v>14341.0</v>
+        <v>30.0</v>
       </c>
       <c r="E792" s="7" t="s">
         <v>12</v>
@@ -23624,10 +23624,10 @@
         <v>13</v>
       </c>
       <c r="C793" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D793" s="6" t="n">
-        <v>2237.0</v>
+        <v>14341.0</v>
       </c>
       <c r="E793" s="7" t="s">
         <v>12</v>
@@ -23653,10 +23653,10 @@
         <v>13</v>
       </c>
       <c r="C794" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D794" s="6" t="n">
-        <v>1218.0</v>
+        <v>2237.0</v>
       </c>
       <c r="E794" s="7" t="s">
         <v>12</v>
@@ -23682,10 +23682,10 @@
         <v>13</v>
       </c>
       <c r="C795" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D795" s="6" t="n">
-        <v>612419.0</v>
+        <v>1218.0</v>
       </c>
       <c r="E795" s="7" t="s">
         <v>12</v>
@@ -23943,10 +23943,10 @@
         <v>30</v>
       </c>
       <c r="C804" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D804" s="6" t="n">
-        <v>1256.0</v>
+        <v>10263.0</v>
       </c>
       <c r="E804" s="7" t="s">
         <v>12</v>
@@ -23975,7 +23975,7 @@
         <v>33</v>
       </c>
       <c r="D805" s="6" t="n">
-        <v>155520.0</v>
+        <v>156318.0</v>
       </c>
       <c r="E805" s="7" t="s">
         <v>12</v>
@@ -24027,19 +24027,19 @@
         <v>84</v>
       </c>
       <c r="B807" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C807" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D807" s="6" t="n">
-        <v>133656.0</v>
+        <v>297089.0</v>
       </c>
       <c r="E807" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F807" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G807" s="8" t="s">
         <v>84</v>
@@ -24172,19 +24172,19 @@
         <v>84</v>
       </c>
       <c r="B812" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C812" s="5" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D812" s="6" t="n">
-        <v>297089.0</v>
+        <v>1256.0</v>
       </c>
       <c r="E812" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F812" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F812" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G812" s="8" t="s">
         <v>84</v>
@@ -24230,13 +24230,13 @@
         <v>84</v>
       </c>
       <c r="B814" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C814" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D814" s="6" t="n">
-        <v>6010.0</v>
+        <v>126580.0</v>
       </c>
       <c r="E814" s="7" t="s">
         <v>12</v>
@@ -24259,13 +24259,13 @@
         <v>84</v>
       </c>
       <c r="B815" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C815" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D815" s="6" t="n">
-        <v>126580.0</v>
+        <v>29645.0</v>
       </c>
       <c r="E815" s="7" t="s">
         <v>12</v>
@@ -24291,10 +24291,10 @@
         <v>13</v>
       </c>
       <c r="C816" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D816" s="6" t="n">
-        <v>29645.0</v>
+        <v>46372.0</v>
       </c>
       <c r="E816" s="7" t="s">
         <v>12</v>
@@ -24320,10 +24320,10 @@
         <v>13</v>
       </c>
       <c r="C817" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D817" s="6" t="n">
-        <v>46372.0</v>
+        <v>6010.0</v>
       </c>
       <c r="E817" s="7" t="s">
         <v>12</v>
@@ -24346,19 +24346,19 @@
         <v>84</v>
       </c>
       <c r="B818" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C818" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D818" s="6" t="n">
-        <v>10263.0</v>
+        <v>133656.0</v>
       </c>
       <c r="E818" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F818" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F818" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G818" s="8" t="s">
         <v>84</v>
@@ -24378,10 +24378,10 @@
         <v>13</v>
       </c>
       <c r="C819" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D819" s="6" t="n">
-        <v>10158.0</v>
+        <v>1484.0</v>
       </c>
       <c r="E819" s="7" t="s">
         <v>12</v>
@@ -24407,10 +24407,10 @@
         <v>13</v>
       </c>
       <c r="C820" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D820" s="6" t="n">
-        <v>652.0</v>
+        <v>13466.0</v>
       </c>
       <c r="E820" s="7" t="s">
         <v>12</v>
@@ -24436,10 +24436,10 @@
         <v>13</v>
       </c>
       <c r="C821" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D821" s="6" t="n">
-        <v>3760.0</v>
+        <v>652.0</v>
       </c>
       <c r="E821" s="7" t="s">
         <v>12</v>
@@ -24465,10 +24465,10 @@
         <v>13</v>
       </c>
       <c r="C822" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D822" s="6" t="n">
-        <v>1484.0</v>
+        <v>5295.0</v>
       </c>
       <c r="E822" s="7" t="s">
         <v>12</v>
@@ -24494,10 +24494,10 @@
         <v>13</v>
       </c>
       <c r="C823" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D823" s="6" t="n">
-        <v>2390.0</v>
+        <v>3232.0</v>
       </c>
       <c r="E823" s="7" t="s">
         <v>12</v>
@@ -24520,19 +24520,19 @@
         <v>85</v>
       </c>
       <c r="B824" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C824" s="5" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="D824" s="6" t="n">
-        <v>513433.0</v>
+        <v>9893.0</v>
       </c>
       <c r="E824" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F824" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F824" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G824" s="8" t="s">
         <v>85</v>
@@ -24552,10 +24552,10 @@
         <v>13</v>
       </c>
       <c r="C825" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D825" s="6" t="n">
-        <v>30780.0</v>
+        <v>4053.0</v>
       </c>
       <c r="E825" s="7" t="s">
         <v>12</v>
@@ -24581,16 +24581,16 @@
         <v>13</v>
       </c>
       <c r="C826" s="5" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="D826" s="6" t="n">
-        <v>2526.0</v>
+        <v>641391.0</v>
       </c>
       <c r="E826" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F826" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F826" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G826" s="8" t="s">
         <v>85</v>
@@ -24607,13 +24607,13 @@
         <v>85</v>
       </c>
       <c r="B827" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C827" s="5" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="D827" s="6" t="n">
-        <v>54198.0</v>
+        <v>32988.0</v>
       </c>
       <c r="E827" s="7" t="s">
         <v>12</v>
@@ -24636,13 +24636,13 @@
         <v>85</v>
       </c>
       <c r="B828" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C828" s="5" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="D828" s="6" t="n">
-        <v>7313.0</v>
+        <v>2390.0</v>
       </c>
       <c r="E828" s="7" t="s">
         <v>12</v>
@@ -24668,10 +24668,10 @@
         <v>13</v>
       </c>
       <c r="C829" s="5" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D829" s="6" t="n">
-        <v>240.0</v>
+        <v>4958.0</v>
       </c>
       <c r="E829" s="7" t="s">
         <v>12</v>
@@ -24694,13 +24694,13 @@
         <v>85</v>
       </c>
       <c r="B830" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C830" s="5" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="D830" s="6" t="n">
-        <v>10602.0</v>
+        <v>63891.0</v>
       </c>
       <c r="E830" s="7" t="s">
         <v>12</v>
@@ -24723,13 +24723,13 @@
         <v>85</v>
       </c>
       <c r="B831" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C831" s="5" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D831" s="6" t="n">
-        <v>396974.0</v>
+        <v>1031.0</v>
       </c>
       <c r="E831" s="7" t="s">
         <v>12</v>
@@ -24755,10 +24755,10 @@
         <v>13</v>
       </c>
       <c r="C832" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D832" s="6" t="n">
-        <v>206898.0</v>
+        <v>10684.0</v>
       </c>
       <c r="E832" s="7" t="s">
         <v>12</v>
@@ -24781,13 +24781,13 @@
         <v>85</v>
       </c>
       <c r="B833" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C833" s="5" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D833" s="6" t="n">
-        <v>95795.0</v>
+        <v>149.0</v>
       </c>
       <c r="E833" s="7" t="s">
         <v>12</v>
@@ -24813,10 +24813,10 @@
         <v>13</v>
       </c>
       <c r="C834" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D834" s="6" t="n">
-        <v>91459.0</v>
+        <v>271560.0</v>
       </c>
       <c r="E834" s="7" t="s">
         <v>12</v>
@@ -24842,10 +24842,10 @@
         <v>13</v>
       </c>
       <c r="C835" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D835" s="6" t="n">
-        <v>61719.0</v>
+        <v>123954.0</v>
       </c>
       <c r="E835" s="7" t="s">
         <v>12</v>
@@ -24871,10 +24871,10 @@
         <v>13</v>
       </c>
       <c r="C836" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D836" s="6" t="n">
-        <v>17817.0</v>
+        <v>111491.0</v>
       </c>
       <c r="E836" s="7" t="s">
         <v>12</v>
@@ -24897,13 +24897,13 @@
         <v>85</v>
       </c>
       <c r="B837" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C837" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D837" s="6" t="n">
-        <v>7396.0</v>
+        <v>76596.0</v>
       </c>
       <c r="E837" s="7" t="s">
         <v>12</v>
@@ -24926,13 +24926,13 @@
         <v>85</v>
       </c>
       <c r="B838" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C838" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D838" s="6" t="n">
-        <v>60593.0</v>
+        <v>19552.0</v>
       </c>
       <c r="E838" s="7" t="s">
         <v>12</v>
@@ -24958,10 +24958,10 @@
         <v>30</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D839" s="6" t="n">
-        <v>14453.0</v>
+        <v>7396.0</v>
       </c>
       <c r="E839" s="7" t="s">
         <v>12</v>
@@ -24987,16 +24987,16 @@
         <v>30</v>
       </c>
       <c r="C840" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D840" s="6" t="n">
-        <v>33087.0</v>
+        <v>76674.0</v>
       </c>
       <c r="E840" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F840" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F840" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G840" s="8" t="s">
         <v>85</v>
@@ -25013,19 +25013,19 @@
         <v>85</v>
       </c>
       <c r="B841" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C841" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D841" s="6" t="n">
-        <v>14672.0</v>
+        <v>499330.0</v>
       </c>
       <c r="E841" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F841" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F841" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G841" s="8" t="s">
         <v>85</v>
@@ -25042,13 +25042,13 @@
         <v>85</v>
       </c>
       <c r="B842" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C842" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D842" s="6" t="n">
-        <v>174546.0</v>
+        <v>5111.0</v>
       </c>
       <c r="E842" s="7" t="s">
         <v>12</v>
@@ -25071,13 +25071,13 @@
         <v>85</v>
       </c>
       <c r="B843" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C843" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D843" s="6" t="n">
-        <v>18850.0</v>
+        <v>15684.0</v>
       </c>
       <c r="E843" s="7" t="s">
         <v>12</v>
@@ -25100,13 +25100,13 @@
         <v>85</v>
       </c>
       <c r="B844" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C844" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D844" s="6" t="n">
-        <v>201553.0</v>
+        <v>45086.0</v>
       </c>
       <c r="E844" s="7" t="s">
         <v>12</v>
@@ -25132,10 +25132,10 @@
         <v>10</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="D845" s="6" t="n">
-        <v>122124.0</v>
+        <v>17175.0</v>
       </c>
       <c r="E845" s="7" t="s">
         <v>12</v>
@@ -25150,6 +25150,122 @@
         <v>85</v>
       </c>
       <c r="I845" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B846" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C846" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D846" s="6" t="n">
+        <v>233348.0</v>
+      </c>
+      <c r="E846" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F846" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G846" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H846" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I846" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B847" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C847" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D847" s="6" t="n">
+        <v>37556.0</v>
+      </c>
+      <c r="E847" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F847" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G847" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H847" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I847" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B848" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C848" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D848" s="6" t="n">
+        <v>236036.0</v>
+      </c>
+      <c r="E848" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F848" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G848" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H848" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I848" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B849" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C849" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D849" s="6" t="n">
+        <v>149368.0</v>
+      </c>
+      <c r="E849" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F849" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G849" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H849" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I849" s="7" t="s">
         <v>12</v>
       </c>
     </row>
